--- a/benchmarking/search_for_best_combination/results_basic.xlsx
+++ b/benchmarking/search_for_best_combination/results_basic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33EB1EC8-3FBA-9B41-8527-2895603CE2D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACCD2C3-6A08-184F-AC6D-F499FA3BA618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="78">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -125,9 +125,6 @@
     <t>"text + claim/premise", "year"</t>
   </si>
   <si>
-    <t>"text - claim/premise", "speaker", "year"</t>
-  </si>
-  <si>
     <t>support, attack, equivalent, said by, role</t>
   </si>
   <si>
@@ -165,6 +162,114 @@
   </si>
   <si>
     <t>TP HITS@10</t>
+  </si>
+  <si>
+    <t>0.045053681</t>
+  </si>
+  <si>
+    <t>0.0059432515</t>
+  </si>
+  <si>
+    <t>0.5254312985</t>
+  </si>
+  <si>
+    <t>0.0042177914</t>
+  </si>
+  <si>
+    <t>0.5241982173</t>
+  </si>
+  <si>
+    <t>0.1042944785</t>
+  </si>
+  <si>
+    <t>0.0032592025</t>
+  </si>
+  <si>
+    <t>0.538006114</t>
+  </si>
+  <si>
+    <t>0.0394636015</t>
+  </si>
+  <si>
+    <t>0.0055555555</t>
+  </si>
+  <si>
+    <t>0.5303272668</t>
+  </si>
+  <si>
+    <t>0.0350574713</t>
+  </si>
+  <si>
+    <t>0.0084291188</t>
+  </si>
+  <si>
+    <t>0.501360684</t>
+  </si>
+  <si>
+    <t>0.0639846743</t>
+  </si>
+  <si>
+    <t>0.003256705</t>
+  </si>
+  <si>
+    <t>0.5270099546</t>
+  </si>
+  <si>
+    <t>0.0064678971</t>
+  </si>
+  <si>
+    <t>0.2741757375</t>
+  </si>
+  <si>
+    <t>0.5251275737</t>
+  </si>
+  <si>
+    <t>0.4068465058</t>
+  </si>
+  <si>
+    <t>0.0000788768</t>
+  </si>
+  <si>
+    <t>0.8575875039</t>
+  </si>
+  <si>
+    <t>0.3013882316</t>
+  </si>
+  <si>
+    <t>0.1729768102</t>
+  </si>
+  <si>
+    <t>0.8729570507</t>
+  </si>
+  <si>
+    <t>0.2946584245</t>
+  </si>
+  <si>
+    <t>0.2965604692</t>
+  </si>
+  <si>
+    <t>0.6309717027</t>
+  </si>
+  <si>
+    <t>0.0820256776</t>
+  </si>
+  <si>
+    <t>0.0025360596</t>
+  </si>
+  <si>
+    <t>0.3920198287</t>
+  </si>
+  <si>
+    <t>0.326596925</t>
+  </si>
+  <si>
+    <t>0.2587573308</t>
+  </si>
+  <si>
+    <t>0.4555089196</t>
+  </si>
+  <si>
+    <t>"text + claim/premise", "speaker", "year"</t>
   </si>
 </sst>
 </file>
@@ -259,7 +364,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -279,17 +384,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -615,9 +714,9 @@
     <col min="2" max="2" width="13.83203125" style="5" customWidth="1"/>
     <col min="3" max="3" width="58.33203125" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="60" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5" style="6" customWidth="1"/>
-    <col min="6" max="6" width="22" style="6" customWidth="1"/>
-    <col min="7" max="7" width="26.5" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.5" style="5" customWidth="1"/>
+    <col min="6" max="6" width="22" style="5" customWidth="1"/>
+    <col min="7" max="7" width="26.5" style="5" customWidth="1"/>
     <col min="8" max="8" width="100.1640625" style="5" bestFit="1" customWidth="1"/>
     <col min="9" max="16384" width="51.33203125" style="5"/>
   </cols>
@@ -642,7 +741,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>16</v>
@@ -662,6 +761,15 @@
       <c r="D2" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="E2" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>49</v>
+      </c>
       <c r="H2" s="5" t="s">
         <v>17</v>
       </c>
@@ -679,6 +787,15 @@
       <c r="D3" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="E3" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>46</v>
+      </c>
       <c r="H3" s="5" t="s">
         <v>17</v>
       </c>
@@ -696,6 +813,15 @@
       <c r="D4" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="E4" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="H4" s="5" t="s">
         <v>17</v>
       </c>
@@ -713,6 +839,15 @@
       <c r="D6" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="E6" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>58</v>
+      </c>
       <c r="H6" s="5" t="s">
         <v>18</v>
       </c>
@@ -730,6 +865,15 @@
       <c r="D7" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="E7" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>55</v>
+      </c>
       <c r="H7" s="5" t="s">
         <v>18</v>
       </c>
@@ -747,16 +891,25 @@
       <c r="D8" s="6" t="s">
         <v>15</v>
       </c>
+      <c r="E8" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>52</v>
+      </c>
       <c r="H8" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="B10" s="11"/>
-      <c r="C10" s="11"/>
+    <row r="10" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -771,6 +924,15 @@
       <c r="D12" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="E12" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>76</v>
+      </c>
       <c r="H12" s="5" t="s">
         <v>20</v>
       </c>
@@ -788,6 +950,15 @@
       <c r="D13" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="E13" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>73</v>
+      </c>
       <c r="H13" s="5" t="s">
         <v>20</v>
       </c>
@@ -805,68 +976,68 @@
       <c r="D14" s="6" t="s">
         <v>19</v>
       </c>
+      <c r="E14" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>70</v>
+      </c>
       <c r="H14" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="D16" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H16" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="8" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
+      <c r="D17" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="8" t="s">
-        <v>39</v>
+      <c r="D18" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
@@ -880,10 +1051,10 @@
         <v>22</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
@@ -897,10 +1068,10 @@
         <v>22</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -914,10 +1085,10 @@
         <v>22</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -931,7 +1102,7 @@
         <v>23</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -945,7 +1116,7 @@
         <v>23</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -959,7 +1130,7 @@
         <v>23</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -973,7 +1144,7 @@
         <v>24</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -987,7 +1158,7 @@
         <v>24</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1001,59 +1172,50 @@
         <v>24</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="8" t="s">
+      <c r="B32" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="9" t="s">
+      <c r="C32" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D32" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E32" s="9"/>
-      <c r="F32" s="9"/>
-      <c r="G32" s="9"/>
-    </row>
-    <row r="33" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="D32" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B33" s="8" t="s">
+      <c r="B33" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="9" t="s">
+      <c r="C33" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D33" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E33" s="9"/>
-      <c r="F33" s="9"/>
-      <c r="G33" s="9"/>
-    </row>
-    <row r="34" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+      <c r="D33" s="6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="8" t="s">
+      <c r="B34" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="9" t="s">
+      <c r="C34" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="E34" s="9"/>
-      <c r="F34" s="9"/>
-      <c r="G34" s="9"/>
+      <c r="D34" s="6" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
@@ -1066,7 +1228,7 @@
         <v>26</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -1080,7 +1242,7 @@
         <v>26</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -1094,15 +1256,15 @@
         <v>26</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" s="10" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="11"/>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
@@ -1115,10 +1277,19 @@
         <v>27</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="E42" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="G42" s="8" t="s">
+        <v>67</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -1132,10 +1303,19 @@
         <v>27</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="G43" s="5" t="s">
+        <v>64</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -1149,10 +1329,19 @@
         <v>27</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="G44" s="5" t="s">
+        <v>61</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -1166,10 +1355,10 @@
         <v>28</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H46" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -1183,10 +1372,10 @@
         <v>28</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H47" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -1200,10 +1389,10 @@
         <v>28</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H48" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -1214,10 +1403,10 @@
         <v>7</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -1228,10 +1417,10 @@
         <v>8</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -1242,10 +1431,10 @@
         <v>9</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">

--- a/benchmarking/search_for_best_combination/results_basic.xlsx
+++ b/benchmarking/search_for_best_combination/results_basic.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3ACCD2C3-6A08-184F-AC6D-F499FA3BA618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6A40CF-D42C-A244-848C-CD554CA7D83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
+    <sheet name="Results" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>

--- a/benchmarking/search_for_best_combination/results_basic.xlsx
+++ b/benchmarking/search_for_best_combination/results_basic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B6A40CF-D42C-A244-848C-CD554CA7D83B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E32CD50-C654-3849-A6B5-336EC676399E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="123">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -270,6 +270,141 @@
   </si>
   <si>
     <t>"text + claim/premise", "speaker", "year"</t>
+  </si>
+  <si>
+    <t>0.1485446235</t>
+  </si>
+  <si>
+    <t>0.1511907626</t>
+  </si>
+  <si>
+    <t>0.5214631904</t>
+  </si>
+  <si>
+    <t>0.3464437495</t>
+  </si>
+  <si>
+    <t>0.0200866009</t>
+  </si>
+  <si>
+    <t>0.7744152557</t>
+  </si>
+  <si>
+    <t>0.3736268142</t>
+  </si>
+  <si>
+    <t>0.3365006816</t>
+  </si>
+  <si>
+    <t>0.9354785447</t>
+  </si>
+  <si>
+    <t>0.0162427975</t>
+  </si>
+  <si>
+    <t>0.3716471289</t>
+  </si>
+  <si>
+    <t>0.6143862942</t>
+  </si>
+  <si>
+    <t>0.5640770912</t>
+  </si>
+  <si>
+    <t>0.0799721836</t>
+  </si>
+  <si>
+    <t>0.9263769971</t>
+  </si>
+  <si>
+    <t>0.5714782436</t>
+  </si>
+  <si>
+    <t>0.0848897278</t>
+  </si>
+  <si>
+    <t>0.951135693</t>
+  </si>
+  <si>
+    <t>0.2007205076</t>
+  </si>
+  <si>
+    <t>0.0232283041</t>
+  </si>
+  <si>
+    <t>0.5792298707</t>
+  </si>
+  <si>
+    <t>0.2473921927</t>
+  </si>
+  <si>
+    <t>0.0100010754</t>
+  </si>
+  <si>
+    <t>0.6778958419</t>
+  </si>
+  <si>
+    <t>0.4729540811</t>
+  </si>
+  <si>
+    <t>0.2002365846</t>
+  </si>
+  <si>
+    <t>0.6294142495</t>
+  </si>
+  <si>
+    <t>0.0591762664</t>
+  </si>
+  <si>
+    <t>0.295092315</t>
+  </si>
+  <si>
+    <t>0.5645150548</t>
+  </si>
+  <si>
+    <t>0.48177371</t>
+  </si>
+  <si>
+    <t>0.0135710904</t>
+  </si>
+  <si>
+    <t>0.8897140327</t>
+  </si>
+  <si>
+    <t>0.4629162064</t>
+  </si>
+  <si>
+    <t>0.0155436326</t>
+  </si>
+  <si>
+    <t>0.889457195</t>
+  </si>
+  <si>
+    <t>0.1084962796</t>
+  </si>
+  <si>
+    <t>0.2654438484</t>
+  </si>
+  <si>
+    <t>0.6036877664</t>
+  </si>
+  <si>
+    <t>0.3382938225</t>
+  </si>
+  <si>
+    <t>0.0198131165</t>
+  </si>
+  <si>
+    <t>0.852653512</t>
+  </si>
+  <si>
+    <t>0.3966949299</t>
+  </si>
+  <si>
+    <t>0.2246928535</t>
+  </si>
+  <si>
+    <t>0.9016586409</t>
   </si>
 </sst>
 </file>
@@ -364,7 +499,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -378,20 +513,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -707,18 +839,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{438262D8-2430-9140-9A7B-2FDAF8B91602}">
-  <dimension ref="A1:I68"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="51.33203125" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:I52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="51.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" style="5" customWidth="1"/>
-    <col min="2" max="2" width="13.83203125" style="5" customWidth="1"/>
-    <col min="3" max="3" width="58.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="60" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.5" style="5" customWidth="1"/>
-    <col min="6" max="6" width="22" style="5" customWidth="1"/>
-    <col min="7" max="7" width="26.5" style="5" customWidth="1"/>
-    <col min="8" max="8" width="100.1640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="51.33203125" style="5"/>
+    <col min="1" max="1" width="26.1640625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="13.83203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="58.33203125" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="60" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.5" style="4" customWidth="1"/>
+    <col min="6" max="6" width="22" style="4" customWidth="1"/>
+    <col min="7" max="7" width="26.5" style="4" customWidth="1"/>
+    <col min="8" max="8" width="100.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="51.33203125" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -748,730 +880,829 @@
       </c>
       <c r="I1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="E2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="G2" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="H2" s="5" t="s">
+      <c r="H2" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="F4" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E6" s="8" t="s">
+      <c r="E6" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="G8" s="8" t="s">
+      <c r="G8" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="9" t="s">
+    <row r="10" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="8" t="s">
+      <c r="E12" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="4" t="s">
         <v>73</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="8" t="s">
+      <c r="F14" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="G14" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="E16" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="G16" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="E17" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="H17" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="6" t="s">
+      <c r="C18" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="E18" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="H18" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="6" t="s">
+      <c r="C20" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="6" t="s">
+      <c r="D20" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="C21" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D21" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="5" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="6" t="s">
+      <c r="C28" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="6" t="s">
+      <c r="D28" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E28" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="G28" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="6" t="s">
+      <c r="C29" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D29" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E29" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="G29" s="6" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="5" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E30" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="6" t="s">
+      <c r="C32" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D32" s="6" t="s">
+      <c r="D32" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B33" s="5" t="s">
+      <c r="B33" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="6" t="s">
+      <c r="C33" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="D33" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C34" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D34" s="5" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="6" t="s">
+      <c r="C36" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D36" s="6" t="s">
+      <c r="D36" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E36" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="G36" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="6" t="s">
+      <c r="C37" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D37" s="6" t="s">
+      <c r="D37" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E37" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="G37" s="4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="6" t="s">
+      <c r="C38" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="6" t="s">
+      <c r="D38" s="5" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="40" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="9" t="s">
+      <c r="E38" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="7"/>
+      <c r="C40" s="7"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="6" t="s">
+      <c r="C42" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E42" s="5" t="s">
+      <c r="E42" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F42" s="5" t="s">
+      <c r="F42" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G42" s="8" t="s">
+      <c r="G42" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="H42" s="5" t="s">
+      <c r="H42" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="6" t="s">
+      <c r="C43" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D43" s="6" t="s">
+      <c r="D43" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E43" s="8" t="s">
+      <c r="E43" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="F43" s="5" t="s">
+      <c r="F43" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="G43" s="5" t="s">
+      <c r="G43" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="H43" s="5" t="s">
+      <c r="H43" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="6" t="s">
+      <c r="C44" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D44" s="6" t="s">
+      <c r="D44" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E44" s="5" t="s">
+      <c r="E44" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F44" s="8" t="s">
+      <c r="F44" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="G44" s="4" t="s">
         <v>61</v>
       </c>
-      <c r="H44" s="5" t="s">
+      <c r="H44" s="4" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="6" t="s">
+      <c r="C46" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D46" s="6" t="s">
+      <c r="D46" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H46" s="5" t="s">
+      <c r="E46" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="G46" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="H46" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="6" t="s">
+      <c r="C47" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D47" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H47" s="5" t="s">
+      <c r="E47" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="G47" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="H47" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C48" s="6" t="s">
+      <c r="C48" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D48" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="H48" s="5" t="s">
+      <c r="E48" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F48" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G48" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H48" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C50" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D50" s="6" t="s">
+      <c r="D50" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E50" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="G50" s="6" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C51" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D51" s="6" t="s">
+      <c r="D51" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E51" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G51" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="6" t="s">
+      <c r="C52" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="D52" s="6" t="s">
+      <c r="D52" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A54" s="4"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A55" s="4"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A56" s="4"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A58" s="4"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A59" s="4"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A60" s="4"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A62" s="4"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A63" s="4"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A64" s="4"/>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" s="4"/>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" s="4"/>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" s="4"/>
+      <c r="E52" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="F52" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="G52" s="4" t="s">
+        <v>89</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/benchmarking/search_for_best_combination/results_basic.xlsx
+++ b/benchmarking/search_for_best_combination/results_basic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E32CD50-C654-3849-A6B5-336EC676399E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD39E321-4878-E24C-AB93-7E6D67DADDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="150">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -405,6 +405,87 @@
   </si>
   <si>
     <t>0.9016586409</t>
+  </si>
+  <si>
+    <t>0.0102320675</t>
+  </si>
+  <si>
+    <t>0.0009493671</t>
+  </si>
+  <si>
+    <t>0.7770683767</t>
+  </si>
+  <si>
+    <t>0.1726793249</t>
+  </si>
+  <si>
+    <t>0.0093881856</t>
+  </si>
+  <si>
+    <t>0.6188406519</t>
+  </si>
+  <si>
+    <t>0.3818565401</t>
+  </si>
+  <si>
+    <t>0.2227848101</t>
+  </si>
+  <si>
+    <t>0.7011053182</t>
+  </si>
+  <si>
+    <t>0.0036488027</t>
+  </si>
+  <si>
+    <t>0.0022234892</t>
+  </si>
+  <si>
+    <t>0.7828517558</t>
+  </si>
+  <si>
+    <t>0.5326111745</t>
+  </si>
+  <si>
+    <t>0.0733751425</t>
+  </si>
+  <si>
+    <t>0.9275131787</t>
+  </si>
+  <si>
+    <t>0.0299885975</t>
+  </si>
+  <si>
+    <t>0.5575256556</t>
+  </si>
+  <si>
+    <t>0.9541501829</t>
+  </si>
+  <si>
+    <t>0.0003572705</t>
+  </si>
+  <si>
+    <t>0.0012504466</t>
+  </si>
+  <si>
+    <t>0.6587461798</t>
+  </si>
+  <si>
+    <t>0.2938549482</t>
+  </si>
+  <si>
+    <t>0.0200071454</t>
+  </si>
+  <si>
+    <t>0.8420770719</t>
+  </si>
+  <si>
+    <t>0.4853519114</t>
+  </si>
+  <si>
+    <t>0.2437477671</t>
+  </si>
+  <si>
+    <t>0.919034264</t>
   </si>
 </sst>
 </file>
@@ -443,7 +524,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -459,6 +540,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -499,7 +586,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -523,6 +610,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1036,12 +1132,12 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="7" t="s">
+    <row r="10" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
@@ -1121,29 +1217,29 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="11" t="s">
         <v>120</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="11" t="s">
         <v>122</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="9" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1199,20 +1295,29 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="E20" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>149</v>
+      </c>
+      <c r="H20" s="9" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1229,6 +1334,15 @@
       <c r="D21" s="5" t="s">
         <v>30</v>
       </c>
+      <c r="E21" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F21" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>146</v>
+      </c>
       <c r="H21" s="4" t="s">
         <v>37</v>
       </c>
@@ -1246,22 +1360,40 @@
       <c r="D22" s="5" t="s">
         <v>30</v>
       </c>
+      <c r="E22" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>143</v>
+      </c>
       <c r="H22" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A24" s="4" t="s">
+    <row r="24" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="10" t="s">
         <v>34</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G24" s="9" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -1277,6 +1409,15 @@
       <c r="D25" s="5" t="s">
         <v>34</v>
       </c>
+      <c r="E25" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="G25" s="4" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="4" t="s">
@@ -1291,6 +1432,15 @@
       <c r="D26" s="5" t="s">
         <v>34</v>
       </c>
+      <c r="E26" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>125</v>
+      </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="4" t="s">
@@ -1374,6 +1524,15 @@
       <c r="D32" s="5" t="s">
         <v>31</v>
       </c>
+      <c r="E32" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G32" s="6" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="4" t="s">
@@ -1388,6 +1547,15 @@
       <c r="D33" s="5" t="s">
         <v>31</v>
       </c>
+      <c r="E33" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G33" s="4" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="4" t="s">
@@ -1402,27 +1570,36 @@
       <c r="D34" s="5" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A36" s="4" t="s">
+      <c r="E34" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="E36" s="6" t="s">
+      <c r="E36" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="F36" s="6" t="s">
+      <c r="F36" s="11" t="s">
         <v>85</v>
       </c>
-      <c r="G36" s="6" t="s">
+      <c r="G36" s="11" t="s">
         <v>86</v>
       </c>
     </row>
@@ -1472,36 +1649,36 @@
         <v>80</v>
       </c>
     </row>
-    <row r="40" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="7" t="s">
+    <row r="40" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-    </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A42" s="4" t="s">
+      <c r="B40" s="8"/>
+      <c r="C40" s="8"/>
+    </row>
+    <row r="42" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="10" t="s">
         <v>29</v>
       </c>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="F42" s="4" t="s">
+      <c r="F42" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="G42" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="H42" s="4" t="s">
+      <c r="H42" s="9" t="s">
         <v>32</v>
       </c>
     </row>

--- a/benchmarking/search_for_best_combination/results_basic.xlsx
+++ b/benchmarking/search_for_best_combination/results_basic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD39E321-4878-E24C-AB93-7E6D67DADDB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19041EAA-8588-7543-AC3B-3117C1E71214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -161,9 +161,6 @@
     <t>ADDED NODES TO GRAPH WITH  TEXT AND NODE TYPE AS FEATURE NODE</t>
   </si>
   <si>
-    <t>TP HITS@10</t>
-  </si>
-  <si>
     <t>0.045053681</t>
   </si>
   <si>
@@ -486,6 +483,9 @@
   </si>
   <si>
     <t>0.919034264</t>
+  </si>
+  <si>
+    <t>TP F1-MACRO</t>
   </si>
 </sst>
 </file>
@@ -609,9 +609,6 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -619,6 +616,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -969,7 +969,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>41</v>
+        <v>149</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>16</v>
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="E2" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="G2" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="H2" s="4" t="s">
         <v>17</v>
@@ -1016,13 +1016,13 @@
         <v>15</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>46</v>
       </c>
       <c r="H3" s="4" t="s">
         <v>17</v>
@@ -1042,13 +1042,13 @@
         <v>15</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>17</v>
@@ -1068,13 +1068,13 @@
         <v>15</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>18</v>
@@ -1094,13 +1094,13 @@
         <v>15</v>
       </c>
       <c r="E7" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="G7" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>55</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>18</v>
@@ -1120,24 +1120,24 @@
         <v>15</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="F8" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="G8" s="6" t="s">
         <v>51</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>52</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="8" t="s">
+      <c r="A10" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4" t="s">
@@ -1153,13 +1153,13 @@
         <v>19</v>
       </c>
       <c r="E12" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="G12" s="4" t="s">
         <v>75</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>76</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>20</v>
@@ -1179,13 +1179,13 @@
         <v>19</v>
       </c>
       <c r="E13" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="G13" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>20</v>
@@ -1205,41 +1205,41 @@
         <v>19</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="G14" s="6" t="s">
         <v>69</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>70</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="9" t="s">
+    <row r="16" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E16" s="11" t="s">
+      <c r="E16" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="G16" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="G16" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="H16" s="9" t="s">
+      <c r="H16" s="8" t="s">
         <v>38</v>
       </c>
     </row>
@@ -1257,13 +1257,13 @@
         <v>29</v>
       </c>
       <c r="E17" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="G17" s="4" t="s">
         <v>118</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>119</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>38</v>
@@ -1283,41 +1283,41 @@
         <v>29</v>
       </c>
       <c r="E18" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="F18" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="G18" s="4" t="s">
         <v>115</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>116</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="9" t="s">
+    <row r="20" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="11" t="s">
+      <c r="E20" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="F20" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="F20" s="11" t="s">
+      <c r="G20" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="G20" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="H20" s="9" t="s">
+      <c r="H20" s="8" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1335,13 +1335,13 @@
         <v>30</v>
       </c>
       <c r="E21" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="G21" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>146</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>37</v>
@@ -1361,39 +1361,39 @@
         <v>30</v>
       </c>
       <c r="E22" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F22" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="G22" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="9" t="s">
+    <row r="24" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="E24" s="11" t="s">
+      <c r="E24" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="F24" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="G24" s="8" t="s">
         <v>130</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
@@ -1410,13 +1410,13 @@
         <v>34</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="F25" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="G25" s="4" t="s">
         <v>127</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
@@ -1433,13 +1433,13 @@
         <v>34</v>
       </c>
       <c r="E26" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F26" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="G26" s="6" t="s">
         <v>124</v>
-      </c>
-      <c r="G26" s="6" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
@@ -1456,13 +1456,13 @@
         <v>35</v>
       </c>
       <c r="E28" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="F28" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="F28" s="6" t="s">
+      <c r="G28" s="4" t="s">
         <v>103</v>
-      </c>
-      <c r="G28" s="4" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
@@ -1479,13 +1479,13 @@
         <v>35</v>
       </c>
       <c r="E29" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="F29" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="G29" s="6" t="s">
         <v>100</v>
-      </c>
-      <c r="G29" s="6" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
@@ -1502,13 +1502,13 @@
         <v>35</v>
       </c>
       <c r="E30" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="F30" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="G30" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
@@ -1525,13 +1525,13 @@
         <v>31</v>
       </c>
       <c r="E32" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="F32" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="G32" s="6" t="s">
         <v>139</v>
-      </c>
-      <c r="F32" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="G32" s="6" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
@@ -1548,13 +1548,13 @@
         <v>31</v>
       </c>
       <c r="E33" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F33" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="F33" s="6" t="s">
+      <c r="G33" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
@@ -1571,36 +1571,36 @@
         <v>31</v>
       </c>
       <c r="E34" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="G34" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="G34" s="4" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="9" t="s">
+    </row>
+    <row r="36" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B36" s="9" t="s">
+      <c r="B36" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="E36" s="11" t="s">
+      <c r="E36" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="F36" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="F36" s="11" t="s">
+      <c r="G36" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="G36" s="11" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -1617,13 +1617,13 @@
         <v>36</v>
       </c>
       <c r="E37" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="G37" s="4" t="s">
         <v>82</v>
-      </c>
-      <c r="G37" s="4" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
@@ -1640,45 +1640,45 @@
         <v>36</v>
       </c>
       <c r="E38" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="F38" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="G38" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="G38" s="4" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="40" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="8"/>
-      <c r="C40" s="8"/>
-    </row>
-    <row r="42" spans="1:8" s="9" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="9" t="s">
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+    </row>
+    <row r="42" spans="1:8" s="8" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="9" t="s">
+      <c r="B42" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="10" t="s">
+      <c r="C42" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="E42" s="9" t="s">
+      <c r="E42" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F42" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="F42" s="9" t="s">
+      <c r="G42" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="G42" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="H42" s="9" t="s">
+      <c r="H42" s="8" t="s">
         <v>32</v>
       </c>
     </row>
@@ -1696,13 +1696,13 @@
         <v>29</v>
       </c>
       <c r="E43" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="G43" s="4" t="s">
         <v>63</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>64</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>32</v>
@@ -1722,13 +1722,13 @@
         <v>29</v>
       </c>
       <c r="E44" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="F44" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="F44" s="6" t="s">
+      <c r="G44" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="H44" s="4" t="s">
         <v>32</v>
@@ -1748,13 +1748,13 @@
         <v>30</v>
       </c>
       <c r="E46" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="F46" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="G46" s="4" t="s">
         <v>112</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>113</v>
       </c>
       <c r="H46" s="4" t="s">
         <v>33</v>
@@ -1774,13 +1774,13 @@
         <v>30</v>
       </c>
       <c r="E47" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F47" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="G47" s="6" t="s">
         <v>109</v>
-      </c>
-      <c r="G47" s="6" t="s">
-        <v>110</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>33</v>
@@ -1800,13 +1800,13 @@
         <v>30</v>
       </c>
       <c r="E48" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="F48" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="F48" s="6" t="s">
+      <c r="G48" s="4" t="s">
         <v>106</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>107</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>33</v>
@@ -1820,19 +1820,19 @@
         <v>7</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E50" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="F50" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="G50" s="6" t="s">
         <v>94</v>
-      </c>
-      <c r="G50" s="6" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.2">
@@ -1843,19 +1843,19 @@
         <v>8</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E51" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="F51" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="G51" s="4" t="s">
         <v>91</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.2">
@@ -1866,19 +1866,19 @@
         <v>9</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>31</v>
       </c>
       <c r="E52" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="F52" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="F52" s="6" t="s">
+      <c r="G52" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="G52" s="4" t="s">
-        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/benchmarking/search_for_best_combination/results_basic.xlsx
+++ b/benchmarking/search_for_best_combination/results_basic.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19041EAA-8588-7543-AC3B-3117C1E71214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41ABB316-1640-4B41-8080-934038161B4B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="1" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
+    <sheet name="Experiments with special triple" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="165">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -486,6 +487,51 @@
   </si>
   <si>
     <t>TP F1-MACRO</t>
+  </si>
+  <si>
+    <t>TYPE OF EXPERIMENT</t>
+  </si>
+  <si>
+    <t>NAME EXPERIMENT</t>
+  </si>
+  <si>
+    <t>TP HITS@10</t>
+  </si>
+  <si>
+    <t>RP HITS@1</t>
+  </si>
+  <si>
+    <t>RC F1-MACRO</t>
+  </si>
+  <si>
+    <t>only text - upsampling</t>
+  </si>
+  <si>
+    <t>text + speaker - upsampling</t>
+  </si>
+  <si>
+    <t>text + speaker - downsampling</t>
+  </si>
+  <si>
+    <t>text + year - upsampling</t>
+  </si>
+  <si>
+    <t>text + year - downsampling</t>
+  </si>
+  <si>
+    <t>different loss functions</t>
+  </si>
+  <si>
+    <t>different optimizers</t>
+  </si>
+  <si>
+    <t>DistMult</t>
+  </si>
+  <si>
+    <t>ConvE</t>
+  </si>
+  <si>
+    <t>only_text_upsampling</t>
   </si>
 </sst>
 </file>
@@ -524,7 +570,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -546,6 +592,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -586,7 +638,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -619,6 +671,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1888,4 +1946,206 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F1BB833-377A-D44F-92A0-3B5384834C0E}">
+  <dimension ref="A1:H28"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="2" width="33.33203125" style="4" customWidth="1"/>
+    <col min="3" max="3" width="32.1640625" style="4" customWidth="1"/>
+    <col min="4" max="4" width="21.83203125" style="4" customWidth="1"/>
+    <col min="5" max="5" width="22.33203125" style="4" customWidth="1"/>
+    <col min="6" max="6" width="20.5" style="4" customWidth="1"/>
+    <col min="7" max="7" width="21.83203125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="22.6640625" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="10.83203125" style="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="12" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="13" t="s">
+        <v>155</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="13"/>
+      <c r="B3" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="C3" s="13"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="13"/>
+      <c r="B4" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="13"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="13" t="s">
+        <v>156</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="13"/>
+      <c r="B7" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="13"/>
+      <c r="B8" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="13" t="s">
+        <v>157</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="13"/>
+      <c r="B11" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="13"/>
+      <c r="B12" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="13"/>
+      <c r="B15" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="13"/>
+      <c r="B16" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A18" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A19" s="13"/>
+      <c r="B19" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A20" s="13"/>
+      <c r="B20" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A22" s="13" t="s">
+        <v>160</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A23" s="13"/>
+      <c r="B23" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A24" s="13"/>
+      <c r="B24" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A26" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A27" s="13"/>
+      <c r="B27" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A28" s="13"/>
+      <c r="B28" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A22:A24"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
 </file>
--- a/benchmarking/search_for_best_combination/results_basic.xlsx
+++ b/benchmarking/search_for_best_combination/results_basic.xlsx
@@ -2,19 +2,20 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11127"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D34A2B0-2837-9644-A491-67F1B06E1C7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D21CB4-5EE7-8B4E-BE05-9F7B72CB52CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
-    <sheet name="Results" sheetId="1" r:id="rId1"/>
-    <sheet name="trial 1" sheetId="2" r:id="rId2"/>
+    <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>
+    <sheet name="Results SPECIAL" sheetId="5" r:id="rId2"/>
+    <sheet name="trial 1" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="405">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -913,9 +914,6 @@
     <t>0.437631721</t>
   </si>
   <si>
-    <t>RC HITS@1</t>
-  </si>
-  <si>
     <t>0.0004465881</t>
   </si>
   <si>
@@ -1352,6 +1350,66 @@
   </si>
   <si>
     <t>0.5781646619</t>
+  </si>
+  <si>
+    <t>LINK PREDICTION HITS@10</t>
+  </si>
+  <si>
+    <t>LINK DELETION HITS@10</t>
+  </si>
+  <si>
+    <t>RELATION PREDICTION HITS@1</t>
+  </si>
+  <si>
+    <t>TRIPLE CLASSIFICATION F1-MACRO</t>
+  </si>
+  <si>
+    <t>RELATION CLASSIFICATION HITS@1</t>
+  </si>
+  <si>
+    <t>0.1553265707</t>
+  </si>
+  <si>
+    <t>0.1835130909</t>
+  </si>
+  <si>
+    <t>0.085040696</t>
+  </si>
+  <si>
+    <t>0.5413628802</t>
+  </si>
+  <si>
+    <t>0.2837090587</t>
+  </si>
+  <si>
+    <t>0.2992261738</t>
+  </si>
+  <si>
+    <t>0.0097028989</t>
+  </si>
+  <si>
+    <t>0.4982157893</t>
+  </si>
+  <si>
+    <t>0.7652014035</t>
+  </si>
+  <si>
+    <t>0.5578453728</t>
+  </si>
+  <si>
+    <t>0.3535744357</t>
+  </si>
+  <si>
+    <t>0.2477045828</t>
+  </si>
+  <si>
+    <t>0.7812437352</t>
+  </si>
+  <si>
+    <t>0.9180933969</t>
+  </si>
+  <si>
+    <t>0.5795910651</t>
   </si>
 </sst>
 </file>
@@ -1422,36 +1480,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1463,21 +1497,27 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1502,41 +1542,8 @@
     <xf numFmtId="49" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1544,13 +1551,34 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1870,1024 +1898,1070 @@
   <dimension ref="A1:L52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="51.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.1640625" style="4" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="34.5" style="4" customWidth="1"/>
-    <col min="4" max="4" width="50.33203125" style="24" customWidth="1"/>
-    <col min="5" max="5" width="50.83203125" style="24" customWidth="1"/>
-    <col min="6" max="6" width="22.5" style="4" customWidth="1"/>
-    <col min="7" max="8" width="22" style="4" customWidth="1"/>
-    <col min="9" max="10" width="26.5" style="4" customWidth="1"/>
-    <col min="11" max="11" width="105.6640625" style="9" customWidth="1"/>
-    <col min="12" max="16384" width="51.33203125" style="4"/>
+    <col min="1" max="1" width="26.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="34.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="50.33203125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="50" style="10" customWidth="1"/>
+    <col min="6" max="6" width="24" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="27.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="27.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="31.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="68.33203125" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="51.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" ht="44" x14ac:dyDescent="0.2">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:12" s="20" customFormat="1" ht="66" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="21"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="18" t="s">
         <v>285</v>
       </c>
-      <c r="D1" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J1" s="2" t="s">
+      <c r="D2" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="K3" s="14"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="K4" s="14"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>307</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>309</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>310</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>304</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>305</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="K7" s="14"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>298</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>299</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="K8" s="14"/>
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="11"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="16"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="K13" s="14"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="K14" s="14"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="K17" s="14"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="1" t="s">
+        <v>269</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="K18" s="14"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>251</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>252</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>247</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>248</v>
+      </c>
+      <c r="K21" s="14"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="K1" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="3"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="4" t="s">
+      <c r="G22" s="1" t="s">
+        <v>240</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>242</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="K22" s="14"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="18" t="s">
-        <v>286</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="20" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>351</v>
-      </c>
-      <c r="G2" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>353</v>
-      </c>
-      <c r="I2" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="J2" s="4" t="s">
+      <c r="C24" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>366</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="1" t="s">
+        <v>360</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>361</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>362</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>363</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="K2" s="26" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="4" t="s">
+      <c r="G26" s="1" t="s">
+        <v>356</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>358</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>336</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>337</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>339</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="4" t="s">
-        <v>347</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>350</v>
-      </c>
-      <c r="K3" s="13"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="4" t="s">
+      <c r="C29" s="16"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="1" t="s">
+        <v>331</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>332</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>333</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>334</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>345</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>346</v>
-      </c>
-      <c r="K4" s="13"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="4" t="s">
+      <c r="C30" s="16"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="1" t="s">
+        <v>326</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>327</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>328</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="15" t="s">
-        <v>287</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="21" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="H6" s="4" t="s">
-        <v>310</v>
-      </c>
-      <c r="I6" s="4" t="s">
-        <v>311</v>
-      </c>
-      <c r="J6" s="4" t="s">
+      <c r="C32" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="16"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="16"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="16"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="16"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="11"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>321</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>322</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>323</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>324</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>325</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="16"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="K43" s="14"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="16"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="F44" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="K6" s="13" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="4" t="s">
+      <c r="G44" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="K44" s="14"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>264</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>266</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21"/>
-      <c r="F7" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>304</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="K7" s="13"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="4" t="s">
+      <c r="C47" s="16"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="F47" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>263</v>
+      </c>
+      <c r="K47" s="14"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="15"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="K8" s="13"/>
-    </row>
-    <row r="10" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="12"/>
-      <c r="C10" s="12"/>
-      <c r="D10" s="12"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="17"/>
-      <c r="G10" s="17"/>
-      <c r="H10" s="17"/>
-      <c r="I10" s="17"/>
-      <c r="J10" s="17"/>
-      <c r="K10" s="25"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="4" t="s">
+      <c r="C48" s="16"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="F48" s="1" t="s">
+        <v>254</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>258</v>
+      </c>
+      <c r="K48" s="14"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="15" t="s">
-        <v>288</v>
-      </c>
-      <c r="D12" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>19</v>
-      </c>
-      <c r="K12" s="13" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="4" t="s">
+      <c r="C50" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="K13" s="13"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="4" t="s">
+      <c r="C51" s="16"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="15"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="K14" s="13"/>
-    </row>
-    <row r="16" spans="1:12" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="D16" s="22" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>280</v>
-      </c>
-      <c r="G16" s="16" t="s">
-        <v>281</v>
-      </c>
-      <c r="H16" s="16" t="s">
-        <v>282</v>
-      </c>
-      <c r="I16" s="16" t="s">
-        <v>283</v>
-      </c>
-      <c r="J16" s="16" t="s">
-        <v>284</v>
-      </c>
-      <c r="K16" s="27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="19"/>
-      <c r="D17" s="22"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="4" t="s">
-        <v>275</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="K17" s="27"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="19"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>274</v>
-      </c>
-      <c r="K18" s="27"/>
-    </row>
-    <row r="20" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="D20" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="22" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>250</v>
-      </c>
-      <c r="G20" s="16" t="s">
-        <v>251</v>
-      </c>
-      <c r="H20" s="16" t="s">
-        <v>252</v>
-      </c>
-      <c r="I20" s="16" t="s">
-        <v>253</v>
-      </c>
-      <c r="J20" s="16" t="s">
-        <v>254</v>
-      </c>
-      <c r="K20" s="27" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="19"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="22"/>
-      <c r="F21" s="16" t="s">
-        <v>245</v>
-      </c>
-      <c r="G21" s="16" t="s">
-        <v>246</v>
-      </c>
-      <c r="H21" s="16" t="s">
-        <v>247</v>
-      </c>
-      <c r="I21" s="16" t="s">
-        <v>248</v>
-      </c>
-      <c r="J21" s="16" t="s">
-        <v>249</v>
-      </c>
-      <c r="K21" s="27"/>
-    </row>
-    <row r="22" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="16" t="s">
-        <v>240</v>
-      </c>
-      <c r="G22" s="16" t="s">
-        <v>241</v>
-      </c>
-      <c r="H22" s="16" t="s">
-        <v>242</v>
-      </c>
-      <c r="I22" s="16" t="s">
-        <v>243</v>
-      </c>
-      <c r="J22" s="16" t="s">
-        <v>244</v>
-      </c>
-      <c r="K22" s="27"/>
-    </row>
-    <row r="23" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D23" s="23"/>
-      <c r="E23" s="23"/>
-      <c r="K23" s="28"/>
-    </row>
-    <row r="24" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>291</v>
-      </c>
-      <c r="D24" s="22" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="22" t="s">
-        <v>34</v>
-      </c>
-      <c r="F24" s="16" t="s">
-        <v>366</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>367</v>
-      </c>
-      <c r="H24" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="I24" s="16" t="s">
-        <v>369</v>
-      </c>
-      <c r="J24" s="16" t="s">
+      <c r="C52" s="16"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="K24" s="28"/>
-    </row>
-    <row r="25" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="19"/>
-      <c r="D25" s="22"/>
-      <c r="E25" s="22"/>
-      <c r="F25" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="G25" s="16" t="s">
-        <v>362</v>
-      </c>
-      <c r="H25" s="16" t="s">
-        <v>363</v>
-      </c>
-      <c r="I25" s="16" t="s">
-        <v>364</v>
-      </c>
-      <c r="J25" s="16" t="s">
-        <v>365</v>
-      </c>
-      <c r="K25" s="28"/>
-    </row>
-    <row r="26" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="19"/>
-      <c r="D26" s="22"/>
-      <c r="E26" s="22"/>
-      <c r="F26" s="16" t="s">
-        <v>356</v>
-      </c>
-      <c r="G26" s="16" t="s">
-        <v>357</v>
-      </c>
-      <c r="H26" s="16" t="s">
-        <v>358</v>
-      </c>
-      <c r="I26" s="16" t="s">
-        <v>359</v>
-      </c>
-      <c r="J26" s="16" t="s">
-        <v>360</v>
-      </c>
-      <c r="K26" s="28"/>
-    </row>
-    <row r="27" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D27" s="23"/>
-      <c r="E27" s="23"/>
-      <c r="K27" s="28"/>
-    </row>
-    <row r="28" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="19" t="s">
-        <v>292</v>
-      </c>
-      <c r="D28" s="22" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="22" t="s">
-        <v>35</v>
-      </c>
-      <c r="F28" s="16" t="s">
-        <v>337</v>
-      </c>
-      <c r="G28" s="16" t="s">
-        <v>338</v>
-      </c>
-      <c r="H28" s="16" t="s">
-        <v>339</v>
-      </c>
-      <c r="I28" s="16" t="s">
-        <v>340</v>
-      </c>
-      <c r="J28" s="16" t="s">
-        <v>341</v>
-      </c>
-      <c r="K28" s="28"/>
-    </row>
-    <row r="29" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="19"/>
-      <c r="D29" s="22"/>
-      <c r="E29" s="22"/>
-      <c r="F29" s="16" t="s">
-        <v>332</v>
-      </c>
-      <c r="G29" s="16" t="s">
-        <v>333</v>
-      </c>
-      <c r="H29" s="16" t="s">
-        <v>334</v>
-      </c>
-      <c r="I29" s="16" t="s">
-        <v>335</v>
-      </c>
-      <c r="J29" s="16" t="s">
-        <v>336</v>
-      </c>
-      <c r="K29" s="28"/>
-    </row>
-    <row r="30" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="19"/>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="16" t="s">
-        <v>327</v>
-      </c>
-      <c r="G30" s="16" t="s">
-        <v>328</v>
-      </c>
-      <c r="H30" s="16" t="s">
-        <v>329</v>
-      </c>
-      <c r="I30" s="16" t="s">
-        <v>330</v>
-      </c>
-      <c r="J30" s="16" t="s">
-        <v>331</v>
-      </c>
-      <c r="K30" s="28"/>
-    </row>
-    <row r="31" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D31" s="23"/>
-      <c r="E31" s="23"/>
-      <c r="K31" s="28"/>
-    </row>
-    <row r="32" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="D32" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="22" t="s">
-        <v>31</v>
-      </c>
-      <c r="K32" s="28"/>
-    </row>
-    <row r="33" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="19"/>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="K33" s="28"/>
-    </row>
-    <row r="34" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="16" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="K34" s="28"/>
-    </row>
-    <row r="35" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="D35" s="23"/>
-      <c r="E35" s="23"/>
-      <c r="K35" s="28"/>
-    </row>
-    <row r="36" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="19" t="s">
-        <v>294</v>
-      </c>
-      <c r="D36" s="22" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="22" t="s">
-        <v>36</v>
-      </c>
-      <c r="K36" s="28"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="19"/>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" s="19"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="22"/>
-    </row>
-    <row r="40" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="25"/>
-      <c r="F40" s="17"/>
-      <c r="G40" s="17"/>
-      <c r="H40" s="17"/>
-      <c r="I40" s="17"/>
-      <c r="J40" s="17"/>
-      <c r="K40" s="25"/>
-    </row>
-    <row r="42" spans="1:11" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="16" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>295</v>
-      </c>
-      <c r="D42" s="22" t="s">
-        <v>27</v>
-      </c>
-      <c r="E42" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="F42" s="16" t="s">
-        <v>322</v>
-      </c>
-      <c r="G42" s="16" t="s">
-        <v>323</v>
-      </c>
-      <c r="H42" s="16" t="s">
-        <v>324</v>
-      </c>
-      <c r="I42" s="16" t="s">
-        <v>325</v>
-      </c>
-      <c r="J42" s="16" t="s">
-        <v>326</v>
-      </c>
-      <c r="K42" s="27" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="19"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="22"/>
-      <c r="F43" s="4" t="s">
-        <v>318</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="K43" s="27"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="19"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="22"/>
-      <c r="F44" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="G44" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>316</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="K44" s="27"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>296</v>
-      </c>
-      <c r="D46" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="E46" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="G46" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>267</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="J46" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="K46" s="13" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="15"/>
-      <c r="D47" s="21"/>
-      <c r="E47" s="21"/>
-      <c r="F47" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="G47" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>264</v>
-      </c>
-      <c r="K47" s="13"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A48" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" s="15"/>
-      <c r="D48" s="21"/>
-      <c r="E48" s="21"/>
-      <c r="F48" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="K48" s="13"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A50" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>297</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="E50" s="21" t="s">
-        <v>31</v>
-      </c>
-      <c r="F50" s="4" t="s">
-        <v>381</v>
-      </c>
-      <c r="G50" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="H50" s="4" t="s">
-        <v>383</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>384</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A51" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" s="15"/>
-      <c r="D51" s="21"/>
-      <c r="E51" s="21"/>
-      <c r="F51" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="G51" s="4" t="s">
-        <v>377</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="I51" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A52" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" s="15"/>
-      <c r="D52" s="21"/>
-      <c r="E52" s="21"/>
-      <c r="F52" s="4" t="s">
+      <c r="G52" s="1" t="s">
         <v>371</v>
       </c>
-      <c r="G52" s="4" t="s">
+      <c r="H52" s="1" t="s">
         <v>372</v>
       </c>
-      <c r="H52" s="4" t="s">
+      <c r="I52" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="I52" s="4" t="s">
+      <c r="J52" s="1" t="s">
         <v>374</v>
-      </c>
-      <c r="J52" s="4" t="s">
-        <v>375</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C36:C38"/>
     <mergeCell ref="E46:E48"/>
     <mergeCell ref="E50:E52"/>
     <mergeCell ref="K2:K4"/>
@@ -2904,935 +2978,1568 @@
     <mergeCell ref="E42:E44"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E6:E8"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C36:C38"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ED27533-334C-8545-BBC4-8C9F3EE864EF}">
+  <dimension ref="A1:L52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="51.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="34.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="50.33203125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="50" style="10" customWidth="1"/>
+    <col min="6" max="6" width="24" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="27.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="27.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="31.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="68.33203125" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="51.33203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="20" customFormat="1" ht="66" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="21" t="s">
+        <v>284</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="21" t="s">
+        <v>385</v>
+      </c>
+      <c r="G1" s="21" t="s">
+        <v>386</v>
+      </c>
+      <c r="H1" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="I1" s="21" t="s">
+        <v>388</v>
+      </c>
+      <c r="J1" s="21" t="s">
+        <v>389</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="21"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>285</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="12"/>
+      <c r="E3" s="12"/>
+      <c r="K3" s="14"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="12"/>
+      <c r="K4" s="14"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="12"/>
+      <c r="E7" s="12"/>
+      <c r="K7" s="14"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="12"/>
+      <c r="E8" s="12"/>
+      <c r="K8" s="14"/>
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="17"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="17"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="11"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="16"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="K13" s="14"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="K14" s="14"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="D16" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="16"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="K17" s="14"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="16"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="K18" s="14"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="D20" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="K21" s="14"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="16"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="K22" s="14"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>290</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="16"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="D28" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="16"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="16"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>292</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="16"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="16"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>293</v>
+      </c>
+      <c r="D36" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="16"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="16"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+    </row>
+    <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="11"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="16"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="K43" s="14"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="16"/>
+      <c r="D44" s="12"/>
+      <c r="E44" s="12"/>
+      <c r="K44" s="14"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="D46" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="E46" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="16"/>
+      <c r="D47" s="12"/>
+      <c r="E47" s="12"/>
+      <c r="K47" s="14"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="16"/>
+      <c r="D48" s="12"/>
+      <c r="E48" s="12"/>
+      <c r="K48" s="14"/>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" s="12" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="16"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="16"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="45">
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="K6:K8"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F1BB833-377A-D44F-92A0-3B5384834C0E}">
   <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="38.6640625" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="50.1640625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="35.1640625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="42.5" style="10" customWidth="1"/>
-    <col min="4" max="16384" width="38.6640625" style="4"/>
+    <col min="1" max="1" width="50.1640625" style="6" customWidth="1"/>
+    <col min="2" max="2" width="35.1640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="42.5" style="7" customWidth="1"/>
+    <col min="4" max="16384" width="38.6640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="7" customFormat="1" ht="22" x14ac:dyDescent="0.2">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:9" s="4" customFormat="1" ht="22" x14ac:dyDescent="0.2">
+      <c r="A1" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="4" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="13"/>
-      <c r="B3" s="15"/>
-      <c r="C3" s="14"/>
-      <c r="D3" s="4" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="16"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="13"/>
-      <c r="B4" s="15"/>
-      <c r="C4" s="14"/>
-      <c r="D4" s="4" t="s">
+      <c r="A4" s="14"/>
+      <c r="B4" s="16"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="1" t="s">
         <v>126</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="1" t="s">
         <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="14" t="s">
         <v>186</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="1" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="13"/>
-      <c r="B7" s="15"/>
-      <c r="C7" s="14"/>
-      <c r="D7" s="4" t="s">
+      <c r="A7" s="14"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="H7" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="1" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="13"/>
-      <c r="B8" s="15"/>
-      <c r="C8" s="14"/>
-      <c r="D8" s="4" t="s">
+      <c r="A8" s="14"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="14" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C10" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="1" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="13"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="4" t="s">
+      <c r="A11" s="14"/>
+      <c r="B11" s="16"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="1" t="s">
         <v>131</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="1" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
-      <c r="B12" s="15"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="4" t="s">
+      <c r="A12" s="14"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="13" t="s">
+    <row r="14" spans="1:9" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="F14" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="H14" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="3" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="13"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="4" t="s">
+      <c r="A15" s="14"/>
+      <c r="B15" s="16"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="1" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="13"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="4" t="s">
+      <c r="A16" s="14"/>
+      <c r="B16" s="16"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="1" t="s">
         <v>138</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="1" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="18" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="B18" s="15" t="s">
+      <c r="B18" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="1" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="13"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="4" t="s">
+      <c r="A19" s="14"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="1" t="s">
         <v>111</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="13"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="4" t="s">
+      <c r="A20" s="14"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="1" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="22" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="13" t="s">
+      <c r="A22" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="B22" s="15" t="s">
+      <c r="B22" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="14" t="s">
+      <c r="C22" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="1" t="s">
         <v>116</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="13"/>
-      <c r="B23" s="15"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="4" t="s">
+      <c r="A23" s="14"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="1" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="13"/>
-      <c r="B24" s="15"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="4" t="s">
+      <c r="A24" s="14"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="1" t="s">
         <v>146</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="1" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="14" t="s">
+    <row r="26" spans="1:9" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I26" s="3" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="4" t="s">
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="H27" s="4" t="s">
+      <c r="H27" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="I27" s="4" t="s">
+      <c r="I27" s="1" t="s">
         <v>158</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="4" t="s">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="1" t="s">
         <v>159</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" s="1" t="s">
         <v>163</v>
       </c>
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
     </row>
     <row r="30" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="14" t="s">
+      <c r="A30" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="1" t="s">
         <v>225</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="1" t="s">
         <v>226</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="I30" s="4" t="s">
+      <c r="I30" s="1" t="s">
         <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="4" t="s">
+      <c r="A31" s="19"/>
+      <c r="B31" s="19"/>
+      <c r="C31" s="19"/>
+      <c r="D31" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="1" t="s">
         <v>230</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="1" t="s">
         <v>231</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I31" s="1" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="4" t="s">
+      <c r="A32" s="19"/>
+      <c r="B32" s="19"/>
+      <c r="C32" s="19"/>
+      <c r="D32" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="1" t="s">
         <v>234</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="1" t="s">
         <v>236</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H32" s="1" t="s">
         <v>237</v>
       </c>
-      <c r="I32" s="4" t="s">
+      <c r="I32" s="1" t="s">
         <v>238</v>
       </c>
     </row>
     <row r="34" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="13" t="s">
+      <c r="A34" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B34" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="14" t="s">
+      <c r="C34" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="F34" s="4" t="s">
+      <c r="F34" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="G34" s="4" t="s">
+      <c r="G34" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="H34" s="4" t="s">
+      <c r="H34" s="1" t="s">
         <v>167</v>
       </c>
-      <c r="I34" s="4" t="s">
+      <c r="I34" s="1" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="13"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="4" t="s">
+      <c r="A35" s="14"/>
+      <c r="B35" s="19"/>
+      <c r="C35" s="19"/>
+      <c r="D35" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="H35" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="I35" s="4" t="s">
+      <c r="I35" s="1" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" s="13"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="4" t="s">
+      <c r="A36" s="14"/>
+      <c r="B36" s="19"/>
+      <c r="C36" s="19"/>
+      <c r="D36" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="F36" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="G36" s="4" t="s">
+      <c r="G36" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="H36" s="4" t="s">
+      <c r="H36" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="I36" s="4" t="s">
+      <c r="I36" s="1" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="38" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="13" t="s">
+      <c r="A38" s="14" t="s">
         <v>182</v>
       </c>
-      <c r="B38" s="13" t="s">
+      <c r="B38" s="14" t="s">
         <v>177</v>
       </c>
-      <c r="C38" s="14" t="s">
+      <c r="C38" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="13"/>
-      <c r="B39" s="13"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="4" t="s">
+      <c r="A39" s="14"/>
+      <c r="B39" s="14"/>
+      <c r="C39" s="19"/>
+      <c r="D39" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="13"/>
-      <c r="B40" s="13"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="4" t="s">
+      <c r="A40" s="14"/>
+      <c r="B40" s="14"/>
+      <c r="C40" s="19"/>
+      <c r="D40" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="6" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="13" t="s">
+    <row r="42" spans="1:9" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="B42" s="13" t="s">
+      <c r="B42" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="D42" s="6" t="s">
+      <c r="D42" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="E42" s="6" t="s">
+      <c r="E42" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="F42" s="6" t="s">
+      <c r="F42" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="G42" s="6" t="s">
+      <c r="G42" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="H42" s="6" t="s">
+      <c r="H42" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="I42" s="6" t="s">
+      <c r="I42" s="3" t="s">
         <v>223</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" s="13"/>
-      <c r="B43" s="13"/>
-      <c r="C43" s="14"/>
-      <c r="D43" s="4" t="s">
+      <c r="A43" s="14"/>
+      <c r="B43" s="14"/>
+      <c r="C43" s="19"/>
+      <c r="D43" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="F43" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="G43" s="4" t="s">
+      <c r="G43" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="H43" s="4" t="s">
+      <c r="H43" s="1" t="s">
         <v>217</v>
       </c>
-      <c r="I43" s="4" t="s">
+      <c r="I43" s="1" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" s="13"/>
-      <c r="B44" s="13"/>
-      <c r="C44" s="14"/>
-      <c r="D44" s="4" t="s">
+      <c r="A44" s="14"/>
+      <c r="B44" s="14"/>
+      <c r="C44" s="19"/>
+      <c r="D44" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F44" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G44" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="H44" s="1" t="s">
         <v>213</v>
       </c>
-      <c r="I44" s="4" t="s">
+      <c r="I44" s="1" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="13" t="s">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A46" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="B46" s="13" t="s">
+      <c r="B46" s="14" t="s">
         <v>194</v>
       </c>
-      <c r="C46" s="14" t="s">
+      <c r="C46" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="16" t="s">
+      <c r="E46" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F46" s="16" t="s">
+      <c r="F46" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="G46" s="16" t="s">
+      <c r="G46" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="H46" s="16" t="s">
+      <c r="H46" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="I46" s="16" t="s">
+      <c r="I46" s="1" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" s="13"/>
-      <c r="B47" s="13"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="4" t="s">
+      <c r="A47" s="14"/>
+      <c r="B47" s="14"/>
+      <c r="C47" s="19"/>
+      <c r="D47" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="F47" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="G47" s="4" t="s">
+      <c r="G47" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="H47" s="4" t="s">
+      <c r="H47" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="I47" s="4" t="s">
+      <c r="I47" s="1" t="s">
         <v>203</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A48" s="13"/>
-      <c r="B48" s="13"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="4" t="s">
+      <c r="A48" s="14"/>
+      <c r="B48" s="14"/>
+      <c r="C48" s="19"/>
+      <c r="D48" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="F48" s="4" t="s">
+      <c r="F48" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G48" s="4" t="s">
+      <c r="G48" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="H48" s="4" t="s">
+      <c r="H48" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="I48" s="4" t="s">
+      <c r="I48" s="1" t="s">
         <v>198</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A22:A24"/>
     <mergeCell ref="C22:C24"/>
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="B26:B28"/>
@@ -3847,28 +4554,6 @@
     <mergeCell ref="C18:C20"/>
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B22:B24"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C34:C36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/benchmarking/search_for_best_combination/results_basic.xlsx
+++ b/benchmarking/search_for_best_combination/results_basic.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11210"/>
   <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D21CB4-5EE7-8B4E-BE05-9F7B72CB52CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A72004-59BA-5642-BFD9-989F351B320B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4280" yWindow="500" windowWidth="46920" windowHeight="26600" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>
     <sheet name="Results SPECIAL" sheetId="5" r:id="rId2"/>
-    <sheet name="trial 1" sheetId="2" r:id="rId3"/>
+    <sheet name="Results PRETRAINED" sheetId="6" r:id="rId3"/>
+    <sheet name="trial 1" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="405">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="567">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -1364,9 +1365,6 @@
     <t>TRIPLE CLASSIFICATION F1-MACRO</t>
   </si>
   <si>
-    <t>RELATION CLASSIFICATION HITS@1</t>
-  </si>
-  <si>
     <t>0.1553265707</t>
   </si>
   <si>
@@ -1410,13 +1408,502 @@
   </si>
   <si>
     <t>0.5795910651</t>
+  </si>
+  <si>
+    <t>0.2933740192</t>
+  </si>
+  <si>
+    <t>0.2942062297</t>
+  </si>
+  <si>
+    <t>0.0105413331</t>
+  </si>
+  <si>
+    <t>0.5956281515</t>
+  </si>
+  <si>
+    <t>0.3391163611</t>
+  </si>
+  <si>
+    <t>0.054569232</t>
+  </si>
+  <si>
+    <t>0.007212491</t>
+  </si>
+  <si>
+    <t>0.1673931997</t>
+  </si>
+  <si>
+    <t>0.3931609777</t>
+  </si>
+  <si>
+    <t>0.2490125493</t>
+  </si>
+  <si>
+    <t>0.3218276928</t>
+  </si>
+  <si>
+    <t>0.2502179599</t>
+  </si>
+  <si>
+    <t>0.4032654355</t>
+  </si>
+  <si>
+    <t>0.4791558137</t>
+  </si>
+  <si>
+    <t>0.4535694682</t>
+  </si>
+  <si>
+    <t>0.0002280632</t>
+  </si>
+  <si>
+    <t>0.0066708478</t>
+  </si>
+  <si>
+    <t>0.000285079</t>
+  </si>
+  <si>
+    <t>0.6088653148</t>
+  </si>
+  <si>
+    <t>0.2564452529</t>
+  </si>
+  <si>
+    <t>0.4661326187</t>
+  </si>
+  <si>
+    <t>0.0280232624</t>
+  </si>
+  <si>
+    <t>0.6831062204</t>
+  </si>
+  <si>
+    <t>0.910646471</t>
+  </si>
+  <si>
+    <t>0.6919275876</t>
+  </si>
+  <si>
+    <t>0.480671646</t>
+  </si>
+  <si>
+    <t>0.0175323564</t>
+  </si>
+  <si>
+    <t>0.7417754718</t>
+  </si>
+  <si>
+    <t>0.9276287858</t>
+  </si>
+  <si>
+    <t>0.5094550589</t>
+  </si>
+  <si>
+    <t>0.0170661553</t>
+  </si>
+  <si>
+    <t>0.2404602109</t>
+  </si>
+  <si>
+    <t>0.5804005453</t>
+  </si>
+  <si>
+    <t>0.465284563</t>
+  </si>
+  <si>
+    <t>0.0310642378</t>
+  </si>
+  <si>
+    <t>0.0023969319</t>
+  </si>
+  <si>
+    <t>0.3355704698</t>
+  </si>
+  <si>
+    <t>0.5299550926</t>
+  </si>
+  <si>
+    <t>0.5122215883</t>
+  </si>
+  <si>
+    <t>0.0723873442</t>
+  </si>
+  <si>
+    <t>0.3039309684</t>
+  </si>
+  <si>
+    <t>0.4956840512</t>
+  </si>
+  <si>
+    <t>RELATION CLASSIFICATION F1-MACRO</t>
+  </si>
+  <si>
+    <t>RELATION CLASSIFICATION  F1-MACRO</t>
+  </si>
+  <si>
+    <t>0.4994655866</t>
+  </si>
+  <si>
+    <t>0.0166698601</t>
+  </si>
+  <si>
+    <t>0.0008622341</t>
+  </si>
+  <si>
+    <t>0.3402950757</t>
+  </si>
+  <si>
+    <t>0.5492511854</t>
+  </si>
+  <si>
+    <t>0.478671288</t>
+  </si>
+  <si>
+    <t>0.0433033148</t>
+  </si>
+  <si>
+    <t>0.0017244683</t>
+  </si>
+  <si>
+    <t>0.2019543974</t>
+  </si>
+  <si>
+    <t>0.4589542718</t>
+  </si>
+  <si>
+    <t>0.4385853739</t>
+  </si>
+  <si>
+    <t>0.0453151945</t>
+  </si>
+  <si>
+    <t>0.0023950949</t>
+  </si>
+  <si>
+    <t>0.4433799578</t>
+  </si>
+  <si>
+    <t>0.5099332866</t>
+  </si>
+  <si>
+    <t>0.5044039011</t>
+  </si>
+  <si>
+    <t>0.0002876318</t>
+  </si>
+  <si>
+    <t>0.001725791</t>
+  </si>
+  <si>
+    <t>0.0418024928</t>
+  </si>
+  <si>
+    <t>0.4571895079</t>
+  </si>
+  <si>
+    <t>0.4699553022</t>
+  </si>
+  <si>
+    <t>0.00105465</t>
+  </si>
+  <si>
+    <t>0.0032598274</t>
+  </si>
+  <si>
+    <t>0.3911792905</t>
+  </si>
+  <si>
+    <t>0.5119392176</t>
+  </si>
+  <si>
+    <t>0.4891058816</t>
+  </si>
+  <si>
+    <t>0.0708533078</t>
+  </si>
+  <si>
+    <t>0.0011505273</t>
+  </si>
+  <si>
+    <t>0.4381591563</t>
+  </si>
+  <si>
+    <t>0.5397296813</t>
+  </si>
+  <si>
+    <t>0.490206793</t>
+  </si>
+  <si>
+    <t>0.0007670182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.1702780441 </t>
+  </si>
+  <si>
+    <t>0.4649348343</t>
+  </si>
+  <si>
+    <t>0.4712773825</t>
+  </si>
+  <si>
+    <t>0.0821668265</t>
+  </si>
+  <si>
+    <t>0.0000958773</t>
+  </si>
+  <si>
+    <t>0.4207094919</t>
+  </si>
+  <si>
+    <t>0.8129029676</t>
+  </si>
+  <si>
+    <t>0.4417925586</t>
+  </si>
+  <si>
+    <t>0.0566634708</t>
+  </si>
+  <si>
+    <t>0.0092042186</t>
+  </si>
+  <si>
+    <t>0.421093001</t>
+  </si>
+  <si>
+    <t>0.8192002356</t>
+  </si>
+  <si>
+    <t>0.4449338285</t>
+  </si>
+  <si>
+    <t>0.474982833</t>
+  </si>
+  <si>
+    <t>0.4543683036</t>
+  </si>
+  <si>
+    <t>0.0687440077</t>
+  </si>
+  <si>
+    <t>0.0061361457</t>
+  </si>
+  <si>
+    <t>0.4496644295</t>
+  </si>
+  <si>
+    <t>0.7975278513</t>
+  </si>
+  <si>
+    <t>0.4432182786</t>
+  </si>
+  <si>
+    <t>0.0473633749</t>
+  </si>
+  <si>
+    <t>0.5944391179</t>
+  </si>
+  <si>
+    <t>0.7450181117</t>
+  </si>
+  <si>
+    <t>0.4971688589</t>
+  </si>
+  <si>
+    <t>0.1474592522</t>
+  </si>
+  <si>
+    <t>0.4981744002</t>
+  </si>
+  <si>
+    <t>0.4820336929</t>
+  </si>
+  <si>
+    <t>0.0029721956</t>
+  </si>
+  <si>
+    <t>0.0056567594</t>
+  </si>
+  <si>
+    <t>0.2316395014</t>
+  </si>
+  <si>
+    <t>0.550814014</t>
+  </si>
+  <si>
+    <t>0.4688587232</t>
+  </si>
+  <si>
+    <t>0.0262703739</t>
+  </si>
+  <si>
+    <t>0.3942473634</t>
+  </si>
+  <si>
+    <t>0.8530152464</t>
+  </si>
+  <si>
+    <t>0.433872699</t>
+  </si>
+  <si>
+    <t>0.1035474593</t>
+  </si>
+  <si>
+    <t>0.4897956212</t>
+  </si>
+  <si>
+    <t>0.4776966775</t>
+  </si>
+  <si>
+    <t>0.0208053692</t>
+  </si>
+  <si>
+    <t>0.752541512</t>
+  </si>
+  <si>
+    <t>0.4026642602</t>
+  </si>
+  <si>
+    <t>0.0307766059</t>
+  </si>
+  <si>
+    <t>0.0077660594</t>
+  </si>
+  <si>
+    <t>0.5117929051</t>
+  </si>
+  <si>
+    <t>0.8680892299</t>
+  </si>
+  <si>
+    <t>0.392412305</t>
+  </si>
+  <si>
+    <t>0.0000958038</t>
+  </si>
+  <si>
+    <t>0.0010538418</t>
+  </si>
+  <si>
+    <t>0.5284434848</t>
+  </si>
+  <si>
+    <t>0.4763042531</t>
+  </si>
+  <si>
+    <t>0.0118796704</t>
+  </si>
+  <si>
+    <t>0.0143705691</t>
+  </si>
+  <si>
+    <t>0.2843456601</t>
+  </si>
+  <si>
+    <t>0.7458032071</t>
+  </si>
+  <si>
+    <t>0.4556467403</t>
+  </si>
+  <si>
+    <t>0.0413872389</t>
+  </si>
+  <si>
+    <t>0.0026825063</t>
+  </si>
+  <si>
+    <t>0.2952672926</t>
+  </si>
+  <si>
+    <t>0.712570266</t>
+  </si>
+  <si>
+    <t>0.4628218027</t>
+  </si>
+  <si>
+    <t>0.000479019</t>
+  </si>
+  <si>
+    <t>0.1576930446</t>
+  </si>
+  <si>
+    <t>0.4931564825</t>
+  </si>
+  <si>
+    <t>0.4752223436</t>
+  </si>
+  <si>
+    <t>0.022322284</t>
+  </si>
+  <si>
+    <t>0.0076643035</t>
+  </si>
+  <si>
+    <t>0.3834067829</t>
+  </si>
+  <si>
+    <t>0.7842403611</t>
+  </si>
+  <si>
+    <t>0.4533371352</t>
+  </si>
+  <si>
+    <t>0.0319026633</t>
+  </si>
+  <si>
+    <t>0.0036405442</t>
+  </si>
+  <si>
+    <t>0.3127035831</t>
+  </si>
+  <si>
+    <t>0.721887472</t>
+  </si>
+  <si>
+    <t>0.4495049349</t>
+  </si>
+  <si>
+    <t>0.000958038</t>
+  </si>
+  <si>
+    <t>0.5260962449</t>
+  </si>
+  <si>
+    <t>0.4644065847</t>
+  </si>
+  <si>
+    <t>0.0005748228</t>
+  </si>
+  <si>
+    <t>0.2935428243</t>
+  </si>
+  <si>
+    <t>0.5019272767</t>
+  </si>
+  <si>
+    <t>0.4860498285</t>
+  </si>
+  <si>
+    <t>0.0295075685</t>
+  </si>
+  <si>
+    <t>0.003257329</t>
+  </si>
+  <si>
+    <t>0.2780226097</t>
+  </si>
+  <si>
+    <t>0.8206246848</t>
+  </si>
+  <si>
+    <t>0.392822447</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1446,6 +1933,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -1516,7 +2009,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1551,6 +2044,18 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1575,11 +2080,11 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1912,41 +2417,41 @@
     <col min="12" max="16384" width="51.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="20" customFormat="1" ht="66" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:12" s="12" customFormat="1" ht="66" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="J1" s="21" t="s">
-        <v>389</v>
-      </c>
-      <c r="K1" s="21" t="s">
+      <c r="J1" s="13" t="s">
+        <v>447</v>
+      </c>
+      <c r="K1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="21"/>
+      <c r="L1" s="13"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -1955,31 +2460,31 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="14" t="s">
         <v>350</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>351</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="14" t="s">
         <v>352</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="14" t="s">
         <v>353</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="K2" s="17" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1990,9 +2495,9 @@
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
       <c r="F3" s="1" t="s">
         <v>346</v>
       </c>
@@ -2008,7 +2513,7 @@
       <c r="J3" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="K3" s="14"/>
+      <c r="K3" s="18"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2017,13 +2522,13 @@
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
       <c r="F4" s="1" t="s">
         <v>341</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="14" t="s">
         <v>342</v>
       </c>
       <c r="H4" s="1" t="s">
@@ -2035,7 +2540,7 @@
       <c r="J4" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="K4" s="14"/>
+      <c r="K4" s="18"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -2044,22 +2549,22 @@
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="14" t="s">
         <v>307</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>308</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="14" t="s">
         <v>309</v>
       </c>
       <c r="I6" s="1" t="s">
@@ -2068,7 +2573,7 @@
       <c r="J6" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="K6" s="18" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2079,9 +2584,9 @@
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
       <c r="F7" s="1" t="s">
         <v>302</v>
       </c>
@@ -2094,10 +2599,10 @@
       <c r="I7" s="1" t="s">
         <v>305</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="J7" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="K7" s="14"/>
+      <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -2106,33 +2611,33 @@
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
       <c r="F8" s="1" t="s">
         <v>297</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="14" t="s">
         <v>298</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>299</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="14" t="s">
         <v>300</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="K8" s="14"/>
+      <c r="K8" s="18"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="11"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
@@ -2148,16 +2653,31 @@
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="F12" s="14" t="s">
+        <v>414</v>
+      </c>
+      <c r="G12" s="14" t="s">
+        <v>415</v>
+      </c>
+      <c r="H12" s="14" t="s">
+        <v>416</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="J12" s="14" t="s">
+        <v>418</v>
+      </c>
+      <c r="K12" s="18" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2168,10 +2688,25 @@
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="K13" s="14"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="K13" s="18"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2180,10 +2715,25 @@
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="K14" s="14"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="I14" s="14" t="s">
+        <v>407</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="K14" s="18"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -2192,31 +2742,31 @@
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="14" t="s">
         <v>279</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="14" t="s">
         <v>281</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="14" t="s">
         <v>282</v>
       </c>
       <c r="J16" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="K16" s="14" t="s">
+      <c r="K16" s="18" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2227,9 +2777,9 @@
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
       <c r="F17" s="1" t="s">
         <v>274</v>
       </c>
@@ -2242,10 +2792,10 @@
       <c r="I17" s="1" t="s">
         <v>277</v>
       </c>
-      <c r="J17" s="1" t="s">
+      <c r="J17" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="K17" s="14"/>
+      <c r="K17" s="18"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -2254,13 +2804,13 @@
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
       <c r="F18" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="14" t="s">
         <v>270</v>
       </c>
       <c r="H18" s="1" t="s">
@@ -2272,7 +2822,7 @@
       <c r="J18" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="K18" s="14"/>
+      <c r="K18" s="18"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -2281,31 +2831,31 @@
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="14" t="s">
         <v>250</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" s="14" t="s">
         <v>252</v>
       </c>
       <c r="J20" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="K20" s="14" t="s">
+      <c r="K20" s="18" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2316,25 +2866,25 @@
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
       <c r="F21" s="1" t="s">
         <v>244</v>
       </c>
       <c r="G21" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="14" t="s">
         <v>246</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="J21" s="1" t="s">
+      <c r="J21" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="K21" s="14"/>
+      <c r="K21" s="18"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -2343,9 +2893,9 @@
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
       <c r="F22" s="1" t="s">
         <v>239</v>
       </c>
@@ -2361,7 +2911,7 @@
       <c r="J22" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="K22" s="14"/>
+      <c r="K22" s="18"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -2370,28 +2920,28 @@
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="14" t="s">
         <v>366</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" s="14" t="s">
         <v>368</v>
       </c>
-      <c r="J24" s="1" t="s">
+      <c r="J24" s="14" t="s">
         <v>369</v>
       </c>
     </row>
@@ -2402,9 +2952,9 @@
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
       <c r="F25" s="1" t="s">
         <v>360</v>
       </c>
@@ -2428,9 +2978,9 @@
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
       <c r="F26" s="1" t="s">
         <v>355</v>
       </c>
@@ -2454,19 +3004,19 @@
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="14" t="s">
         <v>336</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="14" t="s">
         <v>337</v>
       </c>
       <c r="H28" s="1" t="s">
@@ -2475,7 +3025,7 @@
       <c r="I28" s="1" t="s">
         <v>339</v>
       </c>
-      <c r="J28" s="1" t="s">
+      <c r="J28" s="14" t="s">
         <v>340</v>
       </c>
     </row>
@@ -2486,9 +3036,9 @@
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
       <c r="F29" s="1" t="s">
         <v>331</v>
       </c>
@@ -2498,7 +3048,7 @@
       <c r="H29" s="1" t="s">
         <v>333</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I29" s="14" t="s">
         <v>334</v>
       </c>
       <c r="J29" s="1" t="s">
@@ -2512,16 +3062,16 @@
       <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
       <c r="F30" s="1" t="s">
         <v>326</v>
       </c>
       <c r="G30" s="1" t="s">
         <v>327</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" s="14" t="s">
         <v>328</v>
       </c>
       <c r="I30" s="1" t="s">
@@ -2538,14 +3088,29 @@
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="16" t="s">
         <v>31</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="H32" s="14" t="s">
+        <v>431</v>
+      </c>
+      <c r="I32" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.2">
@@ -2555,9 +3120,24 @@
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+      <c r="F33" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="G33" s="14" t="s">
+        <v>425</v>
+      </c>
+      <c r="H33" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="J33" s="14" t="s">
+        <v>428</v>
+      </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
@@ -2566,9 +3146,24 @@
       <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>423</v>
+      </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
@@ -2577,29 +3172,29 @@
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="14" t="s">
+        <v>399</v>
+      </c>
+      <c r="G36" s="14" t="s">
         <v>400</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="H36" s="15" t="s">
         <v>401</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="I36" s="14" t="s">
         <v>402</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="J36" s="14" t="s">
         <v>403</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>404</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -2609,23 +3204,23 @@
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="16"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
       <c r="F37" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="G37" s="1" t="s">
         <v>395</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="H37" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="I37" s="1" t="s">
         <v>397</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="J37" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>399</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
@@ -2635,32 +3230,32 @@
       <c r="B38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
       <c r="F38" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>390</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="H38" s="1" t="s">
         <v>391</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="I38" s="1" t="s">
         <v>392</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="J38" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>394</v>
-      </c>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="11"/>
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
@@ -2676,31 +3271,31 @@
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="E42" s="16" t="s">
         <v>29</v>
       </c>
       <c r="F42" s="1" t="s">
         <v>321</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="14" t="s">
         <v>322</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" s="14" t="s">
         <v>323</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I42" s="14" t="s">
         <v>324</v>
       </c>
       <c r="J42" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="K42" s="14" t="s">
+      <c r="K42" s="18" t="s">
         <v>32</v>
       </c>
     </row>
@@ -2711,10 +3306,10 @@
       <c r="B43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="16"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="1" t="s">
+      <c r="C43" s="20"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="14" t="s">
         <v>317</v>
       </c>
       <c r="G43" s="1" t="s">
@@ -2726,10 +3321,10 @@
       <c r="I43" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="J43" s="1" t="s">
+      <c r="J43" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="K43" s="14"/>
+      <c r="K43" s="18"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -2738,9 +3333,9 @@
       <c r="B44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
       <c r="F44" s="1" t="s">
         <v>312</v>
       </c>
@@ -2756,7 +3351,7 @@
       <c r="J44" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="K44" s="14"/>
+      <c r="K44" s="18"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -2765,13 +3360,13 @@
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E46" s="12" t="s">
+      <c r="E46" s="16" t="s">
         <v>30</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -2783,13 +3378,13 @@
       <c r="H46" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="I46" s="14" t="s">
         <v>267</v>
       </c>
       <c r="J46" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="K46" s="14" t="s">
+      <c r="K46" s="18" t="s">
         <v>33</v>
       </c>
     </row>
@@ -2800,25 +3395,25 @@
       <c r="B47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="16"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="1" t="s">
+      <c r="C47" s="20"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="14" t="s">
         <v>259</v>
       </c>
       <c r="G47" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" s="14" t="s">
         <v>261</v>
       </c>
       <c r="I47" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="J47" s="1" t="s">
+      <c r="J47" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="K47" s="14"/>
+      <c r="K47" s="18"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -2827,13 +3422,13 @@
       <c r="B48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C48" s="16"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
       <c r="F48" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="14" t="s">
         <v>255</v>
       </c>
       <c r="H48" s="1" t="s">
@@ -2845,7 +3440,7 @@
       <c r="J48" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="K48" s="14"/>
+      <c r="K48" s="18"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -2854,25 +3449,25 @@
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="E50" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="14" t="s">
         <v>380</v>
       </c>
       <c r="G50" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H50" s="14" t="s">
         <v>382</v>
       </c>
-      <c r="I50" s="1" t="s">
+      <c r="I50" s="14" t="s">
         <v>383</v>
       </c>
       <c r="J50" s="1" t="s">
@@ -2886,9 +3481,9 @@
       <c r="B51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="16"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
+      <c r="C51" s="20"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
       <c r="F51" s="1" t="s">
         <v>375</v>
       </c>
@@ -2901,7 +3496,7 @@
       <c r="I51" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="J51" s="1" t="s">
+      <c r="J51" s="14" t="s">
         <v>379</v>
       </c>
     </row>
@@ -2912,13 +3507,13 @@
       <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="16"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
       <c r="F52" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G52" s="15" t="s">
         <v>371</v>
       </c>
       <c r="H52" s="1" t="s">
@@ -2954,7 +3549,6 @@
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C2:C4"/>
-    <mergeCell ref="E12:E14"/>
     <mergeCell ref="E16:E18"/>
     <mergeCell ref="E20:E22"/>
     <mergeCell ref="C42:C44"/>
@@ -2978,6 +3572,7 @@
     <mergeCell ref="E42:E44"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E6:E8"/>
+    <mergeCell ref="E12:E14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3002,41 +3597,41 @@
     <col min="12" max="16384" width="51.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="20" customFormat="1" ht="66" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+    <row r="1" spans="1:12" s="12" customFormat="1" ht="66" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="21" t="s">
+      <c r="C1" s="13" t="s">
         <v>284</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="21" t="s">
+      <c r="E1" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="21" t="s">
+      <c r="F1" s="13" t="s">
         <v>385</v>
       </c>
-      <c r="G1" s="21" t="s">
+      <c r="G1" s="13" t="s">
         <v>386</v>
       </c>
-      <c r="H1" s="21" t="s">
+      <c r="H1" s="13" t="s">
         <v>387</v>
       </c>
-      <c r="I1" s="21" t="s">
+      <c r="I1" s="13" t="s">
         <v>388</v>
       </c>
-      <c r="J1" s="21" t="s">
-        <v>389</v>
-      </c>
-      <c r="K1" s="21" t="s">
+      <c r="J1" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="K1" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="21"/>
+      <c r="L1" s="13"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
@@ -3045,16 +3640,31 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="C2" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="13" t="s">
+      <c r="F2" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="K2" s="17" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3065,10 +3675,25 @@
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="K3" s="14"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="K3" s="18"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3077,10 +3702,25 @@
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="K4" s="14"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="K4" s="18"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -3089,16 +3729,31 @@
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="16" t="s">
+      <c r="C6" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="K6" s="14" t="s">
+      <c r="F6" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="K6" s="18" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3109,10 +3764,25 @@
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="K7" s="14"/>
+      <c r="C7" s="20"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="K7" s="18"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -3121,18 +3791,33 @@
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12"/>
-      <c r="K8" s="14"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="K8" s="18"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="11"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
@@ -3148,16 +3833,31 @@
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="16" t="s">
+      <c r="C12" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="D12" s="12" t="s">
+      <c r="D12" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="12" t="s">
+      <c r="E12" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="F12" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="K12" s="18" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3168,10 +3868,25 @@
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="16"/>
-      <c r="D13" s="12"/>
-      <c r="E13" s="12"/>
-      <c r="K13" s="14"/>
+      <c r="C13" s="20"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="K13" s="18"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -3180,10 +3895,25 @@
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="K14" s="14"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="K14" s="18"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -3192,16 +3922,31 @@
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="16" t="s">
+      <c r="C16" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="D16" s="12" t="s">
+      <c r="D16" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="K16" s="14" t="s">
+      <c r="F16" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="K16" s="18" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3212,10 +3957,25 @@
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="K17" s="14"/>
+      <c r="C17" s="20"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>484</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="K17" s="18"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -3224,10 +3984,25 @@
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="16"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="K18" s="14"/>
+      <c r="C18" s="20"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="K18" s="18"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -3236,16 +4011,16 @@
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="D20" s="12" t="s">
+      <c r="D20" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="K20" s="14" t="s">
+      <c r="K20" s="18" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3256,10 +4031,10 @@
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="K21" s="14"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="K21" s="18"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -3268,10 +4043,10 @@
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="16"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="K22" s="14"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="K22" s="18"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -3280,14 +4055,29 @@
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D24" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="16" t="s">
         <v>34</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>503</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -3297,9 +4087,24 @@
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
+      <c r="C25" s="20"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>499</v>
+      </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
@@ -3308,9 +4113,24 @@
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
+      <c r="C26" s="20"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>494</v>
+      </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
@@ -3319,14 +4139,29 @@
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="D28" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="16" t="s">
         <v>35</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>515</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -3336,9 +4171,24 @@
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="16"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>511</v>
+      </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -3347,9 +4197,24 @@
       <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="16"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>506</v>
+      </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
@@ -3358,13 +4223,13 @@
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="D32" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="16" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3375,9 +4240,9 @@
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="16"/>
-      <c r="D33" s="12"/>
-      <c r="E33" s="12"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
@@ -3386,9 +4251,9 @@
       <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
@@ -3397,14 +4262,29 @@
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="16" t="s">
         <v>36</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>526</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -3414,9 +4294,24 @@
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="16"/>
-      <c r="D37" s="12"/>
-      <c r="E37" s="12"/>
+      <c r="C37" s="20"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>521</v>
+      </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
@@ -3425,17 +4320,32 @@
       <c r="B38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12"/>
+      <c r="C38" s="20"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>518</v>
+      </c>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="17" t="s">
+      <c r="A40" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="11"/>
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
@@ -3451,16 +4361,31 @@
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="D42" s="12" t="s">
+      <c r="D42" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="E42" s="12" t="s">
+      <c r="E42" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="K42" s="14" t="s">
+      <c r="F42" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="K42" s="18" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3471,10 +4396,25 @@
       <c r="B43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="16"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="K43" s="14"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="K43" s="18"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -3483,10 +4423,25 @@
       <c r="B44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="16"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="K44" s="14"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="K44" s="18"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -3495,16 +4450,31 @@
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="D46" s="12" t="s">
+      <c r="D46" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="E46" s="12" t="s">
+      <c r="E46" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="K46" s="14" t="s">
+      <c r="F46" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="K46" s="18" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3515,10 +4485,25 @@
       <c r="B47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="16"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="K47" s="14"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="K47" s="18"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -3527,49 +4512,1199 @@
       <c r="B48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C48" s="16"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="K48" s="14"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C48" s="20"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="K48" s="18"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="16" t="s">
+      <c r="C50" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="D50" s="12" t="s">
+      <c r="D50" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="E50" s="12" t="s">
+      <c r="E50" s="16" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="F50" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="16"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="C51" s="20"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="16"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
+      <c r="C52" s="20"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="25" t="s">
+        <v>527</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>557</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="45">
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34A06E9C-6A0D-1745-934A-9CD3EA122E2E}">
+  <dimension ref="A1:L52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="51.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="34.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="50.33203125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="50" style="10" customWidth="1"/>
+    <col min="6" max="6" width="24" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="27.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="27.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="31.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="68.33203125" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="51.33203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="12" customFormat="1" ht="66" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="13"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="22" t="s">
+        <v>285</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>443</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="K2" s="17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="20"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="K3" s="18"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="20"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="K4" s="18"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>286</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="K6" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="20"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="K7" s="18"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="20"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="K8" s="18"/>
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="11"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>287</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="K12" s="18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="20"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="K13" s="18"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="K14" s="18"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>288</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="K16" s="18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="G17" s="24" t="s">
+        <v>484</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="K17" s="18"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="20"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="K18" s="18"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>289</v>
+      </c>
+      <c r="D20" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="K20" s="18" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="20"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="K21" s="18"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="20"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="K22" s="18"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>290</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="20"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="20"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>291</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="20"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="20"/>
+      <c r="D30" s="16"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="D32" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="20"/>
+      <c r="D33" s="16"/>
+      <c r="E33" s="16"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="20"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>293</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="20"/>
+      <c r="D37" s="16"/>
+      <c r="E37" s="16"/>
+      <c r="F37" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="20"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="11"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>294</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="K42" s="18" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="20"/>
+      <c r="D43" s="16"/>
+      <c r="E43" s="16"/>
+      <c r="F43" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="K43" s="18"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="20"/>
+      <c r="D44" s="16"/>
+      <c r="E44" s="16"/>
+      <c r="F44" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="K44" s="18"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>295</v>
+      </c>
+      <c r="D46" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="E46" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="K46" s="18" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="20"/>
+      <c r="D47" s="16"/>
+      <c r="E47" s="16"/>
+      <c r="F47" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="K47" s="18"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="20"/>
+      <c r="D48" s="16"/>
+      <c r="E48" s="16"/>
+      <c r="F48" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="K48" s="18"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="20" t="s">
+        <v>296</v>
+      </c>
+      <c r="D50" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="20"/>
+      <c r="D51" s="16"/>
+      <c r="E51" s="16"/>
+      <c r="F51" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="20"/>
+      <c r="D52" s="16"/>
+      <c r="E52" s="16"/>
+      <c r="F52" s="25" t="s">
+        <v>527</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>557</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="45">
@@ -3623,7 +5758,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F1BB833-377A-D44F-92A0-3B5384834C0E}">
   <dimension ref="A1:I48"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="38.6640625" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
@@ -3664,13 +5799,13 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="23" t="s">
         <v>58</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -3693,9 +5828,9 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="14"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="19"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="23"/>
       <c r="D3" s="1" t="s">
         <v>46</v>
       </c>
@@ -3716,9 +5851,9 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="14"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="19"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="23"/>
       <c r="D4" s="1" t="s">
         <v>47</v>
       </c>
@@ -3739,13 +5874,13 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="14" t="s">
+      <c r="A6" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="23" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -3768,9 +5903,9 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="14"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="19"/>
+      <c r="A7" s="18"/>
+      <c r="B7" s="20"/>
+      <c r="C7" s="23"/>
       <c r="D7" s="1" t="s">
         <v>46</v>
       </c>
@@ -3791,9 +5926,9 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="14"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="19"/>
+      <c r="A8" s="18"/>
+      <c r="B8" s="20"/>
+      <c r="C8" s="23"/>
       <c r="D8" s="1" t="s">
         <v>47</v>
       </c>
@@ -3814,13 +5949,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="14" t="s">
+      <c r="A10" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="23" t="s">
         <v>56</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -3843,9 +5978,9 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="14"/>
-      <c r="B11" s="16"/>
-      <c r="C11" s="19"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="20"/>
+      <c r="C11" s="23"/>
       <c r="D11" s="1" t="s">
         <v>46</v>
       </c>
@@ -3866,9 +6001,9 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="14"/>
-      <c r="B12" s="16"/>
-      <c r="C12" s="19"/>
+      <c r="A12" s="18"/>
+      <c r="B12" s="20"/>
+      <c r="C12" s="23"/>
       <c r="D12" s="1" t="s">
         <v>47</v>
       </c>
@@ -3886,13 +6021,13 @@
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="14" t="s">
+      <c r="A14" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="23" t="s">
         <v>55</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -3915,9 +6050,9 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="14"/>
-      <c r="B15" s="16"/>
-      <c r="C15" s="19"/>
+      <c r="A15" s="18"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="23"/>
       <c r="D15" s="1" t="s">
         <v>46</v>
       </c>
@@ -3938,9 +6073,9 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="14"/>
-      <c r="B16" s="16"/>
-      <c r="C16" s="19"/>
+      <c r="A16" s="18"/>
+      <c r="B16" s="20"/>
+      <c r="C16" s="23"/>
       <c r="D16" s="1" t="s">
         <v>47</v>
       </c>
@@ -3961,13 +6096,13 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="23" t="s">
         <v>59</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -3990,9 +6125,9 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="14"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="19"/>
+      <c r="A19" s="18"/>
+      <c r="B19" s="20"/>
+      <c r="C19" s="23"/>
       <c r="D19" s="1" t="s">
         <v>46</v>
       </c>
@@ -4013,9 +6148,9 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="14"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="19"/>
+      <c r="A20" s="18"/>
+      <c r="B20" s="20"/>
+      <c r="C20" s="23"/>
       <c r="D20" s="1" t="s">
         <v>47</v>
       </c>
@@ -4033,13 +6168,13 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="14" t="s">
+      <c r="A22" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="20" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="23" t="s">
         <v>60</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -4062,9 +6197,9 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="14"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="19"/>
+      <c r="A23" s="18"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="23"/>
       <c r="D23" s="1" t="s">
         <v>46</v>
       </c>
@@ -4085,9 +6220,9 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="14"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="19"/>
+      <c r="A24" s="18"/>
+      <c r="B24" s="20"/>
+      <c r="C24" s="23"/>
       <c r="D24" s="1" t="s">
         <v>47</v>
       </c>
@@ -4108,13 +6243,13 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="19" t="s">
+      <c r="A26" s="23" t="s">
         <v>192</v>
       </c>
-      <c r="B26" s="19" t="s">
+      <c r="B26" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="23" t="s">
         <v>122</v>
       </c>
       <c r="D26" s="3" t="s">
@@ -4137,9 +6272,9 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
-      <c r="C27" s="19"/>
+      <c r="A27" s="23"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
       <c r="D27" s="1" t="s">
         <v>46</v>
       </c>
@@ -4160,9 +6295,9 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="19"/>
-      <c r="B28" s="19"/>
-      <c r="C28" s="19"/>
+      <c r="A28" s="23"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
       <c r="D28" s="1" t="s">
         <v>47</v>
       </c>
@@ -4187,13 +6322,13 @@
       <c r="B29" s="7"/>
     </row>
     <row r="30" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="23" t="s">
         <v>193</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="23" t="s">
         <v>190</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="23" t="s">
         <v>122</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -4216,9 +6351,9 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
+      <c r="A31" s="23"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
       <c r="D31" s="1" t="s">
         <v>46</v>
       </c>
@@ -4239,9 +6374,9 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="19"/>
-      <c r="B32" s="19"/>
-      <c r="C32" s="19"/>
+      <c r="A32" s="23"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
       <c r="D32" s="1" t="s">
         <v>47</v>
       </c>
@@ -4262,13 +6397,13 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="14" t="s">
+      <c r="A34" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="B34" s="19" t="s">
+      <c r="B34" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="23" t="s">
         <v>180</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -4291,9 +6426,9 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="14"/>
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
+      <c r="A35" s="18"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
       <c r="D35" s="1" t="s">
         <v>46</v>
       </c>
@@ -4314,9 +6449,9 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" s="14"/>
-      <c r="B36" s="19"/>
-      <c r="C36" s="19"/>
+      <c r="A36" s="18"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
       <c r="D36" s="1" t="s">
         <v>47</v>
       </c>
@@ -4337,13 +6472,13 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="14" t="s">
+      <c r="A38" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B38" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="23" t="s">
         <v>55</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -4351,29 +6486,29 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="14"/>
-      <c r="B39" s="14"/>
-      <c r="C39" s="19"/>
+      <c r="A39" s="18"/>
+      <c r="B39" s="18"/>
+      <c r="C39" s="23"/>
       <c r="D39" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="14"/>
-      <c r="B40" s="14"/>
-      <c r="C40" s="19"/>
+      <c r="A40" s="18"/>
+      <c r="B40" s="18"/>
+      <c r="C40" s="23"/>
       <c r="D40" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="14" t="s">
+      <c r="A42" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B42" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="C42" s="19" t="s">
+      <c r="C42" s="23" t="s">
         <v>60</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -4396,9 +6531,9 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" s="14"/>
-      <c r="B43" s="14"/>
-      <c r="C43" s="19"/>
+      <c r="A43" s="18"/>
+      <c r="B43" s="18"/>
+      <c r="C43" s="23"/>
       <c r="D43" s="1" t="s">
         <v>46</v>
       </c>
@@ -4419,9 +6554,9 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" s="14"/>
-      <c r="B44" s="14"/>
-      <c r="C44" s="19"/>
+      <c r="A44" s="18"/>
+      <c r="B44" s="18"/>
+      <c r="C44" s="23"/>
       <c r="D44" s="1" t="s">
         <v>47</v>
       </c>
@@ -4442,13 +6577,13 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46" s="14" t="s">
+      <c r="A46" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B46" s="18" t="s">
         <v>194</v>
       </c>
-      <c r="C46" s="19" t="s">
+      <c r="C46" s="23" t="s">
         <v>209</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -4471,9 +6606,9 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" s="14"/>
-      <c r="B47" s="14"/>
-      <c r="C47" s="19"/>
+      <c r="A47" s="18"/>
+      <c r="B47" s="18"/>
+      <c r="C47" s="23"/>
       <c r="D47" s="1" t="s">
         <v>46</v>
       </c>
@@ -4494,9 +6629,9 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A48" s="14"/>
-      <c r="B48" s="14"/>
-      <c r="C48" s="19"/>
+      <c r="A48" s="18"/>
+      <c r="B48" s="18"/>
+      <c r="C48" s="23"/>
       <c r="D48" s="1" t="s">
         <v>47</v>
       </c>

--- a/benchmarking/search_for_best_combination/results_basic.xlsx
+++ b/benchmarking/search_for_best_combination/results_basic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6A72004-59BA-5642-BFD9-989F351B320B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F92F4EE-1B42-7D4D-961A-0011771379A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="2" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="593">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -1898,6 +1898,84 @@
   <si>
     <t>0.392822447</t>
   </si>
+  <si>
+    <t>0.3532118888</t>
+  </si>
+  <si>
+    <t>0.5520313963</t>
+  </si>
+  <si>
+    <t>0.4477544779</t>
+  </si>
+  <si>
+    <t>0.0041227229</t>
+  </si>
+  <si>
+    <t>0.2565675935</t>
+  </si>
+  <si>
+    <t>0.5509203869</t>
+  </si>
+  <si>
+    <t>0.4742471747</t>
+  </si>
+  <si>
+    <t>0.0209971237</t>
+  </si>
+  <si>
+    <t>0.0023010547</t>
+  </si>
+  <si>
+    <t>0.3390220518</t>
+  </si>
+  <si>
+    <t>0.8012936808</t>
+  </si>
+  <si>
+    <t>0.4286266132</t>
+  </si>
+  <si>
+    <t>0.0005752637</t>
+  </si>
+  <si>
+    <t>0.6839884947</t>
+  </si>
+  <si>
+    <t>0.5024597125</t>
+  </si>
+  <si>
+    <t>0.4818168789</t>
+  </si>
+  <si>
+    <t>0.0620325983</t>
+  </si>
+  <si>
+    <t>0.0099712368</t>
+  </si>
+  <si>
+    <t>0.221093001</t>
+  </si>
+  <si>
+    <t>0.8361363854</t>
+  </si>
+  <si>
+    <t>0.3803620451</t>
+  </si>
+  <si>
+    <t>0.0265580058</t>
+  </si>
+  <si>
+    <t>0.0792905081</t>
+  </si>
+  <si>
+    <t>0.8982784427</t>
+  </si>
+  <si>
+    <t>0.4274209012</t>
+  </si>
+  <si>
+    <t>0.3460864386</t>
+  </si>
 </sst>
 </file>
 
@@ -1941,7 +2019,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1969,6 +2047,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2009,7 +2093,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2056,6 +2140,12 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2080,11 +2170,20 @@
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2460,13 +2559,13 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="21" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="14" t="s">
@@ -2484,7 +2583,7 @@
       <c r="J2" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="19" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2495,9 +2594,9 @@
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
       <c r="F3" s="1" t="s">
         <v>346</v>
       </c>
@@ -2513,7 +2612,7 @@
       <c r="J3" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="K3" s="18"/>
+      <c r="K3" s="20"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2522,9 +2621,9 @@
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
       <c r="F4" s="1" t="s">
         <v>341</v>
       </c>
@@ -2540,7 +2639,7 @@
       <c r="J4" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="K4" s="18"/>
+      <c r="K4" s="20"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -2549,13 +2648,13 @@
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="18" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="14" t="s">
@@ -2573,7 +2672,7 @@
       <c r="J6" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K6" s="20" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2584,9 +2683,9 @@
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
       <c r="F7" s="1" t="s">
         <v>302</v>
       </c>
@@ -2602,7 +2701,7 @@
       <c r="J7" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="K7" s="18"/>
+      <c r="K7" s="20"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -2611,9 +2710,9 @@
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
       <c r="F8" s="1" t="s">
         <v>297</v>
       </c>
@@ -2629,15 +2728,15 @@
       <c r="J8" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="K8" s="18"/>
+      <c r="K8" s="20"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="11"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
@@ -2653,13 +2752,13 @@
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="22" t="s">
         <v>287</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="18" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="14" t="s">
@@ -2677,7 +2776,7 @@
       <c r="J12" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="K12" s="18" t="s">
+      <c r="K12" s="20" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2688,9 +2787,9 @@
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
       <c r="F13" s="1" t="s">
         <v>409</v>
       </c>
@@ -2706,7 +2805,7 @@
       <c r="J13" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="K13" s="18"/>
+      <c r="K13" s="20"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2715,9 +2814,9 @@
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
       <c r="F14" s="1" t="s">
         <v>404</v>
       </c>
@@ -2733,7 +2832,7 @@
       <c r="J14" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="K14" s="18"/>
+      <c r="K14" s="20"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -2742,13 +2841,13 @@
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="22" t="s">
         <v>288</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="18" t="s">
         <v>29</v>
       </c>
       <c r="F16" s="14" t="s">
@@ -2766,7 +2865,7 @@
       <c r="J16" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="K16" s="18" t="s">
+      <c r="K16" s="20" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2777,9 +2876,9 @@
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
       <c r="F17" s="1" t="s">
         <v>274</v>
       </c>
@@ -2795,7 +2894,7 @@
       <c r="J17" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="K17" s="18"/>
+      <c r="K17" s="20"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -2804,9 +2903,9 @@
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
       <c r="F18" s="1" t="s">
         <v>269</v>
       </c>
@@ -2822,7 +2921,7 @@
       <c r="J18" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="K18" s="18"/>
+      <c r="K18" s="20"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -2831,13 +2930,13 @@
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="22" t="s">
         <v>289</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="18" t="s">
         <v>30</v>
       </c>
       <c r="F20" s="14" t="s">
@@ -2855,7 +2954,7 @@
       <c r="J20" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="K20" s="18" t="s">
+      <c r="K20" s="20" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2866,9 +2965,9 @@
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
       <c r="F21" s="1" t="s">
         <v>244</v>
       </c>
@@ -2884,7 +2983,7 @@
       <c r="J21" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="K21" s="18"/>
+      <c r="K21" s="20"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -2893,9 +2992,9 @@
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
       <c r="F22" s="1" t="s">
         <v>239</v>
       </c>
@@ -2911,7 +3010,7 @@
       <c r="J22" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="K22" s="18"/>
+      <c r="K22" s="20"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -2920,13 +3019,13 @@
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="18" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="14" t="s">
@@ -2952,9 +3051,9 @@
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
       <c r="F25" s="1" t="s">
         <v>360</v>
       </c>
@@ -2978,9 +3077,9 @@
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
       <c r="F26" s="1" t="s">
         <v>355</v>
       </c>
@@ -3004,13 +3103,13 @@
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="22" t="s">
         <v>291</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="18" t="s">
         <v>35</v>
       </c>
       <c r="F28" s="14" t="s">
@@ -3036,9 +3135,9 @@
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="20"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
       <c r="F29" s="1" t="s">
         <v>331</v>
       </c>
@@ -3062,9 +3161,9 @@
       <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="20"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
       <c r="F30" s="1" t="s">
         <v>326</v>
       </c>
@@ -3088,13 +3187,13 @@
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="18" t="s">
         <v>31</v>
       </c>
       <c r="F32" s="15" t="s">
@@ -3120,9 +3219,9 @@
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="20"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
       <c r="F33" s="1" t="s">
         <v>424</v>
       </c>
@@ -3146,9 +3245,9 @@
       <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="20"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
       <c r="F34" s="1" t="s">
         <v>419</v>
       </c>
@@ -3172,13 +3271,13 @@
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="C36" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E36" s="16" t="s">
+      <c r="E36" s="18" t="s">
         <v>36</v>
       </c>
       <c r="F36" s="14" t="s">
@@ -3204,9 +3303,9 @@
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="20"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
       <c r="F37" s="1" t="s">
         <v>394</v>
       </c>
@@ -3230,9 +3329,9 @@
       <c r="B38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
       <c r="F38" s="1" t="s">
         <v>389</v>
       </c>
@@ -3250,12 +3349,12 @@
       </c>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
       <c r="E40" s="11"/>
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
@@ -3271,13 +3370,13 @@
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="20" t="s">
+      <c r="C42" s="22" t="s">
         <v>294</v>
       </c>
-      <c r="D42" s="16" t="s">
+      <c r="D42" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="E42" s="18" t="s">
         <v>29</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -3295,7 +3394,7 @@
       <c r="J42" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="K42" s="18" t="s">
+      <c r="K42" s="20" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3306,9 +3405,9 @@
       <c r="B43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="20"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
       <c r="F43" s="14" t="s">
         <v>317</v>
       </c>
@@ -3324,7 +3423,7 @@
       <c r="J43" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="K43" s="18"/>
+      <c r="K43" s="20"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -3333,9 +3432,9 @@
       <c r="B44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
       <c r="F44" s="1" t="s">
         <v>312</v>
       </c>
@@ -3351,7 +3450,7 @@
       <c r="J44" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="K44" s="18"/>
+      <c r="K44" s="20"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -3360,13 +3459,13 @@
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="C46" s="22" t="s">
         <v>295</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E46" s="16" t="s">
+      <c r="E46" s="18" t="s">
         <v>30</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -3384,7 +3483,7 @@
       <c r="J46" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="K46" s="18" t="s">
+      <c r="K46" s="20" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3395,9 +3494,9 @@
       <c r="B47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="20"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
       <c r="F47" s="14" t="s">
         <v>259</v>
       </c>
@@ -3413,7 +3512,7 @@
       <c r="J47" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="K47" s="18"/>
+      <c r="K47" s="20"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -3422,9 +3521,9 @@
       <c r="B48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
       <c r="F48" s="1" t="s">
         <v>254</v>
       </c>
@@ -3440,7 +3539,7 @@
       <c r="J48" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="K48" s="18"/>
+      <c r="K48" s="20"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -3449,13 +3548,13 @@
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="20" t="s">
+      <c r="C50" s="22" t="s">
         <v>296</v>
       </c>
-      <c r="D50" s="16" t="s">
+      <c r="D50" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E50" s="16" t="s">
+      <c r="E50" s="18" t="s">
         <v>31</v>
       </c>
       <c r="F50" s="14" t="s">
@@ -3481,9 +3580,9 @@
       <c r="B51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="20"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
       <c r="F51" s="1" t="s">
         <v>375</v>
       </c>
@@ -3507,9 +3606,9 @@
       <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="20"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
       <c r="F52" s="1" t="s">
         <v>370</v>
       </c>
@@ -3640,13 +3739,13 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="24" t="s">
         <v>285</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="21" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -3664,7 +3763,7 @@
       <c r="J2" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="K2" s="17" t="s">
+      <c r="K2" s="19" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3675,9 +3774,9 @@
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
       <c r="F3" s="1" t="s">
         <v>438</v>
       </c>
@@ -3693,7 +3792,7 @@
       <c r="J3" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="K3" s="18"/>
+      <c r="K3" s="20"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3702,9 +3801,9 @@
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
       <c r="F4" s="1" t="s">
         <v>434</v>
       </c>
@@ -3720,7 +3819,7 @@
       <c r="J4" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="K4" s="18"/>
+      <c r="K4" s="20"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -3729,13 +3828,13 @@
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="C6" s="22" t="s">
         <v>286</v>
       </c>
-      <c r="D6" s="16" t="s">
+      <c r="D6" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="16" t="s">
+      <c r="E6" s="18" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -3753,7 +3852,7 @@
       <c r="J6" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="K6" s="18" t="s">
+      <c r="K6" s="20" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3764,9 +3863,9 @@
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
       <c r="F7" s="1" t="s">
         <v>454</v>
       </c>
@@ -3782,7 +3881,7 @@
       <c r="J7" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="K7" s="18"/>
+      <c r="K7" s="20"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -3791,9 +3890,9 @@
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
       <c r="F8" s="1" t="s">
         <v>449</v>
       </c>
@@ -3809,15 +3908,15 @@
       <c r="J8" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="K8" s="18"/>
+      <c r="K8" s="20"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="23" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
       <c r="E10" s="11"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
@@ -3833,13 +3932,13 @@
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="22" t="s">
         <v>287</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="18" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -3857,7 +3956,7 @@
       <c r="J12" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="K12" s="18" t="s">
+      <c r="K12" s="20" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3868,9 +3967,9 @@
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
       <c r="F13" s="1" t="s">
         <v>469</v>
       </c>
@@ -3886,7 +3985,7 @@
       <c r="J13" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="K13" s="18"/>
+      <c r="K13" s="20"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -3895,9 +3994,9 @@
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
       <c r="F14" s="1" t="s">
         <v>464</v>
       </c>
@@ -3913,7 +4012,7 @@
       <c r="J14" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="K14" s="18"/>
+      <c r="K14" s="20"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -3922,13 +4021,13 @@
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="20" t="s">
+      <c r="C16" s="22" t="s">
         <v>288</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="18" t="s">
         <v>29</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -3946,7 +4045,7 @@
       <c r="J16" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="K16" s="18" t="s">
+      <c r="K16" s="20" t="s">
         <v>38</v>
       </c>
     </row>
@@ -3957,13 +4056,13 @@
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
       <c r="F17" s="1" t="s">
         <v>483</v>
       </c>
-      <c r="G17" s="24" t="s">
+      <c r="G17" s="16" t="s">
         <v>484</v>
       </c>
       <c r="H17" s="1" t="s">
@@ -3975,7 +4074,7 @@
       <c r="J17" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="K17" s="18"/>
+      <c r="K17" s="20"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -3984,9 +4083,9 @@
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
       <c r="F18" s="1" t="s">
         <v>479</v>
       </c>
@@ -4002,7 +4101,7 @@
       <c r="J18" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="K18" s="18"/>
+      <c r="K18" s="20"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -4011,16 +4110,16 @@
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="C20" s="22" t="s">
         <v>289</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="K20" s="18" t="s">
+      <c r="K20" s="20" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4031,10 +4130,10 @@
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="K21" s="18"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="K21" s="20"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -4043,10 +4142,10 @@
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="K22" s="18"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="K22" s="20"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -4055,13 +4154,13 @@
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="20" t="s">
+      <c r="C24" s="22" t="s">
         <v>290</v>
       </c>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="18" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -4087,9 +4186,9 @@
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
       <c r="F25" s="1" t="s">
         <v>495</v>
       </c>
@@ -4113,9 +4212,9 @@
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
       <c r="F26" s="1" t="s">
         <v>464</v>
       </c>
@@ -4139,13 +4238,13 @@
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="22" t="s">
         <v>291</v>
       </c>
-      <c r="D28" s="16" t="s">
+      <c r="D28" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="18" t="s">
         <v>35</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -4171,9 +4270,9 @@
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="20"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
       <c r="F29" s="1" t="s">
         <v>507</v>
       </c>
@@ -4197,9 +4296,9 @@
       <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="20"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
       <c r="F30" s="1" t="s">
         <v>211</v>
       </c>
@@ -4223,13 +4322,13 @@
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="22" t="s">
         <v>292</v>
       </c>
-      <c r="D32" s="16" t="s">
+      <c r="D32" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E32" s="16" t="s">
+      <c r="E32" s="18" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4240,9 +4339,9 @@
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="20"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
@@ -4251,9 +4350,9 @@
       <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="20"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
@@ -4262,13 +4361,13 @@
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="C36" s="22" t="s">
         <v>293</v>
       </c>
-      <c r="D36" s="16" t="s">
+      <c r="D36" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E36" s="16" t="s">
+      <c r="E36" s="18" t="s">
         <v>36</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -4294,9 +4393,9 @@
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="20"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
       <c r="F37" s="1" t="s">
         <v>496</v>
       </c>
@@ -4320,9 +4419,9 @@
       <c r="B38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
       <c r="F38" s="1" t="s">
         <v>141</v>
       </c>
@@ -4340,12 +4439,12 @@
       </c>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="23" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
       <c r="E40" s="11"/>
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
@@ -4361,13 +4460,13 @@
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="20" t="s">
+      <c r="C42" s="22" t="s">
         <v>294</v>
       </c>
-      <c r="D42" s="16" t="s">
+      <c r="D42" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E42" s="16" t="s">
+      <c r="E42" s="18" t="s">
         <v>29</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -4385,7 +4484,7 @@
       <c r="J42" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="K42" s="18" t="s">
+      <c r="K42" s="20" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4396,9 +4495,9 @@
       <c r="B43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="20"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
+      <c r="C43" s="22"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
       <c r="F43" s="1" t="s">
         <v>531</v>
       </c>
@@ -4414,7 +4513,7 @@
       <c r="J43" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="K43" s="18"/>
+      <c r="K43" s="20"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -4423,9 +4522,9 @@
       <c r="B44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
+      <c r="C44" s="22"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
       <c r="F44" s="1" t="s">
         <v>527</v>
       </c>
@@ -4441,7 +4540,7 @@
       <c r="J44" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="K44" s="18"/>
+      <c r="K44" s="20"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -4450,13 +4549,13 @@
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="20" t="s">
+      <c r="C46" s="22" t="s">
         <v>295</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="E46" s="16" t="s">
+      <c r="E46" s="18" t="s">
         <v>30</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -4474,7 +4573,7 @@
       <c r="J46" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="K46" s="18" t="s">
+      <c r="K46" s="20" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4485,9 +4584,9 @@
       <c r="B47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="20"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
+      <c r="C47" s="22"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
       <c r="F47" s="1" t="s">
         <v>545</v>
       </c>
@@ -4503,7 +4602,7 @@
       <c r="J47" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="K47" s="18"/>
+      <c r="K47" s="20"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -4512,9 +4611,9 @@
       <c r="B48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
+      <c r="C48" s="22"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
       <c r="F48" s="1" t="s">
         <v>541</v>
       </c>
@@ -4530,7 +4629,7 @@
       <c r="J48" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="K48" s="18"/>
+      <c r="K48" s="20"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -4539,13 +4638,13 @@
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="20" t="s">
+      <c r="C50" s="22" t="s">
         <v>296</v>
       </c>
-      <c r="D50" s="16" t="s">
+      <c r="D50" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E50" s="16" t="s">
+      <c r="E50" s="18" t="s">
         <v>31</v>
       </c>
       <c r="F50" s="1" t="s">
@@ -4571,9 +4670,9 @@
       <c r="B51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="20"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
       <c r="F51" s="1" t="s">
         <v>558</v>
       </c>
@@ -4597,10 +4696,1193 @@
       <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="20"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="25" t="s">
+      <c r="C52" s="22"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="17" t="s">
+        <v>527</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>555</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>556</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>557</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="45">
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34A06E9C-6A0D-1745-934A-9CD3EA122E2E}">
+  <dimension ref="A1:L52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="51.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="26.1640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="34.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="50.33203125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="50" style="10" customWidth="1"/>
+    <col min="6" max="6" width="24" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.1640625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="27.5" style="1" customWidth="1"/>
+    <col min="9" max="9" width="27.33203125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="31.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="68.33203125" style="6" customWidth="1"/>
+    <col min="12" max="16384" width="51.33203125" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="12" customFormat="1" ht="66" x14ac:dyDescent="0.2">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>385</v>
+      </c>
+      <c r="G1" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="H1" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="J1" s="13" t="s">
+        <v>446</v>
+      </c>
+      <c r="K1" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="L1" s="13"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="14" t="s">
+        <v>443</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>445</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>448</v>
+      </c>
+      <c r="K2" s="19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>442</v>
+      </c>
+      <c r="K3" s="20"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="K4" s="20"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>286</v>
+      </c>
+      <c r="D6" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>463</v>
+      </c>
+      <c r="K6" s="20" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="K7" s="20"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="1" t="s">
+        <v>449</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>450</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>451</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>452</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="K8" s="20"/>
+    </row>
+    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="23"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="9"/>
+      <c r="I10" s="9"/>
+      <c r="J10" s="9"/>
+      <c r="K10" s="11"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="D12" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="K12" s="20" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="22"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="K13" s="20"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="22"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="G14" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="K14" s="20"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>288</v>
+      </c>
+      <c r="D16" s="18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="K16" s="20" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="22"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>484</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="K17" s="20"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="22"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="K18" s="20"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A20" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="22" t="s">
+        <v>289</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>22</v>
+      </c>
+      <c r="E20" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>574</v>
+      </c>
+      <c r="G20" s="1" t="s">
+        <v>575</v>
+      </c>
+      <c r="H20" s="1" t="s">
+        <v>576</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>577</v>
+      </c>
+      <c r="J20" s="1" t="s">
+        <v>578</v>
+      </c>
+      <c r="K20" s="20" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A21" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="22"/>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="K21" s="20"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="22"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G22" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>567</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="J22" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="K22" s="20"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A24" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="22" t="s">
+        <v>290</v>
+      </c>
+      <c r="D24" s="18" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="22"/>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="22"/>
+      <c r="D26" s="18"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="D28" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C29" s="22"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="22"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="26" t="s">
+        <v>4</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="27" t="s">
+        <v>292</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="F32" s="26" t="s">
+        <v>588</v>
+      </c>
+      <c r="G32" s="29" t="s">
+        <v>589</v>
+      </c>
+      <c r="H32" s="26" t="s">
+        <v>591</v>
+      </c>
+      <c r="I32" s="29" t="s">
+        <v>590</v>
+      </c>
+      <c r="J32" s="26" t="s">
+        <v>592</v>
+      </c>
+      <c r="K32" s="30"/>
+    </row>
+    <row r="33" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>8</v>
+      </c>
+      <c r="C33" s="27"/>
+      <c r="D33" s="28"/>
+      <c r="E33" s="28"/>
+      <c r="F33" s="26" t="s">
+        <v>583</v>
+      </c>
+      <c r="G33" s="26" t="s">
+        <v>584</v>
+      </c>
+      <c r="H33" s="26" t="s">
+        <v>585</v>
+      </c>
+      <c r="I33" s="26" t="s">
+        <v>586</v>
+      </c>
+      <c r="J33" s="26" t="s">
+        <v>587</v>
+      </c>
+      <c r="K33" s="30"/>
+    </row>
+    <row r="34" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="26" t="s">
+        <v>6</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C34" s="27"/>
+      <c r="D34" s="28"/>
+      <c r="E34" s="28"/>
+      <c r="F34" s="26" t="s">
+        <v>579</v>
+      </c>
+      <c r="G34" s="26" t="s">
+        <v>475</v>
+      </c>
+      <c r="H34" s="29" t="s">
+        <v>580</v>
+      </c>
+      <c r="I34" s="26" t="s">
+        <v>581</v>
+      </c>
+      <c r="J34" s="26" t="s">
+        <v>582</v>
+      </c>
+      <c r="K34" s="30"/>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="D36" s="18" t="s">
+        <v>26</v>
+      </c>
+      <c r="E36" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A37" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="22"/>
+      <c r="D37" s="18"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="22"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="11"/>
+      <c r="F40" s="9"/>
+      <c r="G40" s="9"/>
+      <c r="H40" s="9"/>
+      <c r="I40" s="9"/>
+      <c r="J40" s="9"/>
+      <c r="K40" s="11"/>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="D42" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="G42" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="H42" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="I42" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="J42" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="K42" s="20" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C43" s="22"/>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="1" t="s">
+        <v>531</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>532</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>533</v>
+      </c>
+      <c r="I43" s="1" t="s">
+        <v>534</v>
+      </c>
+      <c r="J43" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="K43" s="20"/>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C44" s="22"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="H44" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="I44" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="J44" s="1" t="s">
+        <v>530</v>
+      </c>
+      <c r="K44" s="20"/>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="D46" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="E46" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>550</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>551</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>552</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>553</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>554</v>
+      </c>
+      <c r="K46" s="20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A47" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="22"/>
+      <c r="D47" s="18"/>
+      <c r="E47" s="18"/>
+      <c r="F47" s="1" t="s">
+        <v>545</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>546</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>547</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>548</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>549</v>
+      </c>
+      <c r="K47" s="20"/>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" s="22"/>
+      <c r="D48" s="18"/>
+      <c r="E48" s="18"/>
+      <c r="F48" s="1" t="s">
+        <v>541</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>542</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>543</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>544</v>
+      </c>
+      <c r="K48" s="20"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A50" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="D50" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>563</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>564</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>565</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A51" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="22"/>
+      <c r="D51" s="18"/>
+      <c r="E51" s="18"/>
+      <c r="F51" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C52" s="22"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="17" t="s">
         <v>527</v>
       </c>
       <c r="G52" s="1" t="s">
@@ -4668,1096 +5950,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34A06E9C-6A0D-1745-934A-9CD3EA122E2E}">
-  <dimension ref="A1:L52"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="51.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
-  <cols>
-    <col min="1" max="1" width="26.1640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="17.6640625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="34.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="50.33203125" style="10" customWidth="1"/>
-    <col min="5" max="5" width="50" style="10" customWidth="1"/>
-    <col min="6" max="6" width="24" style="1" customWidth="1"/>
-    <col min="7" max="7" width="23.1640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="27.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="27.33203125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="31.33203125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="68.33203125" style="6" customWidth="1"/>
-    <col min="12" max="16384" width="51.33203125" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" s="12" customFormat="1" ht="66" x14ac:dyDescent="0.2">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>385</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>386</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="J1" s="13" t="s">
-        <v>446</v>
-      </c>
-      <c r="K1" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="L1" s="13"/>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="22" t="s">
-        <v>285</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>443</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>444</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>445</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="K2" s="17" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="20"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="1" t="s">
-        <v>438</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>439</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>440</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>441</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="K3" s="18"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="20"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>435</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>436</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="K4" s="18"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>286</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>459</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>460</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>461</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>463</v>
-      </c>
-      <c r="K6" s="18" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C7" s="20"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="1" t="s">
-        <v>454</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>456</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>457</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="K7" s="18"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="20"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="1" t="s">
-        <v>449</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>450</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>451</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>452</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="K8" s="18"/>
-    </row>
-    <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
-      <c r="K10" s="11"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="20" t="s">
-        <v>287</v>
-      </c>
-      <c r="D12" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>474</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>475</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>476</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>477</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="K12" s="18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16"/>
-      <c r="F13" s="1" t="s">
-        <v>469</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>471</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>472</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="K13" s="18"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>465</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>466</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>467</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="K14" s="18"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="20" t="s">
-        <v>288</v>
-      </c>
-      <c r="D16" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="E16" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="K16" s="18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A17" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="G17" s="24" t="s">
-        <v>484</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="K17" s="18"/>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A18" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C18" s="20"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="K18" s="18"/>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A20" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="D20" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="K20" s="18" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A21" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="K21" s="18"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A22" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C22" s="20"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="K22" s="18"/>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A24" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>290</v>
-      </c>
-      <c r="D24" s="16" t="s">
-        <v>23</v>
-      </c>
-      <c r="E24" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A25" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="20"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A26" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="20"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A28" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>291</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A29" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="20"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>511</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="20"/>
-      <c r="D30" s="16"/>
-      <c r="E30" s="16"/>
-      <c r="F30" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A32" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="20" t="s">
-        <v>292</v>
-      </c>
-      <c r="D32" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E32" s="16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A33" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="20"/>
-      <c r="D33" s="16"/>
-      <c r="E33" s="16"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A34" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="20"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C36" s="20" t="s">
-        <v>293</v>
-      </c>
-      <c r="D36" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="E36" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A37" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C37" s="20"/>
-      <c r="D37" s="16"/>
-      <c r="E37" s="16"/>
-      <c r="F37" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A38" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" s="20"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="9"/>
-      <c r="H40" s="9"/>
-      <c r="I40" s="9"/>
-      <c r="J40" s="9"/>
-      <c r="K40" s="11"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A42" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>294</v>
-      </c>
-      <c r="D42" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="E42" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>538</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>539</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="K42" s="18" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C43" s="20"/>
-      <c r="D43" s="16"/>
-      <c r="E43" s="16"/>
-      <c r="F43" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>532</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="K43" s="18"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A44" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="20"/>
-      <c r="D44" s="16"/>
-      <c r="E44" s="16"/>
-      <c r="F44" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="G44" s="1" t="s">
-        <v>528</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>529</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="K44" s="18"/>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="20" t="s">
-        <v>295</v>
-      </c>
-      <c r="D46" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="E46" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="K46" s="18" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A47" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="20"/>
-      <c r="D47" s="16"/>
-      <c r="E47" s="16"/>
-      <c r="F47" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="K47" s="18"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" s="20"/>
-      <c r="D48" s="16"/>
-      <c r="E48" s="16"/>
-      <c r="F48" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="K48" s="18"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C50" s="20" t="s">
-        <v>296</v>
-      </c>
-      <c r="D50" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="E50" s="16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A51" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" s="20"/>
-      <c r="D51" s="16"/>
-      <c r="E51" s="16"/>
-      <c r="F51" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C52" s="20"/>
-      <c r="D52" s="16"/>
-      <c r="E52" s="16"/>
-      <c r="F52" s="25" t="s">
-        <v>527</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>557</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="45">
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="K46:K48"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="E50:E52"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="K6:K8"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F1BB833-377A-D44F-92A0-3B5384834C0E}">
   <dimension ref="A1:I48"/>
@@ -5799,13 +5991,13 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="20" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="25" t="s">
         <v>58</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -5828,9 +6020,9 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="18"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="23"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="25"/>
       <c r="D3" s="1" t="s">
         <v>46</v>
       </c>
@@ -5851,9 +6043,9 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="18"/>
-      <c r="B4" s="20"/>
-      <c r="C4" s="23"/>
+      <c r="A4" s="20"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="25"/>
       <c r="D4" s="1" t="s">
         <v>47</v>
       </c>
@@ -5874,13 +6066,13 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="20" t="s">
         <v>186</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="23" t="s">
+      <c r="C6" s="25" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -5903,9 +6095,9 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="18"/>
-      <c r="B7" s="20"/>
-      <c r="C7" s="23"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="25"/>
       <c r="D7" s="1" t="s">
         <v>46</v>
       </c>
@@ -5926,9 +6118,9 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="18"/>
-      <c r="B8" s="20"/>
-      <c r="C8" s="23"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="25"/>
       <c r="D8" s="1" t="s">
         <v>47</v>
       </c>
@@ -5949,13 +6141,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="18" t="s">
+      <c r="A10" s="20" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="25" t="s">
         <v>56</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -5978,9 +6170,9 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="18"/>
-      <c r="B11" s="20"/>
-      <c r="C11" s="23"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="25"/>
       <c r="D11" s="1" t="s">
         <v>46</v>
       </c>
@@ -6001,9 +6193,9 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="18"/>
-      <c r="B12" s="20"/>
-      <c r="C12" s="23"/>
+      <c r="A12" s="20"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="25"/>
       <c r="D12" s="1" t="s">
         <v>47</v>
       </c>
@@ -6021,13 +6213,13 @@
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="22" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="23" t="s">
+      <c r="C14" s="25" t="s">
         <v>55</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -6050,9 +6242,9 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="18"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="23"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="25"/>
       <c r="D15" s="1" t="s">
         <v>46</v>
       </c>
@@ -6073,9 +6265,9 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="18"/>
-      <c r="B16" s="20"/>
-      <c r="C16" s="23"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="25"/>
       <c r="D16" s="1" t="s">
         <v>47</v>
       </c>
@@ -6096,13 +6288,13 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="20" t="s">
         <v>183</v>
       </c>
-      <c r="B18" s="20" t="s">
+      <c r="B18" s="22" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="23" t="s">
+      <c r="C18" s="25" t="s">
         <v>59</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -6125,9 +6317,9 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="18"/>
-      <c r="B19" s="20"/>
-      <c r="C19" s="23"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="22"/>
+      <c r="C19" s="25"/>
       <c r="D19" s="1" t="s">
         <v>46</v>
       </c>
@@ -6148,9 +6340,9 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="18"/>
-      <c r="B20" s="20"/>
-      <c r="C20" s="23"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="22"/>
+      <c r="C20" s="25"/>
       <c r="D20" s="1" t="s">
         <v>47</v>
       </c>
@@ -6168,13 +6360,13 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="18" t="s">
+      <c r="A22" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="B22" s="20" t="s">
+      <c r="B22" s="22" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="25" t="s">
         <v>60</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -6197,9 +6389,9 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="18"/>
-      <c r="B23" s="20"/>
-      <c r="C23" s="23"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="22"/>
+      <c r="C23" s="25"/>
       <c r="D23" s="1" t="s">
         <v>46</v>
       </c>
@@ -6220,9 +6412,9 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="18"/>
-      <c r="B24" s="20"/>
-      <c r="C24" s="23"/>
+      <c r="A24" s="20"/>
+      <c r="B24" s="22"/>
+      <c r="C24" s="25"/>
       <c r="D24" s="1" t="s">
         <v>47</v>
       </c>
@@ -6243,13 +6435,13 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="23" t="s">
+      <c r="A26" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="B26" s="23" t="s">
+      <c r="B26" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="23" t="s">
+      <c r="C26" s="25" t="s">
         <v>122</v>
       </c>
       <c r="D26" s="3" t="s">
@@ -6272,9 +6464,9 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="23"/>
-      <c r="B27" s="23"/>
-      <c r="C27" s="23"/>
+      <c r="A27" s="25"/>
+      <c r="B27" s="25"/>
+      <c r="C27" s="25"/>
       <c r="D27" s="1" t="s">
         <v>46</v>
       </c>
@@ -6295,9 +6487,9 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="23"/>
-      <c r="B28" s="23"/>
-      <c r="C28" s="23"/>
+      <c r="A28" s="25"/>
+      <c r="B28" s="25"/>
+      <c r="C28" s="25"/>
       <c r="D28" s="1" t="s">
         <v>47</v>
       </c>
@@ -6322,13 +6514,13 @@
       <c r="B29" s="7"/>
     </row>
     <row r="30" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="25" t="s">
         <v>122</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -6351,9 +6543,9 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="23"/>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
+      <c r="A31" s="25"/>
+      <c r="B31" s="25"/>
+      <c r="C31" s="25"/>
       <c r="D31" s="1" t="s">
         <v>46</v>
       </c>
@@ -6374,9 +6566,9 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="23"/>
-      <c r="B32" s="23"/>
-      <c r="C32" s="23"/>
+      <c r="A32" s="25"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
       <c r="D32" s="1" t="s">
         <v>47</v>
       </c>
@@ -6397,13 +6589,13 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="B34" s="23" t="s">
+      <c r="B34" s="25" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="23" t="s">
+      <c r="C34" s="25" t="s">
         <v>180</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -6426,9 +6618,9 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="18"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
+      <c r="A35" s="20"/>
+      <c r="B35" s="25"/>
+      <c r="C35" s="25"/>
       <c r="D35" s="1" t="s">
         <v>46</v>
       </c>
@@ -6449,9 +6641,9 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" s="18"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
+      <c r="A36" s="20"/>
+      <c r="B36" s="25"/>
+      <c r="C36" s="25"/>
       <c r="D36" s="1" t="s">
         <v>47</v>
       </c>
@@ -6472,13 +6664,13 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="18" t="s">
+      <c r="A38" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="C38" s="23" t="s">
+      <c r="C38" s="25" t="s">
         <v>55</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -6486,29 +6678,29 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="18"/>
-      <c r="B39" s="18"/>
-      <c r="C39" s="23"/>
+      <c r="A39" s="20"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="25"/>
       <c r="D39" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="18"/>
-      <c r="B40" s="18"/>
-      <c r="C40" s="23"/>
+      <c r="A40" s="20"/>
+      <c r="B40" s="20"/>
+      <c r="C40" s="25"/>
       <c r="D40" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="18" t="s">
+      <c r="A42" s="20" t="s">
         <v>188</v>
       </c>
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="20" t="s">
         <v>189</v>
       </c>
-      <c r="C42" s="23" t="s">
+      <c r="C42" s="25" t="s">
         <v>60</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -6531,9 +6723,9 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" s="18"/>
-      <c r="B43" s="18"/>
-      <c r="C43" s="23"/>
+      <c r="A43" s="20"/>
+      <c r="B43" s="20"/>
+      <c r="C43" s="25"/>
       <c r="D43" s="1" t="s">
         <v>46</v>
       </c>
@@ -6554,9 +6746,9 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" s="18"/>
-      <c r="B44" s="18"/>
-      <c r="C44" s="23"/>
+      <c r="A44" s="20"/>
+      <c r="B44" s="20"/>
+      <c r="C44" s="25"/>
       <c r="D44" s="1" t="s">
         <v>47</v>
       </c>
@@ -6577,13 +6769,13 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46" s="18" t="s">
+      <c r="A46" s="20" t="s">
         <v>191</v>
       </c>
-      <c r="B46" s="18" t="s">
+      <c r="B46" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="C46" s="23" t="s">
+      <c r="C46" s="25" t="s">
         <v>209</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -6606,9 +6798,9 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" s="18"/>
-      <c r="B47" s="18"/>
-      <c r="C47" s="23"/>
+      <c r="A47" s="20"/>
+      <c r="B47" s="20"/>
+      <c r="C47" s="25"/>
       <c r="D47" s="1" t="s">
         <v>46</v>
       </c>
@@ -6629,9 +6821,9 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A48" s="18"/>
-      <c r="B48" s="18"/>
-      <c r="C48" s="23"/>
+      <c r="A48" s="20"/>
+      <c r="B48" s="20"/>
+      <c r="C48" s="25"/>
       <c r="D48" s="1" t="s">
         <v>47</v>
       </c>

--- a/benchmarking/search_for_best_combination/results_basic.xlsx
+++ b/benchmarking/search_for_best_combination/results_basic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F92F4EE-1B42-7D4D-961A-0011771379A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B844ED1-B5BA-B24B-BDFD-1E9A5AEBC9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="2" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="619">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -1899,82 +1899,160 @@
     <t>0.392822447</t>
   </si>
   <si>
-    <t>0.3532118888</t>
-  </si>
-  <si>
-    <t>0.5520313963</t>
-  </si>
-  <si>
-    <t>0.4477544779</t>
-  </si>
-  <si>
-    <t>0.0041227229</t>
-  </si>
-  <si>
-    <t>0.2565675935</t>
-  </si>
-  <si>
-    <t>0.5509203869</t>
-  </si>
-  <si>
-    <t>0.4742471747</t>
-  </si>
-  <si>
-    <t>0.0209971237</t>
-  </si>
-  <si>
-    <t>0.0023010547</t>
-  </si>
-  <si>
-    <t>0.3390220518</t>
-  </si>
-  <si>
-    <t>0.8012936808</t>
-  </si>
-  <si>
-    <t>0.4286266132</t>
-  </si>
-  <si>
     <t>0.0005752637</t>
   </si>
   <si>
-    <t>0.6839884947</t>
-  </si>
-  <si>
-    <t>0.5024597125</t>
-  </si>
-  <si>
-    <t>0.4818168789</t>
-  </si>
-  <si>
-    <t>0.0620325983</t>
-  </si>
-  <si>
-    <t>0.0099712368</t>
-  </si>
-  <si>
-    <t>0.221093001</t>
-  </si>
-  <si>
-    <t>0.8361363854</t>
-  </si>
-  <si>
-    <t>0.3803620451</t>
-  </si>
-  <si>
-    <t>0.0265580058</t>
-  </si>
-  <si>
-    <t>0.0792905081</t>
-  </si>
-  <si>
-    <t>0.8982784427</t>
-  </si>
-  <si>
-    <t>0.4274209012</t>
-  </si>
-  <si>
-    <t>0.3460864386</t>
+    <t>0.0220517737</t>
+  </si>
+  <si>
+    <t>0.2607861937</t>
+  </si>
+  <si>
+    <t>0.5385824907</t>
+  </si>
+  <si>
+    <t>0.4074792697</t>
+  </si>
+  <si>
+    <t>0.083029722</t>
+  </si>
+  <si>
+    <t>0.2186001918</t>
+  </si>
+  <si>
+    <t>0.4934296451</t>
+  </si>
+  <si>
+    <t>0.4387721039</t>
+  </si>
+  <si>
+    <t>0.0911792905</t>
+  </si>
+  <si>
+    <t>0.2174496644</t>
+  </si>
+  <si>
+    <t>0.6639219361</t>
+  </si>
+  <si>
+    <t>0.4464361979</t>
+  </si>
+  <si>
+    <t>0.037171872</t>
+  </si>
+  <si>
+    <t>0.3494922399</t>
+  </si>
+  <si>
+    <t>0.4993320499</t>
+  </si>
+  <si>
+    <t>0.4255859946</t>
+  </si>
+  <si>
+    <t>0.044165549</t>
+  </si>
+  <si>
+    <t>0.002299291</t>
+  </si>
+  <si>
+    <t>0.3031232037</t>
+  </si>
+  <si>
+    <t>0.5179041185</t>
+  </si>
+  <si>
+    <t>0.4984225494</t>
+  </si>
+  <si>
+    <t>0.0420578655</t>
+  </si>
+  <si>
+    <t>0.1324008431</t>
+  </si>
+  <si>
+    <t>0.5080369989</t>
+  </si>
+  <si>
+    <t>0.3896901907</t>
+  </si>
+  <si>
+    <t>0.0255033557</t>
+  </si>
+  <si>
+    <t>0.5082465565</t>
+  </si>
+  <si>
+    <t>0.4652703056</t>
+  </si>
+  <si>
+    <t>0.0048897411</t>
+  </si>
+  <si>
+    <t>0.000671141</t>
+  </si>
+  <si>
+    <t>0.2851390221</t>
+  </si>
+  <si>
+    <t>0.5020983002</t>
+  </si>
+  <si>
+    <t>0.4881992368</t>
+  </si>
+  <si>
+    <t>0.0657718121</t>
+  </si>
+  <si>
+    <t>0.4945349952</t>
+  </si>
+  <si>
+    <t>0.5594059158</t>
+  </si>
+  <si>
+    <t>0.5183008532</t>
+  </si>
+  <si>
+    <t>0.0016286645</t>
+  </si>
+  <si>
+    <t>0.7286836559</t>
+  </si>
+  <si>
+    <t>0.4909162253</t>
+  </si>
+  <si>
+    <t>0.4915265534</t>
+  </si>
+  <si>
+    <t>0.0293159609</t>
+  </si>
+  <si>
+    <t>0.0035447404</t>
+  </si>
+  <si>
+    <t>0.3314811267</t>
+  </si>
+  <si>
+    <t>0.6347145411</t>
+  </si>
+  <si>
+    <t>0.4622564189</t>
+  </si>
+  <si>
+    <t>0.0333397203</t>
+  </si>
+  <si>
+    <t>0.0033531328</t>
+  </si>
+  <si>
+    <t>0.3939452002</t>
+  </si>
+  <si>
+    <t>0.6628225181</t>
+  </si>
+  <si>
+    <t>0.475877356</t>
   </si>
 </sst>
 </file>
@@ -2019,7 +2097,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2047,12 +2125,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2093,7 +2165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2146,8 +2218,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2155,35 +2239,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2559,13 +2634,13 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="19" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="14" t="s">
@@ -2583,7 +2658,7 @@
       <c r="J2" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="23" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2594,9 +2669,9 @@
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
       <c r="F3" s="1" t="s">
         <v>346</v>
       </c>
@@ -2612,7 +2687,7 @@
       <c r="J3" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="K3" s="20"/>
+      <c r="K3" s="24"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2621,9 +2696,9 @@
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
       <c r="F4" s="1" t="s">
         <v>341</v>
       </c>
@@ -2639,7 +2714,7 @@
       <c r="J4" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="K4" s="20"/>
+      <c r="K4" s="24"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -2648,13 +2723,13 @@
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="18" t="s">
         <v>286</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="20" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="14" t="s">
@@ -2672,7 +2747,7 @@
       <c r="J6" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="K6" s="20" t="s">
+      <c r="K6" s="24" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2683,9 +2758,9 @@
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
       <c r="F7" s="1" t="s">
         <v>302</v>
       </c>
@@ -2701,7 +2776,7 @@
       <c r="J7" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="K7" s="20"/>
+      <c r="K7" s="24"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -2710,9 +2785,9 @@
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
       <c r="F8" s="1" t="s">
         <v>297</v>
       </c>
@@ -2728,15 +2803,15 @@
       <c r="J8" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="K8" s="20"/>
+      <c r="K8" s="24"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="11"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
@@ -2752,13 +2827,13 @@
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="20" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="14" t="s">
@@ -2776,7 +2851,7 @@
       <c r="J12" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="K12" s="20" t="s">
+      <c r="K12" s="24" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2787,9 +2862,9 @@
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="1" t="s">
         <v>409</v>
       </c>
@@ -2805,7 +2880,7 @@
       <c r="J13" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="K13" s="20"/>
+      <c r="K13" s="24"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2814,9 +2889,9 @@
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
       <c r="F14" s="1" t="s">
         <v>404</v>
       </c>
@@ -2832,7 +2907,7 @@
       <c r="J14" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="K14" s="20"/>
+      <c r="K14" s="24"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -2841,13 +2916,13 @@
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="18" t="s">
         <v>288</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="20" t="s">
         <v>29</v>
       </c>
       <c r="F16" s="14" t="s">
@@ -2865,7 +2940,7 @@
       <c r="J16" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="K16" s="20" t="s">
+      <c r="K16" s="24" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2876,9 +2951,9 @@
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
       <c r="F17" s="1" t="s">
         <v>274</v>
       </c>
@@ -2894,7 +2969,7 @@
       <c r="J17" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="K17" s="20"/>
+      <c r="K17" s="24"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -2903,9 +2978,9 @@
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
       <c r="F18" s="1" t="s">
         <v>269</v>
       </c>
@@ -2921,7 +2996,7 @@
       <c r="J18" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="K18" s="20"/>
+      <c r="K18" s="24"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -2930,13 +3005,13 @@
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="18" t="s">
         <v>289</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="20" t="s">
         <v>30</v>
       </c>
       <c r="F20" s="14" t="s">
@@ -2954,7 +3029,7 @@
       <c r="J20" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="K20" s="20" t="s">
+      <c r="K20" s="24" t="s">
         <v>37</v>
       </c>
     </row>
@@ -2965,9 +3040,9 @@
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
       <c r="F21" s="1" t="s">
         <v>244</v>
       </c>
@@ -2983,7 +3058,7 @@
       <c r="J21" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="K21" s="20"/>
+      <c r="K21" s="24"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -2992,9 +3067,9 @@
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
       <c r="F22" s="1" t="s">
         <v>239</v>
       </c>
@@ -3010,7 +3085,7 @@
       <c r="J22" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="K22" s="20"/>
+      <c r="K22" s="24"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -3019,13 +3094,13 @@
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="18" t="s">
         <v>290</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="20" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="14" t="s">
@@ -3051,9 +3126,9 @@
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
       <c r="F25" s="1" t="s">
         <v>360</v>
       </c>
@@ -3077,9 +3152,9 @@
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
       <c r="F26" s="1" t="s">
         <v>355</v>
       </c>
@@ -3103,13 +3178,13 @@
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="18" t="s">
         <v>291</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="20" t="s">
         <v>35</v>
       </c>
       <c r="F28" s="14" t="s">
@@ -3135,9 +3210,9 @@
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
       <c r="F29" s="1" t="s">
         <v>331</v>
       </c>
@@ -3161,9 +3236,9 @@
       <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
       <c r="F30" s="1" t="s">
         <v>326</v>
       </c>
@@ -3187,13 +3262,13 @@
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="18" t="s">
         <v>292</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="20" t="s">
         <v>31</v>
       </c>
       <c r="F32" s="15" t="s">
@@ -3219,9 +3294,9 @@
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="22"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
       <c r="F33" s="1" t="s">
         <v>424</v>
       </c>
@@ -3245,9 +3320,9 @@
       <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="22"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
       <c r="F34" s="1" t="s">
         <v>419</v>
       </c>
@@ -3271,13 +3346,13 @@
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="20" t="s">
         <v>36</v>
       </c>
       <c r="F36" s="14" t="s">
@@ -3303,9 +3378,9 @@
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="22"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
       <c r="F37" s="1" t="s">
         <v>394</v>
       </c>
@@ -3329,9 +3404,9 @@
       <c r="B38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="22"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
       <c r="F38" s="1" t="s">
         <v>389</v>
       </c>
@@ -3349,12 +3424,12 @@
       </c>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="23" t="s">
+      <c r="A40" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="11"/>
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
@@ -3370,13 +3445,13 @@
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="20" t="s">
         <v>29</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -3394,7 +3469,7 @@
       <c r="J42" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="K42" s="20" t="s">
+      <c r="K42" s="24" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3405,9 +3480,9 @@
       <c r="B43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="22"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
       <c r="F43" s="14" t="s">
         <v>317</v>
       </c>
@@ -3423,7 +3498,7 @@
       <c r="J43" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="K43" s="20"/>
+      <c r="K43" s="24"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -3432,9 +3507,9 @@
       <c r="B44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
       <c r="F44" s="1" t="s">
         <v>312</v>
       </c>
@@ -3450,7 +3525,7 @@
       <c r="J44" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="K44" s="20"/>
+      <c r="K44" s="24"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -3459,13 +3534,13 @@
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="22" t="s">
+      <c r="C46" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="D46" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="E46" s="18" t="s">
+      <c r="E46" s="20" t="s">
         <v>30</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -3483,7 +3558,7 @@
       <c r="J46" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="K46" s="20" t="s">
+      <c r="K46" s="24" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3494,9 +3569,9 @@
       <c r="B47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="22"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
       <c r="F47" s="14" t="s">
         <v>259</v>
       </c>
@@ -3512,7 +3587,7 @@
       <c r="J47" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="K47" s="20"/>
+      <c r="K47" s="24"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -3521,9 +3596,9 @@
       <c r="B48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C48" s="22"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
       <c r="F48" s="1" t="s">
         <v>254</v>
       </c>
@@ -3539,7 +3614,7 @@
       <c r="J48" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="K48" s="20"/>
+      <c r="K48" s="24"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -3548,13 +3623,13 @@
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="22" t="s">
+      <c r="C50" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="D50" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="E50" s="18" t="s">
+      <c r="E50" s="20" t="s">
         <v>31</v>
       </c>
       <c r="F50" s="14" t="s">
@@ -3580,9 +3655,9 @@
       <c r="B51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="22"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
       <c r="F51" s="1" t="s">
         <v>375</v>
       </c>
@@ -3606,9 +3681,9 @@
       <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="22"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
       <c r="F52" s="1" t="s">
         <v>370</v>
       </c>
@@ -3627,11 +3702,30 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="E46:E48"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="D6:D8"/>
@@ -3648,30 +3742,11 @@
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C2:C4"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="E50:E52"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="K46:K48"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C24:C26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3739,13 +3814,13 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="19" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -3763,7 +3838,7 @@
       <c r="J2" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="23" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3774,9 +3849,9 @@
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
       <c r="F3" s="1" t="s">
         <v>438</v>
       </c>
@@ -3792,7 +3867,7 @@
       <c r="J3" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="K3" s="20"/>
+      <c r="K3" s="24"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3801,9 +3876,9 @@
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
       <c r="F4" s="1" t="s">
         <v>434</v>
       </c>
@@ -3819,7 +3894,7 @@
       <c r="J4" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="K4" s="20"/>
+      <c r="K4" s="24"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -3828,13 +3903,13 @@
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="18" t="s">
         <v>286</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="20" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -3852,7 +3927,7 @@
       <c r="J6" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="K6" s="20" t="s">
+      <c r="K6" s="24" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3863,9 +3938,9 @@
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
       <c r="F7" s="1" t="s">
         <v>454</v>
       </c>
@@ -3881,7 +3956,7 @@
       <c r="J7" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="K7" s="20"/>
+      <c r="K7" s="24"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -3890,9 +3965,9 @@
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
       <c r="F8" s="1" t="s">
         <v>449</v>
       </c>
@@ -3908,15 +3983,15 @@
       <c r="J8" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="K8" s="20"/>
+      <c r="K8" s="24"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="11"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
@@ -3932,13 +4007,13 @@
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="20" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -3956,7 +4031,7 @@
       <c r="J12" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="K12" s="20" t="s">
+      <c r="K12" s="24" t="s">
         <v>20</v>
       </c>
     </row>
@@ -3967,9 +4042,9 @@
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="1" t="s">
         <v>469</v>
       </c>
@@ -3985,7 +4060,7 @@
       <c r="J13" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="K13" s="20"/>
+      <c r="K13" s="24"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -3994,9 +4069,9 @@
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
       <c r="F14" s="1" t="s">
         <v>464</v>
       </c>
@@ -4012,7 +4087,7 @@
       <c r="J14" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="K14" s="20"/>
+      <c r="K14" s="24"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -4021,13 +4096,13 @@
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="18" t="s">
         <v>288</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="20" t="s">
         <v>29</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -4045,7 +4120,7 @@
       <c r="J16" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="K16" s="20" t="s">
+      <c r="K16" s="24" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4056,9 +4131,9 @@
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
       <c r="F17" s="1" t="s">
         <v>483</v>
       </c>
@@ -4074,7 +4149,7 @@
       <c r="J17" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="K17" s="20"/>
+      <c r="K17" s="24"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -4083,9 +4158,9 @@
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
       <c r="F18" s="1" t="s">
         <v>479</v>
       </c>
@@ -4101,7 +4176,7 @@
       <c r="J18" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="K18" s="20"/>
+      <c r="K18" s="24"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -4110,16 +4185,16 @@
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="18" t="s">
         <v>289</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="K20" s="20" t="s">
+      <c r="K20" s="24" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4130,10 +4205,10 @@
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="K21" s="20"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="K21" s="24"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -4142,10 +4217,10 @@
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="K22" s="20"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="K22" s="24"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -4154,13 +4229,13 @@
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="18" t="s">
         <v>290</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="20" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -4186,9 +4261,9 @@
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
+      <c r="C25" s="18"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
       <c r="F25" s="1" t="s">
         <v>495</v>
       </c>
@@ -4212,9 +4287,9 @@
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
+      <c r="C26" s="18"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
       <c r="F26" s="1" t="s">
         <v>464</v>
       </c>
@@ -4238,13 +4313,13 @@
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="18" t="s">
         <v>291</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="20" t="s">
         <v>35</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -4270,9 +4345,9 @@
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
       <c r="F29" s="1" t="s">
         <v>507</v>
       </c>
@@ -4296,9 +4371,9 @@
       <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
+      <c r="C30" s="18"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
       <c r="F30" s="1" t="s">
         <v>211</v>
       </c>
@@ -4322,13 +4397,13 @@
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="18" t="s">
         <v>292</v>
       </c>
-      <c r="D32" s="18" t="s">
+      <c r="D32" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="E32" s="18" t="s">
+      <c r="E32" s="20" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4339,9 +4414,9 @@
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="22"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="20"/>
+      <c r="E33" s="20"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
@@ -4350,9 +4425,9 @@
       <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="22"/>
-      <c r="D34" s="18"/>
-      <c r="E34" s="18"/>
+      <c r="C34" s="18"/>
+      <c r="D34" s="20"/>
+      <c r="E34" s="20"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
@@ -4361,13 +4436,13 @@
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="20" t="s">
         <v>36</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -4393,9 +4468,9 @@
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="22"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
+      <c r="C37" s="18"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
       <c r="F37" s="1" t="s">
         <v>496</v>
       </c>
@@ -4419,9 +4494,9 @@
       <c r="B38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="22"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
       <c r="F38" s="1" t="s">
         <v>141</v>
       </c>
@@ -4439,12 +4514,12 @@
       </c>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="23" t="s">
+      <c r="A40" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="11"/>
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
@@ -4460,13 +4535,13 @@
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="20" t="s">
         <v>29</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -4484,7 +4559,7 @@
       <c r="J42" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="K42" s="20" t="s">
+      <c r="K42" s="24" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4495,9 +4570,9 @@
       <c r="B43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="22"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
       <c r="F43" s="1" t="s">
         <v>531</v>
       </c>
@@ -4513,7 +4588,7 @@
       <c r="J43" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="K43" s="20"/>
+      <c r="K43" s="24"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -4522,9 +4597,9 @@
       <c r="B44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
+      <c r="C44" s="18"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
       <c r="F44" s="1" t="s">
         <v>527</v>
       </c>
@@ -4540,7 +4615,7 @@
       <c r="J44" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="K44" s="20"/>
+      <c r="K44" s="24"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -4549,13 +4624,13 @@
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="22" t="s">
+      <c r="C46" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="D46" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="E46" s="18" t="s">
+      <c r="E46" s="20" t="s">
         <v>30</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -4573,7 +4648,7 @@
       <c r="J46" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="K46" s="20" t="s">
+      <c r="K46" s="24" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4584,9 +4659,9 @@
       <c r="B47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="22"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
       <c r="F47" s="1" t="s">
         <v>545</v>
       </c>
@@ -4602,7 +4677,7 @@
       <c r="J47" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="K47" s="20"/>
+      <c r="K47" s="24"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -4611,9 +4686,9 @@
       <c r="B48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C48" s="22"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
+      <c r="C48" s="18"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
       <c r="F48" s="1" t="s">
         <v>541</v>
       </c>
@@ -4629,7 +4704,7 @@
       <c r="J48" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="K48" s="20"/>
+      <c r="K48" s="24"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -4638,13 +4713,13 @@
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="22" t="s">
+      <c r="C50" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="D50" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="E50" s="18" t="s">
+      <c r="E50" s="20" t="s">
         <v>31</v>
       </c>
       <c r="F50" s="1" t="s">
@@ -4670,9 +4745,9 @@
       <c r="B51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="22"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
+      <c r="C51" s="18"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
       <c r="F51" s="1" t="s">
         <v>558</v>
       </c>
@@ -4696,9 +4771,9 @@
       <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="22"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
+      <c r="C52" s="18"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
       <c r="F52" s="17" t="s">
         <v>527</v>
       </c>
@@ -4717,11 +4792,33 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="D32:D34"/>
     <mergeCell ref="E32:E34"/>
@@ -4735,33 +4832,11 @@
     <mergeCell ref="C42:C44"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="E42:E44"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="K46:K48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4829,31 +4904,31 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="22" t="s">
         <v>285</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="14" t="s">
-        <v>443</v>
+      <c r="F2" s="1" t="s">
+        <v>576</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>444</v>
+        <v>577</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>445</v>
+        <v>578</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>448</v>
-      </c>
-      <c r="K2" s="19" t="s">
+        <v>579</v>
+      </c>
+      <c r="K2" s="23" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4864,25 +4939,25 @@
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
       <c r="F3" s="1" t="s">
-        <v>438</v>
+        <v>572</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>439</v>
+        <v>567</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>440</v>
+        <v>573</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>441</v>
+        <v>574</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>442</v>
-      </c>
-      <c r="K3" s="20"/>
+        <v>575</v>
+      </c>
+      <c r="K3" s="24"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -4891,25 +4966,25 @@
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
       <c r="F4" s="1" t="s">
-        <v>434</v>
+        <v>568</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>108</v>
+        <v>211</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>435</v>
+        <v>569</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>436</v>
+        <v>570</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>437</v>
-      </c>
-      <c r="K4" s="20"/>
+        <v>571</v>
+      </c>
+      <c r="K4" s="24"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -4918,31 +4993,31 @@
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="18" t="s">
         <v>286</v>
       </c>
-      <c r="D6" s="18" t="s">
+      <c r="D6" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="20" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>459</v>
+        <v>589</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>460</v>
+        <v>555</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>461</v>
+        <v>590</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>462</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>463</v>
-      </c>
-      <c r="K6" s="20" t="s">
+        <v>591</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>592</v>
+      </c>
+      <c r="K6" s="24" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4953,25 +5028,25 @@
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="20"/>
       <c r="F7" s="1" t="s">
-        <v>454</v>
+        <v>584</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>455</v>
+        <v>585</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>456</v>
+        <v>586</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>457</v>
+        <v>587</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>458</v>
-      </c>
-      <c r="K7" s="20"/>
+        <v>588</v>
+      </c>
+      <c r="K7" s="24"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -4980,33 +5055,33 @@
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
       <c r="F8" s="1" t="s">
-        <v>449</v>
+        <v>580</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>450</v>
+        <v>211</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>451</v>
+        <v>581</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>452</v>
+        <v>582</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>453</v>
-      </c>
-      <c r="K8" s="20"/>
+        <v>583</v>
+      </c>
+      <c r="K8" s="24"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="23" t="s">
+      <c r="A10" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="23"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="21"/>
       <c r="E10" s="11"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
@@ -5022,31 +5097,31 @@
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="20" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>474</v>
+        <v>601</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>475</v>
+        <v>439</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>476</v>
+        <v>602</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>477</v>
+        <v>603</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>478</v>
-      </c>
-      <c r="K12" s="20" t="s">
+        <v>604</v>
+      </c>
+      <c r="K12" s="24" t="s">
         <v>20</v>
       </c>
     </row>
@@ -5057,25 +5132,25 @@
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="22"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
       <c r="F13" s="1" t="s">
-        <v>469</v>
+        <v>596</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>470</v>
+        <v>597</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>471</v>
+        <v>598</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>472</v>
+        <v>599</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>473</v>
-      </c>
-      <c r="K13" s="20"/>
+        <v>600</v>
+      </c>
+      <c r="K13" s="24"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -5084,25 +5159,25 @@
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="22"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
       <c r="F14" s="1" t="s">
-        <v>464</v>
+        <v>141</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>465</v>
+        <v>74</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>466</v>
+        <v>593</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>467</v>
+        <v>594</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>468</v>
-      </c>
-      <c r="K14" s="20"/>
+        <v>595</v>
+      </c>
+      <c r="K14" s="24"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -5111,31 +5186,16 @@
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="18" t="s">
         <v>288</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>488</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>489</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>490</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>491</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>492</v>
-      </c>
-      <c r="K16" s="20" t="s">
+      <c r="K16" s="24" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5146,25 +5206,11 @@
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="22"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="1" t="s">
-        <v>483</v>
-      </c>
-      <c r="G17" s="16" t="s">
-        <v>484</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>485</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>486</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>487</v>
-      </c>
-      <c r="K17" s="20"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="20"/>
+      <c r="G17" s="16"/>
+      <c r="K17" s="24"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -5173,25 +5219,10 @@
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="22"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="1" t="s">
-        <v>479</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>480</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>481</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>482</v>
-      </c>
-      <c r="K18" s="20"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20"/>
+      <c r="K18" s="24"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -5200,31 +5231,16 @@
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="18" t="s">
         <v>289</v>
       </c>
-      <c r="D20" s="18" t="s">
+      <c r="D20" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="E20" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>575</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>576</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>577</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>578</v>
-      </c>
-      <c r="K20" s="20" t="s">
+      <c r="K20" s="24" t="s">
         <v>37</v>
       </c>
     </row>
@@ -5235,25 +5251,10 @@
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="22"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="1" t="s">
-        <v>470</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>570</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>571</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>572</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>573</v>
-      </c>
-      <c r="K21" s="20"/>
+      <c r="C21" s="18"/>
+      <c r="D21" s="20"/>
+      <c r="E21" s="20"/>
+      <c r="K21" s="24"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -5262,25 +5263,10 @@
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="22"/>
-      <c r="D22" s="18"/>
-      <c r="E22" s="18"/>
-      <c r="F22" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>567</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>568</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>569</v>
-      </c>
-      <c r="K22" s="20"/>
+      <c r="C22" s="18"/>
+      <c r="D22" s="20"/>
+      <c r="E22" s="20"/>
+      <c r="K22" s="24"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -5289,29 +5275,14 @@
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="18" t="s">
         <v>290</v>
       </c>
-      <c r="D24" s="18" t="s">
+      <c r="D24" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="18" t="s">
+      <c r="E24" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="F24" s="1" t="s">
-        <v>500</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>501</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>502</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -5321,24 +5292,9 @@
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="22"/>
-      <c r="D25" s="18"/>
-      <c r="E25" s="18"/>
-      <c r="F25" s="1" t="s">
-        <v>495</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>497</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>498</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>499</v>
-      </c>
+      <c r="C25" s="18"/>
+      <c r="D25" s="20"/>
+      <c r="E25" s="20"/>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
@@ -5347,24 +5303,9 @@
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="22"/>
-      <c r="D26" s="18"/>
-      <c r="E26" s="18"/>
-      <c r="F26" s="1" t="s">
-        <v>464</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>493</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>494</v>
-      </c>
+      <c r="C26" s="18"/>
+      <c r="D26" s="20"/>
+      <c r="E26" s="20"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
@@ -5373,29 +5314,14 @@
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="18" t="s">
         <v>291</v>
       </c>
-      <c r="D28" s="18" t="s">
+      <c r="D28" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="18" t="s">
+      <c r="E28" s="20" t="s">
         <v>35</v>
-      </c>
-      <c r="F28" s="1" t="s">
-        <v>512</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>513</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>514</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>515</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -5405,24 +5331,9 @@
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>508</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>509</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>510</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>511</v>
-      </c>
+      <c r="C29" s="18"/>
+      <c r="D29" s="20"/>
+      <c r="E29" s="20"/>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -5431,24 +5342,9 @@
       <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="22"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>504</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>505</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>506</v>
-      </c>
+      <c r="C30" s="18"/>
+      <c r="D30" s="20"/>
+      <c r="E30" s="20"/>
     </row>
     <row r="32" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="26" t="s">
@@ -5466,21 +5362,8 @@
       <c r="E32" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="F32" s="26" t="s">
-        <v>588</v>
-      </c>
-      <c r="G32" s="29" t="s">
-        <v>589</v>
-      </c>
-      <c r="H32" s="26" t="s">
-        <v>591</v>
-      </c>
-      <c r="I32" s="29" t="s">
-        <v>590</v>
-      </c>
-      <c r="J32" s="26" t="s">
-        <v>592</v>
-      </c>
+      <c r="G32" s="29"/>
+      <c r="I32" s="29"/>
       <c r="K32" s="30"/>
     </row>
     <row r="33" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.2">
@@ -5493,21 +5376,6 @@
       <c r="C33" s="27"/>
       <c r="D33" s="28"/>
       <c r="E33" s="28"/>
-      <c r="F33" s="26" t="s">
-        <v>583</v>
-      </c>
-      <c r="G33" s="26" t="s">
-        <v>584</v>
-      </c>
-      <c r="H33" s="26" t="s">
-        <v>585</v>
-      </c>
-      <c r="I33" s="26" t="s">
-        <v>586</v>
-      </c>
-      <c r="J33" s="26" t="s">
-        <v>587</v>
-      </c>
       <c r="K33" s="30"/>
     </row>
     <row r="34" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.2">
@@ -5520,21 +5388,7 @@
       <c r="C34" s="27"/>
       <c r="D34" s="28"/>
       <c r="E34" s="28"/>
-      <c r="F34" s="26" t="s">
-        <v>579</v>
-      </c>
-      <c r="G34" s="26" t="s">
-        <v>475</v>
-      </c>
-      <c r="H34" s="29" t="s">
-        <v>580</v>
-      </c>
-      <c r="I34" s="26" t="s">
-        <v>581</v>
-      </c>
-      <c r="J34" s="26" t="s">
-        <v>582</v>
-      </c>
+      <c r="H34" s="29"/>
       <c r="K34" s="30"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
@@ -5544,29 +5398,14 @@
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="D36" s="18" t="s">
+      <c r="D36" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="E36" s="18" t="s">
+      <c r="E36" s="20" t="s">
         <v>36</v>
-      </c>
-      <c r="F36" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -5576,24 +5415,9 @@
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="22"/>
-      <c r="D37" s="18"/>
-      <c r="E37" s="18"/>
-      <c r="F37" s="1" t="s">
-        <v>496</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>521</v>
-      </c>
+      <c r="C37" s="18"/>
+      <c r="D37" s="20"/>
+      <c r="E37" s="20"/>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
@@ -5602,32 +5426,17 @@
       <c r="B38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="22"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>516</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>517</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>518</v>
-      </c>
+      <c r="C38" s="18"/>
+      <c r="D38" s="20"/>
+      <c r="E38" s="20"/>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="23" t="s">
+      <c r="A40" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="D40" s="23"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="21"/>
+      <c r="D40" s="21"/>
       <c r="E40" s="11"/>
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
@@ -5643,31 +5452,31 @@
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="D42" s="18" t="s">
+      <c r="D42" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E42" s="18" t="s">
+      <c r="E42" s="20" t="s">
         <v>29</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>536</v>
+        <v>614</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>537</v>
+        <v>615</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>538</v>
+        <v>616</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>539</v>
+        <v>617</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>540</v>
-      </c>
-      <c r="K42" s="20" t="s">
+        <v>618</v>
+      </c>
+      <c r="K42" s="24" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5678,25 +5487,25 @@
       <c r="B43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="22"/>
-      <c r="D43" s="18"/>
-      <c r="E43" s="18"/>
+      <c r="C43" s="18"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
       <c r="F43" s="1" t="s">
-        <v>531</v>
+        <v>609</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>532</v>
+        <v>610</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>533</v>
+        <v>611</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>534</v>
+        <v>612</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="K43" s="20"/>
+        <v>613</v>
+      </c>
+      <c r="K43" s="24"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -5705,25 +5514,25 @@
       <c r="B44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="22"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="1" t="s">
+      <c r="C44" s="18"/>
+      <c r="D44" s="20"/>
+      <c r="E44" s="20"/>
+      <c r="F44" s="31" t="s">
         <v>527</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>528</v>
+        <v>605</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>241</v>
+        <v>606</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>529</v>
+        <v>607</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="K44" s="20"/>
+        <v>608</v>
+      </c>
+      <c r="K44" s="24"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -5732,31 +5541,16 @@
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="22" t="s">
+      <c r="C46" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="D46" s="18" t="s">
+      <c r="D46" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="E46" s="18" t="s">
+      <c r="E46" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="F46" s="1" t="s">
-        <v>550</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>551</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>552</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>553</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="K46" s="20" t="s">
+      <c r="K46" s="24" t="s">
         <v>33</v>
       </c>
     </row>
@@ -5767,25 +5561,10 @@
       <c r="B47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="22"/>
-      <c r="D47" s="18"/>
-      <c r="E47" s="18"/>
-      <c r="F47" s="1" t="s">
-        <v>545</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>546</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>547</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>548</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>549</v>
-      </c>
-      <c r="K47" s="20"/>
+      <c r="C47" s="18"/>
+      <c r="D47" s="20"/>
+      <c r="E47" s="20"/>
+      <c r="K47" s="24"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -5794,117 +5573,80 @@
       <c r="B48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C48" s="22"/>
-      <c r="D48" s="18"/>
-      <c r="E48" s="18"/>
-      <c r="F48" s="1" t="s">
-        <v>541</v>
-      </c>
-      <c r="G48" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="H48" s="1" t="s">
-        <v>542</v>
-      </c>
-      <c r="I48" s="1" t="s">
-        <v>543</v>
-      </c>
-      <c r="J48" s="1" t="s">
-        <v>544</v>
-      </c>
-      <c r="K48" s="20"/>
-    </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C48" s="18"/>
+      <c r="D48" s="20"/>
+      <c r="E48" s="20"/>
+      <c r="K48" s="24"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="22" t="s">
+      <c r="C50" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="D50" s="18" t="s">
+      <c r="D50" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="E50" s="18" t="s">
+      <c r="E50" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="F50" s="1" t="s">
-        <v>562</v>
-      </c>
-      <c r="G50" s="1" t="s">
-        <v>563</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>564</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>565</v>
-      </c>
-      <c r="J50" s="1" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="22"/>
-      <c r="D51" s="18"/>
-      <c r="E51" s="18"/>
-      <c r="F51" s="1" t="s">
-        <v>558</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>455</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>559</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>560</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="C51" s="18"/>
+      <c r="D51" s="20"/>
+      <c r="E51" s="20"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="22"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
-      <c r="F52" s="17" t="s">
-        <v>527</v>
-      </c>
-      <c r="G52" s="1" t="s">
-        <v>555</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>556</v>
-      </c>
-      <c r="J52" s="1" t="s">
-        <v>557</v>
-      </c>
+      <c r="C52" s="18"/>
+      <c r="D52" s="20"/>
+      <c r="E52" s="20"/>
+      <c r="F52" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="D32:D34"/>
     <mergeCell ref="E32:E34"/>
@@ -5918,33 +5660,11 @@
     <mergeCell ref="C42:C44"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="E42:E44"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="K46:K48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5991,10 +5711,10 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="24" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="22" t="s">
+      <c r="B2" s="18" t="s">
         <v>48</v>
       </c>
       <c r="C2" s="25" t="s">
@@ -6020,8 +5740,8 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="20"/>
-      <c r="B3" s="22"/>
+      <c r="A3" s="24"/>
+      <c r="B3" s="18"/>
       <c r="C3" s="25"/>
       <c r="D3" s="1" t="s">
         <v>46</v>
@@ -6043,8 +5763,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="20"/>
-      <c r="B4" s="22"/>
+      <c r="A4" s="24"/>
+      <c r="B4" s="18"/>
       <c r="C4" s="25"/>
       <c r="D4" s="1" t="s">
         <v>47</v>
@@ -6066,10 +5786,10 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="20" t="s">
+      <c r="A6" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="B6" s="22" t="s">
+      <c r="B6" s="18" t="s">
         <v>49</v>
       </c>
       <c r="C6" s="25" t="s">
@@ -6095,8 +5815,8 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="20"/>
-      <c r="B7" s="22"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="18"/>
       <c r="C7" s="25"/>
       <c r="D7" s="1" t="s">
         <v>46</v>
@@ -6118,8 +5838,8 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="20"/>
-      <c r="B8" s="22"/>
+      <c r="A8" s="24"/>
+      <c r="B8" s="18"/>
       <c r="C8" s="25"/>
       <c r="D8" s="1" t="s">
         <v>47</v>
@@ -6141,10 +5861,10 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="24" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="22" t="s">
+      <c r="B10" s="18" t="s">
         <v>50</v>
       </c>
       <c r="C10" s="25" t="s">
@@ -6170,8 +5890,8 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="20"/>
-      <c r="B11" s="22"/>
+      <c r="A11" s="24"/>
+      <c r="B11" s="18"/>
       <c r="C11" s="25"/>
       <c r="D11" s="1" t="s">
         <v>46</v>
@@ -6193,8 +5913,8 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="20"/>
-      <c r="B12" s="22"/>
+      <c r="A12" s="24"/>
+      <c r="B12" s="18"/>
       <c r="C12" s="25"/>
       <c r="D12" s="1" t="s">
         <v>47</v>
@@ -6213,10 +5933,10 @@
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="24" t="s">
         <v>184</v>
       </c>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="18" t="s">
         <v>51</v>
       </c>
       <c r="C14" s="25" t="s">
@@ -6242,8 +5962,8 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="20"/>
-      <c r="B15" s="22"/>
+      <c r="A15" s="24"/>
+      <c r="B15" s="18"/>
       <c r="C15" s="25"/>
       <c r="D15" s="1" t="s">
         <v>46</v>
@@ -6265,8 +5985,8 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="20"/>
-      <c r="B16" s="22"/>
+      <c r="A16" s="24"/>
+      <c r="B16" s="18"/>
       <c r="C16" s="25"/>
       <c r="D16" s="1" t="s">
         <v>47</v>
@@ -6288,10 +6008,10 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="20" t="s">
+      <c r="A18" s="24" t="s">
         <v>183</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="18" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="25" t="s">
@@ -6317,8 +6037,8 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="20"/>
-      <c r="B19" s="22"/>
+      <c r="A19" s="24"/>
+      <c r="B19" s="18"/>
       <c r="C19" s="25"/>
       <c r="D19" s="1" t="s">
         <v>46</v>
@@ -6340,8 +6060,8 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="20"/>
-      <c r="B20" s="22"/>
+      <c r="A20" s="24"/>
+      <c r="B20" s="18"/>
       <c r="C20" s="25"/>
       <c r="D20" s="1" t="s">
         <v>47</v>
@@ -6360,10 +6080,10 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="20" t="s">
+      <c r="A22" s="24" t="s">
         <v>181</v>
       </c>
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="18" t="s">
         <v>53</v>
       </c>
       <c r="C22" s="25" t="s">
@@ -6389,8 +6109,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="20"/>
-      <c r="B23" s="22"/>
+      <c r="A23" s="24"/>
+      <c r="B23" s="18"/>
       <c r="C23" s="25"/>
       <c r="D23" s="1" t="s">
         <v>46</v>
@@ -6412,8 +6132,8 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="20"/>
-      <c r="B24" s="22"/>
+      <c r="A24" s="24"/>
+      <c r="B24" s="18"/>
       <c r="C24" s="25"/>
       <c r="D24" s="1" t="s">
         <v>47</v>
@@ -6589,7 +6309,7 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="20" t="s">
+      <c r="A34" s="24" t="s">
         <v>179</v>
       </c>
       <c r="B34" s="25" t="s">
@@ -6618,7 +6338,7 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="20"/>
+      <c r="A35" s="24"/>
       <c r="B35" s="25"/>
       <c r="C35" s="25"/>
       <c r="D35" s="1" t="s">
@@ -6641,7 +6361,7 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" s="20"/>
+      <c r="A36" s="24"/>
       <c r="B36" s="25"/>
       <c r="C36" s="25"/>
       <c r="D36" s="1" t="s">
@@ -6664,10 +6384,10 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="20" t="s">
+      <c r="A38" s="24" t="s">
         <v>182</v>
       </c>
-      <c r="B38" s="20" t="s">
+      <c r="B38" s="24" t="s">
         <v>177</v>
       </c>
       <c r="C38" s="25" t="s">
@@ -6678,26 +6398,26 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="20"/>
-      <c r="B39" s="20"/>
+      <c r="A39" s="24"/>
+      <c r="B39" s="24"/>
       <c r="C39" s="25"/>
       <c r="D39" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="20"/>
-      <c r="B40" s="20"/>
+      <c r="A40" s="24"/>
+      <c r="B40" s="24"/>
       <c r="C40" s="25"/>
       <c r="D40" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="20" t="s">
+      <c r="A42" s="24" t="s">
         <v>188</v>
       </c>
-      <c r="B42" s="20" t="s">
+      <c r="B42" s="24" t="s">
         <v>189</v>
       </c>
       <c r="C42" s="25" t="s">
@@ -6723,8 +6443,8 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" s="20"/>
-      <c r="B43" s="20"/>
+      <c r="A43" s="24"/>
+      <c r="B43" s="24"/>
       <c r="C43" s="25"/>
       <c r="D43" s="1" t="s">
         <v>46</v>
@@ -6746,8 +6466,8 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" s="20"/>
-      <c r="B44" s="20"/>
+      <c r="A44" s="24"/>
+      <c r="B44" s="24"/>
       <c r="C44" s="25"/>
       <c r="D44" s="1" t="s">
         <v>47</v>
@@ -6769,10 +6489,10 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46" s="20" t="s">
+      <c r="A46" s="24" t="s">
         <v>191</v>
       </c>
-      <c r="B46" s="20" t="s">
+      <c r="B46" s="24" t="s">
         <v>194</v>
       </c>
       <c r="C46" s="25" t="s">
@@ -6798,8 +6518,8 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" s="20"/>
-      <c r="B47" s="20"/>
+      <c r="A47" s="24"/>
+      <c r="B47" s="24"/>
       <c r="C47" s="25"/>
       <c r="D47" s="1" t="s">
         <v>46</v>
@@ -6821,8 +6541,8 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A48" s="20"/>
-      <c r="B48" s="20"/>
+      <c r="A48" s="24"/>
+      <c r="B48" s="24"/>
       <c r="C48" s="25"/>
       <c r="D48" s="1" t="s">
         <v>47</v>
@@ -6845,28 +6565,6 @@
     </row>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A22:A24"/>
     <mergeCell ref="C22:C24"/>
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="B26:B28"/>
@@ -6881,6 +6579,28 @@
     <mergeCell ref="C18:C20"/>
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B22:B24"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C34:C36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/benchmarking/search_for_best_combination/results_basic.xlsx
+++ b/benchmarking/search_for_best_combination/results_basic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B844ED1-B5BA-B24B-BDFD-1E9A5AEBC9B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{729BB551-3FFC-8C4B-B5C4-6334CDDFEFFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="2" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="2" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="696">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -2053,6 +2053,237 @@
   </si>
   <si>
     <t>0.475877356</t>
+  </si>
+  <si>
+    <t>0.7902205177</t>
+  </si>
+  <si>
+    <t>0.4976437488</t>
+  </si>
+  <si>
+    <t>0.4874254286</t>
+  </si>
+  <si>
+    <t>0.0285714286</t>
+  </si>
+  <si>
+    <t>0.0019175456</t>
+  </si>
+  <si>
+    <t>0.4504314477</t>
+  </si>
+  <si>
+    <t>0.7441433405</t>
+  </si>
+  <si>
+    <t>0.4613762457</t>
+  </si>
+  <si>
+    <t>0.0454458293</t>
+  </si>
+  <si>
+    <t>0.0066155322</t>
+  </si>
+  <si>
+    <t>0.4571428571</t>
+  </si>
+  <si>
+    <t>0.7071709677</t>
+  </si>
+  <si>
+    <t>0.5096424539</t>
+  </si>
+  <si>
+    <t>0.0019175455</t>
+  </si>
+  <si>
+    <t>0.5027231525</t>
+  </si>
+  <si>
+    <t>0.472441798</t>
+  </si>
+  <si>
+    <t>0.0104506232</t>
+  </si>
+  <si>
+    <t>0.4232023011</t>
+  </si>
+  <si>
+    <t>0.6175134171</t>
+  </si>
+  <si>
+    <t>0.4859710207</t>
+  </si>
+  <si>
+    <t>0.055704698</t>
+  </si>
+  <si>
+    <t>0.0044103547</t>
+  </si>
+  <si>
+    <t>0.3263662512</t>
+  </si>
+  <si>
+    <t>0.6999883965</t>
+  </si>
+  <si>
+    <t>0.4451974898</t>
+  </si>
+  <si>
+    <t>0.6751677852</t>
+  </si>
+  <si>
+    <t>0.4935165554</t>
+  </si>
+  <si>
+    <t>0.4830861398</t>
+  </si>
+  <si>
+    <t>0.0057526366</t>
+  </si>
+  <si>
+    <t>0.0043144774</t>
+  </si>
+  <si>
+    <t>0.3725790988</t>
+  </si>
+  <si>
+    <t>0.5962318213</t>
+  </si>
+  <si>
+    <t>0.4785982514</t>
+  </si>
+  <si>
+    <t>0.0528283797</t>
+  </si>
+  <si>
+    <t>0.3758389262</t>
+  </si>
+  <si>
+    <t>0.6902831215</t>
+  </si>
+  <si>
+    <t>0.4638848996</t>
+  </si>
+  <si>
+    <t>0.0015340365</t>
+  </si>
+  <si>
+    <t>0.7739213806</t>
+  </si>
+  <si>
+    <t>0.4969657788</t>
+  </si>
+  <si>
+    <t>0.4857278292</t>
+  </si>
+  <si>
+    <t>0.0024928093</t>
+  </si>
+  <si>
+    <t>0.3697027804</t>
+  </si>
+  <si>
+    <t>0.499257617</t>
+  </si>
+  <si>
+    <t>0.4727516111</t>
+  </si>
+  <si>
+    <t>0.0453499521</t>
+  </si>
+  <si>
+    <t>0.0097794822</t>
+  </si>
+  <si>
+    <t>0.398274209</t>
+  </si>
+  <si>
+    <t>0.7934300469</t>
+  </si>
+  <si>
+    <t>0.4222978336</t>
+  </si>
+  <si>
+    <t>0.3408698984</t>
+  </si>
+  <si>
+    <t>0.5218191085</t>
+  </si>
+  <si>
+    <t>0.4662032722</t>
+  </si>
+  <si>
+    <t>0.0558536118</t>
+  </si>
+  <si>
+    <t>0.0021076835</t>
+  </si>
+  <si>
+    <t>0.5941751293</t>
+  </si>
+  <si>
+    <t>0.8157861987</t>
+  </si>
+  <si>
+    <t>0.4603975207</t>
+  </si>
+  <si>
+    <t>0.0610270167</t>
+  </si>
+  <si>
+    <t>0.012550297</t>
+  </si>
+  <si>
+    <t>0.2872197739</t>
+  </si>
+  <si>
+    <t>0.7467059894</t>
+  </si>
+  <si>
+    <t>0.4446678791</t>
+  </si>
+  <si>
+    <t>0.0034489366</t>
+  </si>
+  <si>
+    <t>0.0258670243</t>
+  </si>
+  <si>
+    <t>0.4747838898</t>
+  </si>
+  <si>
+    <t>0.460331891</t>
+  </si>
+  <si>
+    <t>0.0444529603</t>
+  </si>
+  <si>
+    <t>0.0002874114</t>
+  </si>
+  <si>
+    <t>0.5391837517</t>
+  </si>
+  <si>
+    <t>0.8902503168</t>
+  </si>
+  <si>
+    <t>0.4030020035</t>
+  </si>
+  <si>
+    <t>0.0001916076</t>
+  </si>
+  <si>
+    <t>0.0022034872</t>
+  </si>
+  <si>
+    <t>0.0319984671</t>
+  </si>
+  <si>
+    <t>0.3927241792</t>
+  </si>
+  <si>
+    <t>0.3462054259</t>
   </si>
 </sst>
 </file>
@@ -2165,7 +2396,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2218,14 +2449,23 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2233,32 +2473,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2634,13 +2850,13 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="25" t="s">
         <v>285</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="14" t="s">
@@ -2658,7 +2874,7 @@
       <c r="J2" s="14" t="s">
         <v>354</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="20" t="s">
         <v>17</v>
       </c>
     </row>
@@ -2669,9 +2885,9 @@
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
       <c r="F3" s="1" t="s">
         <v>346</v>
       </c>
@@ -2687,7 +2903,7 @@
       <c r="J3" s="1" t="s">
         <v>349</v>
       </c>
-      <c r="K3" s="24"/>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2696,9 +2912,9 @@
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
       <c r="F4" s="1" t="s">
         <v>341</v>
       </c>
@@ -2714,7 +2930,7 @@
       <c r="J4" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="K4" s="24"/>
+      <c r="K4" s="21"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -2723,13 +2939,13 @@
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="23" t="s">
         <v>286</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="19" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="14" t="s">
@@ -2747,7 +2963,7 @@
       <c r="J6" s="1" t="s">
         <v>311</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="K6" s="21" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2758,9 +2974,9 @@
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
       <c r="F7" s="1" t="s">
         <v>302</v>
       </c>
@@ -2776,7 +2992,7 @@
       <c r="J7" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="K7" s="24"/>
+      <c r="K7" s="21"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -2785,9 +3001,9 @@
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
       <c r="F8" s="1" t="s">
         <v>297</v>
       </c>
@@ -2803,15 +3019,15 @@
       <c r="J8" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="K8" s="24"/>
+      <c r="K8" s="21"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
       <c r="E10" s="11"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
@@ -2827,13 +3043,13 @@
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="19" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="14" t="s">
@@ -2851,7 +3067,7 @@
       <c r="J12" s="14" t="s">
         <v>418</v>
       </c>
-      <c r="K12" s="24" t="s">
+      <c r="K12" s="21" t="s">
         <v>20</v>
       </c>
     </row>
@@ -2862,9 +3078,9 @@
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="1" t="s">
         <v>409</v>
       </c>
@@ -2880,7 +3096,7 @@
       <c r="J13" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="K13" s="24"/>
+      <c r="K13" s="21"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2889,9 +3105,9 @@
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
       <c r="F14" s="1" t="s">
         <v>404</v>
       </c>
@@ -2907,7 +3123,7 @@
       <c r="J14" s="1" t="s">
         <v>408</v>
       </c>
-      <c r="K14" s="24"/>
+      <c r="K14" s="21"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -2916,13 +3132,13 @@
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="19" t="s">
         <v>29</v>
       </c>
       <c r="F16" s="14" t="s">
@@ -2940,7 +3156,7 @@
       <c r="J16" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="K16" s="21" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2951,9 +3167,9 @@
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="1" t="s">
         <v>274</v>
       </c>
@@ -2969,7 +3185,7 @@
       <c r="J17" s="14" t="s">
         <v>278</v>
       </c>
-      <c r="K17" s="24"/>
+      <c r="K17" s="21"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -2978,9 +3194,9 @@
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="18"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
       <c r="F18" s="1" t="s">
         <v>269</v>
       </c>
@@ -2996,7 +3212,7 @@
       <c r="J18" s="1" t="s">
         <v>273</v>
       </c>
-      <c r="K18" s="24"/>
+      <c r="K18" s="21"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -3005,13 +3221,13 @@
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="23" t="s">
         <v>289</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="19" t="s">
         <v>30</v>
       </c>
       <c r="F20" s="14" t="s">
@@ -3029,7 +3245,7 @@
       <c r="J20" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="K20" s="24" t="s">
+      <c r="K20" s="21" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3040,9 +3256,9 @@
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="18"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
       <c r="F21" s="1" t="s">
         <v>244</v>
       </c>
@@ -3058,7 +3274,7 @@
       <c r="J21" s="15" t="s">
         <v>248</v>
       </c>
-      <c r="K21" s="24"/>
+      <c r="K21" s="21"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -3067,9 +3283,9 @@
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
       <c r="F22" s="1" t="s">
         <v>239</v>
       </c>
@@ -3085,7 +3301,7 @@
       <c r="J22" s="1" t="s">
         <v>243</v>
       </c>
-      <c r="K22" s="24"/>
+      <c r="K22" s="21"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -3094,13 +3310,13 @@
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="23" t="s">
         <v>290</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="19" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="14" t="s">
@@ -3126,9 +3342,9 @@
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
       <c r="F25" s="1" t="s">
         <v>360</v>
       </c>
@@ -3152,9 +3368,9 @@
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
       <c r="F26" s="1" t="s">
         <v>355</v>
       </c>
@@ -3178,13 +3394,13 @@
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="19" t="s">
         <v>35</v>
       </c>
       <c r="F28" s="14" t="s">
@@ -3210,9 +3426,9 @@
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
       <c r="F29" s="1" t="s">
         <v>331</v>
       </c>
@@ -3236,9 +3452,9 @@
       <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
       <c r="F30" s="1" t="s">
         <v>326</v>
       </c>
@@ -3262,13 +3478,13 @@
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="19" t="s">
         <v>31</v>
       </c>
       <c r="F32" s="15" t="s">
@@ -3294,9 +3510,9 @@
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
       <c r="F33" s="1" t="s">
         <v>424</v>
       </c>
@@ -3320,9 +3536,9 @@
       <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
       <c r="F34" s="1" t="s">
         <v>419</v>
       </c>
@@ -3346,13 +3562,13 @@
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="D36" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="E36" s="19" t="s">
         <v>36</v>
       </c>
       <c r="F36" s="14" t="s">
@@ -3378,9 +3594,9 @@
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
       <c r="F37" s="1" t="s">
         <v>394</v>
       </c>
@@ -3404,9 +3620,9 @@
       <c r="B38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
       <c r="F38" s="1" t="s">
         <v>389</v>
       </c>
@@ -3424,12 +3640,12 @@
       </c>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
       <c r="E40" s="11"/>
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
@@ -3445,13 +3661,13 @@
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="D42" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="19" t="s">
         <v>29</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -3469,7 +3685,7 @@
       <c r="J42" s="1" t="s">
         <v>325</v>
       </c>
-      <c r="K42" s="24" t="s">
+      <c r="K42" s="21" t="s">
         <v>32</v>
       </c>
     </row>
@@ -3480,9 +3696,9 @@
       <c r="B43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="18"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
       <c r="F43" s="14" t="s">
         <v>317</v>
       </c>
@@ -3498,7 +3714,7 @@
       <c r="J43" s="14" t="s">
         <v>320</v>
       </c>
-      <c r="K43" s="24"/>
+      <c r="K43" s="21"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -3507,9 +3723,9 @@
       <c r="B44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
       <c r="F44" s="1" t="s">
         <v>312</v>
       </c>
@@ -3525,7 +3741,7 @@
       <c r="J44" s="1" t="s">
         <v>316</v>
       </c>
-      <c r="K44" s="24"/>
+      <c r="K44" s="21"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -3534,13 +3750,13 @@
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="D46" s="20" t="s">
+      <c r="D46" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E46" s="20" t="s">
+      <c r="E46" s="19" t="s">
         <v>30</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -3558,7 +3774,7 @@
       <c r="J46" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="K46" s="24" t="s">
+      <c r="K46" s="21" t="s">
         <v>33</v>
       </c>
     </row>
@@ -3569,9 +3785,9 @@
       <c r="B47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="18"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
       <c r="F47" s="14" t="s">
         <v>259</v>
       </c>
@@ -3587,7 +3803,7 @@
       <c r="J47" s="14" t="s">
         <v>263</v>
       </c>
-      <c r="K47" s="24"/>
+      <c r="K47" s="21"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -3596,9 +3812,9 @@
       <c r="B48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C48" s="18"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
       <c r="F48" s="1" t="s">
         <v>254</v>
       </c>
@@ -3614,7 +3830,7 @@
       <c r="J48" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="K48" s="24"/>
+      <c r="K48" s="21"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -3623,13 +3839,13 @@
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="C50" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="D50" s="20" t="s">
+      <c r="D50" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E50" s="20" t="s">
+      <c r="E50" s="19" t="s">
         <v>31</v>
       </c>
       <c r="F50" s="14" t="s">
@@ -3655,9 +3871,9 @@
       <c r="B51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="18"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
       <c r="F51" s="1" t="s">
         <v>375</v>
       </c>
@@ -3681,9 +3897,9 @@
       <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="18"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
       <c r="F52" s="1" t="s">
         <v>370</v>
       </c>
@@ -3702,6 +3918,35 @@
     </row>
   </sheetData>
   <mergeCells count="45">
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="E46:E48"/>
     <mergeCell ref="E50:E52"/>
     <mergeCell ref="K2:K4"/>
     <mergeCell ref="K6:K8"/>
@@ -3718,35 +3963,6 @@
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E6:E8"/>
     <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C24:C26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3814,13 +4030,13 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="25" t="s">
         <v>285</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -3838,7 +4054,7 @@
       <c r="J2" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="20" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3849,9 +4065,9 @@
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
       <c r="F3" s="1" t="s">
         <v>438</v>
       </c>
@@ -3867,7 +4083,7 @@
       <c r="J3" s="1" t="s">
         <v>442</v>
       </c>
-      <c r="K3" s="24"/>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3876,9 +4092,9 @@
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
       <c r="F4" s="1" t="s">
         <v>434</v>
       </c>
@@ -3894,7 +4110,7 @@
       <c r="J4" s="1" t="s">
         <v>437</v>
       </c>
-      <c r="K4" s="24"/>
+      <c r="K4" s="21"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -3903,13 +4119,13 @@
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="23" t="s">
         <v>286</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="19" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -3927,7 +4143,7 @@
       <c r="J6" s="1" t="s">
         <v>463</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="K6" s="21" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3938,9 +4154,9 @@
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
       <c r="F7" s="1" t="s">
         <v>454</v>
       </c>
@@ -3956,7 +4172,7 @@
       <c r="J7" s="1" t="s">
         <v>458</v>
       </c>
-      <c r="K7" s="24"/>
+      <c r="K7" s="21"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -3965,9 +4181,9 @@
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
       <c r="F8" s="1" t="s">
         <v>449</v>
       </c>
@@ -3983,15 +4199,15 @@
       <c r="J8" s="1" t="s">
         <v>453</v>
       </c>
-      <c r="K8" s="24"/>
+      <c r="K8" s="21"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
       <c r="E10" s="11"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
@@ -4007,13 +4223,13 @@
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="19" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -4031,7 +4247,7 @@
       <c r="J12" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="K12" s="24" t="s">
+      <c r="K12" s="21" t="s">
         <v>20</v>
       </c>
     </row>
@@ -4042,9 +4258,9 @@
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="1" t="s">
         <v>469</v>
       </c>
@@ -4060,7 +4276,7 @@
       <c r="J13" s="1" t="s">
         <v>473</v>
       </c>
-      <c r="K13" s="24"/>
+      <c r="K13" s="21"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -4069,9 +4285,9 @@
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
       <c r="F14" s="1" t="s">
         <v>464</v>
       </c>
@@ -4087,7 +4303,7 @@
       <c r="J14" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="K14" s="24"/>
+      <c r="K14" s="21"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -4096,13 +4312,13 @@
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="19" t="s">
         <v>29</v>
       </c>
       <c r="F16" s="1" t="s">
@@ -4120,7 +4336,7 @@
       <c r="J16" s="1" t="s">
         <v>492</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="K16" s="21" t="s">
         <v>38</v>
       </c>
     </row>
@@ -4131,9 +4347,9 @@
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
       <c r="F17" s="1" t="s">
         <v>483</v>
       </c>
@@ -4149,7 +4365,7 @@
       <c r="J17" s="1" t="s">
         <v>487</v>
       </c>
-      <c r="K17" s="24"/>
+      <c r="K17" s="21"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -4158,9 +4374,9 @@
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="18"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
       <c r="F18" s="1" t="s">
         <v>479</v>
       </c>
@@ -4176,7 +4392,7 @@
       <c r="J18" s="1" t="s">
         <v>482</v>
       </c>
-      <c r="K18" s="24"/>
+      <c r="K18" s="21"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -4185,16 +4401,16 @@
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="23" t="s">
         <v>289</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="K20" s="24" t="s">
+      <c r="K20" s="21" t="s">
         <v>37</v>
       </c>
     </row>
@@ -4205,10 +4421,10 @@
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="18"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="K21" s="24"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="K21" s="21"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -4217,10 +4433,10 @@
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="K22" s="24"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="K22" s="21"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -4229,13 +4445,13 @@
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="23" t="s">
         <v>290</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="19" t="s">
         <v>34</v>
       </c>
       <c r="F24" s="1" t="s">
@@ -4261,9 +4477,9 @@
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
       <c r="F25" s="1" t="s">
         <v>495</v>
       </c>
@@ -4287,9 +4503,9 @@
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
       <c r="F26" s="1" t="s">
         <v>464</v>
       </c>
@@ -4313,13 +4529,13 @@
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="19" t="s">
         <v>35</v>
       </c>
       <c r="F28" s="1" t="s">
@@ -4345,9 +4561,9 @@
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
       <c r="F29" s="1" t="s">
         <v>507</v>
       </c>
@@ -4371,9 +4587,9 @@
       <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
       <c r="F30" s="1" t="s">
         <v>211</v>
       </c>
@@ -4397,13 +4613,13 @@
       <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="18" t="s">
+      <c r="C32" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="19" t="s">
         <v>31</v>
       </c>
     </row>
@@ -4414,9 +4630,9 @@
       <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="20"/>
-      <c r="E33" s="20"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A34" s="1" t="s">
@@ -4425,9 +4641,9 @@
       <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="18"/>
-      <c r="D34" s="20"/>
-      <c r="E34" s="20"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
@@ -4436,13 +4652,13 @@
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="D36" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="E36" s="19" t="s">
         <v>36</v>
       </c>
       <c r="F36" s="1" t="s">
@@ -4468,9 +4684,9 @@
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
       <c r="F37" s="1" t="s">
         <v>496</v>
       </c>
@@ -4494,9 +4710,9 @@
       <c r="B38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
       <c r="F38" s="1" t="s">
         <v>141</v>
       </c>
@@ -4514,12 +4730,12 @@
       </c>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
       <c r="E40" s="11"/>
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
@@ -4535,13 +4751,13 @@
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="D42" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="19" t="s">
         <v>29</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -4559,7 +4775,7 @@
       <c r="J42" s="1" t="s">
         <v>540</v>
       </c>
-      <c r="K42" s="24" t="s">
+      <c r="K42" s="21" t="s">
         <v>32</v>
       </c>
     </row>
@@ -4570,9 +4786,9 @@
       <c r="B43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="18"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
       <c r="F43" s="1" t="s">
         <v>531</v>
       </c>
@@ -4588,7 +4804,7 @@
       <c r="J43" s="1" t="s">
         <v>535</v>
       </c>
-      <c r="K43" s="24"/>
+      <c r="K43" s="21"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -4597,9 +4813,9 @@
       <c r="B44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
       <c r="F44" s="1" t="s">
         <v>527</v>
       </c>
@@ -4615,7 +4831,7 @@
       <c r="J44" s="1" t="s">
         <v>530</v>
       </c>
-      <c r="K44" s="24"/>
+      <c r="K44" s="21"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -4624,13 +4840,13 @@
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="D46" s="20" t="s">
+      <c r="D46" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E46" s="20" t="s">
+      <c r="E46" s="19" t="s">
         <v>30</v>
       </c>
       <c r="F46" s="1" t="s">
@@ -4648,7 +4864,7 @@
       <c r="J46" s="1" t="s">
         <v>554</v>
       </c>
-      <c r="K46" s="24" t="s">
+      <c r="K46" s="21" t="s">
         <v>33</v>
       </c>
     </row>
@@ -4659,9 +4875,9 @@
       <c r="B47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="18"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
       <c r="F47" s="1" t="s">
         <v>545</v>
       </c>
@@ -4677,7 +4893,7 @@
       <c r="J47" s="1" t="s">
         <v>549</v>
       </c>
-      <c r="K47" s="24"/>
+      <c r="K47" s="21"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -4686,9 +4902,9 @@
       <c r="B48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C48" s="18"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
+      <c r="C48" s="23"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
       <c r="F48" s="1" t="s">
         <v>541</v>
       </c>
@@ -4704,7 +4920,7 @@
       <c r="J48" s="1" t="s">
         <v>544</v>
       </c>
-      <c r="K48" s="24"/>
+      <c r="K48" s="21"/>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -4713,13 +4929,13 @@
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="C50" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="D50" s="20" t="s">
+      <c r="D50" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E50" s="20" t="s">
+      <c r="E50" s="19" t="s">
         <v>31</v>
       </c>
       <c r="F50" s="1" t="s">
@@ -4745,9 +4961,9 @@
       <c r="B51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="18"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
       <c r="F51" s="1" t="s">
         <v>558</v>
       </c>
@@ -4771,9 +4987,9 @@
       <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="18"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
       <c r="F52" s="17" t="s">
         <v>527</v>
       </c>
@@ -4792,33 +5008,11 @@
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="K46:K48"/>
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="D32:D34"/>
     <mergeCell ref="E32:E34"/>
@@ -4832,11 +5026,33 @@
     <mergeCell ref="C42:C44"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="E42:E44"/>
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4904,13 +5120,13 @@
       <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="25" t="s">
         <v>285</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="22" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="22" t="s">
         <v>15</v>
       </c>
       <c r="F2" s="1" t="s">
@@ -4928,7 +5144,7 @@
       <c r="J2" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="K2" s="23" t="s">
+      <c r="K2" s="20" t="s">
         <v>17</v>
       </c>
     </row>
@@ -4939,9 +5155,9 @@
       <c r="B3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="18"/>
-      <c r="D3" s="20"/>
-      <c r="E3" s="20"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
       <c r="F3" s="1" t="s">
         <v>572</v>
       </c>
@@ -4957,7 +5173,7 @@
       <c r="J3" s="1" t="s">
         <v>575</v>
       </c>
-      <c r="K3" s="24"/>
+      <c r="K3" s="21"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -4966,9 +5182,9 @@
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
       <c r="F4" s="1" t="s">
         <v>568</v>
       </c>
@@ -4984,7 +5200,7 @@
       <c r="J4" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="K4" s="24"/>
+      <c r="K4" s="21"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -4993,13 +5209,13 @@
       <c r="B6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="23" t="s">
         <v>286</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="19" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="19" t="s">
         <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
@@ -5017,7 +5233,7 @@
       <c r="J6" s="1" t="s">
         <v>592</v>
       </c>
-      <c r="K6" s="24" t="s">
+      <c r="K6" s="21" t="s">
         <v>18</v>
       </c>
     </row>
@@ -5028,9 +5244,9 @@
       <c r="B7" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="20"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
       <c r="F7" s="1" t="s">
         <v>584</v>
       </c>
@@ -5046,7 +5262,7 @@
       <c r="J7" s="1" t="s">
         <v>588</v>
       </c>
-      <c r="K7" s="24"/>
+      <c r="K7" s="21"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -5055,9 +5271,9 @@
       <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="18"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="20"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
       <c r="F8" s="1" t="s">
         <v>580</v>
       </c>
@@ -5073,15 +5289,15 @@
       <c r="J8" s="1" t="s">
         <v>583</v>
       </c>
-      <c r="K8" s="24"/>
+      <c r="K8" s="21"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="21"/>
-      <c r="C10" s="21"/>
-      <c r="D10" s="21"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
       <c r="E10" s="11"/>
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
@@ -5097,13 +5313,13 @@
       <c r="B12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="18" t="s">
+      <c r="C12" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="19" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="1" t="s">
@@ -5121,7 +5337,7 @@
       <c r="J12" s="1" t="s">
         <v>604</v>
       </c>
-      <c r="K12" s="24" t="s">
+      <c r="K12" s="21" t="s">
         <v>20</v>
       </c>
     </row>
@@ -5132,9 +5348,9 @@
       <c r="B13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
       <c r="F13" s="1" t="s">
         <v>596</v>
       </c>
@@ -5150,7 +5366,7 @@
       <c r="J13" s="1" t="s">
         <v>600</v>
       </c>
-      <c r="K13" s="24"/>
+      <c r="K13" s="21"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -5159,9 +5375,9 @@
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
       <c r="F14" s="1" t="s">
         <v>141</v>
       </c>
@@ -5177,7 +5393,7 @@
       <c r="J14" s="1" t="s">
         <v>595</v>
       </c>
-      <c r="K14" s="24"/>
+      <c r="K14" s="21"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -5186,16 +5402,31 @@
       <c r="B16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="18" t="s">
+      <c r="C16" s="23" t="s">
         <v>288</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="D16" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="E16" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="K16" s="24" t="s">
+      <c r="F16" s="1" t="s">
+        <v>627</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>628</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>629</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>630</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>631</v>
+      </c>
+      <c r="K16" s="21" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5206,11 +5437,25 @@
       <c r="B17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C17" s="18"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="G17" s="16"/>
-      <c r="K17" s="24"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="1" t="s">
+        <v>622</v>
+      </c>
+      <c r="G17" s="16" t="s">
+        <v>623</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>624</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>625</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>626</v>
+      </c>
+      <c r="K17" s="21"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -5219,10 +5464,25 @@
       <c r="B18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C18" s="18"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="K18" s="24"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="J18" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="K18" s="21"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -5231,16 +5491,16 @@
       <c r="B20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="18" t="s">
+      <c r="C20" s="23" t="s">
         <v>289</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="D20" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="K20" s="24" t="s">
+      <c r="K20" s="21" t="s">
         <v>37</v>
       </c>
     </row>
@@ -5251,10 +5511,10 @@
       <c r="B21" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="18"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="K21" s="24"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="K21" s="21"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -5263,10 +5523,10 @@
       <c r="B22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="18"/>
-      <c r="D22" s="20"/>
-      <c r="E22" s="20"/>
-      <c r="K22" s="24"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="K22" s="21"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -5275,14 +5535,29 @@
       <c r="B24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="18" t="s">
+      <c r="C24" s="23" t="s">
         <v>290</v>
       </c>
-      <c r="D24" s="20" t="s">
+      <c r="D24" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="19" t="s">
         <v>34</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>639</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>640</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>641</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>642</v>
+      </c>
+      <c r="J24" s="1" t="s">
+        <v>643</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.2">
@@ -5292,9 +5567,24 @@
       <c r="B25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="18"/>
-      <c r="D25" s="20"/>
-      <c r="E25" s="20"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="1" t="s">
+        <v>635</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>636</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>637</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>638</v>
+      </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
@@ -5303,9 +5593,24 @@
       <c r="B26" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="18"/>
-      <c r="D26" s="20"/>
-      <c r="E26" s="20"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>632</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>593</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>633</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>634</v>
+      </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
@@ -5314,14 +5619,29 @@
       <c r="B28" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="18" t="s">
+      <c r="C28" s="23" t="s">
         <v>291</v>
       </c>
-      <c r="D28" s="20" t="s">
+      <c r="D28" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="E28" s="20" t="s">
+      <c r="E28" s="19" t="s">
         <v>35</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>652</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="J28" s="1" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.2">
@@ -5331,9 +5651,24 @@
       <c r="B29" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="18"/>
-      <c r="D29" s="20"/>
-      <c r="E29" s="20"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>649</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>651</v>
+      </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
@@ -5342,54 +5677,66 @@
       <c r="B30" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C30" s="18"/>
-      <c r="D30" s="20"/>
-      <c r="E30" s="20"/>
-    </row>
-    <row r="32" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="26" t="s">
+      <c r="C30" s="23"/>
+      <c r="D30" s="19"/>
+      <c r="E30" s="19"/>
+      <c r="F30" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H30" s="1" t="s">
+        <v>644</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>645</v>
+      </c>
+      <c r="J30" s="1" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A32" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="26" t="s">
+      <c r="B32" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C32" s="27" t="s">
+      <c r="C32" s="23" t="s">
         <v>292</v>
       </c>
-      <c r="D32" s="28" t="s">
+      <c r="D32" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="E32" s="28" t="s">
+      <c r="E32" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="G32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="K32" s="30"/>
-    </row>
-    <row r="33" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="26" t="s">
+      <c r="G32" s="14"/>
+      <c r="I32" s="14"/>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B33" s="26" t="s">
+      <c r="B33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C33" s="27"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
-      <c r="K33" s="30"/>
-    </row>
-    <row r="34" spans="1:11" s="26" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="26" t="s">
+      <c r="C33" s="23"/>
+      <c r="D33" s="19"/>
+      <c r="E33" s="19"/>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="27"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
-      <c r="H34" s="29"/>
-      <c r="K34" s="30"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="H34" s="14"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
@@ -5398,14 +5745,29 @@
       <c r="B36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="18" t="s">
+      <c r="C36" s="23" t="s">
         <v>293</v>
       </c>
-      <c r="D36" s="20" t="s">
+      <c r="D36" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="E36" s="20" t="s">
+      <c r="E36" s="19" t="s">
         <v>36</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>664</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="J36" s="1" t="s">
+        <v>668</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
@@ -5415,9 +5777,24 @@
       <c r="B37" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="18"/>
-      <c r="D37" s="20"/>
-      <c r="E37" s="20"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="19"/>
+      <c r="E37" s="19"/>
+      <c r="F37" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>660</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>661</v>
+      </c>
+      <c r="I37" s="1" t="s">
+        <v>662</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>663</v>
+      </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
@@ -5426,17 +5803,32 @@
       <c r="B38" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C38" s="18"/>
-      <c r="D38" s="20"/>
-      <c r="E38" s="20"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>656</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="I38" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>659</v>
+      </c>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B40" s="21"/>
-      <c r="C40" s="21"/>
-      <c r="D40" s="21"/>
+      <c r="B40" s="24"/>
+      <c r="C40" s="24"/>
+      <c r="D40" s="24"/>
       <c r="E40" s="11"/>
       <c r="F40" s="9"/>
       <c r="G40" s="9"/>
@@ -5452,13 +5844,13 @@
       <c r="B42" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="18" t="s">
+      <c r="C42" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="D42" s="20" t="s">
+      <c r="D42" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="E42" s="20" t="s">
+      <c r="E42" s="19" t="s">
         <v>29</v>
       </c>
       <c r="F42" s="1" t="s">
@@ -5476,7 +5868,7 @@
       <c r="J42" s="1" t="s">
         <v>618</v>
       </c>
-      <c r="K42" s="24" t="s">
+      <c r="K42" s="21" t="s">
         <v>32</v>
       </c>
     </row>
@@ -5487,9 +5879,9 @@
       <c r="B43" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C43" s="18"/>
-      <c r="D43" s="20"/>
-      <c r="E43" s="20"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="19"/>
       <c r="F43" s="1" t="s">
         <v>609</v>
       </c>
@@ -5505,7 +5897,7 @@
       <c r="J43" s="1" t="s">
         <v>613</v>
       </c>
-      <c r="K43" s="24"/>
+      <c r="K43" s="21"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -5514,10 +5906,10 @@
       <c r="B44" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C44" s="18"/>
-      <c r="D44" s="20"/>
-      <c r="E44" s="20"/>
-      <c r="F44" s="31" t="s">
+      <c r="C44" s="23"/>
+      <c r="D44" s="19"/>
+      <c r="E44" s="19"/>
+      <c r="F44" s="18" t="s">
         <v>527</v>
       </c>
       <c r="G44" s="1" t="s">
@@ -5532,7 +5924,7 @@
       <c r="J44" s="1" t="s">
         <v>608</v>
       </c>
-      <c r="K44" s="24"/>
+      <c r="K44" s="21"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -5541,16 +5933,31 @@
       <c r="B46" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C46" s="18" t="s">
+      <c r="C46" s="23" t="s">
         <v>295</v>
       </c>
-      <c r="D46" s="20" t="s">
+      <c r="D46" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="E46" s="20" t="s">
+      <c r="E46" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="K46" s="24" t="s">
+      <c r="F46" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="J46" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="K46" s="21" t="s">
         <v>33</v>
       </c>
     </row>
@@ -5561,10 +5968,25 @@
       <c r="B47" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C47" s="18"/>
-      <c r="D47" s="20"/>
-      <c r="E47" s="20"/>
-      <c r="K47" s="24"/>
+      <c r="C47" s="23"/>
+      <c r="D47" s="19"/>
+      <c r="E47" s="19"/>
+      <c r="F47" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="I47" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="J47" s="1" t="s">
+        <v>676</v>
+      </c>
+      <c r="K47" s="21"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -5573,80 +5995,117 @@
       <c r="B48" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C48" s="18"/>
-      <c r="D48" s="20"/>
-      <c r="E48" s="20"/>
-      <c r="K48" s="24"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C48" s="23"/>
+      <c r="D48" s="19"/>
+      <c r="E48" s="19"/>
+      <c r="F48" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="I48" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="J48" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="K48" s="21"/>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C50" s="18" t="s">
+      <c r="C50" s="23" t="s">
         <v>296</v>
       </c>
-      <c r="D50" s="20" t="s">
+      <c r="D50" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="E50" s="20" t="s">
+      <c r="E50" s="19" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="F50" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="I50" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="J50" s="1" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>5</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="18"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="C51" s="23"/>
+      <c r="D51" s="19"/>
+      <c r="E51" s="19"/>
+      <c r="F51" s="1" t="s">
+        <v>686</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>6</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="18"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="17"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="G52" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="H52" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="I52" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="J52" s="1" t="s">
+        <v>685</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="45">
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="K46:K48"/>
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="D32:D34"/>
     <mergeCell ref="E32:E34"/>
@@ -5660,11 +6119,33 @@
     <mergeCell ref="C42:C44"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="E42:E44"/>
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5711,13 +6192,13 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="26" t="s">
         <v>58</v>
       </c>
       <c r="D2" s="1" t="s">
@@ -5740,9 +6221,9 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A3" s="24"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="25"/>
+      <c r="A3" s="21"/>
+      <c r="B3" s="23"/>
+      <c r="C3" s="26"/>
       <c r="D3" s="1" t="s">
         <v>46</v>
       </c>
@@ -5763,9 +6244,9 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A4" s="24"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="25"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="26"/>
       <c r="D4" s="1" t="s">
         <v>47</v>
       </c>
@@ -5786,13 +6267,13 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="21" t="s">
         <v>186</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="25" t="s">
+      <c r="C6" s="26" t="s">
         <v>57</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -5815,9 +6296,9 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A7" s="24"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="25"/>
+      <c r="A7" s="21"/>
+      <c r="B7" s="23"/>
+      <c r="C7" s="26"/>
       <c r="D7" s="1" t="s">
         <v>46</v>
       </c>
@@ -5838,9 +6319,9 @@
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A8" s="24"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="25"/>
+      <c r="A8" s="21"/>
+      <c r="B8" s="23"/>
+      <c r="C8" s="26"/>
       <c r="D8" s="1" t="s">
         <v>47</v>
       </c>
@@ -5861,13 +6342,13 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="21" t="s">
         <v>185</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="23" t="s">
         <v>50</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="26" t="s">
         <v>56</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -5890,9 +6371,9 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A11" s="24"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="25"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="23"/>
+      <c r="C11" s="26"/>
       <c r="D11" s="1" t="s">
         <v>46</v>
       </c>
@@ -5913,9 +6394,9 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" s="24"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="25"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="23"/>
+      <c r="C12" s="26"/>
       <c r="D12" s="1" t="s">
         <v>47</v>
       </c>
@@ -5933,13 +6414,13 @@
       </c>
     </row>
     <row r="14" spans="1:9" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="24" t="s">
+      <c r="A14" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="26" t="s">
         <v>55</v>
       </c>
       <c r="D14" s="3" t="s">
@@ -5962,9 +6443,9 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A15" s="24"/>
-      <c r="B15" s="18"/>
-      <c r="C15" s="25"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="23"/>
+      <c r="C15" s="26"/>
       <c r="D15" s="1" t="s">
         <v>46</v>
       </c>
@@ -5985,9 +6466,9 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A16" s="24"/>
-      <c r="B16" s="18"/>
-      <c r="C16" s="25"/>
+      <c r="A16" s="21"/>
+      <c r="B16" s="23"/>
+      <c r="C16" s="26"/>
       <c r="D16" s="1" t="s">
         <v>47</v>
       </c>
@@ -6008,13 +6489,13 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="24" t="s">
+      <c r="A18" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="26" t="s">
         <v>59</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -6037,9 +6518,9 @@
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A19" s="24"/>
-      <c r="B19" s="18"/>
-      <c r="C19" s="25"/>
+      <c r="A19" s="21"/>
+      <c r="B19" s="23"/>
+      <c r="C19" s="26"/>
       <c r="D19" s="1" t="s">
         <v>46</v>
       </c>
@@ -6060,9 +6541,9 @@
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A20" s="24"/>
-      <c r="B20" s="18"/>
-      <c r="C20" s="25"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="23"/>
+      <c r="C20" s="26"/>
       <c r="D20" s="1" t="s">
         <v>47</v>
       </c>
@@ -6080,13 +6561,13 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="24" t="s">
+      <c r="A22" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="26" t="s">
         <v>60</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -6109,9 +6590,9 @@
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A23" s="24"/>
-      <c r="B23" s="18"/>
-      <c r="C23" s="25"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="26"/>
       <c r="D23" s="1" t="s">
         <v>46</v>
       </c>
@@ -6132,9 +6613,9 @@
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A24" s="24"/>
-      <c r="B24" s="18"/>
-      <c r="C24" s="25"/>
+      <c r="A24" s="21"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="26"/>
       <c r="D24" s="1" t="s">
         <v>47</v>
       </c>
@@ -6155,13 +6636,13 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="25" t="s">
+      <c r="A26" s="26" t="s">
         <v>192</v>
       </c>
-      <c r="B26" s="25" t="s">
+      <c r="B26" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C26" s="26" t="s">
         <v>122</v>
       </c>
       <c r="D26" s="3" t="s">
@@ -6184,9 +6665,9 @@
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A27" s="25"/>
-      <c r="B27" s="25"/>
-      <c r="C27" s="25"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="26"/>
       <c r="D27" s="1" t="s">
         <v>46</v>
       </c>
@@ -6207,9 +6688,9 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="25"/>
-      <c r="B28" s="25"/>
-      <c r="C28" s="25"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="26"/>
       <c r="D28" s="1" t="s">
         <v>47</v>
       </c>
@@ -6234,13 +6715,13 @@
       <c r="B29" s="7"/>
     </row>
     <row r="30" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="25" t="s">
+      <c r="A30" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B30" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="C30" s="25" t="s">
+      <c r="C30" s="26" t="s">
         <v>122</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -6263,9 +6744,9 @@
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A31" s="25"/>
-      <c r="B31" s="25"/>
-      <c r="C31" s="25"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="26"/>
       <c r="D31" s="1" t="s">
         <v>46</v>
       </c>
@@ -6286,9 +6767,9 @@
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A32" s="25"/>
-      <c r="B32" s="25"/>
-      <c r="C32" s="25"/>
+      <c r="A32" s="26"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
       <c r="D32" s="1" t="s">
         <v>47</v>
       </c>
@@ -6309,13 +6790,13 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="24" t="s">
+      <c r="A34" s="21" t="s">
         <v>179</v>
       </c>
-      <c r="B34" s="25" t="s">
+      <c r="B34" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="C34" s="25" t="s">
+      <c r="C34" s="26" t="s">
         <v>180</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -6338,9 +6819,9 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="24"/>
-      <c r="B35" s="25"/>
-      <c r="C35" s="25"/>
+      <c r="A35" s="21"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
       <c r="D35" s="1" t="s">
         <v>46</v>
       </c>
@@ -6361,9 +6842,9 @@
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A36" s="24"/>
-      <c r="B36" s="25"/>
-      <c r="C36" s="25"/>
+      <c r="A36" s="21"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
       <c r="D36" s="1" t="s">
         <v>47</v>
       </c>
@@ -6384,13 +6865,13 @@
       </c>
     </row>
     <row r="38" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="24" t="s">
+      <c r="A38" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="B38" s="24" t="s">
+      <c r="B38" s="21" t="s">
         <v>177</v>
       </c>
-      <c r="C38" s="25" t="s">
+      <c r="C38" s="26" t="s">
         <v>55</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -6398,29 +6879,29 @@
       </c>
     </row>
     <row r="39" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A39" s="24"/>
-      <c r="B39" s="24"/>
-      <c r="C39" s="25"/>
+      <c r="A39" s="21"/>
+      <c r="B39" s="21"/>
+      <c r="C39" s="26"/>
       <c r="D39" s="1" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="24"/>
-      <c r="B40" s="24"/>
-      <c r="C40" s="25"/>
+      <c r="A40" s="21"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="26"/>
       <c r="D40" s="1" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="24" t="s">
+      <c r="A42" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="B42" s="24" t="s">
+      <c r="B42" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="C42" s="25" t="s">
+      <c r="C42" s="26" t="s">
         <v>60</v>
       </c>
       <c r="D42" s="3" t="s">
@@ -6443,9 +6924,9 @@
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A43" s="24"/>
-      <c r="B43" s="24"/>
-      <c r="C43" s="25"/>
+      <c r="A43" s="21"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="26"/>
       <c r="D43" s="1" t="s">
         <v>46</v>
       </c>
@@ -6466,9 +6947,9 @@
       </c>
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A44" s="24"/>
-      <c r="B44" s="24"/>
-      <c r="C44" s="25"/>
+      <c r="A44" s="21"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="26"/>
       <c r="D44" s="1" t="s">
         <v>47</v>
       </c>
@@ -6489,13 +6970,13 @@
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A46" s="24" t="s">
+      <c r="A46" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="B46" s="24" t="s">
+      <c r="B46" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="C46" s="25" t="s">
+      <c r="C46" s="26" t="s">
         <v>209</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -6518,9 +6999,9 @@
       </c>
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A47" s="24"/>
-      <c r="B47" s="24"/>
-      <c r="C47" s="25"/>
+      <c r="A47" s="21"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="26"/>
       <c r="D47" s="1" t="s">
         <v>46</v>
       </c>
@@ -6541,9 +7022,9 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A48" s="24"/>
-      <c r="B48" s="24"/>
-      <c r="C48" s="25"/>
+      <c r="A48" s="21"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="26"/>
       <c r="D48" s="1" t="s">
         <v>47</v>
       </c>
@@ -6565,6 +7046,28 @@
     </row>
   </sheetData>
   <mergeCells count="36">
+    <mergeCell ref="A46:A48"/>
+    <mergeCell ref="B46:B48"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="B38:B40"/>
+    <mergeCell ref="C38:C40"/>
+    <mergeCell ref="A42:A44"/>
+    <mergeCell ref="B42:B44"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="A6:A8"/>
+    <mergeCell ref="A34:A36"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A18:A20"/>
+    <mergeCell ref="A22:A24"/>
     <mergeCell ref="C22:C24"/>
     <mergeCell ref="C26:C28"/>
     <mergeCell ref="B26:B28"/>
@@ -6579,28 +7082,6 @@
     <mergeCell ref="C18:C20"/>
     <mergeCell ref="B18:B20"/>
     <mergeCell ref="B22:B24"/>
-    <mergeCell ref="A6:A8"/>
-    <mergeCell ref="A34:A36"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="A26:A28"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A14:A16"/>
-    <mergeCell ref="A18:A20"/>
-    <mergeCell ref="A22:A24"/>
-    <mergeCell ref="A46:A48"/>
-    <mergeCell ref="B46:B48"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="B30:B32"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="A38:A40"/>
-    <mergeCell ref="B38:B40"/>
-    <mergeCell ref="C38:C40"/>
-    <mergeCell ref="A42:A44"/>
-    <mergeCell ref="B42:B44"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C34:C36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>

--- a/benchmarking/search_for_best_combination/results_basic.xlsx
+++ b/benchmarking/search_for_best_combination/results_basic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2F4A36D-677B-AE49-B949-49F859C691F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C6BA70-4744-7046-9787-82E746AD60AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="1" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="3" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="92">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -289,28 +289,7 @@
     <t>experiment with pretrained embeddings and bernoulli sampler</t>
   </si>
   <si>
-    <t>experiment with pretrained embeddings and downsampling the major class</t>
-  </si>
-  <si>
-    <t>experiment with pretrained embeddings and bernoulli sampler and downsampling the major class</t>
-  </si>
-  <si>
     <t>trial1/downsampling</t>
-  </si>
-  <si>
-    <t>trial1/bernoulli_downsampling</t>
-  </si>
-  <si>
-    <t>experiment with pretrained embeddings and bernoulli sampler and downsampling the major class + focal loss function</t>
-  </si>
-  <si>
-    <t>trial1/focal</t>
-  </si>
-  <si>
-    <t>trial1/optimizer</t>
-  </si>
-  <si>
-    <t>experiment with pretrained embeddings and bernoulli sampler and downsampling the major class + focal loss function + oprimizer</t>
   </si>
   <si>
     <r>
@@ -336,21 +315,6 @@
     <t>pretrained/text_speaker</t>
   </si>
   <si>
-    <t>trial2/bernoulli</t>
-  </si>
-  <si>
-    <t>trial2/downsampling</t>
-  </si>
-  <si>
-    <t>trial2/bernoulli_downsampling</t>
-  </si>
-  <si>
-    <t>trial2/focal</t>
-  </si>
-  <si>
-    <t>trial2/optimizer</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">BEST EXPERIMENT WITH ALL with </t>
     </r>
@@ -374,19 +338,25 @@
     <t>pretrained/text_year</t>
   </si>
   <si>
-    <t>trial3/bernoulli</t>
-  </si>
-  <si>
-    <t>trial3/downsampling</t>
-  </si>
-  <si>
-    <t>trial3/bernoulli_downsampling</t>
-  </si>
-  <si>
-    <t>trial3/focal</t>
-  </si>
-  <si>
-    <t>trial3/optimizer</t>
+    <t>trial1/corruption_scheme</t>
+  </si>
+  <si>
+    <t>experiment with pretrained embeddings and different corruption scheme</t>
+  </si>
+  <si>
+    <t>experiment with pretrained embeddings, basic sampler and downsampling the major class</t>
+  </si>
+  <si>
+    <t>experiment with pretrained embeddings, bernoulli sampler and downsampling the major class</t>
+  </si>
+  <si>
+    <t>trial1/downsampling_basic</t>
+  </si>
+  <si>
+    <t>trial1/downsampling_bernoulli</t>
+  </si>
+  <si>
+    <t>experiment with  basic sampler and downsampling the major class</t>
   </si>
 </sst>
 </file>
@@ -396,7 +366,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000000000"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -438,13 +408,6 @@
       <i/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -554,7 +517,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -613,179 +576,158 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1167,13 +1109,13 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="59" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="12">
@@ -1191,7 +1133,7 @@
       <c r="J2" s="12">
         <v>0.51636704079999995</v>
       </c>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="57" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1202,9 +1144,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
       <c r="F3" s="12">
         <v>5.23489933E-2</v>
       </c>
@@ -1220,7 +1162,7 @@
       <c r="J3" s="12">
         <v>0.49172142549999998</v>
       </c>
-      <c r="K3" s="27"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1229,9 +1171,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
       <c r="F4" s="12">
         <v>3.73921381E-2</v>
       </c>
@@ -1247,7 +1189,7 @@
       <c r="J4" s="12">
         <v>0.44867621930000001</v>
       </c>
-      <c r="K4" s="27"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -1256,13 +1198,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="56" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="12">
@@ -1280,7 +1222,7 @@
       <c r="J6" s="12">
         <v>0.49915964429999998</v>
       </c>
-      <c r="K6" s="27" t="s">
+      <c r="K6" s="58" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1291,9 +1233,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
       <c r="F7" s="12">
         <v>2.7399884999999999E-2</v>
       </c>
@@ -1309,7 +1251,7 @@
       <c r="J7" s="12">
         <v>0.48493602559999999</v>
       </c>
-      <c r="K7" s="27"/>
+      <c r="K7" s="58"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -1318,9 +1260,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
       <c r="F8" s="12">
         <v>2.4717378799999998E-2</v>
       </c>
@@ -1336,15 +1278,15 @@
       <c r="J8" s="12">
         <v>0.43282600290000001</v>
       </c>
-      <c r="K8" s="27"/>
+      <c r="K8" s="58"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
       <c r="E10" s="5"/>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
@@ -1360,13 +1302,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="56" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="12">
@@ -1384,7 +1326,7 @@
       <c r="J12" s="12">
         <v>0.45356946819999999</v>
       </c>
-      <c r="K12" s="27" t="s">
+      <c r="K12" s="58" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1395,9 +1337,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
       <c r="F13" s="12">
         <v>5.4569232000000002E-2</v>
       </c>
@@ -1413,7 +1355,7 @@
       <c r="J13" s="12">
         <v>0.2490125493</v>
       </c>
-      <c r="K13" s="27"/>
+      <c r="K13" s="58"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -1422,9 +1364,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
       <c r="F14" s="12">
         <v>0.2933740192</v>
       </c>
@@ -1440,7 +1382,7 @@
       <c r="J14" s="12">
         <v>0.33911636109999999</v>
       </c>
-      <c r="K14" s="27"/>
+      <c r="K14" s="58"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -1449,13 +1391,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="23" t="s">
+      <c r="E16" s="56" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="12">
@@ -1473,7 +1415,7 @@
       <c r="J16" s="12">
         <v>0.46862206229999998</v>
       </c>
-      <c r="K16" s="27" t="s">
+      <c r="K16" s="58" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1484,9 +1426,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
       <c r="F17" s="12">
         <v>0.2220972487</v>
       </c>
@@ -1502,7 +1444,7 @@
       <c r="J17" s="12">
         <v>0.61463971539999995</v>
       </c>
-      <c r="K17" s="27"/>
+      <c r="K17" s="58"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -1511,9 +1453,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
       <c r="F18" s="12">
         <v>0.12510815019999999</v>
       </c>
@@ -1529,7 +1471,7 @@
       <c r="J18" s="12">
         <v>0.40298454760000002</v>
       </c>
-      <c r="K18" s="27"/>
+      <c r="K18" s="58"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -1538,13 +1480,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="56" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="12">
@@ -1562,7 +1504,7 @@
       <c r="J20" s="12">
         <v>0.42112340529999998</v>
       </c>
-      <c r="K20" s="27" t="s">
+      <c r="K20" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1573,9 +1515,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
       <c r="F21" s="12">
         <v>0.28648624509999998</v>
       </c>
@@ -1588,10 +1530,10 @@
       <c r="I21" s="12">
         <v>0.79611147660000003</v>
       </c>
-      <c r="J21" s="28">
+      <c r="J21" s="20">
         <v>0.71830903779999999</v>
       </c>
-      <c r="K21" s="27"/>
+      <c r="K21" s="58"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -1600,9 +1542,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
       <c r="F22" s="12">
         <v>4.4658810000000002E-4</v>
       </c>
@@ -1615,7 +1557,7 @@
       <c r="J22" s="12">
         <v>0.41851161510000001</v>
       </c>
-      <c r="K22" s="27"/>
+      <c r="K22" s="58"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -1624,13 +1566,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="56" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="12">
@@ -1656,9 +1598,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
       <c r="F25" s="12">
         <v>0.1240506329</v>
       </c>
@@ -1682,9 +1624,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
       <c r="F26" s="12">
         <v>0.13367616030000001</v>
       </c>
@@ -1708,13 +1650,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="C28" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="56" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="12">
@@ -1740,9 +1682,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="21"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
       <c r="F29" s="12">
         <v>0.20128508440000001</v>
       </c>
@@ -1766,9 +1708,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="21"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
       <c r="F30" s="12">
         <v>0.1974137004</v>
       </c>
@@ -1792,16 +1734,16 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="E32" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="F32" s="28">
+      <c r="F32" s="20">
         <v>0.48067164600000001</v>
       </c>
       <c r="G32" s="12">
@@ -1810,7 +1752,7 @@
       <c r="H32" s="12">
         <v>0.74177547180000003</v>
       </c>
-      <c r="I32" s="28">
+      <c r="I32" s="20">
         <v>0.92762878579999997</v>
       </c>
       <c r="J32" s="12">
@@ -1824,9 +1766,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
+      <c r="C33" s="60"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
       <c r="F33" s="12">
         <v>0.4661326187</v>
       </c>
@@ -1850,9 +1792,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="21"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
       <c r="F34" s="12">
         <v>2.2806319999999999E-4</v>
       </c>
@@ -1876,13 +1818,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="C36" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="23" t="s">
+      <c r="D36" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="23" t="s">
+      <c r="E36" s="56" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="12">
@@ -1891,7 +1833,7 @@
       <c r="G36" s="12">
         <v>0.24770458279999999</v>
       </c>
-      <c r="H36" s="28">
+      <c r="H36" s="20">
         <v>0.78124373520000001</v>
       </c>
       <c r="I36" s="12">
@@ -1908,9 +1850,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="21"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
+      <c r="C37" s="60"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
       <c r="F37" s="12">
         <v>0.29922617379999999</v>
       </c>
@@ -1934,9 +1876,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
       <c r="F38" s="12">
         <v>0.1553265707</v>
       </c>
@@ -1954,12 +1896,12 @@
       </c>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
+      <c r="B40" s="61"/>
+      <c r="C40" s="61"/>
+      <c r="D40" s="61"/>
       <c r="E40" s="5"/>
       <c r="F40" s="14"/>
       <c r="G40" s="14"/>
@@ -1975,13 +1917,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="21" t="s">
+      <c r="C42" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="23" t="s">
+      <c r="D42" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="23" t="s">
+      <c r="E42" s="56" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="12">
@@ -1999,7 +1941,7 @@
       <c r="J42" s="12">
         <v>0.50415219909999998</v>
       </c>
-      <c r="K42" s="27" t="s">
+      <c r="K42" s="58" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2010,9 +1952,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="21"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
+      <c r="C43" s="60"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="56"/>
       <c r="F43" s="12">
         <v>0.27900922929999999</v>
       </c>
@@ -2028,7 +1970,7 @@
       <c r="J43" s="12">
         <v>0.6867986989</v>
       </c>
-      <c r="K43" s="27"/>
+      <c r="K43" s="58"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -2037,9 +1979,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="21"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
+      <c r="C44" s="60"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
       <c r="F44" s="12">
         <v>1.08858563E-2</v>
       </c>
@@ -2055,7 +1997,7 @@
       <c r="J44" s="12">
         <v>0.34279394219999998</v>
       </c>
-      <c r="K44" s="27"/>
+      <c r="K44" s="58"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -2064,13 +2006,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="21" t="s">
+      <c r="C46" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="23" t="s">
+      <c r="D46" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="23" t="s">
+      <c r="E46" s="56" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="12">
@@ -2088,7 +2030,7 @@
       <c r="J46" s="12">
         <v>0.43511184339999998</v>
       </c>
-      <c r="K46" s="27" t="s">
+      <c r="K46" s="58" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2099,9 +2041,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="21"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="23"/>
+      <c r="C47" s="60"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="56"/>
       <c r="F47" s="12">
         <v>0.36941770550000003</v>
       </c>
@@ -2117,7 +2059,7 @@
       <c r="J47" s="12">
         <v>0.67778323610000002</v>
       </c>
-      <c r="K47" s="27"/>
+      <c r="K47" s="58"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -2126,9 +2068,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="21"/>
-      <c r="D48" s="23"/>
-      <c r="E48" s="23"/>
+      <c r="C48" s="60"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="56"/>
       <c r="F48" s="12">
         <v>7.1050970500000005E-2</v>
       </c>
@@ -2144,7 +2086,7 @@
       <c r="J48" s="12">
         <v>0.33626401280000001</v>
       </c>
-      <c r="K48" s="27"/>
+      <c r="K48" s="58"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -2153,13 +2095,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="21" t="s">
+      <c r="C50" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="23" t="s">
+      <c r="D50" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="23" t="s">
+      <c r="E50" s="56" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="12">
@@ -2185,9 +2127,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="21"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
+      <c r="C51" s="60"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
       <c r="F51" s="12">
         <v>0.46868170079999999</v>
       </c>
@@ -2211,13 +2153,13 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="21"/>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
+      <c r="C52" s="60"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="56"/>
       <c r="F52" s="12">
         <v>4.2022650500000001E-2</v>
       </c>
-      <c r="G52" s="28">
+      <c r="G52" s="20">
         <v>0.37070335789999997</v>
       </c>
       <c r="H52" s="12">
@@ -2230,68 +2172,99 @@
         <v>0.4546958096</v>
       </c>
     </row>
-    <row r="55" spans="1:11" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="56" t="s">
+    <row r="55" spans="1:11" s="45" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="56"/>
-      <c r="C55" s="56"/>
-      <c r="D55" s="56"/>
-      <c r="E55" s="57"/>
-      <c r="F55" s="58">
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="43">
         <f>MAX(F2:F52)</f>
         <v>0.48067164600000001</v>
       </c>
-      <c r="G55" s="58">
+      <c r="G55" s="43">
         <f>MAX(G2:G52)</f>
         <v>0.37070335789999997</v>
       </c>
-      <c r="H55" s="58">
+      <c r="H55" s="43">
         <f>MAX(H2:H52)</f>
         <v>0.78124373520000001</v>
       </c>
-      <c r="I55" s="58">
+      <c r="I55" s="43">
         <f>MAX(I2:I52)</f>
         <v>0.92762878579999997</v>
       </c>
-      <c r="J55" s="58">
+      <c r="J55" s="43">
         <f>MAX(J2:J52)</f>
         <v>0.71830903779999999</v>
       </c>
-      <c r="K55" s="59"/>
-    </row>
-    <row r="56" spans="1:11" s="65" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="61" t="s">
+      <c r="K55" s="44"/>
+    </row>
+    <row r="56" spans="1:11" s="49" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="61"/>
-      <c r="C56" s="61"/>
-      <c r="D56" s="61"/>
-      <c r="E56" s="62"/>
-      <c r="F56" s="63">
+      <c r="B56" s="55"/>
+      <c r="C56" s="55"/>
+      <c r="D56" s="55"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="47">
         <f>AVERAGE(F2:F52)</f>
         <v>0.21716488937777773</v>
       </c>
-      <c r="G56" s="63">
+      <c r="G56" s="47">
         <f>AVERAGE(G2:G52)</f>
         <v>0.10282875713333334</v>
       </c>
-      <c r="H56" s="63">
+      <c r="H56" s="47">
         <f>AVERAGE(H2:H52)</f>
         <v>0.37310816464857149</v>
       </c>
-      <c r="I56" s="63">
+      <c r="I56" s="47">
         <f>AVERAGE(I2:I52)</f>
         <v>0.66562983308333334</v>
       </c>
-      <c r="J56" s="63">
+      <c r="J56" s="47">
         <f>AVERAGE(J2:J52)</f>
         <v>0.46911950566388888</v>
       </c>
-      <c r="K56" s="64"/>
+      <c r="K56" s="48"/>
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="E46:E48"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="E50:E52"/>
     <mergeCell ref="K2:K4"/>
@@ -2308,37 +2281,6 @@
     <mergeCell ref="E42:E44"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E6:E8"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="A40:D40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2406,13 +2348,13 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="59" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="12">
@@ -2430,7 +2372,7 @@
       <c r="J2" s="12">
         <v>0.49946558660000001</v>
       </c>
-      <c r="K2" s="26" t="s">
+      <c r="K2" s="57" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2441,9 +2383,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
       <c r="F3" s="12">
         <v>3.1543624200000002E-2</v>
       </c>
@@ -2456,10 +2398,10 @@
       <c r="I3" s="12">
         <v>0.52995509259999996</v>
       </c>
-      <c r="J3" s="28">
+      <c r="J3" s="20">
         <v>0.51222158829999997</v>
       </c>
-      <c r="K3" s="27"/>
+      <c r="K3" s="58"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2468,9 +2410,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
       <c r="F4" s="12">
         <v>1.70661553E-2</v>
       </c>
@@ -2486,7 +2428,7 @@
       <c r="J4" s="12">
         <v>0.46528456299999998</v>
       </c>
-      <c r="K4" s="27"/>
+      <c r="K4" s="58"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G5" s="12"/>
@@ -2501,13 +2443,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="56" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="12">
@@ -2525,7 +2467,7 @@
       <c r="J6" s="12">
         <v>0.5044039011</v>
       </c>
-      <c r="K6" s="27" t="s">
+      <c r="K6" s="58" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2536,9 +2478,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
       <c r="F7" s="12">
         <v>4.3303314799999999E-2</v>
       </c>
@@ -2554,7 +2496,7 @@
       <c r="J7" s="12">
         <v>0.43858537390000002</v>
       </c>
-      <c r="K7" s="27"/>
+      <c r="K7" s="58"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -2563,9 +2505,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
       <c r="F8" s="12">
         <v>1.6669860099999999E-2</v>
       </c>
@@ -2581,7 +2523,7 @@
       <c r="J8" s="12">
         <v>0.47867128799999997</v>
       </c>
-      <c r="K8" s="27"/>
+      <c r="K8" s="58"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G9" s="12"/>
@@ -2590,12 +2532,12 @@
       <c r="J9" s="12"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
       <c r="E10" s="5"/>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
@@ -2617,13 +2559,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="56" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="12">
@@ -2641,7 +2583,7 @@
       <c r="J12" s="12">
         <v>0.49020679299999997</v>
       </c>
-      <c r="K12" s="27" t="s">
+      <c r="K12" s="58" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2652,9 +2594,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
       <c r="F13" s="12">
         <v>1.0546500000000001E-3</v>
       </c>
@@ -2670,7 +2612,7 @@
       <c r="J13" s="12">
         <v>0.48910588160000001</v>
       </c>
-      <c r="K13" s="27"/>
+      <c r="K13" s="58"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2679,9 +2621,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
       <c r="F14" s="12">
         <v>2.876318E-4</v>
       </c>
@@ -2697,7 +2639,7 @@
       <c r="J14" s="12">
         <v>0.46995530219999998</v>
       </c>
-      <c r="K14" s="27"/>
+      <c r="K14" s="58"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G15" s="12"/>
@@ -2712,13 +2654,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="23" t="s">
+      <c r="E16" s="56" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="12">
@@ -2736,7 +2678,7 @@
       <c r="J16" s="12">
         <v>0.44493382850000002</v>
       </c>
-      <c r="K16" s="27" t="s">
+      <c r="K16" s="58" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2747,10 +2689,10 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="28">
+      <c r="C17" s="60"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="20">
         <v>8.2166826499999998E-2</v>
       </c>
       <c r="G17" s="12">
@@ -2765,7 +2707,7 @@
       <c r="J17" s="12">
         <v>0.4417925586</v>
       </c>
-      <c r="K17" s="27"/>
+      <c r="K17" s="58"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -2774,9 +2716,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
       <c r="F18" s="12">
         <v>7.6701820000000002E-4</v>
       </c>
@@ -2792,7 +2734,7 @@
       <c r="J18" s="12">
         <v>0.47127738250000001</v>
       </c>
-      <c r="K18" s="27"/>
+      <c r="K18" s="58"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G19" s="12"/>
@@ -2807,13 +2749,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="56" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="12">
@@ -2831,7 +2773,7 @@
       <c r="J20" s="12">
         <v>0.42862661320000001</v>
       </c>
-      <c r="K20" s="27" t="s">
+      <c r="K20" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2842,9 +2784,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
       <c r="F21" s="12">
         <v>3.2598274E-3</v>
       </c>
@@ -2860,7 +2802,7 @@
       <c r="J21" s="12">
         <v>0.4742471747</v>
       </c>
-      <c r="K21" s="27"/>
+      <c r="K21" s="58"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -2869,9 +2811,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
       <c r="F22" s="12">
         <v>0</v>
       </c>
@@ -2887,7 +2829,7 @@
       <c r="J22" s="12">
         <v>0.4477544779</v>
       </c>
-      <c r="K22" s="27"/>
+      <c r="K22" s="58"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G23" s="12"/>
@@ -2902,13 +2844,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="56" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="12">
@@ -2934,9 +2876,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
       <c r="F25" s="12">
         <v>6.8744007699999998E-2</v>
       </c>
@@ -2960,9 +2902,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
       <c r="F26" s="12">
         <v>2.876318E-4</v>
       </c>
@@ -2990,13 +2932,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="C28" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="56" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="12">
@@ -3022,9 +2964,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="21"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
       <c r="F29" s="12">
         <v>2.9721956000000002E-3</v>
       </c>
@@ -3048,9 +2990,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="21"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
       <c r="F30" s="12">
         <v>0</v>
       </c>
@@ -3080,25 +3022,25 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="E32" s="56" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="12">
         <v>2.6558005799999999E-2</v>
       </c>
-      <c r="G32" s="28">
+      <c r="G32" s="20">
         <v>7.9290508100000004E-2</v>
       </c>
       <c r="H32" s="12">
         <v>0.42742090119999998</v>
       </c>
-      <c r="I32" s="28">
+      <c r="I32" s="20">
         <v>0.89827844270000001</v>
       </c>
       <c r="J32" s="12">
@@ -3112,9 +3054,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
+      <c r="C33" s="60"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
       <c r="F33" s="12">
         <v>6.2032598299999998E-2</v>
       </c>
@@ -3138,16 +3080,16 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="21"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
       <c r="F34" s="12">
         <v>5.7526370000000003E-4</v>
       </c>
       <c r="G34" s="12">
         <v>1.1505273E-3</v>
       </c>
-      <c r="H34" s="28">
+      <c r="H34" s="20">
         <v>0.6839884947</v>
       </c>
       <c r="I34" s="12">
@@ -3170,13 +3112,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="C36" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="23" t="s">
+      <c r="D36" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="23" t="s">
+      <c r="E36" s="56" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="12">
@@ -3202,9 +3144,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="21"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
+      <c r="C37" s="60"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
       <c r="F37" s="12">
         <v>6.1361456999999998E-3</v>
       </c>
@@ -3228,9 +3170,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
       <c r="F38" s="12">
         <v>1.917546E-4</v>
       </c>
@@ -3254,12 +3196,12 @@
       <c r="J39" s="12"/>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
+      <c r="B40" s="61"/>
+      <c r="C40" s="61"/>
+      <c r="D40" s="61"/>
       <c r="E40" s="5"/>
       <c r="F40" s="14"/>
       <c r="G40" s="14"/>
@@ -3281,13 +3223,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="21" t="s">
+      <c r="C42" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="23" t="s">
+      <c r="D42" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="23" t="s">
+      <c r="E42" s="56" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="12">
@@ -3305,7 +3247,7 @@
       <c r="J42" s="12">
         <v>0.46282180270000001</v>
       </c>
-      <c r="K42" s="27" t="s">
+      <c r="K42" s="58" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3316,9 +3258,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="21"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
+      <c r="C43" s="60"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="56"/>
       <c r="F43" s="12">
         <v>1.18796704E-2</v>
       </c>
@@ -3334,7 +3276,7 @@
       <c r="J43" s="12">
         <v>0.45564674030000002</v>
       </c>
-      <c r="K43" s="27"/>
+      <c r="K43" s="58"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -3343,9 +3285,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="21"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
+      <c r="C44" s="60"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
       <c r="F44" s="12">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -3359,7 +3301,7 @@
       <c r="J44" s="12">
         <v>0.47630425310000002</v>
       </c>
-      <c r="K44" s="27"/>
+      <c r="K44" s="58"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G45" s="12"/>
@@ -3374,13 +3316,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="21" t="s">
+      <c r="C46" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="23" t="s">
+      <c r="D46" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="23" t="s">
+      <c r="E46" s="56" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="12">
@@ -3398,7 +3340,7 @@
       <c r="J46" s="12">
         <v>0.44950493489999999</v>
       </c>
-      <c r="K46" s="27" t="s">
+      <c r="K46" s="58" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3409,9 +3351,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="21"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="23"/>
+      <c r="C47" s="60"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="56"/>
       <c r="F47" s="12">
         <v>2.2322284000000001E-2</v>
       </c>
@@ -3427,7 +3369,7 @@
       <c r="J47" s="12">
         <v>0.45333713520000002</v>
       </c>
-      <c r="K47" s="27"/>
+      <c r="K47" s="58"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -3436,9 +3378,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="21"/>
-      <c r="D48" s="23"/>
-      <c r="E48" s="23"/>
+      <c r="C48" s="60"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="56"/>
       <c r="F48" s="12">
         <v>4.7901900000000002E-4</v>
       </c>
@@ -3454,7 +3396,7 @@
       <c r="J48" s="12">
         <v>0.47522234359999999</v>
       </c>
-      <c r="K48" s="27"/>
+      <c r="K48" s="58"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
       <c r="G49" s="12"/>
@@ -3469,13 +3411,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="21" t="s">
+      <c r="C50" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="23" t="s">
+      <c r="D50" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="23" t="s">
+      <c r="E50" s="56" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="12">
@@ -3501,9 +3443,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="21"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
+      <c r="C51" s="60"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
       <c r="F51" s="12">
         <v>5.7482279999999995E-4</v>
       </c>
@@ -3527,9 +3469,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="21"/>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
+      <c r="C52" s="60"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="56"/>
       <c r="F52" s="12">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -3556,164 +3498,137 @@
       <c r="I54" s="12"/>
       <c r="J54" s="12"/>
     </row>
-    <row r="55" spans="1:14" s="60" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="56" t="s">
+    <row r="55" spans="1:14" s="45" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="56"/>
-      <c r="C55" s="56"/>
-      <c r="D55" s="56"/>
-      <c r="E55" s="57"/>
-      <c r="F55" s="58">
+      <c r="B55" s="63"/>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="42"/>
+      <c r="F55" s="43">
         <f>MAX(F2:F52)</f>
         <v>8.2166826499999998E-2</v>
       </c>
-      <c r="G55" s="58">
+      <c r="G55" s="43">
         <f>MAX(G2:G52)</f>
         <v>7.9290508100000004E-2</v>
       </c>
-      <c r="H55" s="58">
+      <c r="H55" s="43">
         <f>MAX(H2:H52)</f>
         <v>0.6839884947</v>
       </c>
-      <c r="I55" s="58">
+      <c r="I55" s="43">
         <f>MAX(I2:I52)</f>
         <v>0.89827844270000001</v>
       </c>
-      <c r="J55" s="58">
+      <c r="J55" s="43">
         <f>MAX(J2:J52)</f>
         <v>0.51222158829999997</v>
       </c>
-      <c r="K55" s="59"/>
-    </row>
-    <row r="56" spans="1:14" s="65" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="61" t="s">
+      <c r="K55" s="44"/>
+    </row>
+    <row r="56" spans="1:14" s="49" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="55" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="61"/>
-      <c r="C56" s="61"/>
-      <c r="D56" s="61"/>
-      <c r="E56" s="62"/>
-      <c r="F56" s="63">
+      <c r="B56" s="55"/>
+      <c r="C56" s="55"/>
+      <c r="D56" s="55"/>
+      <c r="E56" s="46"/>
+      <c r="F56" s="47">
         <f>AVERAGE(F2:F52)</f>
         <v>2.4235782825E-2</v>
       </c>
-      <c r="G56" s="63">
+      <c r="G56" s="47">
         <f>AVERAGE(G2:G52)</f>
         <v>6.0500254111111127E-3</v>
       </c>
-      <c r="H56" s="63">
+      <c r="H56" s="47">
         <f>AVERAGE(H2:H52)</f>
         <v>0.32527986028484845</v>
       </c>
-      <c r="I56" s="63">
+      <c r="I56" s="47">
         <f>AVERAGE(I2:I52)</f>
         <v>0.63155286615000006</v>
       </c>
-      <c r="J56" s="63">
+      <c r="J56" s="47">
         <f>AVERAGE(J2:J52)</f>
         <v>0.45647798735000017</v>
       </c>
-      <c r="K56" s="64"/>
-    </row>
-    <row r="58" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="37" t="s">
+      <c r="K56" s="48"/>
+    </row>
+    <row r="58" spans="1:14" s="25" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="B58" s="37"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="43">
+      <c r="B58" s="64"/>
+      <c r="C58" s="64"/>
+      <c r="D58" s="64"/>
+      <c r="E58" s="64"/>
+      <c r="F58" s="32">
         <f>SUM(F55*(1/3),  G55*(1/3), I55*(1/3))</f>
         <v>0.35324525909999999</v>
       </c>
-      <c r="G58" s="35"/>
-      <c r="H58" s="35"/>
-      <c r="I58" s="35"/>
-      <c r="J58" s="35"/>
-      <c r="K58" s="35"/>
-      <c r="L58" s="35"/>
-      <c r="M58" s="35"/>
-      <c r="N58" s="36"/>
-    </row>
-    <row r="59" spans="1:14" s="41" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="38" t="s">
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="26"/>
+      <c r="J58" s="26"/>
+      <c r="K58" s="26"/>
+      <c r="L58" s="26"/>
+      <c r="M58" s="26"/>
+      <c r="N58" s="27"/>
+    </row>
+    <row r="59" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="B59" s="38"/>
-      <c r="C59" s="38"/>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38"/>
-      <c r="F59" s="42">
+      <c r="B59" s="65"/>
+      <c r="C59" s="65"/>
+      <c r="D59" s="65"/>
+      <c r="E59" s="65"/>
+      <c r="F59" s="31">
         <f>SUM(H55*(1/2),  J55*(1/2))</f>
         <v>0.59810504149999999</v>
       </c>
-      <c r="G59" s="39"/>
-      <c r="H59" s="39"/>
-      <c r="I59" s="39"/>
-      <c r="J59" s="39"/>
-      <c r="K59" s="39"/>
-      <c r="L59" s="39"/>
-      <c r="M59" s="39"/>
-      <c r="N59" s="40"/>
-    </row>
-    <row r="60" spans="1:14" s="48" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="44" t="s">
+      <c r="G59" s="28"/>
+      <c r="H59" s="28"/>
+      <c r="I59" s="28"/>
+      <c r="J59" s="28"/>
+      <c r="K59" s="28"/>
+      <c r="L59" s="28"/>
+      <c r="M59" s="28"/>
+      <c r="N59" s="29"/>
+    </row>
+    <row r="60" spans="1:14" s="36" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="B60" s="44"/>
-      <c r="C60" s="44"/>
-      <c r="D60" s="44"/>
-      <c r="E60" s="44"/>
-      <c r="F60" s="45">
+      <c r="B60" s="66"/>
+      <c r="C60" s="66"/>
+      <c r="D60" s="66"/>
+      <c r="E60" s="66"/>
+      <c r="F60" s="33">
         <f>SUM(F55*1/5, G55*1/5, H55*1/5, I55*1/5,J55*1/5)</f>
         <v>0.45118917206000003</v>
       </c>
-      <c r="G60" s="46"/>
-      <c r="H60" s="46"/>
-      <c r="I60" s="46"/>
-      <c r="J60" s="46"/>
-      <c r="K60" s="46"/>
-      <c r="L60" s="46"/>
-      <c r="M60" s="46"/>
-      <c r="N60" s="47"/>
+      <c r="G60" s="34"/>
+      <c r="H60" s="34"/>
+      <c r="I60" s="34"/>
+      <c r="J60" s="34"/>
+      <c r="K60" s="34"/>
+      <c r="L60" s="34"/>
+      <c r="M60" s="34"/>
+      <c r="N60" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="50">
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="E28:E30"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="K46:K48"/>
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D50:D52"/>
@@ -3725,12 +3640,39 @@
     <mergeCell ref="C42:C44"/>
     <mergeCell ref="D42:D44"/>
     <mergeCell ref="E42:E44"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="E28:E30"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="D32:D34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3811,16 +3753,16 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="62" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="22" t="s">
+      <c r="D2" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="22" t="s">
+      <c r="E2" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="20">
         <v>9.1179290499999996E-2</v>
       </c>
       <c r="G2" s="12">
@@ -3847,7 +3789,7 @@
         <f>SUM(F2*1/5,G2*1/5,H2*1/5,I2*1/5,J2*1/5)</f>
         <v>0.28479454145999999</v>
       </c>
-      <c r="N2" s="26" t="s">
+      <c r="N2" s="57" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3858,9 +3800,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
+      <c r="C3" s="60"/>
+      <c r="D3" s="56"/>
+      <c r="E3" s="56"/>
       <c r="F3" s="12">
         <v>8.3029722E-2</v>
       </c>
@@ -3888,7 +3830,7 @@
         <f>SUM(F3*1/5,G3*1/5,H3*1/5,I3*1/5,J3*1/5)</f>
         <v>0.24688138529999998</v>
       </c>
-      <c r="N3" s="27"/>
+      <c r="N3" s="58"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3897,9 +3839,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
+      <c r="C4" s="60"/>
+      <c r="D4" s="56"/>
+      <c r="E4" s="56"/>
       <c r="F4" s="12">
         <v>2.2051773699999999E-2</v>
       </c>
@@ -3927,7 +3869,7 @@
         <f>SUM(F4*1/5,G4*1/5,H4*1/5,I4*1/5,J4*1/5)</f>
         <v>0.24577994555999999</v>
       </c>
-      <c r="N4" s="27"/>
+      <c r="N4" s="58"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -3936,13 +3878,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="21" t="s">
+      <c r="C6" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="56" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="56" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="12">
@@ -3972,7 +3914,7 @@
         <f>SUM(F6*1/5,G6*1/5,H6*1/5,I6*1/5,J6*1/5)</f>
         <v>0.21462878724000001</v>
       </c>
-      <c r="N6" s="27" t="s">
+      <c r="N6" s="58" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3983,9 +3925,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
+      <c r="C7" s="60"/>
+      <c r="D7" s="56"/>
+      <c r="E7" s="56"/>
       <c r="F7" s="12">
         <v>4.4165548999999998E-2</v>
       </c>
@@ -4013,7 +3955,7 @@
         <f>SUM(F7*1/5,G7*1/5,H7*1/5,I7*1/5,J7*1/5)</f>
         <v>0.27318294232000001</v>
       </c>
-      <c r="N7" s="27"/>
+      <c r="N7" s="58"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -4022,9 +3964,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="21"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="56"/>
+      <c r="E8" s="56"/>
       <c r="F8" s="12">
         <v>3.7171872000000002E-2</v>
       </c>
@@ -4052,15 +3994,15 @@
         <f>SUM(F8*1/5,G8*1/5,H8*1/5,I8*1/5,J8*1/5)</f>
         <v>0.26231643128000004</v>
       </c>
-      <c r="N8" s="27"/>
+      <c r="N8" s="58"/>
     </row>
     <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="61" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="24"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
+      <c r="B10" s="61"/>
+      <c r="C10" s="61"/>
+      <c r="D10" s="61"/>
       <c r="E10" s="5"/>
       <c r="F10" s="14"/>
       <c r="G10" s="14"/>
@@ -4079,13 +4021,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="60" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="56" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="12">
@@ -4100,7 +4042,7 @@
       <c r="I12" s="12">
         <v>0.55940591579999999</v>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="20">
         <v>0.51830085319999997</v>
       </c>
       <c r="K12" s="12">
@@ -4115,7 +4057,7 @@
         <f>SUM(F12*1/5,G12*1/5,H12*1/5,I12*1/5,J12*1/5)</f>
         <v>0.32808210163999996</v>
       </c>
-      <c r="N12" s="27" t="s">
+      <c r="N12" s="58" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4126,9 +4068,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="21"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
+      <c r="C13" s="60"/>
+      <c r="D13" s="56"/>
+      <c r="E13" s="56"/>
       <c r="F13" s="12">
         <v>4.8897411E-3</v>
       </c>
@@ -4156,7 +4098,7 @@
         <f>SUM(F13*1/5,G13*1/5,H13*1/5,I13*1/5,J13*1/5)</f>
         <v>0.25619948824</v>
       </c>
-      <c r="N13" s="27"/>
+      <c r="N13" s="58"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -4165,9 +4107,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="21"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="56"/>
+      <c r="E14" s="56"/>
       <c r="F14" s="12">
         <v>1.917546E-4</v>
       </c>
@@ -4195,7 +4137,7 @@
         <f>SUM(F14*1/5,G14*1/5,H14*1/5,I14*1/5,J14*1/5)</f>
         <v>0.20013002629999999</v>
       </c>
-      <c r="N14" s="27"/>
+      <c r="N14" s="58"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -4204,13 +4146,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="60" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="D16" s="56" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="23" t="s">
+      <c r="E16" s="56" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="12">
@@ -4240,7 +4182,7 @@
         <f>SUM(F16*1/5,G16*1/5,H16*1/5,I16*1/5,J16*1/5)</f>
         <v>0.34520352803999999</v>
       </c>
-      <c r="N16" s="27" t="s">
+      <c r="N16" s="58" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4251,9 +4193,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="21"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
+      <c r="C17" s="60"/>
+      <c r="D17" s="56"/>
+      <c r="E17" s="56"/>
       <c r="F17" s="12">
         <v>2.85714286E-2</v>
       </c>
@@ -4281,7 +4223,7 @@
         <f>SUM(F17*1/5,G17*1/5,H17*1/5,I17*1/5,J17*1/5)</f>
         <v>0.33728800162</v>
       </c>
-      <c r="N17" s="27"/>
+      <c r="N17" s="58"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -4290,16 +4232,16 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
+      <c r="C18" s="60"/>
+      <c r="D18" s="56"/>
+      <c r="E18" s="56"/>
       <c r="F18" s="12">
         <v>3.8350910000000001E-4</v>
       </c>
       <c r="G18" s="12">
         <v>1.3422817999999999E-3</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="20">
         <v>0.79022051770000001</v>
       </c>
       <c r="I18" s="12">
@@ -4312,7 +4254,7 @@
         <f>SUM(F18*1/3,G18*1/3,I18*1/3)</f>
         <v>0.16645651323333333</v>
       </c>
-      <c r="L18" s="28">
+      <c r="L18" s="20">
         <f>SUM(H18*1/2,J18*1/2)</f>
         <v>0.63882297315000003</v>
       </c>
@@ -4320,7 +4262,7 @@
         <f>SUM(F18*1/5,G18*1/5,H18*1/5,I18*1/5,J18*1/5)</f>
         <v>0.35540309720000007</v>
       </c>
-      <c r="N18" s="27"/>
+      <c r="N18" s="58"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -4329,13 +4271,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="60" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="23" t="s">
+      <c r="D20" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="23" t="s">
+      <c r="E20" s="56" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="12">
@@ -4365,7 +4307,7 @@
         <f>SUM(F20*1/5,G20*1/5,H20*1/5,I20*1/5,J20*1/5)</f>
         <v>0.33023019046000002</v>
       </c>
-      <c r="N20" s="27" t="s">
+      <c r="N20" s="58" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4376,9 +4318,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="21"/>
-      <c r="D21" s="23"/>
-      <c r="E21" s="23"/>
+      <c r="C21" s="60"/>
+      <c r="D21" s="56"/>
+      <c r="E21" s="56"/>
       <c r="F21" s="12">
         <v>8.59060403E-2</v>
       </c>
@@ -4402,11 +4344,11 @@
         <f>SUM(H21*1/2,J21*1/2)</f>
         <v>0.51470307525000003</v>
       </c>
-      <c r="M21" s="28">
+      <c r="M21" s="20">
         <f>SUM(F21*1/5,G21*1/5,H21*1/5,I21*1/5,J21*1/5)</f>
         <v>0.39507478221999998</v>
       </c>
-      <c r="N21" s="27"/>
+      <c r="N21" s="58"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -4415,9 +4357,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="23"/>
-      <c r="E22" s="23"/>
+      <c r="C22" s="60"/>
+      <c r="D22" s="56"/>
+      <c r="E22" s="56"/>
       <c r="F22" s="12">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4445,7 +4387,7 @@
         <f>SUM(F22*1/5,G22*1/5,H22*1/5,I22*1/5,J22*1/5)</f>
         <v>0.29192671981999996</v>
       </c>
-      <c r="N22" s="27"/>
+      <c r="N22" s="58"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -4454,13 +4396,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="60" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="23" t="s">
+      <c r="D24" s="56" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="23" t="s">
+      <c r="E24" s="56" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="12">
@@ -4498,9 +4440,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="21"/>
-      <c r="D25" s="23"/>
-      <c r="E25" s="23"/>
+      <c r="C25" s="60"/>
+      <c r="D25" s="56"/>
+      <c r="E25" s="56"/>
       <c r="F25" s="12">
         <v>1.04506232E-2</v>
       </c>
@@ -4536,9 +4478,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="21"/>
-      <c r="D26" s="23"/>
-      <c r="E26" s="23"/>
+      <c r="C26" s="60"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
       <c r="F26" s="12">
         <v>2.876318E-4</v>
       </c>
@@ -4574,13 +4516,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="C28" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="56" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="56" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="12">
@@ -4618,9 +4560,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="21"/>
-      <c r="D29" s="23"/>
-      <c r="E29" s="23"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="56"/>
+      <c r="E29" s="56"/>
       <c r="F29" s="12">
         <v>5.7526366000000004E-3</v>
       </c>
@@ -4656,9 +4598,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="21"/>
-      <c r="D30" s="23"/>
-      <c r="E30" s="23"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="56"/>
+      <c r="E30" s="56"/>
       <c r="F30" s="12">
         <v>9.5877299999999998E-5</v>
       </c>
@@ -4694,13 +4636,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="23" t="s">
+      <c r="D32" s="56" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="23" t="s">
+      <c r="E32" s="56" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="12">
@@ -4738,9 +4680,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="21"/>
-      <c r="D33" s="23"/>
-      <c r="E33" s="23"/>
+      <c r="C33" s="60"/>
+      <c r="D33" s="56"/>
+      <c r="E33" s="56"/>
       <c r="F33" s="12">
         <v>7.6701821700000006E-2</v>
       </c>
@@ -4750,13 +4692,13 @@
       <c r="H33" s="12">
         <v>0.4302972196</v>
       </c>
-      <c r="I33" s="28">
+      <c r="I33" s="20">
         <v>0.90418992629999995</v>
       </c>
       <c r="J33" s="12">
         <v>0.3758758888</v>
       </c>
-      <c r="K33" s="28">
+      <c r="K33" s="20">
         <f>SUM(F33*1/3,G33*1/3,I33*1/3)</f>
         <v>0.328689707</v>
       </c>
@@ -4776,9 +4718,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="21"/>
-      <c r="D34" s="23"/>
-      <c r="E34" s="23"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="56"/>
+      <c r="E34" s="56"/>
       <c r="F34" s="12">
         <v>1.917546E-4</v>
       </c>
@@ -4814,13 +4756,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="C36" s="60" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="23" t="s">
+      <c r="D36" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="23" t="s">
+      <c r="E36" s="56" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="12">
@@ -4858,9 +4800,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="21"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
+      <c r="C37" s="60"/>
+      <c r="D37" s="56"/>
+      <c r="E37" s="56"/>
       <c r="F37" s="12">
         <v>1.0546500000000001E-3</v>
       </c>
@@ -4896,9 +4838,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="21"/>
-      <c r="D38" s="23"/>
-      <c r="E38" s="23"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="56"/>
       <c r="F38" s="12">
         <v>1.917546E-4</v>
       </c>
@@ -4928,12 +4870,12 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="24" t="s">
+      <c r="A40" s="61" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="24"/>
-      <c r="C40" s="24"/>
-      <c r="D40" s="24"/>
+      <c r="B40" s="61"/>
+      <c r="C40" s="61"/>
+      <c r="D40" s="61"/>
       <c r="E40" s="5"/>
       <c r="F40" s="14"/>
       <c r="G40" s="14"/>
@@ -4952,13 +4894,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="21" t="s">
+      <c r="C42" s="60" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="23" t="s">
+      <c r="D42" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="23" t="s">
+      <c r="E42" s="56" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="12">
@@ -4988,7 +4930,7 @@
         <f>SUM(F42*1/5,G42*1/5,H42*1/5,I42*1/5,J42*1/5)</f>
         <v>0.31386758548000004</v>
       </c>
-      <c r="N42" s="27" t="s">
+      <c r="N42" s="58" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4999,9 +4941,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="21"/>
-      <c r="D43" s="23"/>
-      <c r="E43" s="23"/>
+      <c r="C43" s="60"/>
+      <c r="D43" s="56"/>
+      <c r="E43" s="56"/>
       <c r="F43" s="12">
         <v>2.93159609E-2</v>
       </c>
@@ -5029,7 +4971,7 @@
         <f>SUM(F43*1/5,G43*1/5,H43*1/5,I43*1/5,J43*1/5)</f>
         <v>0.29226255760000003</v>
       </c>
-      <c r="N43" s="27"/>
+      <c r="N43" s="58"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -5038,9 +4980,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="21"/>
-      <c r="D44" s="23"/>
-      <c r="E44" s="23"/>
+      <c r="C44" s="60"/>
+      <c r="D44" s="56"/>
+      <c r="E44" s="56"/>
       <c r="F44" s="15">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -5068,7 +5010,7 @@
         <f>SUM(F44*1/5,G44*1/5,H44*1/5,I44*1/5,J44*1/5)</f>
         <v>0.34257018057999999</v>
       </c>
-      <c r="N44" s="27"/>
+      <c r="N44" s="58"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -5077,19 +5019,19 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="21" t="s">
+      <c r="C46" s="60" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="23" t="s">
+      <c r="D46" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="23" t="s">
+      <c r="E46" s="56" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="12">
         <v>6.1027016699999999E-2</v>
       </c>
-      <c r="G46" s="28">
+      <c r="G46" s="20">
         <v>1.2550297E-2</v>
       </c>
       <c r="H46" s="12">
@@ -5113,7 +5055,7 @@
         <f>SUM(F46*1/5,G46*1/5,H46*1/5,I46*1/5,J46*1/5)</f>
         <v>0.31043419121999999</v>
       </c>
-      <c r="N46" s="27" t="s">
+      <c r="N46" s="58" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5124,9 +5066,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="21"/>
-      <c r="D47" s="23"/>
-      <c r="E47" s="23"/>
+      <c r="C47" s="60"/>
+      <c r="D47" s="56"/>
+      <c r="E47" s="56"/>
       <c r="F47" s="12">
         <v>5.5853611800000001E-2</v>
       </c>
@@ -5154,7 +5096,7 @@
         <f>SUM(F47*1/5,G47*1/5,H47*1/5,I47*1/5,J47*1/5)</f>
         <v>0.38566402880000006</v>
       </c>
-      <c r="N47" s="27"/>
+      <c r="N47" s="58"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -5163,9 +5105,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="21"/>
-      <c r="D48" s="23"/>
-      <c r="E48" s="23"/>
+      <c r="C48" s="60"/>
+      <c r="D48" s="56"/>
+      <c r="E48" s="56"/>
       <c r="F48" s="12">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -5193,7 +5135,7 @@
         <f>SUM(F48*1/5,G48*1/5,H48*1/5,I48*1/5,J48*1/5)</f>
         <v>0.26614251024000002</v>
       </c>
-      <c r="N48" s="27"/>
+      <c r="N48" s="58"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -5202,13 +5144,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="21" t="s">
+      <c r="C50" s="60" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="23" t="s">
+      <c r="D50" s="56" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="23" t="s">
+      <c r="E50" s="56" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="12">
@@ -5246,9 +5188,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="21"/>
-      <c r="D51" s="23"/>
-      <c r="E51" s="23"/>
+      <c r="C51" s="60"/>
+      <c r="D51" s="56"/>
+      <c r="E51" s="56"/>
       <c r="F51" s="12">
         <v>4.4452960299999997E-2</v>
       </c>
@@ -5284,9 +5226,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="21"/>
-      <c r="D52" s="23"/>
-      <c r="E52" s="23"/>
+      <c r="C52" s="60"/>
+      <c r="D52" s="56"/>
+      <c r="E52" s="56"/>
       <c r="F52" s="15">
         <v>0</v>
       </c>
@@ -5316,227 +5258,222 @@
       </c>
     </row>
     <row r="55" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="20" t="s">
+      <c r="A55" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="20"/>
-      <c r="C55" s="20"/>
-      <c r="D55" s="20"/>
+      <c r="B55" s="70"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
       <c r="E55" s="17"/>
       <c r="F55" s="18">
-        <f>MAX(F2:F52)</f>
+        <f t="shared" ref="F55:M55" si="0">MAX(F2:F52)</f>
         <v>9.1179290499999996E-2</v>
       </c>
       <c r="G55" s="18">
-        <f>MAX(G2:G52)</f>
+        <f t="shared" si="0"/>
         <v>1.2550297E-2</v>
       </c>
       <c r="H55" s="18">
-        <f>MAX(H2:H52)</f>
+        <f t="shared" si="0"/>
         <v>0.79022051770000001</v>
       </c>
       <c r="I55" s="18">
-        <f>MAX(I2:I52)</f>
+        <f t="shared" si="0"/>
         <v>0.90418992629999995</v>
       </c>
       <c r="J55" s="18">
-        <f>MAX(J2:J52)</f>
+        <f t="shared" si="0"/>
         <v>0.51830085319999997</v>
       </c>
       <c r="K55" s="18">
-        <f>MAX(K2:K52)</f>
+        <f t="shared" si="0"/>
         <v>0.328689707</v>
       </c>
       <c r="L55" s="18">
-        <f>MAX(L2:L52)</f>
+        <f t="shared" si="0"/>
         <v>0.63882297315000003</v>
       </c>
       <c r="M55" s="18">
-        <f>MAX(M2:M52)</f>
+        <f t="shared" si="0"/>
         <v>0.39507478221999998</v>
       </c>
       <c r="N55" s="19"/>
     </row>
-    <row r="56" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="30" t="s">
+    <row r="56" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="69" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="30"/>
-      <c r="C56" s="30"/>
-      <c r="D56" s="30"/>
-      <c r="E56" s="31"/>
-      <c r="F56" s="32">
-        <f>AVERAGE(F2:F52)</f>
+      <c r="B56" s="69"/>
+      <c r="C56" s="69"/>
+      <c r="D56" s="69"/>
+      <c r="E56" s="22"/>
+      <c r="F56" s="23">
+        <f t="shared" ref="F56:M56" si="1">AVERAGE(F2:F52)</f>
         <v>3.2159416908333328E-2</v>
       </c>
-      <c r="G56" s="32">
-        <f>AVERAGE(G2:G52)</f>
+      <c r="G56" s="23">
+        <f t="shared" si="1"/>
         <v>3.0273973416666666E-3</v>
       </c>
-      <c r="H56" s="32">
-        <f>AVERAGE(H2:H52)</f>
+      <c r="H56" s="23">
+        <f t="shared" si="1"/>
         <v>0.37973669030833329</v>
       </c>
-      <c r="I56" s="32">
-        <f>AVERAGE(I2:I52)</f>
+      <c r="I56" s="23">
+        <f t="shared" si="1"/>
         <v>0.61381284023055549</v>
       </c>
-      <c r="J56" s="32">
-        <f>AVERAGE(J2:J52)</f>
+      <c r="J56" s="23">
+        <f t="shared" si="1"/>
         <v>0.45620981558055551</v>
       </c>
-      <c r="K56" s="32">
-        <f>AVERAGE(K2:K52)</f>
+      <c r="K56" s="23">
+        <f t="shared" si="1"/>
         <v>0.21633321816018516</v>
       </c>
-      <c r="L56" s="32">
-        <f>AVERAGE(L2:L52)</f>
+      <c r="L56" s="23">
+        <f t="shared" si="1"/>
         <v>0.41797325294444426</v>
       </c>
-      <c r="M56" s="32">
-        <f>AVERAGE(M2:M52)</f>
+      <c r="M56" s="23">
+        <f t="shared" si="1"/>
         <v>0.296989232073889</v>
       </c>
-      <c r="N56" s="33"/>
-    </row>
-    <row r="58" spans="1:14" s="34" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="37" t="s">
+      <c r="N56" s="24"/>
+    </row>
+    <row r="58" spans="1:14" s="25" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="64" t="s">
         <v>68</v>
       </c>
-      <c r="B58" s="37"/>
-      <c r="C58" s="37"/>
-      <c r="D58" s="37"/>
-      <c r="E58" s="37"/>
-      <c r="F58" s="43">
+      <c r="B58" s="64"/>
+      <c r="C58" s="64"/>
+      <c r="D58" s="64"/>
+      <c r="E58" s="64"/>
+      <c r="F58" s="32">
         <f>SUM(F55*(1/3),  G55*(1/3), I55*(1/3))</f>
         <v>0.33597317126666659</v>
       </c>
-      <c r="G58" s="35"/>
-      <c r="H58" s="35"/>
-      <c r="I58" s="35"/>
-      <c r="J58" s="35"/>
-      <c r="K58" s="35"/>
-      <c r="L58" s="35"/>
-      <c r="M58" s="35"/>
-      <c r="N58" s="36"/>
-    </row>
-    <row r="59" spans="1:14" s="41" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="38" t="s">
+      <c r="G58" s="26"/>
+      <c r="H58" s="26"/>
+      <c r="I58" s="26"/>
+      <c r="J58" s="26"/>
+      <c r="K58" s="26"/>
+      <c r="L58" s="26"/>
+      <c r="M58" s="26"/>
+      <c r="N58" s="27"/>
+    </row>
+    <row r="59" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="65" t="s">
         <v>69</v>
       </c>
-      <c r="B59" s="38"/>
-      <c r="C59" s="38"/>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38"/>
-      <c r="F59" s="42">
+      <c r="B59" s="65"/>
+      <c r="C59" s="65"/>
+      <c r="D59" s="65"/>
+      <c r="E59" s="65"/>
+      <c r="F59" s="31">
         <f>SUM(H55*(1/2),  J55*(1/2))</f>
         <v>0.65426068544999993</v>
       </c>
-      <c r="G59" s="39"/>
-      <c r="H59" s="39"/>
-      <c r="I59" s="39"/>
-      <c r="J59" s="39"/>
-      <c r="K59" s="39"/>
-      <c r="L59" s="39"/>
-      <c r="M59" s="39"/>
-      <c r="N59" s="40"/>
-    </row>
-    <row r="60" spans="1:14" s="48" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="44" t="s">
+      <c r="G59" s="28"/>
+      <c r="H59" s="28"/>
+      <c r="I59" s="28"/>
+      <c r="J59" s="28"/>
+      <c r="K59" s="28"/>
+      <c r="L59" s="28"/>
+      <c r="M59" s="28"/>
+      <c r="N59" s="29"/>
+    </row>
+    <row r="60" spans="1:14" s="36" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="66" t="s">
         <v>70</v>
       </c>
-      <c r="B60" s="44"/>
-      <c r="C60" s="44"/>
-      <c r="D60" s="44"/>
-      <c r="E60" s="44"/>
-      <c r="F60" s="45">
+      <c r="B60" s="66"/>
+      <c r="C60" s="66"/>
+      <c r="D60" s="66"/>
+      <c r="E60" s="66"/>
+      <c r="F60" s="33">
         <f>SUM(F55*1/5, G55*1/5, H55*1/5, I55*1/5,J55*1/5)</f>
         <v>0.46328817694000002</v>
       </c>
-      <c r="G60" s="46"/>
-      <c r="H60" s="46"/>
-      <c r="I60" s="46"/>
-      <c r="J60" s="46"/>
-      <c r="K60" s="46"/>
-      <c r="L60" s="46"/>
-      <c r="M60" s="46"/>
-      <c r="N60" s="47"/>
-    </row>
-    <row r="62" spans="1:14" s="53" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="49" t="s">
+      <c r="G60" s="34"/>
+      <c r="H60" s="34"/>
+      <c r="I60" s="34"/>
+      <c r="J60" s="34"/>
+      <c r="K60" s="34"/>
+      <c r="L60" s="34"/>
+      <c r="M60" s="34"/>
+      <c r="N60" s="35"/>
+    </row>
+    <row r="62" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="67" t="s">
         <v>65</v>
       </c>
-      <c r="B62" s="49"/>
-      <c r="C62" s="49"/>
-      <c r="D62" s="49"/>
-      <c r="E62" s="50"/>
-      <c r="F62" s="51"/>
-      <c r="G62" s="51"/>
-      <c r="H62" s="51"/>
-      <c r="I62" s="51"/>
-      <c r="J62" s="51"/>
-      <c r="K62" s="51"/>
-      <c r="L62" s="51"/>
-      <c r="M62" s="51"/>
-      <c r="N62" s="52"/>
-    </row>
-    <row r="63" spans="1:14" s="53" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="49" t="s">
+      <c r="B62" s="67"/>
+      <c r="C62" s="67"/>
+      <c r="D62" s="67"/>
+      <c r="E62" s="37"/>
+      <c r="F62" s="38"/>
+      <c r="G62" s="38"/>
+      <c r="H62" s="38"/>
+      <c r="I62" s="38"/>
+      <c r="J62" s="38"/>
+      <c r="K62" s="38"/>
+      <c r="L62" s="38"/>
+      <c r="M62" s="38"/>
+      <c r="N62" s="39"/>
+    </row>
+    <row r="63" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="B63" s="54"/>
-      <c r="C63" s="54"/>
-      <c r="D63" s="54"/>
-      <c r="E63" s="55"/>
-      <c r="F63" s="51"/>
-      <c r="G63" s="51"/>
-      <c r="H63" s="51"/>
-      <c r="I63" s="51"/>
-      <c r="J63" s="51"/>
-      <c r="K63" s="51"/>
-      <c r="L63" s="51"/>
-      <c r="M63" s="51"/>
-      <c r="N63" s="52"/>
-    </row>
-    <row r="64" spans="1:14" s="53" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="49" t="s">
+      <c r="B63" s="68"/>
+      <c r="C63" s="68"/>
+      <c r="D63" s="68"/>
+      <c r="E63" s="41"/>
+      <c r="F63" s="38"/>
+      <c r="G63" s="38"/>
+      <c r="H63" s="38"/>
+      <c r="I63" s="38"/>
+      <c r="J63" s="38"/>
+      <c r="K63" s="38"/>
+      <c r="L63" s="38"/>
+      <c r="M63" s="38"/>
+      <c r="N63" s="39"/>
+    </row>
+    <row r="64" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="67" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="54"/>
-      <c r="C64" s="54"/>
-      <c r="D64" s="54"/>
-      <c r="E64" s="55"/>
-      <c r="F64" s="51"/>
-      <c r="G64" s="51"/>
-      <c r="H64" s="51"/>
-      <c r="I64" s="51"/>
-      <c r="J64" s="51"/>
-      <c r="K64" s="51"/>
-      <c r="L64" s="51"/>
-      <c r="M64" s="51"/>
-      <c r="N64" s="52"/>
+      <c r="B64" s="68"/>
+      <c r="C64" s="68"/>
+      <c r="D64" s="68"/>
+      <c r="E64" s="41"/>
+      <c r="F64" s="38"/>
+      <c r="G64" s="38"/>
+      <c r="H64" s="38"/>
+      <c r="I64" s="38"/>
+      <c r="J64" s="38"/>
+      <c r="K64" s="38"/>
+      <c r="L64" s="38"/>
+      <c r="M64" s="38"/>
+      <c r="N64" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A62:D62"/>
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="N42:N44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="N46:N48"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
     <mergeCell ref="N12:N14"/>
     <mergeCell ref="C20:C22"/>
     <mergeCell ref="D20:D22"/>
@@ -5546,6 +5483,19 @@
     <mergeCell ref="D16:D18"/>
     <mergeCell ref="E16:E18"/>
     <mergeCell ref="N16:N18"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="E12:E14"/>
     <mergeCell ref="C24:C26"/>
     <mergeCell ref="D24:D26"/>
     <mergeCell ref="E24:E26"/>
@@ -5557,20 +5507,12 @@
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D50:D52"/>
-    <mergeCell ref="E50:E52"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="N42:N44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="N46:N48"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A62:D62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5578,7 +5520,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CDC51E-177F-BF40-BC8B-54510E0AFA97}">
-  <dimension ref="A1:N97"/>
+  <dimension ref="A1:N54"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="51.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.1640625" style="1" customWidth="1"/>
@@ -5650,30 +5592,30 @@
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
     </row>
-    <row r="3" spans="1:14" s="69" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="73" t="s">
+    <row r="3" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="69" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="73"/>
-      <c r="C3" s="73"/>
-      <c r="D3" s="73"/>
-      <c r="E3" s="73"/>
-      <c r="F3" s="73"/>
-      <c r="G3" s="73"/>
-      <c r="H3" s="73"/>
-      <c r="I3" s="73"/>
-      <c r="J3" s="72"/>
-    </row>
-    <row r="4" spans="1:14" s="71" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="70"/>
-      <c r="B4" s="70"/>
-      <c r="C4" s="70"/>
-      <c r="D4" s="77"/>
-      <c r="E4" s="70"/>
-      <c r="F4" s="70"/>
-      <c r="G4" s="70"/>
-      <c r="H4" s="70"/>
-      <c r="I4" s="70"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="69"/>
+      <c r="I3" s="69"/>
+      <c r="J3" s="52"/>
+    </row>
+    <row r="4" spans="1:14" s="51" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="8"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="54"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -5682,25 +5624,25 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="68" t="s">
+      <c r="D5" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="66">
+      <c r="E5" s="12">
         <v>2.6558005799999999E-2</v>
       </c>
-      <c r="F5" s="66">
+      <c r="F5" s="12">
         <v>7.9290508100000004E-2</v>
       </c>
-      <c r="G5" s="66">
+      <c r="G5" s="12">
         <v>0.42742090119999998</v>
       </c>
-      <c r="H5" s="66">
+      <c r="H5" s="12">
         <v>0.89827844270000001</v>
       </c>
-      <c r="I5" s="66">
+      <c r="I5" s="12">
         <v>0.34608643859999999</v>
       </c>
       <c r="J5" s="12">
@@ -5723,21 +5665,21 @@
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="66">
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="12">
         <v>6.2032598299999998E-2</v>
       </c>
-      <c r="F6" s="66">
+      <c r="F6" s="12">
         <v>9.9712367999999999E-3</v>
       </c>
-      <c r="G6" s="66">
+      <c r="G6" s="12">
         <v>0.22109300100000001</v>
       </c>
-      <c r="H6" s="66">
+      <c r="H6" s="12">
         <v>0.83613638540000002</v>
       </c>
-      <c r="I6" s="66">
+      <c r="I6" s="12">
         <v>0.38036204509999999</v>
       </c>
       <c r="J6" s="12">
@@ -5760,21 +5702,21 @@
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="66">
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="12">
         <v>5.7526370000000003E-4</v>
       </c>
-      <c r="F7" s="66">
+      <c r="F7" s="12">
         <v>1.1505273E-3</v>
       </c>
-      <c r="G7" s="66">
+      <c r="G7" s="12">
         <v>0.6839884947</v>
       </c>
-      <c r="H7" s="66">
+      <c r="H7" s="12">
         <v>0.50245971249999999</v>
       </c>
-      <c r="I7" s="66">
+      <c r="I7" s="12">
         <v>0.48181687890000002</v>
       </c>
       <c r="J7" s="12">
@@ -5790,13 +5732,6 @@
         <v>0.33399817541999999</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="E8" s="67"/>
-      <c r="F8" s="67"/>
-      <c r="G8" s="67"/>
-      <c r="H8" s="67"/>
-      <c r="I8" s="67"/>
-    </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>2</v>
@@ -5804,25 +5739,25 @@
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="58" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="68" t="s">
+      <c r="D9" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="66">
+      <c r="E9" s="12">
         <v>6.1553211900000002E-2</v>
       </c>
-      <c r="F9" s="66">
+      <c r="F9" s="12">
         <v>4.6979865999999997E-3</v>
       </c>
-      <c r="G9" s="66">
+      <c r="G9" s="12">
         <v>0.47286673060000001</v>
       </c>
-      <c r="H9" s="66">
+      <c r="H9" s="12">
         <v>0.83432698849999998</v>
       </c>
-      <c r="I9" s="66">
+      <c r="I9" s="12">
         <v>0.44045914829999999</v>
       </c>
       <c r="J9" s="12">
@@ -5845,21 +5780,21 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="27"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="66">
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="12">
         <v>7.6701821700000006E-2</v>
       </c>
-      <c r="F10" s="66">
+      <c r="F10" s="12">
         <v>5.1773729999999999E-3</v>
       </c>
-      <c r="G10" s="66">
+      <c r="G10" s="12">
         <v>0.4302972196</v>
       </c>
-      <c r="H10" s="66">
+      <c r="H10" s="12">
         <v>0.90418992629999995</v>
       </c>
-      <c r="I10" s="66">
+      <c r="I10" s="12">
         <v>0.3758758888</v>
       </c>
       <c r="J10" s="12">
@@ -5882,21 +5817,21 @@
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="66">
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="12">
         <v>1.917546E-4</v>
       </c>
-      <c r="F11" s="66">
+      <c r="F11" s="12">
         <v>1.5340364E-3</v>
       </c>
-      <c r="G11" s="66">
+      <c r="G11" s="12">
         <v>0.32617449659999997</v>
       </c>
-      <c r="H11" s="66">
+      <c r="H11" s="12">
         <v>0.49067845249999997</v>
       </c>
-      <c r="I11" s="66">
+      <c r="I11" s="12">
         <v>0.48153125829999999</v>
       </c>
       <c r="J11" s="12">
@@ -5912,9 +5847,6 @@
         <v>0.26002199968</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C12" s="74"/>
-    </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>2</v>
@@ -5922,11 +5854,11 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="27" t="s">
-        <v>76</v>
-      </c>
-      <c r="D13" s="68" t="s">
-        <v>77</v>
+      <c r="C13" s="58" t="s">
+        <v>78</v>
+      </c>
+      <c r="D13" s="58" t="s">
+        <v>91</v>
       </c>
       <c r="J13" s="12">
         <f>SUM(E13*1/3,F13*1/3,H13*1/3)</f>
@@ -5948,8 +5880,8 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="27"/>
-      <c r="D14" s="68"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
       <c r="J14" s="12">
         <f>SUM(E14*1/3,F14*1/3,H14*1/3)</f>
         <v>0</v>
@@ -5970,8 +5902,9 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="27"/>
-      <c r="D15" s="68"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="F15" s="9"/>
       <c r="J15" s="12">
         <f>SUM(E15*1/3,F15*1/3,H15*1/3)</f>
         <v>0</v>
@@ -5985,6 +5918,16 @@
         <v>0</v>
       </c>
     </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+    </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>2</v>
@@ -5992,12 +5935,17 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" s="68" t="s">
-        <v>78</v>
-      </c>
+      <c r="C17" s="58" t="s">
+        <v>85</v>
+      </c>
+      <c r="D17" s="58" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
       <c r="J17" s="12">
         <f>SUM(E17*1/3,F17*1/3,H17*1/3)</f>
         <v>0</v>
@@ -6018,8 +5966,13 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="27"/>
-      <c r="D18" s="68"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
       <c r="J18" s="12">
         <f>SUM(E18*1/3,F18*1/3,H18*1/3)</f>
         <v>0</v>
@@ -6040,9 +5993,13 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="27"/>
-      <c r="D19" s="68"/>
-      <c r="F19" s="9"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
       <c r="J19" s="12">
         <f>SUM(E19*1/3,F19*1/3,H19*1/3)</f>
         <v>0</v>
@@ -6056,1199 +6013,782 @@
         <v>0</v>
       </c>
     </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C20" s="53"/>
+    </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="75" t="s">
+      <c r="A21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="75" t="s">
+      <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="76" t="s">
-        <v>81</v>
-      </c>
-      <c r="D21" s="68" t="s">
+      <c r="C21" s="58" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" s="58" t="s">
+        <v>77</v>
+      </c>
+      <c r="J21" s="12">
+        <f>SUM(E21*1/3,F21*1/3,H21*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K21" s="12">
+        <f>SUM(G21*1/2,I21*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L21" s="12">
+        <f>SUM(E21*1/5,F21*1/5,G21*1/5,H21*1/5,I21*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="J22" s="12">
+        <f>SUM(E22*1/3,F22*1/3,H22*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K22" s="12">
+        <f>SUM(G22*1/2,I22*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L22" s="12">
+        <f>SUM(E22*1/5,F22*1/5,G22*1/5,H22*1/5,I22*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="J23" s="12">
+        <f>SUM(E23*1/3,F23*1/3,H23*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K23" s="12">
+        <f>SUM(G23*1/2,I23*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L23" s="12">
+        <f>SUM(E23*1/5,F23*1/5,G23*1/5,H23*1/5,I23*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A25" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C25" s="58" t="s">
+        <v>89</v>
+      </c>
+      <c r="D25" s="58" t="s">
+        <v>87</v>
+      </c>
+      <c r="J25" s="12">
+        <f>SUM(E25*1/3,F25*1/3,H25*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K25" s="12">
+        <f>SUM(G25*1/2,I25*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L25" s="12">
+        <f>SUM(E25*1/5,F25*1/5,G25*1/5,H25*1/5,I25*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="J26" s="12">
+        <f>SUM(E26*1/3,F26*1/3,H26*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K26" s="12">
+        <f>SUM(G26*1/2,I26*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L26" s="12">
+        <f>SUM(E26*1/5,F26*1/5,G26*1/5,H26*1/5,I26*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="58"/>
+      <c r="D27" s="58"/>
+      <c r="F27" s="9"/>
+      <c r="J27" s="12">
+        <f>SUM(E27*1/3,F27*1/3,H27*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="12">
+        <f>SUM(G27*1/2,I27*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L27" s="12">
+        <f>SUM(E27*1/5,F27*1/5,G27*1/5,H27*1/5,I27*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C29" s="58" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="58" t="s">
+        <v>88</v>
+      </c>
+      <c r="J29" s="12">
+        <f>SUM(E29*1/3,F29*1/3,H29*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="12">
+        <f>SUM(G29*1/2,I29*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="12">
+        <f>SUM(E29*1/5,F29*1/5,G29*1/5,H29*1/5,I29*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="58"/>
+      <c r="D30" s="58"/>
+      <c r="J30" s="12">
+        <f>SUM(E30*1/3,F30*1/3,H30*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="12">
+        <f>SUM(G30*1/2,I30*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="12">
+        <f>SUM(E30*1/5,F30*1/5,G30*1/5,H30*1/5,I30*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A31" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+      <c r="F31" s="9"/>
+      <c r="J31" s="12">
+        <f>SUM(E31*1/3,F31*1/3,H31*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="12">
+        <f>SUM(G31*1/2,I31*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="12">
+        <f>SUM(E31*1/5,F31*1/5,G31*1/5,H31*1/5,I31*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="F33" s="8"/>
+      <c r="H33" s="8"/>
+    </row>
+    <row r="34" spans="1:12" s="50" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="69" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="B22" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="C22" s="76"/>
-      <c r="D22" s="68"/>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="75" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="76"/>
-      <c r="D23" s="68"/>
-    </row>
-    <row r="25" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="75" t="s">
+      <c r="B34" s="69"/>
+      <c r="C34" s="69"/>
+      <c r="D34" s="69"/>
+      <c r="E34" s="69"/>
+      <c r="F34" s="69"/>
+      <c r="G34" s="69"/>
+      <c r="H34" s="69"/>
+      <c r="I34" s="69"/>
+      <c r="J34" s="52"/>
+    </row>
+    <row r="35" spans="1:12" s="51" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="8"/>
+      <c r="B35" s="8"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="54"/>
+      <c r="E35" s="8"/>
+      <c r="F35" s="8"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="8"/>
+      <c r="I35" s="8"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A36" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="75" t="s">
+      <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="76" t="s">
-        <v>83</v>
-      </c>
-      <c r="D25" s="68" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A26" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="76"/>
-      <c r="D26" s="68"/>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A27" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="75" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="76"/>
-      <c r="D27" s="68"/>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="C28" s="76"/>
-      <c r="D28" s="68"/>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A30" s="75" t="s">
-        <v>2</v>
-      </c>
-      <c r="B30" s="75" t="s">
-        <v>5</v>
-      </c>
-      <c r="C30" s="76" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" s="68" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A31" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="B31" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="76"/>
-      <c r="D31" s="68"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="B32" s="75" t="s">
-        <v>7</v>
-      </c>
-      <c r="C32" s="76"/>
-      <c r="D32" s="68"/>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="C33" s="76"/>
-      <c r="D33" s="68"/>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F34" s="8"/>
-      <c r="H34" s="8"/>
-    </row>
-    <row r="35" spans="1:12" s="69" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="73" t="s">
-        <v>86</v>
-      </c>
-      <c r="B35" s="73"/>
-      <c r="C35" s="73"/>
-      <c r="D35" s="73"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="73"/>
-      <c r="G35" s="73"/>
-      <c r="H35" s="73"/>
-      <c r="I35" s="73"/>
-      <c r="J35" s="72"/>
-    </row>
-    <row r="36" spans="1:12" s="71" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="70"/>
-      <c r="B36" s="70"/>
-      <c r="C36" s="70"/>
-      <c r="D36" s="77"/>
-      <c r="E36" s="70"/>
-      <c r="F36" s="70"/>
-      <c r="G36" s="70"/>
-      <c r="H36" s="70"/>
-      <c r="I36" s="70"/>
+      <c r="C36" s="58" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" s="58" t="s">
+        <v>72</v>
+      </c>
+      <c r="E36" s="12">
+        <v>5.6663470799999997E-2</v>
+      </c>
+      <c r="F36" s="12">
+        <v>9.2042185999999995E-3</v>
+      </c>
+      <c r="G36" s="12">
+        <v>0.42109300100000002</v>
+      </c>
+      <c r="H36" s="12">
+        <v>0.81920023559999999</v>
+      </c>
+      <c r="I36" s="12">
+        <v>0.44493382850000002</v>
+      </c>
+      <c r="J36" s="12">
+        <f>SUM(E36*1/3,F36*1/3,H36*1/3)</f>
+        <v>0.2950226416666667</v>
+      </c>
+      <c r="K36" s="12">
+        <f>SUM(G36*1/2,I36*1/2)</f>
+        <v>0.43301341474999999</v>
+      </c>
+      <c r="L36" s="12">
+        <f>SUM(E36*1/5,F36*1/5,G36*1/5,H36*1/5,I36*1/5)</f>
+        <v>0.35021895089999999</v>
+      </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C37" s="27" t="s">
-        <v>87</v>
-      </c>
-      <c r="D37" s="68" t="s">
-        <v>72</v>
-      </c>
-      <c r="E37" s="66">
-        <v>5.6663470799999997E-2</v>
-      </c>
-      <c r="F37" s="66">
-        <v>9.2042185999999995E-3</v>
-      </c>
-      <c r="G37" s="66">
-        <v>0.42109300100000002</v>
-      </c>
-      <c r="H37" s="66">
-        <v>0.81920023559999999</v>
-      </c>
-      <c r="I37" s="66">
-        <v>0.44493382850000002</v>
+        <v>6</v>
+      </c>
+      <c r="C37" s="58"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="12">
+        <v>8.2166826499999998E-2</v>
+      </c>
+      <c r="F37" s="12">
+        <v>9.5877299999999998E-5</v>
+      </c>
+      <c r="G37" s="12">
+        <v>0.42070949190000001</v>
+      </c>
+      <c r="H37" s="12">
+        <v>0.81290296760000003</v>
+      </c>
+      <c r="I37" s="12">
+        <v>0.4417925586</v>
       </c>
       <c r="J37" s="12">
         <f>SUM(E37*1/3,F37*1/3,H37*1/3)</f>
-        <v>0.2950226416666667</v>
+        <v>0.29838855713333334</v>
       </c>
       <c r="K37" s="12">
         <f>SUM(G37*1/2,I37*1/2)</f>
-        <v>0.43301341474999999</v>
+        <v>0.43125102525000003</v>
       </c>
       <c r="L37" s="12">
         <f>SUM(E37*1/5,F37*1/5,G37*1/5,H37*1/5,I37*1/5)</f>
-        <v>0.35021895089999999</v>
+        <v>0.35153354437999995</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C38" s="27"/>
-      <c r="D38" s="68"/>
-      <c r="E38" s="66">
-        <v>8.2166826499999998E-2</v>
-      </c>
-      <c r="F38" s="66">
-        <v>9.5877299999999998E-5</v>
-      </c>
-      <c r="G38" s="66">
-        <v>0.42070949190000001</v>
-      </c>
-      <c r="H38" s="66">
-        <v>0.81290296760000003</v>
-      </c>
-      <c r="I38" s="66">
-        <v>0.4417925586</v>
+        <v>7</v>
+      </c>
+      <c r="C38" s="58"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="12">
+        <v>7.6701820000000002E-4</v>
+      </c>
+      <c r="F38" s="12">
+        <v>2.0134227999999998E-3</v>
+      </c>
+      <c r="G38" s="12">
+        <v>0.1702780441</v>
+      </c>
+      <c r="H38" s="12">
+        <v>0.46493483429999999</v>
+      </c>
+      <c r="I38" s="12">
+        <v>0.47127738250000001</v>
       </c>
       <c r="J38" s="12">
         <f>SUM(E38*1/3,F38*1/3,H38*1/3)</f>
-        <v>0.29838855713333334</v>
+        <v>0.15590509176666667</v>
       </c>
       <c r="K38" s="12">
         <f>SUM(G38*1/2,I38*1/2)</f>
-        <v>0.43125102525000003</v>
+        <v>0.32077771329999999</v>
       </c>
       <c r="L38" s="12">
         <f>SUM(E38*1/5,F38*1/5,G38*1/5,H38*1/5,I38*1/5)</f>
-        <v>0.35153354437999995</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A39" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="27"/>
-      <c r="D39" s="68"/>
-      <c r="E39" s="66">
-        <v>7.6701820000000002E-4</v>
-      </c>
-      <c r="F39" s="66">
-        <v>2.0134227999999998E-3</v>
-      </c>
-      <c r="G39" s="66">
-        <v>0.1702780441</v>
-      </c>
-      <c r="H39" s="66">
-        <v>0.46493483429999999</v>
-      </c>
-      <c r="I39" s="66">
-        <v>0.47127738250000001</v>
-      </c>
-      <c r="J39" s="12">
-        <f>SUM(E39*1/3,F39*1/3,H39*1/3)</f>
-        <v>0.15590509176666667</v>
-      </c>
-      <c r="K39" s="12">
-        <f>SUM(G39*1/2,I39*1/2)</f>
-        <v>0.32077771329999999</v>
-      </c>
-      <c r="L39" s="12">
-        <f>SUM(E39*1/5,F39*1/5,G39*1/5,H39*1/5,I39*1/5)</f>
         <v>0.22185414038000001</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E40" s="67"/>
-      <c r="F40" s="67"/>
-      <c r="G40" s="67"/>
-      <c r="H40" s="67"/>
-      <c r="I40" s="67"/>
+      <c r="A40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C40" s="58" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="E40" s="12">
+        <v>4.5445829299999997E-2</v>
+      </c>
+      <c r="F40" s="12">
+        <v>6.6155322000000004E-3</v>
+      </c>
+      <c r="G40" s="12">
+        <v>0.45714285710000002</v>
+      </c>
+      <c r="H40" s="12">
+        <v>0.70717096769999999</v>
+      </c>
+      <c r="I40" s="12">
+        <v>0.50964245389999996</v>
+      </c>
+      <c r="J40" s="12">
+        <f>SUM(E40*1/3,F40*1/3,H40*1/3)</f>
+        <v>0.25307744306666669</v>
+      </c>
+      <c r="K40" s="12">
+        <f>SUM(G40*1/2,I40*1/2)</f>
+        <v>0.48339265549999999</v>
+      </c>
+      <c r="L40" s="12">
+        <f>SUM(E40*1/5,F40*1/5,G40*1/5,H40*1/5,I40*1/5)</f>
+        <v>0.34520352803999999</v>
+      </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C41" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="D41" s="68" t="s">
-        <v>74</v>
-      </c>
-      <c r="E41" s="66">
-        <v>4.5445829299999997E-2</v>
-      </c>
-      <c r="F41" s="66">
-        <v>6.6155322000000004E-3</v>
-      </c>
-      <c r="G41" s="66">
-        <v>0.45714285710000002</v>
-      </c>
-      <c r="H41" s="66">
-        <v>0.70717096769999999</v>
-      </c>
-      <c r="I41" s="66">
-        <v>0.50964245389999996</v>
+        <v>6</v>
+      </c>
+      <c r="C41" s="58"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="12">
+        <v>2.85714286E-2</v>
+      </c>
+      <c r="F41" s="12">
+        <v>1.9175456000000001E-3</v>
+      </c>
+      <c r="G41" s="12">
+        <v>0.45043144769999999</v>
+      </c>
+      <c r="H41" s="12">
+        <v>0.74414334049999997</v>
+      </c>
+      <c r="I41" s="12">
+        <v>0.46137624570000002</v>
       </c>
       <c r="J41" s="12">
         <f>SUM(E41*1/3,F41*1/3,H41*1/3)</f>
-        <v>0.25307744306666669</v>
+        <v>0.25821077156666666</v>
       </c>
       <c r="K41" s="12">
         <f>SUM(G41*1/2,I41*1/2)</f>
-        <v>0.48339265549999999</v>
+        <v>0.4559038467</v>
       </c>
       <c r="L41" s="12">
         <f>SUM(E41*1/5,F41*1/5,G41*1/5,H41*1/5,I41*1/5)</f>
-        <v>0.34520352803999999</v>
+        <v>0.33728800162</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C42" s="27"/>
-      <c r="D42" s="68"/>
-      <c r="E42" s="66">
-        <v>2.85714286E-2</v>
-      </c>
-      <c r="F42" s="66">
-        <v>1.9175456000000001E-3</v>
-      </c>
-      <c r="G42" s="66">
-        <v>0.45043144769999999</v>
-      </c>
-      <c r="H42" s="66">
-        <v>0.74414334049999997</v>
-      </c>
-      <c r="I42" s="66">
-        <v>0.46137624570000002</v>
+        <v>7</v>
+      </c>
+      <c r="C42" s="58"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="12">
+        <v>3.8350910000000001E-4</v>
+      </c>
+      <c r="F42" s="12">
+        <v>1.3422817999999999E-3</v>
+      </c>
+      <c r="G42" s="12">
+        <v>0.79022051770000001</v>
+      </c>
+      <c r="H42" s="12">
+        <v>0.49764374880000001</v>
+      </c>
+      <c r="I42" s="12">
+        <v>0.48742542859999999</v>
       </c>
       <c r="J42" s="12">
         <f>SUM(E42*1/3,F42*1/3,H42*1/3)</f>
-        <v>0.25821077156666666</v>
+        <v>0.16645651323333333</v>
       </c>
       <c r="K42" s="12">
         <f>SUM(G42*1/2,I42*1/2)</f>
-        <v>0.4559038467</v>
+        <v>0.63882297315000003</v>
       </c>
       <c r="L42" s="12">
         <f>SUM(E42*1/5,F42*1/5,G42*1/5,H42*1/5,I42*1/5)</f>
-        <v>0.33728800162</v>
+        <v>0.35540309720000007</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A43" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="27"/>
-      <c r="D43" s="68"/>
-      <c r="E43" s="66">
-        <v>3.8350910000000001E-4</v>
-      </c>
-      <c r="F43" s="66">
-        <v>1.3422817999999999E-3</v>
-      </c>
-      <c r="G43" s="66">
-        <v>0.79022051770000001</v>
-      </c>
-      <c r="H43" s="66">
-        <v>0.49764374880000001</v>
-      </c>
-      <c r="I43" s="66">
-        <v>0.48742542859999999</v>
-      </c>
-      <c r="J43" s="12">
-        <f>SUM(E43*1/3,F43*1/3,H43*1/3)</f>
-        <v>0.16645651323333333</v>
-      </c>
-      <c r="K43" s="12">
-        <f>SUM(G43*1/2,I43*1/2)</f>
-        <v>0.63882297315000003</v>
-      </c>
-      <c r="L43" s="12">
-        <f>SUM(E43*1/5,F43*1/5,G43*1/5,H43*1/5,I43*1/5)</f>
-        <v>0.35540309720000007</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="C44" s="74"/>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A45" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C45" s="27" t="s">
-        <v>89</v>
-      </c>
-      <c r="D45" s="68" t="s">
-        <v>77</v>
-      </c>
-      <c r="J45" s="12">
-        <f>SUM(E45*1/3,F45*1/3,H45*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K45" s="12">
-        <f>SUM(G45*1/2,I45*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L45" s="12">
-        <f>SUM(E45*1/5,F45*1/5,G45*1/5,H45*1/5,I45*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A46" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C46" s="27"/>
-      <c r="D46" s="68"/>
-      <c r="J46" s="12">
-        <f>SUM(E46*1/3,F46*1/3,H46*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K46" s="12">
-        <f>SUM(G46*1/2,I46*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L46" s="12">
-        <f>SUM(E46*1/5,F46*1/5,G46*1/5,H46*1/5,I46*1/5)</f>
-        <v>0</v>
-      </c>
+      <c r="E43" s="12"/>
+      <c r="F43" s="12"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+    </row>
+    <row r="45" spans="1:12" s="50" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="69" t="s">
+        <v>82</v>
+      </c>
+      <c r="B45" s="69"/>
+      <c r="C45" s="69"/>
+      <c r="D45" s="69"/>
+      <c r="E45" s="69"/>
+      <c r="F45" s="69"/>
+      <c r="G45" s="69"/>
+      <c r="H45" s="69"/>
+      <c r="I45" s="69"/>
+      <c r="J45" s="52"/>
+    </row>
+    <row r="46" spans="1:12" s="51" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="8"/>
+      <c r="B46" s="8"/>
+      <c r="C46" s="8"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="8"/>
+      <c r="F46" s="8"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="8"/>
+      <c r="I46" s="8"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="27"/>
-      <c r="D47" s="68"/>
+        <v>5</v>
+      </c>
+      <c r="C47" s="58" t="s">
+        <v>83</v>
+      </c>
+      <c r="D47" s="58" t="s">
+        <v>72</v>
+      </c>
+      <c r="E47" s="12">
+        <v>2.0997123699999998E-2</v>
+      </c>
+      <c r="F47" s="12">
+        <v>2.3010547000000001E-3</v>
+      </c>
+      <c r="G47" s="12">
+        <v>0.3390220518</v>
+      </c>
+      <c r="H47" s="12">
+        <v>0.80129368079999996</v>
+      </c>
+      <c r="I47" s="12">
+        <v>0.42862661320000001</v>
+      </c>
       <c r="J47" s="12">
         <f>SUM(E47*1/3,F47*1/3,H47*1/3)</f>
-        <v>0</v>
+        <v>0.27486395306666661</v>
       </c>
       <c r="K47" s="12">
         <f>SUM(G47*1/2,I47*1/2)</f>
-        <v>0</v>
+        <v>0.38382433250000003</v>
       </c>
       <c r="L47" s="12">
         <f>SUM(E47*1/5,F47*1/5,G47*1/5,H47*1/5,I47*1/5)</f>
-        <v>0</v>
+        <v>0.31844810483999997</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A48" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C48" s="58"/>
+      <c r="D48" s="58"/>
+      <c r="E48" s="12">
+        <v>3.2598274E-3</v>
+      </c>
+      <c r="F48" s="12">
+        <v>4.1227229000000004E-3</v>
+      </c>
+      <c r="G48" s="12">
+        <v>0.25656759350000002</v>
+      </c>
+      <c r="H48" s="12">
+        <v>0.5509203869</v>
+      </c>
+      <c r="I48" s="12">
+        <v>0.4742471747</v>
+      </c>
+      <c r="J48" s="12">
+        <f>SUM(E48*1/3,F48*1/3,H48*1/3)</f>
+        <v>0.18610097906666667</v>
+      </c>
+      <c r="K48" s="12">
+        <f>SUM(G48*1/2,I48*1/2)</f>
+        <v>0.36540738410000001</v>
+      </c>
+      <c r="L48" s="12">
+        <f>SUM(E48*1/5,F48*1/5,G48*1/5,H48*1/5,I48*1/5)</f>
+        <v>0.25782354108</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C49" s="27" t="s">
-        <v>90</v>
-      </c>
-      <c r="D49" s="68" t="s">
-        <v>78</v>
+        <v>7</v>
+      </c>
+      <c r="C49" s="58"/>
+      <c r="D49" s="58"/>
+      <c r="E49" s="12">
+        <v>0</v>
+      </c>
+      <c r="F49" s="12">
+        <v>9.5877280000000004E-4</v>
+      </c>
+      <c r="G49" s="12">
+        <v>0.35321188879999998</v>
+      </c>
+      <c r="H49" s="12">
+        <v>0.55203139629999998</v>
+      </c>
+      <c r="I49" s="12">
+        <v>0.4477544779</v>
       </c>
       <c r="J49" s="12">
         <f>SUM(E49*1/3,F49*1/3,H49*1/3)</f>
-        <v>0</v>
+        <v>0.18433005636666666</v>
       </c>
       <c r="K49" s="12">
         <f>SUM(G49*1/2,I49*1/2)</f>
-        <v>0</v>
+        <v>0.40048318334999999</v>
       </c>
       <c r="L49" s="12">
         <f>SUM(E49*1/5,F49*1/5,G49*1/5,H49*1/5,I49*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A50" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="27"/>
-      <c r="D50" s="68"/>
-      <c r="J50" s="12">
-        <f>SUM(E50*1/3,F50*1/3,H50*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K50" s="12">
-        <f>SUM(G50*1/2,I50*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L50" s="12">
-        <f>SUM(E50*1/5,F50*1/5,G50*1/5,H50*1/5,I50*1/5)</f>
-        <v>0</v>
+        <v>0.27079130715999999</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="27"/>
-      <c r="D51" s="68"/>
-      <c r="F51" s="9"/>
+        <v>5</v>
+      </c>
+      <c r="C51" s="58" t="s">
+        <v>84</v>
+      </c>
+      <c r="D51" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="E51" s="12">
+        <v>7.2003835099999997E-2</v>
+      </c>
+      <c r="F51" s="12">
+        <v>7.3825504E-3</v>
+      </c>
+      <c r="G51" s="12">
+        <v>0.3771812081</v>
+      </c>
+      <c r="H51" s="12">
+        <v>0.74268293880000003</v>
+      </c>
+      <c r="I51" s="12">
+        <v>0.45190041990000002</v>
+      </c>
       <c r="J51" s="12">
         <f>SUM(E51*1/3,F51*1/3,H51*1/3)</f>
-        <v>0</v>
+        <v>0.27402310810000002</v>
       </c>
       <c r="K51" s="12">
         <f>SUM(G51*1/2,I51*1/2)</f>
-        <v>0</v>
+        <v>0.41454081399999998</v>
       </c>
       <c r="L51" s="12">
         <f>SUM(E51*1/5,F51*1/5,G51*1/5,H51*1/5,I51*1/5)</f>
-        <v>0</v>
+        <v>0.33023019046000002</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A52" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C52" s="58"/>
+      <c r="D52" s="58"/>
+      <c r="E52" s="12">
+        <v>8.59060403E-2</v>
+      </c>
+      <c r="F52" s="12">
+        <v>5.7526370000000003E-4</v>
+      </c>
+      <c r="G52" s="12">
+        <v>0.59731543620000005</v>
+      </c>
+      <c r="H52" s="12">
+        <v>0.8594864566</v>
+      </c>
+      <c r="I52" s="12">
+        <v>0.43209071430000001</v>
+      </c>
+      <c r="J52" s="12">
+        <f>SUM(E52*1/3,F52*1/3,H52*1/3)</f>
+        <v>0.31532258686666664</v>
+      </c>
+      <c r="K52" s="12">
+        <f>SUM(G52*1/2,I52*1/2)</f>
+        <v>0.51470307525000003</v>
+      </c>
+      <c r="L52" s="12">
+        <f>SUM(E52*1/5,F52*1/5,G52*1/5,H52*1/5,I52*1/5)</f>
+        <v>0.39507478221999998</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A53" s="75" t="s">
-        <v>2</v>
-      </c>
-      <c r="B53" s="75" t="s">
-        <v>5</v>
-      </c>
-      <c r="C53" s="76" t="s">
-        <v>91</v>
-      </c>
-      <c r="D53" s="68" t="s">
-        <v>79</v>
+      <c r="A53" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="58"/>
+      <c r="D53" s="58"/>
+      <c r="E53" s="12">
+        <v>3.8350910000000001E-4</v>
+      </c>
+      <c r="F53" s="12">
+        <v>1.1505274000000001E-3</v>
+      </c>
+      <c r="G53" s="12">
+        <v>0.4678811122</v>
+      </c>
+      <c r="H53" s="12">
+        <v>0.50554854299999996</v>
+      </c>
+      <c r="I53" s="12">
+        <v>0.48466990739999999</v>
+      </c>
+      <c r="J53" s="12">
+        <f>SUM(E53*1/3,F53*1/3,H53*1/3)</f>
+        <v>0.1690275265</v>
+      </c>
+      <c r="K53" s="12">
+        <f>SUM(G53*1/2,I53*1/2)</f>
+        <v>0.4762755098</v>
+      </c>
+      <c r="L53" s="12">
+        <f>SUM(E53*1/5,F53*1/5,G53*1/5,H53*1/5,I53*1/5)</f>
+        <v>0.29192671981999996</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A54" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="B54" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="C54" s="76"/>
-      <c r="D54" s="68"/>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A55" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="B55" s="75" t="s">
-        <v>7</v>
-      </c>
-      <c r="C55" s="76"/>
-      <c r="D55" s="68"/>
-    </row>
-    <row r="57" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="75" t="s">
-        <v>2</v>
-      </c>
-      <c r="B57" s="75" t="s">
-        <v>5</v>
-      </c>
-      <c r="C57" s="76" t="s">
-        <v>92</v>
-      </c>
-      <c r="D57" s="68" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A58" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="B58" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="C58" s="76"/>
-      <c r="D58" s="68"/>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A59" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="B59" s="75" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="76"/>
-      <c r="D59" s="68"/>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="C60" s="76"/>
-      <c r="D60" s="68"/>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A62" s="75" t="s">
-        <v>2</v>
-      </c>
-      <c r="B62" s="75" t="s">
-        <v>5</v>
-      </c>
-      <c r="C62" s="76" t="s">
-        <v>93</v>
-      </c>
-      <c r="D62" s="68" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A63" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="B63" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="C63" s="76"/>
-      <c r="D63" s="68"/>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A64" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="B64" s="75" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="76"/>
-      <c r="D64" s="68"/>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="C65" s="76"/>
-      <c r="D65" s="68"/>
-    </row>
-    <row r="67" spans="1:12" s="69" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="73" t="s">
-        <v>94</v>
-      </c>
-      <c r="B67" s="73"/>
-      <c r="C67" s="73"/>
-      <c r="D67" s="73"/>
-      <c r="E67" s="73"/>
-      <c r="F67" s="73"/>
-      <c r="G67" s="73"/>
-      <c r="H67" s="73"/>
-      <c r="I67" s="73"/>
-      <c r="J67" s="72"/>
-    </row>
-    <row r="68" spans="1:12" s="71" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="70"/>
-      <c r="B68" s="70"/>
-      <c r="C68" s="70"/>
-      <c r="D68" s="77"/>
-      <c r="E68" s="70"/>
-      <c r="F68" s="70"/>
-      <c r="G68" s="70"/>
-      <c r="H68" s="70"/>
-      <c r="I68" s="70"/>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A69" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C69" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="D69" s="68" t="s">
-        <v>72</v>
-      </c>
-      <c r="E69" s="12">
-        <v>2.0997123699999998E-2</v>
-      </c>
-      <c r="F69" s="12">
-        <v>2.3010547000000001E-3</v>
-      </c>
-      <c r="G69" s="12">
-        <v>0.3390220518</v>
-      </c>
-      <c r="H69" s="12">
-        <v>0.80129368079999996</v>
-      </c>
-      <c r="I69" s="12">
-        <v>0.42862661320000001</v>
-      </c>
-      <c r="J69" s="12">
-        <f>SUM(E69*1/3,F69*1/3,H69*1/3)</f>
-        <v>0.27486395306666661</v>
-      </c>
-      <c r="K69" s="12">
-        <f>SUM(G69*1/2,I69*1/2)</f>
-        <v>0.38382433250000003</v>
-      </c>
-      <c r="L69" s="12">
-        <f>SUM(E69*1/5,F69*1/5,G69*1/5,H69*1/5,I69*1/5)</f>
-        <v>0.31844810483999997</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A70" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C70" s="27"/>
-      <c r="D70" s="68"/>
-      <c r="E70" s="12">
-        <v>3.2598274E-3</v>
-      </c>
-      <c r="F70" s="12">
-        <v>4.1227229000000004E-3</v>
-      </c>
-      <c r="G70" s="12">
-        <v>0.25656759350000002</v>
-      </c>
-      <c r="H70" s="12">
-        <v>0.5509203869</v>
-      </c>
-      <c r="I70" s="12">
-        <v>0.4742471747</v>
-      </c>
-      <c r="J70" s="12">
-        <f>SUM(E70*1/3,F70*1/3,H70*1/3)</f>
-        <v>0.18610097906666667</v>
-      </c>
-      <c r="K70" s="12">
-        <f>SUM(G70*1/2,I70*1/2)</f>
-        <v>0.36540738410000001</v>
-      </c>
-      <c r="L70" s="12">
-        <f>SUM(E70*1/5,F70*1/5,G70*1/5,H70*1/5,I70*1/5)</f>
-        <v>0.25782354108</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A71" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B71" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="27"/>
-      <c r="D71" s="68"/>
-      <c r="E71" s="12">
-        <v>0</v>
-      </c>
-      <c r="F71" s="12">
-        <v>9.5877280000000004E-4</v>
-      </c>
-      <c r="G71" s="12">
-        <v>0.35321188879999998</v>
-      </c>
-      <c r="H71" s="12">
-        <v>0.55203139629999998</v>
-      </c>
-      <c r="I71" s="12">
-        <v>0.4477544779</v>
-      </c>
-      <c r="J71" s="12">
-        <f>SUM(E71*1/3,F71*1/3,H71*1/3)</f>
-        <v>0.18433005636666666</v>
-      </c>
-      <c r="K71" s="12">
-        <f>SUM(G71*1/2,I71*1/2)</f>
-        <v>0.40048318334999999</v>
-      </c>
-      <c r="L71" s="12">
-        <f>SUM(E71*1/5,F71*1/5,G71*1/5,H71*1/5,I71*1/5)</f>
-        <v>0.27079130715999999</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E72" s="67"/>
-      <c r="F72" s="67"/>
-      <c r="G72" s="67"/>
-      <c r="H72" s="67"/>
-      <c r="I72" s="67"/>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A73" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C73" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="D73" s="68" t="s">
-        <v>74</v>
-      </c>
-      <c r="E73" s="12">
-        <v>7.2003835099999997E-2</v>
-      </c>
-      <c r="F73" s="12">
-        <v>7.3825504E-3</v>
-      </c>
-      <c r="G73" s="12">
-        <v>0.3771812081</v>
-      </c>
-      <c r="H73" s="12">
-        <v>0.74268293880000003</v>
-      </c>
-      <c r="I73" s="12">
-        <v>0.45190041990000002</v>
-      </c>
-      <c r="J73" s="12">
-        <f>SUM(E73*1/3,F73*1/3,H73*1/3)</f>
-        <v>0.27402310810000002</v>
-      </c>
-      <c r="K73" s="12">
-        <f>SUM(G73*1/2,I73*1/2)</f>
-        <v>0.41454081399999998</v>
-      </c>
-      <c r="L73" s="12">
-        <f>SUM(E73*1/5,F73*1/5,G73*1/5,H73*1/5,I73*1/5)</f>
-        <v>0.33023019046000002</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A74" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C74" s="27"/>
-      <c r="D74" s="68"/>
-      <c r="E74" s="12">
-        <v>8.59060403E-2</v>
-      </c>
-      <c r="F74" s="12">
-        <v>5.7526370000000003E-4</v>
-      </c>
-      <c r="G74" s="12">
-        <v>0.59731543620000005</v>
-      </c>
-      <c r="H74" s="12">
-        <v>0.8594864566</v>
-      </c>
-      <c r="I74" s="12">
-        <v>0.43209071430000001</v>
-      </c>
-      <c r="J74" s="12">
-        <f>SUM(E74*1/3,F74*1/3,H74*1/3)</f>
-        <v>0.31532258686666664</v>
-      </c>
-      <c r="K74" s="12">
-        <f>SUM(G74*1/2,I74*1/2)</f>
-        <v>0.51470307525000003</v>
-      </c>
-      <c r="L74" s="12">
-        <f>SUM(E74*1/5,F74*1/5,G74*1/5,H74*1/5,I74*1/5)</f>
-        <v>0.39507478221999998</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A75" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B75" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75" s="27"/>
-      <c r="D75" s="68"/>
-      <c r="E75" s="12">
-        <v>3.8350910000000001E-4</v>
-      </c>
-      <c r="F75" s="12">
-        <v>1.1505274000000001E-3</v>
-      </c>
-      <c r="G75" s="12">
-        <v>0.4678811122</v>
-      </c>
-      <c r="H75" s="12">
-        <v>0.50554854299999996</v>
-      </c>
-      <c r="I75" s="12">
-        <v>0.48466990739999999</v>
-      </c>
-      <c r="J75" s="12">
-        <f>SUM(E75*1/3,F75*1/3,H75*1/3)</f>
-        <v>0.1690275265</v>
-      </c>
-      <c r="K75" s="12">
-        <f>SUM(G75*1/2,I75*1/2)</f>
-        <v>0.4762755098</v>
-      </c>
-      <c r="L75" s="12">
-        <f>SUM(E75*1/5,F75*1/5,G75*1/5,H75*1/5,I75*1/5)</f>
-        <v>0.29192671981999996</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="C76" s="74"/>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A77" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B77" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C77" s="27" t="s">
-        <v>97</v>
-      </c>
-      <c r="D77" s="68" t="s">
-        <v>77</v>
-      </c>
-      <c r="J77" s="12">
-        <f>SUM(E77*1/3,F77*1/3,H77*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K77" s="12">
-        <f>SUM(G77*1/2,I77*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L77" s="12">
-        <f>SUM(E77*1/5,F77*1/5,G77*1/5,H77*1/5,I77*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A78" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C78" s="27"/>
-      <c r="D78" s="68"/>
-      <c r="J78" s="12">
-        <f>SUM(E78*1/3,F78*1/3,H78*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K78" s="12">
-        <f>SUM(G78*1/2,I78*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L78" s="12">
-        <f>SUM(E78*1/5,F78*1/5,G78*1/5,H78*1/5,I78*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A79" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="27"/>
-      <c r="D79" s="68"/>
-      <c r="J79" s="12">
-        <f>SUM(E79*1/3,F79*1/3,H79*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K79" s="12">
-        <f>SUM(G79*1/2,I79*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L79" s="12">
-        <f>SUM(E79*1/5,F79*1/5,G79*1/5,H79*1/5,I79*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A81" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C81" s="27" t="s">
-        <v>98</v>
-      </c>
-      <c r="D81" s="68" t="s">
-        <v>78</v>
-      </c>
-      <c r="J81" s="12">
-        <f>SUM(E81*1/3,F81*1/3,H81*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K81" s="12">
-        <f>SUM(G81*1/2,I81*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L81" s="12">
-        <f>SUM(E81*1/5,F81*1/5,G81*1/5,H81*1/5,I81*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A82" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B82" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C82" s="27"/>
-      <c r="D82" s="68"/>
-      <c r="J82" s="12">
-        <f>SUM(E82*1/3,F82*1/3,H82*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K82" s="12">
-        <f>SUM(G82*1/2,I82*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L82" s="12">
-        <f>SUM(E82*1/5,F82*1/5,G82*1/5,H82*1/5,I82*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A83" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C83" s="27"/>
-      <c r="D83" s="68"/>
-      <c r="F83" s="9"/>
-      <c r="J83" s="12">
-        <f>SUM(E83*1/3,F83*1/3,H83*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K83" s="12">
-        <f>SUM(G83*1/2,I83*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L83" s="12">
-        <f>SUM(E83*1/5,F83*1/5,G83*1/5,H83*1/5,I83*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A85" s="75" t="s">
-        <v>2</v>
-      </c>
-      <c r="B85" s="75" t="s">
-        <v>5</v>
-      </c>
-      <c r="C85" s="76" t="s">
-        <v>99</v>
-      </c>
-      <c r="D85" s="68" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="86" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A86" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="B86" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="C86" s="76"/>
-      <c r="D86" s="68"/>
-    </row>
-    <row r="87" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A87" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="B87" s="75" t="s">
-        <v>7</v>
-      </c>
-      <c r="C87" s="76"/>
-      <c r="D87" s="68"/>
-    </row>
-    <row r="89" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="75" t="s">
-        <v>2</v>
-      </c>
-      <c r="B89" s="75" t="s">
-        <v>5</v>
-      </c>
-      <c r="C89" s="76" t="s">
-        <v>100</v>
-      </c>
-      <c r="D89" s="68" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="90" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A90" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="B90" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="C90" s="76"/>
-      <c r="D90" s="68"/>
-    </row>
-    <row r="91" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A91" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="B91" s="75" t="s">
-        <v>7</v>
-      </c>
-      <c r="C91" s="76"/>
-      <c r="D91" s="68"/>
-    </row>
-    <row r="92" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="C92" s="76"/>
-      <c r="D92" s="68"/>
-    </row>
-    <row r="94" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A94" s="75" t="s">
-        <v>2</v>
-      </c>
-      <c r="B94" s="75" t="s">
-        <v>5</v>
-      </c>
-      <c r="C94" s="76" t="s">
-        <v>101</v>
-      </c>
-      <c r="D94" s="68" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A95" s="75" t="s">
-        <v>3</v>
-      </c>
-      <c r="B95" s="75" t="s">
-        <v>6</v>
-      </c>
-      <c r="C95" s="76"/>
-      <c r="D95" s="68"/>
-    </row>
-    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A96" s="75" t="s">
-        <v>4</v>
-      </c>
-      <c r="B96" s="75" t="s">
-        <v>7</v>
-      </c>
-      <c r="C96" s="76"/>
-      <c r="D96" s="68"/>
-    </row>
-    <row r="97" spans="3:4" x14ac:dyDescent="0.2">
-      <c r="C97" s="76"/>
-      <c r="D97" s="68"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="12"/>
+      <c r="H54" s="12"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="12"/>
     </row>
   </sheetData>
-  <mergeCells count="45">
-    <mergeCell ref="C89:C92"/>
-    <mergeCell ref="D89:D92"/>
-    <mergeCell ref="C94:C97"/>
-    <mergeCell ref="D94:D97"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="D77:D79"/>
-    <mergeCell ref="C81:C83"/>
-    <mergeCell ref="D81:D83"/>
-    <mergeCell ref="C85:C87"/>
-    <mergeCell ref="D85:D87"/>
-    <mergeCell ref="A67:I67"/>
-    <mergeCell ref="C69:C71"/>
-    <mergeCell ref="D69:D71"/>
-    <mergeCell ref="C73:C75"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="C53:C55"/>
-    <mergeCell ref="D53:D55"/>
-    <mergeCell ref="C57:C60"/>
-    <mergeCell ref="D57:D60"/>
-    <mergeCell ref="C62:C65"/>
-    <mergeCell ref="D62:D65"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="D41:D43"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="D45:D47"/>
-    <mergeCell ref="C49:C51"/>
-    <mergeCell ref="D49:D51"/>
-    <mergeCell ref="C30:C33"/>
-    <mergeCell ref="D30:D33"/>
-    <mergeCell ref="A35:I35"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="D37:D39"/>
+  <mergeCells count="25">
+    <mergeCell ref="C13:C15"/>
+    <mergeCell ref="D13:D15"/>
+    <mergeCell ref="C29:C31"/>
+    <mergeCell ref="D29:D31"/>
+    <mergeCell ref="A3:I3"/>
     <mergeCell ref="C21:C23"/>
     <mergeCell ref="D21:D23"/>
-    <mergeCell ref="D25:D28"/>
-    <mergeCell ref="C25:C28"/>
-    <mergeCell ref="A3:I3"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="C25:C27"/>
+    <mergeCell ref="D25:D27"/>
     <mergeCell ref="D5:D7"/>
     <mergeCell ref="D9:D11"/>
     <mergeCell ref="C5:C7"/>
     <mergeCell ref="C9:C11"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="A34:I34"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="C40:C42"/>
+    <mergeCell ref="D40:D42"/>
+    <mergeCell ref="A45:I45"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="D47:D49"/>
+    <mergeCell ref="C51:C53"/>
+    <mergeCell ref="D51:D53"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/benchmarking/search_for_best_combination/results_basic.xlsx
+++ b/benchmarking/search_for_best_combination/results_basic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4C6BA70-4744-7046-9787-82E746AD60AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C33681-DB34-E047-9FC8-1F0AD9059E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="3" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="100">
   <si>
     <t>MODEL'S TYPE</t>
   </si>
@@ -338,12 +338,6 @@
     <t>pretrained/text_year</t>
   </si>
   <si>
-    <t>trial1/corruption_scheme</t>
-  </si>
-  <si>
-    <t>experiment with pretrained embeddings and different corruption scheme</t>
-  </si>
-  <si>
     <t>experiment with pretrained embeddings, basic sampler and downsampling the major class</t>
   </si>
   <si>
@@ -356,7 +350,37 @@
     <t>trial1/downsampling_bernoulli</t>
   </si>
   <si>
-    <t>experiment with  basic sampler and downsampling the major class</t>
+    <t>experiment with pretrained embeddings and basic sampler with different corruption scheme</t>
+  </si>
+  <si>
+    <t>trial1/basic_sampler</t>
+  </si>
+  <si>
+    <t>trial1/down_basic_focal</t>
+  </si>
+  <si>
+    <t>experiment with pretrained embeddings + basic sampler + downsampling + focal loss</t>
+  </si>
+  <si>
+    <t>trial1/down_basic_soft_margin</t>
+  </si>
+  <si>
+    <t>experiment with pretrained embeddings + basic sampler + downsampling + Soft Margin Ranking Loss</t>
+  </si>
+  <si>
+    <t>trial1/down_basic_hinge</t>
+  </si>
+  <si>
+    <t>experiment with pretrained embeddings + basic sampler + downsampling + Soft Pointwise Hinge Loss</t>
+  </si>
+  <si>
+    <t>trial1/down_basic_focal_reg</t>
+  </si>
+  <si>
+    <t>experiment with pretrained embeddings + basic sampler + downsampling + focal loss + norm limit regularizer</t>
+  </si>
+  <si>
+    <t>experiment with basic sampler and downsampling the major class</t>
   </si>
 </sst>
 </file>
@@ -366,7 +390,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0000000000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -407,6 +431,13 @@
       <b/>
       <i/>
       <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -517,7 +548,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -543,9 +574,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -681,33 +709,36 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -717,17 +748,38 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1057,11 +1109,11 @@
     <col min="3" max="3" width="27.83203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="42.1640625" style="4" customWidth="1"/>
     <col min="5" max="5" width="45.6640625" style="4" customWidth="1"/>
-    <col min="6" max="6" width="24" style="12" customWidth="1"/>
-    <col min="7" max="7" width="23.1640625" style="12" customWidth="1"/>
-    <col min="8" max="8" width="27.5" style="12" customWidth="1"/>
-    <col min="9" max="9" width="27.33203125" style="12" customWidth="1"/>
-    <col min="10" max="10" width="31.33203125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="24" style="11" customWidth="1"/>
+    <col min="7" max="7" width="23.1640625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="27.5" style="11" customWidth="1"/>
+    <col min="9" max="9" width="27.33203125" style="11" customWidth="1"/>
+    <col min="10" max="10" width="31.33203125" style="11" customWidth="1"/>
     <col min="11" max="11" width="68.33203125" style="3" customWidth="1"/>
     <col min="12" max="16384" width="51.33203125" style="1"/>
   </cols>
@@ -1082,19 +1134,19 @@
       <c r="E1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="12" t="s">
         <v>58</v>
       </c>
       <c r="K1" s="7" t="s">
@@ -1109,7 +1161,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="60" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="59" t="s">
@@ -1118,22 +1170,22 @@
       <c r="E2" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="11">
         <v>8.4372003799999998E-2</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="11">
         <v>2.1093001000000002E-3</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="11">
         <v>0.3766059444</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>0.54643480580000003</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="11">
         <v>0.51636704079999995</v>
       </c>
-      <c r="K2" s="57" t="s">
+      <c r="K2" s="62" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1144,25 +1196,25 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="12">
+      <c r="C3" s="56"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="11">
         <v>5.23489933E-2</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="11">
         <v>1.6299137E-3</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="11">
         <v>0.34285714290000002</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="11">
         <v>0.51505644009999996</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3" s="11">
         <v>0.49172142549999998</v>
       </c>
-      <c r="K3" s="58"/>
+      <c r="K3" s="63"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1171,25 +1223,25 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="12">
+      <c r="C4" s="56"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="11">
         <v>3.73921381E-2</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="11">
         <v>3.4515819999999999E-3</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <v>0.1369127517</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <v>0.54488705100000001</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="11">
         <v>0.44867621930000001</v>
       </c>
-      <c r="K4" s="58"/>
+      <c r="K4" s="63"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -1198,31 +1250,31 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="56" t="s">
+      <c r="E6" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="11">
         <v>4.6273232400000003E-2</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="11">
         <v>2.9699176000000001E-3</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <v>0.32420003829999999</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <v>0.51285961440000005</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="11">
         <v>0.49915964429999998</v>
       </c>
-      <c r="K6" s="58" t="s">
+      <c r="K6" s="63" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1233,25 +1285,25 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="12">
+      <c r="C7" s="56"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="11">
         <v>2.7399884999999999E-2</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="11">
         <v>3.9279555000000001E-3</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <v>0.20981030849999999</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <v>0.5043243369</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="11">
         <v>0.48493602559999999</v>
       </c>
-      <c r="K7" s="58"/>
+      <c r="K7" s="63"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -1260,39 +1312,39 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="12">
+      <c r="C8" s="56"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="11">
         <v>2.4717378799999998E-2</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="11">
         <v>6.8978731000000001E-3</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="11">
         <v>8.8905920700000002E-2</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="11">
         <v>0.51459009440000003</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="11">
         <v>0.43282600290000001</v>
       </c>
-      <c r="K8" s="58"/>
+      <c r="K8" s="63"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="61" t="s">
+      <c r="A10" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
       <c r="K10" s="5"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -1302,31 +1354,31 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="56" t="s">
+      <c r="D12" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="56" t="s">
+      <c r="E12" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="11">
         <v>0.32182769280000001</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="11">
         <v>0.25021795990000001</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="11">
         <v>0.40326543549999999</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="11">
         <v>0.47915581369999999</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="11">
         <v>0.45356946819999999</v>
       </c>
-      <c r="K12" s="58" t="s">
+      <c r="K12" s="63" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1337,25 +1389,25 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="60"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="12">
+      <c r="C13" s="56"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="11">
         <v>5.4569232000000002E-2</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="11">
         <v>7.2124909999999997E-3</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="11">
         <v>0.16739319969999999</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="11">
         <v>0.39316097770000002</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="11">
         <v>0.2490125493</v>
       </c>
-      <c r="K13" s="58"/>
+      <c r="K13" s="63"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -1364,25 +1416,25 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="12">
+      <c r="C14" s="56"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="11">
         <v>0.2933740192</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="11">
         <v>0.29420622969999999</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="11">
         <v>1.05413331E-2</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="11">
         <v>0.59562815150000004</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="11">
         <v>0.33911636109999999</v>
       </c>
-      <c r="K14" s="58"/>
+      <c r="K14" s="63"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -1391,31 +1443,31 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="60" t="s">
+      <c r="C16" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="56" t="s">
+      <c r="D16" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="56" t="s">
+      <c r="E16" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="11">
         <v>0.31562554079999999</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="11">
         <v>0.21534867630000001</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="11">
         <v>0.53452154350000003</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="11">
         <v>0.84286526129999995</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="11">
         <v>0.46862206229999998</v>
       </c>
-      <c r="K16" s="58" t="s">
+      <c r="K16" s="63" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1426,25 +1478,25 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="60"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="12">
+      <c r="C17" s="56"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="11">
         <v>0.2220972487</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="11">
         <v>1.9164215200000001E-2</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="11">
         <v>0.43770548539999998</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="11">
         <v>0.68263091610000004</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="11">
         <v>0.61463971539999995</v>
       </c>
-      <c r="K17" s="58"/>
+      <c r="K17" s="63"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -1453,25 +1505,25 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="12">
+      <c r="C18" s="56"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="11">
         <v>0.12510815019999999</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="11">
         <v>0.27396608410000001</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="11">
         <v>7.7608582800000006E-2</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="11">
         <v>0.6107635682</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="11">
         <v>0.40298454760000002</v>
       </c>
-      <c r="K18" s="58"/>
+      <c r="K18" s="63"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -1480,31 +1532,31 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="60" t="s">
+      <c r="C20" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="56" t="s">
+      <c r="D20" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="56" t="s">
+      <c r="E20" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="11">
         <v>0.40934262240000002</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="11">
         <v>0.22999285459999999</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="11">
         <v>0.49758842440000001</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="11">
         <v>0.86018151249999997</v>
       </c>
-      <c r="J20" s="12">
+      <c r="J20" s="11">
         <v>0.42112340529999998</v>
       </c>
-      <c r="K20" s="58" t="s">
+      <c r="K20" s="63" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1515,25 +1567,25 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="12">
+      <c r="C21" s="56"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="11">
         <v>0.28648624509999998</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="11">
         <v>3.9299749999999996E-3</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="11">
         <v>0.58958556630000003</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="11">
         <v>0.79611147660000003</v>
       </c>
-      <c r="J21" s="20">
+      <c r="J21" s="19">
         <v>0.71830903779999999</v>
       </c>
-      <c r="K21" s="58"/>
+      <c r="K21" s="63"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -1542,22 +1594,22 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="12">
+      <c r="C22" s="56"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="11">
         <v>4.4658810000000002E-4</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="11">
         <v>8.9317610000000001E-4</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="11">
         <v>0.62501060450000001</v>
       </c>
-      <c r="J22" s="12">
+      <c r="J22" s="11">
         <v>0.41851161510000001</v>
       </c>
-      <c r="K22" s="58"/>
+      <c r="K22" s="63"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -1566,28 +1618,28 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="60" t="s">
+      <c r="C24" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="56" t="s">
+      <c r="D24" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="56" t="s">
+      <c r="E24" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="11">
         <v>0.3522151899</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="11">
         <v>0.21751054850000001</v>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="11">
         <v>0.3972046414</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="11">
         <v>0.66857872799999996</v>
       </c>
-      <c r="J24" s="12">
+      <c r="J24" s="11">
         <v>0.553198258</v>
       </c>
     </row>
@@ -1598,22 +1650,22 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="60"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="12">
+      <c r="C25" s="56"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="11">
         <v>0.1240506329</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="11">
         <v>9.2827003999999998E-3</v>
       </c>
-      <c r="H25" s="12">
+      <c r="H25" s="11">
         <v>0.29720464140000002</v>
       </c>
-      <c r="I25" s="12">
+      <c r="I25" s="11">
         <v>0.57148156900000002</v>
       </c>
-      <c r="J25" s="12">
+      <c r="J25" s="11">
         <v>0.27348452600000001</v>
       </c>
     </row>
@@ -1624,22 +1676,22 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="60"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="12">
+      <c r="C26" s="56"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="11">
         <v>0.13367616030000001</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="11">
         <v>0.19485759499999999</v>
       </c>
-      <c r="H26" s="12">
+      <c r="H26" s="11">
         <v>0.23855485230000001</v>
       </c>
-      <c r="I26" s="12">
+      <c r="I26" s="11">
         <v>0.57330833420000005</v>
       </c>
-      <c r="J26" s="12">
+      <c r="J26" s="11">
         <v>0.31188195969999999</v>
       </c>
     </row>
@@ -1650,28 +1702,28 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="60" t="s">
+      <c r="C28" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="56" t="s">
+      <c r="D28" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="56" t="s">
+      <c r="E28" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="11">
         <v>0.43023443379999998</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="11">
         <v>0.192117432</v>
       </c>
-      <c r="H28" s="12">
+      <c r="H28" s="11">
         <v>0.38321324870000001</v>
       </c>
-      <c r="I28" s="12">
+      <c r="I28" s="11">
         <v>0.57140164410000005</v>
       </c>
-      <c r="J28" s="12">
+      <c r="J28" s="11">
         <v>0.48018954860000002</v>
       </c>
     </row>
@@ -1682,22 +1734,22 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="60"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="12">
+      <c r="C29" s="56"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="11">
         <v>0.20128508440000001</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="11">
         <v>5.6457683999999999E-3</v>
       </c>
-      <c r="H29" s="12">
+      <c r="H29" s="11">
         <v>0.3749865577</v>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="11">
         <v>0.64851705189999997</v>
       </c>
-      <c r="J29" s="12">
+      <c r="J29" s="11">
         <v>0.34708162910000001</v>
       </c>
     </row>
@@ -1708,22 +1760,22 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="60"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="12">
+      <c r="C30" s="56"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="11">
         <v>0.1974137004</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="11">
         <v>0.1558232068</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H30" s="11">
         <v>0.42434670390000001</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I30" s="11">
         <v>0.55498300369999998</v>
       </c>
-      <c r="J30" s="12">
+      <c r="J30" s="11">
         <v>0.40242775050000001</v>
       </c>
     </row>
@@ -1734,28 +1786,28 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="60" t="s">
+      <c r="C32" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="56" t="s">
+      <c r="D32" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="56" t="s">
+      <c r="E32" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="19">
         <v>0.48067164600000001</v>
       </c>
-      <c r="G32" s="12">
+      <c r="G32" s="11">
         <v>1.7532356400000001E-2</v>
       </c>
-      <c r="H32" s="12">
+      <c r="H32" s="11">
         <v>0.74177547180000003</v>
       </c>
-      <c r="I32" s="20">
+      <c r="I32" s="19">
         <v>0.92762878579999997</v>
       </c>
-      <c r="J32" s="12">
+      <c r="J32" s="11">
         <v>0.50945505889999998</v>
       </c>
     </row>
@@ -1766,22 +1818,22 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="60"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="12">
+      <c r="C33" s="56"/>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="11">
         <v>0.4661326187</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="11">
         <v>2.8023262399999999E-2</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="11">
         <v>0.68310622040000002</v>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="11">
         <v>0.91064647099999996</v>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="11">
         <v>0.69192758759999995</v>
       </c>
     </row>
@@ -1792,22 +1844,22 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="60"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="12">
+      <c r="C34" s="56"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="11">
         <v>2.2806319999999999E-4</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="11">
         <v>6.6708478E-3</v>
       </c>
-      <c r="H34" s="12">
+      <c r="H34" s="11">
         <v>2.8507899999999999E-4</v>
       </c>
-      <c r="I34" s="12">
+      <c r="I34" s="11">
         <v>0.60886531479999995</v>
       </c>
-      <c r="J34" s="12">
+      <c r="J34" s="11">
         <v>0.25644525289999998</v>
       </c>
     </row>
@@ -1818,28 +1870,28 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="60" t="s">
+      <c r="C36" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="56" t="s">
+      <c r="D36" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="56" t="s">
+      <c r="E36" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="11">
         <v>0.35357443570000002</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G36" s="11">
         <v>0.24770458279999999</v>
       </c>
-      <c r="H36" s="20">
+      <c r="H36" s="19">
         <v>0.78124373520000001</v>
       </c>
-      <c r="I36" s="12">
+      <c r="I36" s="11">
         <v>0.91809339690000002</v>
       </c>
-      <c r="J36" s="12">
+      <c r="J36" s="11">
         <v>0.57959106510000002</v>
       </c>
     </row>
@@ -1850,22 +1902,22 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="60"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="12">
+      <c r="C37" s="56"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="11">
         <v>0.29922617379999999</v>
       </c>
-      <c r="G37" s="12">
+      <c r="G37" s="11">
         <v>9.7028988999999996E-3</v>
       </c>
-      <c r="H37" s="12">
+      <c r="H37" s="11">
         <v>0.49821578929999999</v>
       </c>
-      <c r="I37" s="12">
+      <c r="I37" s="11">
         <v>0.76520140349999999</v>
       </c>
-      <c r="J37" s="12">
+      <c r="J37" s="11">
         <v>0.55784537280000002</v>
       </c>
     </row>
@@ -1876,38 +1928,38 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="60"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="12">
+      <c r="C38" s="56"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="11">
         <v>0.1553265707</v>
       </c>
-      <c r="G38" s="12">
+      <c r="G38" s="11">
         <v>0.18351309090000001</v>
       </c>
-      <c r="H38" s="12">
+      <c r="H38" s="11">
         <v>8.5040695999999999E-2</v>
       </c>
-      <c r="I38" s="12">
+      <c r="I38" s="11">
         <v>0.54136288020000001</v>
       </c>
-      <c r="J38" s="12">
+      <c r="J38" s="11">
         <v>0.28370905870000002</v>
       </c>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="61" t="s">
+      <c r="A40" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="61"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="61"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
       <c r="E40" s="5"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="14"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
       <c r="K40" s="5"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
@@ -1917,31 +1969,31 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="60" t="s">
+      <c r="C42" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="56" t="s">
+      <c r="D42" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="56" t="s">
+      <c r="E42" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="F42" s="12">
+      <c r="F42" s="11">
         <v>0.2476532303</v>
       </c>
-      <c r="G42" s="12">
+      <c r="G42" s="11">
         <v>0.1847440246</v>
       </c>
-      <c r="H42" s="12">
+      <c r="H42" s="11">
         <v>0.59296363490000004</v>
       </c>
-      <c r="I42" s="12">
+      <c r="I42" s="11">
         <v>0.78190933159999998</v>
       </c>
-      <c r="J42" s="12">
+      <c r="J42" s="11">
         <v>0.50415219909999998</v>
       </c>
-      <c r="K42" s="58" t="s">
+      <c r="K42" s="63" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1952,25 +2004,25 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="60"/>
-      <c r="D43" s="56"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="12">
+      <c r="C43" s="56"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="11">
         <v>0.27900922929999999</v>
       </c>
-      <c r="G43" s="12">
+      <c r="G43" s="11">
         <v>0</v>
       </c>
-      <c r="H43" s="12">
+      <c r="H43" s="11">
         <v>0.47771554779999997</v>
       </c>
-      <c r="I43" s="12">
+      <c r="I43" s="11">
         <v>0.74131101600000004</v>
       </c>
-      <c r="J43" s="12">
+      <c r="J43" s="11">
         <v>0.6867986989</v>
       </c>
-      <c r="K43" s="58"/>
+      <c r="K43" s="63"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -1979,25 +2031,25 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="60"/>
-      <c r="D44" s="56"/>
-      <c r="E44" s="56"/>
-      <c r="F44" s="12">
+      <c r="C44" s="56"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="11">
         <v>1.08858563E-2</v>
       </c>
-      <c r="G44" s="12">
+      <c r="G44" s="11">
         <v>0.15173148219999999</v>
       </c>
-      <c r="H44" s="12">
+      <c r="H44" s="11">
         <v>4.6777628799999998E-2</v>
       </c>
-      <c r="I44" s="12">
+      <c r="I44" s="11">
         <v>0.61174020819999997</v>
       </c>
-      <c r="J44" s="12">
+      <c r="J44" s="11">
         <v>0.34279394219999998</v>
       </c>
-      <c r="K44" s="58"/>
+      <c r="K44" s="63"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -2006,31 +2058,31 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="60" t="s">
+      <c r="C46" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="56" t="s">
+      <c r="D46" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="56" t="s">
+      <c r="E46" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="11">
         <v>0.36310557049999997</v>
       </c>
-      <c r="G46" s="12">
+      <c r="G46" s="11">
         <v>8.7186364999999998E-3</v>
       </c>
-      <c r="H46" s="12">
+      <c r="H46" s="11">
         <v>0.53274420069999995</v>
       </c>
-      <c r="I46" s="12">
+      <c r="I46" s="11">
         <v>0.81572219999999995</v>
       </c>
-      <c r="J46" s="12">
+      <c r="J46" s="11">
         <v>0.43511184339999998</v>
       </c>
-      <c r="K46" s="58" t="s">
+      <c r="K46" s="63" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2041,25 +2093,25 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="60"/>
-      <c r="D47" s="56"/>
-      <c r="E47" s="56"/>
-      <c r="F47" s="12">
+      <c r="C47" s="56"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="11">
         <v>0.36941770550000003</v>
       </c>
-      <c r="G47" s="12">
+      <c r="G47" s="11">
         <v>1.5464730899999999E-2</v>
       </c>
-      <c r="H47" s="12">
+      <c r="H47" s="11">
         <v>0.56351585920000002</v>
       </c>
-      <c r="I47" s="12">
+      <c r="I47" s="11">
         <v>0.78861496499999995</v>
       </c>
-      <c r="J47" s="12">
+      <c r="J47" s="11">
         <v>0.67778323610000002</v>
       </c>
-      <c r="K47" s="58"/>
+      <c r="K47" s="63"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -2068,25 +2120,25 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="60"/>
-      <c r="D48" s="56"/>
-      <c r="E48" s="56"/>
-      <c r="F48" s="12">
+      <c r="C48" s="56"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="11">
         <v>7.1050970500000005E-2</v>
       </c>
-      <c r="G48" s="12">
+      <c r="G48" s="11">
         <v>0.2945005523</v>
       </c>
-      <c r="H48" s="12">
+      <c r="H48" s="11">
         <v>0.2473567934</v>
       </c>
-      <c r="I48" s="12">
+      <c r="I48" s="11">
         <v>0.50930333279999995</v>
       </c>
-      <c r="J48" s="12">
+      <c r="J48" s="11">
         <v>0.33626401280000001</v>
       </c>
-      <c r="K48" s="58"/>
+      <c r="K48" s="63"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -2095,28 +2147,28 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="60" t="s">
+      <c r="C50" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="56" t="s">
+      <c r="D50" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="56" t="s">
+      <c r="E50" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="F50" s="12">
+      <c r="F50" s="11">
         <v>0.47069342339999998</v>
       </c>
-      <c r="G50" s="12">
+      <c r="G50" s="11">
         <v>4.9970196699999997E-2</v>
       </c>
-      <c r="H50" s="12">
+      <c r="H50" s="11">
         <v>0.74418835679999995</v>
       </c>
-      <c r="I50" s="12">
+      <c r="I50" s="11">
         <v>0.91550606810000001</v>
       </c>
-      <c r="J50" s="12">
+      <c r="J50" s="11">
         <v>0.57816466190000004</v>
       </c>
     </row>
@@ -2127,22 +2179,22 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="60"/>
-      <c r="D51" s="56"/>
-      <c r="E51" s="56"/>
-      <c r="F51" s="12">
+      <c r="C51" s="56"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="11">
         <v>0.46868170079999999</v>
       </c>
-      <c r="G51" s="12">
+      <c r="G51" s="11">
         <v>4.1699781499999998E-2</v>
       </c>
-      <c r="H51" s="12">
+      <c r="H51" s="11">
         <v>0.61643155179999998</v>
       </c>
-      <c r="I51" s="12">
+      <c r="I51" s="11">
         <v>0.84420971109999998</v>
       </c>
-      <c r="J51" s="12">
+      <c r="J51" s="11">
         <v>0.66572561149999998</v>
       </c>
     </row>
@@ -2153,118 +2205,87 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="60"/>
-      <c r="D52" s="56"/>
-      <c r="E52" s="56"/>
-      <c r="F52" s="12">
+      <c r="C52" s="56"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="57"/>
+      <c r="F52" s="11">
         <v>4.2022650500000001E-2</v>
       </c>
-      <c r="G52" s="20">
+      <c r="G52" s="19">
         <v>0.37070335789999997</v>
       </c>
-      <c r="H52" s="12">
+      <c r="H52" s="11">
         <v>0.13441287499999999</v>
       </c>
-      <c r="I52" s="12">
+      <c r="I52" s="11">
         <v>0.67062795040000001</v>
       </c>
-      <c r="J52" s="12">
+      <c r="J52" s="11">
         <v>0.4546958096</v>
       </c>
     </row>
-    <row r="55" spans="1:11" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="63" t="s">
+    <row r="55" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="63"/>
-      <c r="C55" s="63"/>
-      <c r="D55" s="63"/>
-      <c r="E55" s="42"/>
-      <c r="F55" s="43">
+      <c r="B55" s="55"/>
+      <c r="C55" s="55"/>
+      <c r="D55" s="55"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="42">
         <f>MAX(F2:F52)</f>
         <v>0.48067164600000001</v>
       </c>
-      <c r="G55" s="43">
+      <c r="G55" s="42">
         <f>MAX(G2:G52)</f>
         <v>0.37070335789999997</v>
       </c>
-      <c r="H55" s="43">
+      <c r="H55" s="42">
         <f>MAX(H2:H52)</f>
         <v>0.78124373520000001</v>
       </c>
-      <c r="I55" s="43">
+      <c r="I55" s="42">
         <f>MAX(I2:I52)</f>
         <v>0.92762878579999997</v>
       </c>
-      <c r="J55" s="43">
+      <c r="J55" s="42">
         <f>MAX(J2:J52)</f>
         <v>0.71830903779999999</v>
       </c>
-      <c r="K55" s="44"/>
-    </row>
-    <row r="56" spans="1:11" s="49" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="55" t="s">
+      <c r="K55" s="43"/>
+    </row>
+    <row r="56" spans="1:11" s="48" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="55"/>
-      <c r="C56" s="55"/>
-      <c r="D56" s="55"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="47">
+      <c r="B56" s="61"/>
+      <c r="C56" s="61"/>
+      <c r="D56" s="61"/>
+      <c r="E56" s="45"/>
+      <c r="F56" s="46">
         <f>AVERAGE(F2:F52)</f>
         <v>0.21716488937777773</v>
       </c>
-      <c r="G56" s="47">
+      <c r="G56" s="46">
         <f>AVERAGE(G2:G52)</f>
         <v>0.10282875713333334</v>
       </c>
-      <c r="H56" s="47">
+      <c r="H56" s="46">
         <f>AVERAGE(H2:H52)</f>
         <v>0.37310816464857149</v>
       </c>
-      <c r="I56" s="47">
+      <c r="I56" s="46">
         <f>AVERAGE(I2:I52)</f>
         <v>0.66562983308333334</v>
       </c>
-      <c r="J56" s="47">
+      <c r="J56" s="46">
         <f>AVERAGE(J2:J52)</f>
         <v>0.46911950566388888</v>
       </c>
-      <c r="K56" s="48"/>
+      <c r="K56" s="47"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="E46:E48"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="E50:E52"/>
     <mergeCell ref="K2:K4"/>
@@ -2281,6 +2302,37 @@
     <mergeCell ref="E42:E44"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E6:E8"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="A40:D40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2288,7 +2340,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7ED27533-334C-8545-BBC4-8C9F3EE864EF}">
-  <dimension ref="A1:N60"/>
+  <dimension ref="A1:L56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="51.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="26.1640625" style="1" customWidth="1"/>
@@ -2296,7 +2348,7 @@
     <col min="3" max="3" width="34.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="35.33203125" style="4" customWidth="1"/>
     <col min="5" max="5" width="44.33203125" style="4" customWidth="1"/>
-    <col min="6" max="6" width="24" style="12" customWidth="1"/>
+    <col min="6" max="6" width="24" style="11" customWidth="1"/>
     <col min="7" max="7" width="23.1640625" style="1" customWidth="1"/>
     <col min="8" max="8" width="27.5" style="1" customWidth="1"/>
     <col min="9" max="9" width="27.33203125" style="1" customWidth="1"/>
@@ -2321,7 +2373,7 @@
       <c r="E1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>53</v>
       </c>
       <c r="G1" s="7" t="s">
@@ -2348,7 +2400,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="60" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="59" t="s">
@@ -2357,22 +2409,22 @@
       <c r="E2" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="12">
+      <c r="F2" s="11">
         <v>7.2387344199999995E-2</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="11">
         <v>1.6299137E-3</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="11">
         <v>0.3039309684</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>0.49568405119999998</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="11">
         <v>0.49946558660000001</v>
       </c>
-      <c r="K2" s="57" t="s">
+      <c r="K2" s="62" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2383,25 +2435,25 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="12">
+      <c r="C3" s="56"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="11">
         <v>3.1543624200000002E-2</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="11">
         <v>2.3969319E-3</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="11">
         <v>0.33557046979999999</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="11">
         <v>0.52995509259999996</v>
       </c>
-      <c r="J3" s="20">
+      <c r="J3" s="19">
         <v>0.51222158829999997</v>
       </c>
-      <c r="K3" s="58"/>
+      <c r="K3" s="63"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2410,31 +2462,31 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="12">
+      <c r="C4" s="56"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="11">
         <v>1.70661553E-2</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="11">
         <v>4.6021092999999997E-3</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <v>0.2404602109</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <v>0.58040054529999996</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="11">
         <v>0.46528456299999998</v>
       </c>
-      <c r="K4" s="58"/>
+      <c r="K4" s="63"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
+      <c r="G5" s="11"/>
+      <c r="H5" s="11"/>
+      <c r="I5" s="11"/>
+      <c r="J5" s="11"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -2443,31 +2495,31 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="56" t="s">
+      <c r="E6" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="11">
         <v>4.5315194500000003E-2</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="11">
         <v>2.3950948999999998E-3</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <v>0.4433799578</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <v>0.50993328660000004</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="11">
         <v>0.5044039011</v>
       </c>
-      <c r="K6" s="58" t="s">
+      <c r="K6" s="63" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2478,25 +2530,25 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="12">
+      <c r="C7" s="56"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="11">
         <v>4.3303314799999999E-2</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="11">
         <v>1.7244682999999999E-3</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <v>0.20195439740000001</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <v>0.45895427179999998</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="11">
         <v>0.43858537390000002</v>
       </c>
-      <c r="K7" s="58"/>
+      <c r="K7" s="63"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -2505,52 +2557,52 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="12">
+      <c r="C8" s="56"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="11">
         <v>1.6669860099999999E-2</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="11">
         <v>8.6223409999999995E-4</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="11">
         <v>0.3402950757</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="11">
         <v>0.54925118539999995</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="11">
         <v>0.47867128799999997</v>
       </c>
-      <c r="K8" s="58"/>
+      <c r="K8" s="63"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G9" s="12"/>
-      <c r="H9" s="12"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="12"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="11"/>
+      <c r="I9" s="11"/>
+      <c r="J9" s="11"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="61" t="s">
+      <c r="A10" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
       <c r="K10" s="5"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="12"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="11"/>
+      <c r="I11" s="11"/>
+      <c r="J11" s="11"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
@@ -2559,31 +2611,31 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="56" t="s">
+      <c r="D12" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="56" t="s">
+      <c r="E12" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="11">
         <v>7.0853307800000001E-2</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="11">
         <v>1.1505273E-3</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="11">
         <v>0.43815915630000002</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="11">
         <v>0.53972968129999999</v>
       </c>
-      <c r="J12" s="12">
+      <c r="J12" s="11">
         <v>0.49020679299999997</v>
       </c>
-      <c r="K12" s="58" t="s">
+      <c r="K12" s="63" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2594,25 +2646,25 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="60"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="12">
+      <c r="C13" s="56"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="11">
         <v>1.0546500000000001E-3</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="11">
         <v>3.2598274E-3</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="11">
         <v>0.3911792905</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="11">
         <v>0.51193921760000005</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="11">
         <v>0.48910588160000001</v>
       </c>
-      <c r="K13" s="58"/>
+      <c r="K13" s="63"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2621,31 +2673,31 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="12">
+      <c r="C14" s="56"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="11">
         <v>2.876318E-4</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="11">
         <v>1.725791E-3</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="11">
         <v>4.18024928E-2</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="11">
         <v>0.45718950790000001</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="11">
         <v>0.46995530219999998</v>
       </c>
-      <c r="K14" s="58"/>
+      <c r="K14" s="63"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G15" s="12"/>
-      <c r="H15" s="12"/>
-      <c r="I15" s="12"/>
-      <c r="J15" s="12"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="11"/>
+      <c r="I15" s="11"/>
+      <c r="J15" s="11"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -2654,31 +2706,31 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="60" t="s">
+      <c r="C16" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="56" t="s">
+      <c r="D16" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="56" t="s">
+      <c r="E16" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="11">
         <v>5.6663470799999997E-2</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="11">
         <v>9.2042185999999995E-3</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="11">
         <v>0.42109300100000002</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="11">
         <v>0.81920023559999999</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="11">
         <v>0.44493382850000002</v>
       </c>
-      <c r="K16" s="58" t="s">
+      <c r="K16" s="63" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2689,25 +2741,25 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="60"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="20">
+      <c r="C17" s="56"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="19">
         <v>8.2166826499999998E-2</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="11">
         <v>9.5877299999999998E-5</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="11">
         <v>0.42070949190000001</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="11">
         <v>0.81290296760000003</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="11">
         <v>0.4417925586</v>
       </c>
-      <c r="K17" s="58"/>
+      <c r="K17" s="63"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -2716,31 +2768,31 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="12">
+      <c r="C18" s="56"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="11">
         <v>7.6701820000000002E-4</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="11">
         <v>2.0134227999999998E-3</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="11">
         <v>0.1702780441</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="11">
         <v>0.46493483429999999</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="11">
         <v>0.47127738250000001</v>
       </c>
-      <c r="K18" s="58"/>
+      <c r="K18" s="63"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -2749,31 +2801,31 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="60" t="s">
+      <c r="C20" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="56" t="s">
+      <c r="D20" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="56" t="s">
+      <c r="E20" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="11">
         <v>2.0997123699999998E-2</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="11">
         <v>2.3010547000000001E-3</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="11">
         <v>0.3390220518</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="11">
         <v>0.80129368079999996</v>
       </c>
-      <c r="J20" s="12">
+      <c r="J20" s="11">
         <v>0.42862661320000001</v>
       </c>
-      <c r="K20" s="58" t="s">
+      <c r="K20" s="63" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2784,25 +2836,25 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="12">
+      <c r="C21" s="56"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="11">
         <v>3.2598274E-3</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="11">
         <v>4.1227229000000004E-3</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="11">
         <v>0.25656759350000002</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="11">
         <v>0.5509203869</v>
       </c>
-      <c r="J21" s="12">
+      <c r="J21" s="11">
         <v>0.4742471747</v>
       </c>
-      <c r="K21" s="58"/>
+      <c r="K21" s="63"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -2811,31 +2863,31 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="12">
+      <c r="C22" s="56"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="11">
         <v>0</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="11">
         <v>9.5877280000000004E-4</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="11">
         <v>0.35321188879999998</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="11">
         <v>0.55203139629999998</v>
       </c>
-      <c r="J22" s="12">
+      <c r="J22" s="11">
         <v>0.4477544779</v>
       </c>
-      <c r="K22" s="58"/>
+      <c r="K22" s="63"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="G23" s="12"/>
-      <c r="H23" s="12"/>
-      <c r="I23" s="12"/>
-      <c r="J23" s="12"/>
+      <c r="G23" s="11"/>
+      <c r="H23" s="11"/>
+      <c r="I23" s="11"/>
+      <c r="J23" s="11"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -2844,28 +2896,28 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="60" t="s">
+      <c r="C24" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="56" t="s">
+      <c r="D24" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="56" t="s">
+      <c r="E24" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="11">
         <v>4.7363374899999998E-2</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="11">
         <v>6.0402685000000003E-3</v>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="11">
         <v>0.59443911790000004</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="11">
         <v>0.74501811169999999</v>
       </c>
-      <c r="J24" s="12">
+      <c r="J24" s="11">
         <v>0.49716885890000001</v>
       </c>
     </row>
@@ -2876,22 +2928,22 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="60"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="12">
+      <c r="C25" s="56"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="11">
         <v>6.8744007699999998E-2</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="11">
         <v>6.1361456999999998E-3</v>
       </c>
-      <c r="H25" s="12">
+      <c r="H25" s="11">
         <v>0.44966442950000002</v>
       </c>
-      <c r="I25" s="12">
+      <c r="I25" s="11">
         <v>0.79752785130000003</v>
       </c>
-      <c r="J25" s="12">
+      <c r="J25" s="11">
         <v>0.44321827860000002</v>
       </c>
     </row>
@@ -2902,28 +2954,28 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="60"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="12">
+      <c r="C26" s="56"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="11">
         <v>2.876318E-4</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="11">
         <v>9.5877280000000004E-4</v>
       </c>
-      <c r="H26" s="12"/>
-      <c r="I26" s="12">
+      <c r="H26" s="11"/>
+      <c r="I26" s="11">
         <v>0.47498283299999999</v>
       </c>
-      <c r="J26" s="12">
+      <c r="J26" s="11">
         <v>0.45436830360000002</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="G27" s="12"/>
-      <c r="H27" s="12"/>
-      <c r="I27" s="12"/>
-      <c r="J27" s="12"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="11"/>
+      <c r="I27" s="11"/>
+      <c r="J27" s="11"/>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
@@ -2932,28 +2984,28 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="60" t="s">
+      <c r="C28" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="56" t="s">
+      <c r="D28" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="56" t="s">
+      <c r="E28" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="11">
         <v>2.6270373900000001E-2</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="11">
         <v>1.0546500999999999E-3</v>
       </c>
-      <c r="H28" s="12">
+      <c r="H28" s="11">
         <v>0.39424736339999999</v>
       </c>
-      <c r="I28" s="12">
+      <c r="I28" s="11">
         <v>0.85301524640000004</v>
       </c>
-      <c r="J28" s="12">
+      <c r="J28" s="11">
         <v>0.43387269899999997</v>
       </c>
     </row>
@@ -2964,22 +3016,22 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="60"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="12">
+      <c r="C29" s="56"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="11">
         <v>2.9721956000000002E-3</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="11">
         <v>5.6567594000000001E-3</v>
       </c>
-      <c r="H29" s="12">
+      <c r="H29" s="11">
         <v>0.2316395014</v>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="11">
         <v>0.55081401399999996</v>
       </c>
-      <c r="J29" s="12">
+      <c r="J29" s="11">
         <v>0.46885872319999999</v>
       </c>
     </row>
@@ -2990,30 +3042,30 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="60"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="12">
+      <c r="C30" s="56"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="11">
         <v>0</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="11">
         <v>2.1093001000000002E-3</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H30" s="11">
         <v>0.1474592522</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I30" s="11">
         <v>0.49817440019999998</v>
       </c>
-      <c r="J30" s="12">
+      <c r="J30" s="11">
         <v>0.48203369289999998</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
+      <c r="G31" s="11"/>
+      <c r="H31" s="11"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
@@ -3022,28 +3074,28 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="60" t="s">
+      <c r="C32" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="56" t="s">
+      <c r="D32" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="56" t="s">
+      <c r="E32" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="11">
         <v>2.6558005799999999E-2</v>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="19">
         <v>7.9290508100000004E-2</v>
       </c>
-      <c r="H32" s="12">
+      <c r="H32" s="11">
         <v>0.42742090119999998</v>
       </c>
-      <c r="I32" s="20">
+      <c r="I32" s="19">
         <v>0.89827844270000001</v>
       </c>
-      <c r="J32" s="12">
+      <c r="J32" s="11">
         <v>0.34608643859999999</v>
       </c>
     </row>
@@ -3054,22 +3106,22 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="60"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="12">
+      <c r="C33" s="56"/>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="11">
         <v>6.2032598299999998E-2</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="11">
         <v>9.9712367999999999E-3</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="11">
         <v>0.22109300100000001</v>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="11">
         <v>0.83613638540000002</v>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="11">
         <v>0.38036204509999999</v>
       </c>
     </row>
@@ -3080,30 +3132,30 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="60"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="12">
+      <c r="C34" s="56"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="11">
         <v>1.1505273E-3</v>
       </c>
-      <c r="H34" s="20">
+      <c r="H34" s="19">
         <v>0.6839884947</v>
       </c>
-      <c r="I34" s="12">
+      <c r="I34" s="11">
         <v>0.50245971249999999</v>
       </c>
-      <c r="J34" s="12">
+      <c r="J34" s="11">
         <v>0.48181687890000002</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="G35" s="12"/>
-      <c r="H35" s="12"/>
-      <c r="I35" s="12"/>
-      <c r="J35" s="12"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="11"/>
+      <c r="I35" s="11"/>
+      <c r="J35" s="11"/>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
@@ -3112,28 +3164,28 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="60" t="s">
+      <c r="C36" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="56" t="s">
+      <c r="D36" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="56" t="s">
+      <c r="E36" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="11">
         <v>3.07766059E-2</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G36" s="11">
         <v>7.7660593999999998E-3</v>
       </c>
-      <c r="H36" s="12">
+      <c r="H36" s="11">
         <v>0.51179290509999997</v>
       </c>
-      <c r="I36" s="12">
+      <c r="I36" s="11">
         <v>0.86808922990000004</v>
       </c>
-      <c r="J36" s="12">
+      <c r="J36" s="11">
         <v>0.39241230500000002</v>
       </c>
     </row>
@@ -3144,22 +3196,22 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="60"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="12">
+      <c r="C37" s="56"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="11">
         <v>6.1361456999999998E-3</v>
       </c>
-      <c r="G37" s="12">
+      <c r="G37" s="11">
         <v>2.08053692E-2</v>
       </c>
-      <c r="H37" s="12">
+      <c r="H37" s="11">
         <v>0.26634707569999999</v>
       </c>
-      <c r="I37" s="12">
+      <c r="I37" s="11">
         <v>0.75254151199999997</v>
       </c>
-      <c r="J37" s="12">
+      <c r="J37" s="11">
         <v>0.40266426020000001</v>
       </c>
     </row>
@@ -3170,51 +3222,51 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="60"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="12">
+      <c r="C38" s="56"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="11">
         <v>1.917546E-4</v>
       </c>
-      <c r="G38" s="12">
+      <c r="G38" s="11">
         <v>1.3422818999999999E-3</v>
       </c>
-      <c r="H38" s="12">
+      <c r="H38" s="11">
         <v>0.10354745930000001</v>
       </c>
-      <c r="I38" s="12">
+      <c r="I38" s="11">
         <v>0.48979562119999998</v>
       </c>
-      <c r="J38" s="12">
+      <c r="J38" s="11">
         <v>0.4776966775</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="G39" s="12"/>
-      <c r="H39" s="12"/>
-      <c r="I39" s="12"/>
-      <c r="J39" s="12"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="11"/>
+      <c r="I39" s="11"/>
+      <c r="J39" s="11"/>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="61" t="s">
+      <c r="A40" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="61"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="61"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
       <c r="E40" s="5"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="14"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
       <c r="K40" s="5"/>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="G41" s="12"/>
-      <c r="H41" s="12"/>
-      <c r="I41" s="12"/>
-      <c r="J41" s="12"/>
+      <c r="G41" s="11"/>
+      <c r="H41" s="11"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
@@ -3223,31 +3275,31 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="60" t="s">
+      <c r="C42" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="56" t="s">
+      <c r="D42" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="56" t="s">
+      <c r="E42" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="F42" s="12">
+      <c r="F42" s="11">
         <v>4.1387238899999998E-2</v>
       </c>
-      <c r="G42" s="12">
+      <c r="G42" s="11">
         <v>2.6825063E-3</v>
       </c>
-      <c r="H42" s="12">
+      <c r="H42" s="11">
         <v>0.29526729260000001</v>
       </c>
-      <c r="I42" s="12">
+      <c r="I42" s="11">
         <v>0.71257026599999995</v>
       </c>
-      <c r="J42" s="12">
+      <c r="J42" s="11">
         <v>0.46282180270000001</v>
       </c>
-      <c r="K42" s="58" t="s">
+      <c r="K42" s="63" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3258,25 +3310,25 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="60"/>
-      <c r="D43" s="56"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="12">
+      <c r="C43" s="56"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="11">
         <v>1.18796704E-2</v>
       </c>
-      <c r="G43" s="12">
+      <c r="G43" s="11">
         <v>1.4370569099999999E-2</v>
       </c>
-      <c r="H43" s="12">
+      <c r="H43" s="11">
         <v>0.28434566010000001</v>
       </c>
-      <c r="I43" s="12">
+      <c r="I43" s="11">
         <v>0.74580320710000003</v>
       </c>
-      <c r="J43" s="12">
+      <c r="J43" s="11">
         <v>0.45564674030000002</v>
       </c>
-      <c r="K43" s="58"/>
+      <c r="K43" s="63"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -3285,29 +3337,29 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="60"/>
-      <c r="D44" s="56"/>
-      <c r="E44" s="56"/>
-      <c r="F44" s="12">
+      <c r="C44" s="56"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="11">
         <v>9.5803800000000006E-5</v>
       </c>
-      <c r="G44" s="12">
+      <c r="G44" s="11">
         <v>1.0538418000000001E-3</v>
       </c>
-      <c r="H44" s="12"/>
-      <c r="I44" s="12">
+      <c r="H44" s="11"/>
+      <c r="I44" s="11">
         <v>0.52844348480000003</v>
       </c>
-      <c r="J44" s="12">
+      <c r="J44" s="11">
         <v>0.47630425310000002</v>
       </c>
-      <c r="K44" s="58"/>
+      <c r="K44" s="63"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="G45" s="12"/>
-      <c r="H45" s="12"/>
-      <c r="I45" s="12"/>
-      <c r="J45" s="12"/>
+      <c r="G45" s="11"/>
+      <c r="H45" s="11"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -3316,31 +3368,31 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="60" t="s">
+      <c r="C46" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="56" t="s">
+      <c r="D46" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="56" t="s">
+      <c r="E46" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="11">
         <v>3.1902663300000002E-2</v>
       </c>
-      <c r="G46" s="12">
+      <c r="G46" s="11">
         <v>3.6405442E-3</v>
       </c>
-      <c r="H46" s="12">
+      <c r="H46" s="11">
         <v>0.31270358310000002</v>
       </c>
-      <c r="I46" s="12">
+      <c r="I46" s="11">
         <v>0.72188747200000003</v>
       </c>
-      <c r="J46" s="12">
+      <c r="J46" s="11">
         <v>0.44950493489999999</v>
       </c>
-      <c r="K46" s="58" t="s">
+      <c r="K46" s="63" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3351,25 +3403,25 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="60"/>
-      <c r="D47" s="56"/>
-      <c r="E47" s="56"/>
-      <c r="F47" s="12">
+      <c r="C47" s="56"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="11">
         <v>2.2322284000000001E-2</v>
       </c>
-      <c r="G47" s="12">
+      <c r="G47" s="11">
         <v>7.6643034999999997E-3</v>
       </c>
-      <c r="H47" s="12">
+      <c r="H47" s="11">
         <v>0.38340678290000002</v>
       </c>
-      <c r="I47" s="12">
+      <c r="I47" s="11">
         <v>0.78424036109999995</v>
       </c>
-      <c r="J47" s="12">
+      <c r="J47" s="11">
         <v>0.45333713520000002</v>
       </c>
-      <c r="K47" s="58"/>
+      <c r="K47" s="63"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -3378,289 +3430,189 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="60"/>
-      <c r="D48" s="56"/>
-      <c r="E48" s="56"/>
-      <c r="F48" s="12">
+      <c r="C48" s="56"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="11">
         <v>4.7901900000000002E-4</v>
       </c>
-      <c r="G48" s="12">
+      <c r="G48" s="11">
         <v>1.7244682999999999E-3</v>
       </c>
-      <c r="H48" s="12">
+      <c r="H48" s="11">
         <v>0.1576930446</v>
       </c>
-      <c r="I48" s="12">
+      <c r="I48" s="11">
         <v>0.49315648249999999</v>
       </c>
-      <c r="J48" s="12">
+      <c r="J48" s="11">
         <v>0.47522234359999999</v>
       </c>
-      <c r="K48" s="58"/>
-    </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="G49" s="12"/>
-      <c r="H49" s="12"/>
-      <c r="I49" s="12"/>
-      <c r="J49" s="12"/>
-    </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="K48" s="63"/>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G49" s="11"/>
+      <c r="H49" s="11"/>
+      <c r="I49" s="11"/>
+      <c r="J49" s="11"/>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="60" t="s">
+      <c r="C50" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="56" t="s">
+      <c r="D50" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="56" t="s">
+      <c r="E50" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="F50" s="12">
+      <c r="F50" s="11">
         <v>2.9507568500000001E-2</v>
       </c>
-      <c r="G50" s="12">
+      <c r="G50" s="11">
         <v>3.2573290000000002E-3</v>
       </c>
-      <c r="H50" s="12">
+      <c r="H50" s="11">
         <v>0.27802260969999998</v>
       </c>
-      <c r="I50" s="12">
+      <c r="I50" s="11">
         <v>0.82062468479999995</v>
       </c>
-      <c r="J50" s="12">
+      <c r="J50" s="11">
         <v>0.39282244700000002</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="60"/>
-      <c r="D51" s="56"/>
-      <c r="E51" s="56"/>
-      <c r="F51" s="12">
+      <c r="C51" s="56"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="11">
         <v>5.7482279999999995E-4</v>
       </c>
-      <c r="G51" s="12">
+      <c r="G51" s="11">
         <v>1.7244682999999999E-3</v>
       </c>
-      <c r="H51" s="12">
+      <c r="H51" s="11">
         <v>0.2935428243</v>
       </c>
-      <c r="I51" s="12">
+      <c r="I51" s="11">
         <v>0.50192727670000004</v>
       </c>
-      <c r="J51" s="12">
+      <c r="J51" s="11">
         <v>0.4860498285</v>
       </c>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>4</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="60"/>
-      <c r="D52" s="56"/>
-      <c r="E52" s="56"/>
-      <c r="F52" s="12">
+      <c r="C52" s="56"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="57"/>
+      <c r="F52" s="11">
         <v>9.5803800000000006E-5</v>
       </c>
-      <c r="G52" s="12">
+      <c r="G52" s="11">
         <v>9.5803800000000003E-4</v>
       </c>
-      <c r="H52" s="12"/>
-      <c r="I52" s="12">
+      <c r="H52" s="11"/>
+      <c r="I52" s="11">
         <v>0.52609624489999995</v>
       </c>
-      <c r="J52" s="12">
+      <c r="J52" s="11">
         <v>0.46440658470000001</v>
       </c>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="G53" s="12"/>
-      <c r="H53" s="12"/>
-      <c r="I53" s="12"/>
-      <c r="J53" s="12"/>
-    </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
-    </row>
-    <row r="55" spans="1:14" s="45" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="63" t="s">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G53" s="11"/>
+      <c r="H53" s="11"/>
+      <c r="I53" s="11"/>
+      <c r="J53" s="11"/>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G54" s="11"/>
+      <c r="H54" s="11"/>
+      <c r="I54" s="11"/>
+      <c r="J54" s="11"/>
+    </row>
+    <row r="55" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="63"/>
-      <c r="C55" s="63"/>
-      <c r="D55" s="63"/>
-      <c r="E55" s="42"/>
-      <c r="F55" s="43">
+      <c r="B55" s="55"/>
+      <c r="C55" s="55"/>
+      <c r="D55" s="55"/>
+      <c r="E55" s="41"/>
+      <c r="F55" s="42">
         <f>MAX(F2:F52)</f>
         <v>8.2166826499999998E-2</v>
       </c>
-      <c r="G55" s="43">
+      <c r="G55" s="42">
         <f>MAX(G2:G52)</f>
         <v>7.9290508100000004E-2</v>
       </c>
-      <c r="H55" s="43">
+      <c r="H55" s="42">
         <f>MAX(H2:H52)</f>
         <v>0.6839884947</v>
       </c>
-      <c r="I55" s="43">
+      <c r="I55" s="42">
         <f>MAX(I2:I52)</f>
         <v>0.89827844270000001</v>
       </c>
-      <c r="J55" s="43">
+      <c r="J55" s="42">
         <f>MAX(J2:J52)</f>
         <v>0.51222158829999997</v>
       </c>
-      <c r="K55" s="44"/>
-    </row>
-    <row r="56" spans="1:14" s="49" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="55" t="s">
+      <c r="K55" s="43"/>
+    </row>
+    <row r="56" spans="1:11" s="48" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="55"/>
-      <c r="C56" s="55"/>
-      <c r="D56" s="55"/>
-      <c r="E56" s="46"/>
-      <c r="F56" s="47">
+      <c r="B56" s="61"/>
+      <c r="C56" s="61"/>
+      <c r="D56" s="61"/>
+      <c r="E56" s="45"/>
+      <c r="F56" s="46">
         <f>AVERAGE(F2:F52)</f>
         <v>2.4235782825E-2</v>
       </c>
-      <c r="G56" s="47">
+      <c r="G56" s="46">
         <f>AVERAGE(G2:G52)</f>
         <v>6.0500254111111127E-3</v>
       </c>
-      <c r="H56" s="47">
+      <c r="H56" s="46">
         <f>AVERAGE(H2:H52)</f>
         <v>0.32527986028484845</v>
       </c>
-      <c r="I56" s="47">
+      <c r="I56" s="46">
         <f>AVERAGE(I2:I52)</f>
         <v>0.63155286615000006</v>
       </c>
-      <c r="J56" s="47">
+      <c r="J56" s="46">
         <f>AVERAGE(J2:J52)</f>
         <v>0.45647798735000017</v>
       </c>
-      <c r="K56" s="48"/>
-    </row>
-    <row r="58" spans="1:14" s="25" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="64" t="s">
-        <v>68</v>
-      </c>
-      <c r="B58" s="64"/>
-      <c r="C58" s="64"/>
-      <c r="D58" s="64"/>
-      <c r="E58" s="64"/>
-      <c r="F58" s="32">
-        <f>SUM(F55*(1/3),  G55*(1/3), I55*(1/3))</f>
-        <v>0.35324525909999999</v>
-      </c>
-      <c r="G58" s="26"/>
-      <c r="H58" s="26"/>
-      <c r="I58" s="26"/>
-      <c r="J58" s="26"/>
-      <c r="K58" s="26"/>
-      <c r="L58" s="26"/>
-      <c r="M58" s="26"/>
-      <c r="N58" s="27"/>
-    </row>
-    <row r="59" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="65" t="s">
-        <v>69</v>
-      </c>
-      <c r="B59" s="65"/>
-      <c r="C59" s="65"/>
-      <c r="D59" s="65"/>
-      <c r="E59" s="65"/>
-      <c r="F59" s="31">
-        <f>SUM(H55*(1/2),  J55*(1/2))</f>
-        <v>0.59810504149999999</v>
-      </c>
-      <c r="G59" s="28"/>
-      <c r="H59" s="28"/>
-      <c r="I59" s="28"/>
-      <c r="J59" s="28"/>
-      <c r="K59" s="28"/>
-      <c r="L59" s="28"/>
-      <c r="M59" s="28"/>
-      <c r="N59" s="29"/>
-    </row>
-    <row r="60" spans="1:14" s="36" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="66" t="s">
-        <v>70</v>
-      </c>
-      <c r="B60" s="66"/>
-      <c r="C60" s="66"/>
-      <c r="D60" s="66"/>
-      <c r="E60" s="66"/>
-      <c r="F60" s="33">
-        <f>SUM(F55*1/5, G55*1/5, H55*1/5, I55*1/5,J55*1/5)</f>
-        <v>0.45118917206000003</v>
-      </c>
-      <c r="G60" s="34"/>
-      <c r="H60" s="34"/>
-      <c r="I60" s="34"/>
-      <c r="J60" s="34"/>
-      <c r="K60" s="34"/>
-      <c r="L60" s="34"/>
-      <c r="M60" s="34"/>
-      <c r="N60" s="35"/>
+      <c r="K56" s="47"/>
     </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="K46:K48"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="E50:E52"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="K6:K8"/>
+  <mergeCells count="47">
     <mergeCell ref="A56:D56"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A60:E60"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C12:C14"/>
     <mergeCell ref="D12:D14"/>
@@ -3673,6 +3625,40 @@
     <mergeCell ref="E28:E30"/>
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="D32:D34"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="K6:K8"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="K46:K48"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3689,14 +3675,14 @@
     <col min="3" max="3" width="34.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="50.33203125" style="4" customWidth="1"/>
     <col min="5" max="5" width="50" style="4" customWidth="1"/>
-    <col min="6" max="6" width="24" style="12" customWidth="1"/>
-    <col min="7" max="7" width="23.1640625" style="12" customWidth="1"/>
-    <col min="8" max="8" width="27.5" style="12" customWidth="1"/>
-    <col min="9" max="9" width="27.33203125" style="12" customWidth="1"/>
-    <col min="10" max="10" width="31.33203125" style="12" customWidth="1"/>
-    <col min="11" max="11" width="30.83203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="31.33203125" style="12" customWidth="1"/>
-    <col min="13" max="13" width="28.1640625" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24" style="11" customWidth="1"/>
+    <col min="7" max="7" width="23.1640625" style="11" customWidth="1"/>
+    <col min="8" max="8" width="27.5" style="11" customWidth="1"/>
+    <col min="9" max="9" width="27.33203125" style="11" customWidth="1"/>
+    <col min="10" max="10" width="31.33203125" style="11" customWidth="1"/>
+    <col min="11" max="11" width="30.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="31.33203125" style="11" customWidth="1"/>
+    <col min="13" max="13" width="28.1640625" style="11" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="50.83203125" style="3" customWidth="1"/>
     <col min="15" max="16384" width="51.33203125" style="1"/>
   </cols>
@@ -3717,28 +3703,28 @@
       <c r="E1" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="13" t="s">
+      <c r="G1" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="13" t="s">
+      <c r="H1" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="13" t="s">
+      <c r="I1" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="M1" s="12" t="s">
         <v>64</v>
       </c>
       <c r="N1" s="7" t="s">
@@ -3753,7 +3739,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="62" t="s">
+      <c r="C2" s="60" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="59" t="s">
@@ -3762,34 +3748,34 @@
       <c r="E2" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="20">
+      <c r="F2" s="19">
         <v>9.1179290499999996E-2</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="11">
         <v>4.9856184E-3</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="11">
         <v>0.21744966439999999</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>0.66392193610000005</v>
       </c>
-      <c r="J2" s="12">
+      <c r="J2" s="11">
         <v>0.4464361979</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="11">
         <f>SUM(F2*1/3,G2*1/3,I2*1/3)</f>
         <v>0.25336228166666669</v>
       </c>
-      <c r="L2" s="12">
+      <c r="L2" s="11">
         <f>SUM(H2*1/2,J2*1/2)</f>
         <v>0.33194293115000001</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="11">
         <f>SUM(F2*1/5,G2*1/5,H2*1/5,I2*1/5,J2*1/5)</f>
         <v>0.28479454145999999</v>
       </c>
-      <c r="N2" s="57" t="s">
+      <c r="N2" s="62" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3800,37 +3786,37 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="60"/>
-      <c r="D3" s="56"/>
-      <c r="E3" s="56"/>
-      <c r="F3" s="12">
+      <c r="C3" s="56"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="11">
         <v>8.3029722E-2</v>
       </c>
-      <c r="G3" s="12">
+      <c r="G3" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="11">
         <v>0.21860019180000001</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="11">
         <v>0.49342964509999998</v>
       </c>
-      <c r="J3" s="12">
+      <c r="J3" s="11">
         <v>0.43877210389999999</v>
       </c>
-      <c r="K3" s="12">
+      <c r="K3" s="11">
         <f>SUM(F3*1/3,G3*1/3,I3*1/3)</f>
         <v>0.19234487693333333</v>
       </c>
-      <c r="L3" s="12">
+      <c r="L3" s="11">
         <f>SUM(H3*1/2,J3*1/2)</f>
         <v>0.32868614785</v>
       </c>
-      <c r="M3" s="12">
+      <c r="M3" s="11">
         <f>SUM(F3*1/5,G3*1/5,H3*1/5,I3*1/5,J3*1/5)</f>
         <v>0.24688138529999998</v>
       </c>
-      <c r="N3" s="58"/>
+      <c r="N3" s="63"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3839,37 +3825,37 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="60"/>
-      <c r="D4" s="56"/>
-      <c r="E4" s="56"/>
-      <c r="F4" s="12">
+      <c r="C4" s="56"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="11">
         <v>2.2051773699999999E-2</v>
       </c>
-      <c r="G4" s="12">
+      <c r="G4" s="11">
         <v>0</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <v>0.2607861937</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <v>0.53858249069999997</v>
       </c>
-      <c r="J4" s="12">
+      <c r="J4" s="11">
         <v>0.40747926969999998</v>
       </c>
-      <c r="K4" s="12">
+      <c r="K4" s="11">
         <f>SUM(F4*1/3,G4*1/3,I4*1/3)</f>
         <v>0.18687808813333334</v>
       </c>
-      <c r="L4" s="12">
+      <c r="L4" s="11">
         <f>SUM(H4*1/2,J4*1/2)</f>
         <v>0.33413273170000002</v>
       </c>
-      <c r="M4" s="12">
+      <c r="M4" s="11">
         <f>SUM(F4*1/5,G4*1/5,H4*1/5,I4*1/5,J4*1/5)</f>
         <v>0.24577994555999999</v>
       </c>
-      <c r="N4" s="58"/>
+      <c r="N4" s="63"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -3878,43 +3864,43 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="60" t="s">
+      <c r="C6" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="D6" s="57" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="56" t="s">
+      <c r="E6" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="11">
         <v>4.20578655E-2</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="11">
         <v>9.5803800000000003E-4</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <v>0.1324008431</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <v>0.50803699889999998</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="11">
         <v>0.38969019069999999</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="11">
         <f>SUM(F6*1/3,G6*1/3,I6*1/3)</f>
         <v>0.18368430080000001</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="11">
         <f>SUM(H6*1/2,J6*1/2)</f>
         <v>0.2610455169</v>
       </c>
-      <c r="M6" s="12">
+      <c r="M6" s="11">
         <f>SUM(F6*1/5,G6*1/5,H6*1/5,I6*1/5,J6*1/5)</f>
         <v>0.21462878724000001</v>
       </c>
-      <c r="N6" s="58" t="s">
+      <c r="N6" s="63" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3925,37 +3911,37 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="60"/>
-      <c r="D7" s="56"/>
-      <c r="E7" s="56"/>
-      <c r="F7" s="12">
+      <c r="C7" s="56"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="11">
         <v>4.4165548999999998E-2</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="11">
         <v>2.2992910000000002E-3</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <v>0.30312320370000001</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <v>0.51790411849999995</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="11">
         <v>0.49842254940000003</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="11">
         <f>SUM(F7*1/3,G7*1/3,I7*1/3)</f>
         <v>0.18812298616666664</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="11">
         <f>SUM(H7*1/2,J7*1/2)</f>
         <v>0.40077287655000005</v>
       </c>
-      <c r="M7" s="12">
+      <c r="M7" s="11">
         <f>SUM(F7*1/5,G7*1/5,H7*1/5,I7*1/5,J7*1/5)</f>
         <v>0.27318294232000001</v>
       </c>
-      <c r="N7" s="58"/>
+      <c r="N7" s="63"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -3964,54 +3950,54 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="60"/>
-      <c r="D8" s="56"/>
-      <c r="E8" s="56"/>
-      <c r="F8" s="12">
+      <c r="C8" s="56"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="11">
         <v>3.7171872000000002E-2</v>
       </c>
-      <c r="G8" s="12">
+      <c r="G8" s="11">
         <v>0</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="11">
         <v>0.3494922399</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="11">
         <v>0.49933204990000002</v>
       </c>
-      <c r="J8" s="12">
+      <c r="J8" s="11">
         <v>0.42558599460000002</v>
       </c>
-      <c r="K8" s="12">
+      <c r="K8" s="11">
         <f>SUM(F8*1/3,G8*1/3,I8*1/3)</f>
         <v>0.17883464063333332</v>
       </c>
-      <c r="L8" s="12">
+      <c r="L8" s="11">
         <f>SUM(H8*1/2,J8*1/2)</f>
         <v>0.38753911725000001</v>
       </c>
-      <c r="M8" s="12">
+      <c r="M8" s="11">
         <f>SUM(F8*1/5,G8*1/5,H8*1/5,I8*1/5,J8*1/5)</f>
         <v>0.26231643128000004</v>
       </c>
-      <c r="N8" s="58"/>
+      <c r="N8" s="63"/>
     </row>
     <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="61" t="s">
+      <c r="A10" s="58" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="61"/>
-      <c r="C10" s="61"/>
-      <c r="D10" s="61"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
       <c r="E10" s="5"/>
-      <c r="F10" s="14"/>
-      <c r="G10" s="14"/>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
+      <c r="F10" s="13"/>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="13"/>
+      <c r="L10" s="13"/>
+      <c r="M10" s="13"/>
       <c r="N10" s="5"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.2">
@@ -4021,43 +4007,43 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="60" t="s">
+      <c r="C12" s="56" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="56" t="s">
+      <c r="D12" s="57" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="56" t="s">
+      <c r="E12" s="57" t="s">
         <v>17</v>
       </c>
-      <c r="F12" s="12">
+      <c r="F12" s="11">
         <v>6.5771812099999993E-2</v>
       </c>
-      <c r="G12" s="12">
+      <c r="G12" s="11">
         <v>2.3969319E-3</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="11">
         <v>0.49453499519999999</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="11">
         <v>0.55940591579999999</v>
       </c>
-      <c r="J12" s="20">
+      <c r="J12" s="19">
         <v>0.51830085319999997</v>
       </c>
-      <c r="K12" s="12">
+      <c r="K12" s="11">
         <f>SUM(F12*1/3,G12*1/3,I12*1/3)</f>
         <v>0.20919155326666666</v>
       </c>
-      <c r="L12" s="12">
+      <c r="L12" s="11">
         <f>SUM(H12*1/2,J12*1/2)</f>
         <v>0.50641792419999998</v>
       </c>
-      <c r="M12" s="12">
+      <c r="M12" s="11">
         <f>SUM(F12*1/5,G12*1/5,H12*1/5,I12*1/5,J12*1/5)</f>
         <v>0.32808210163999996</v>
       </c>
-      <c r="N12" s="58" t="s">
+      <c r="N12" s="63" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4068,37 +4054,37 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="60"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="56"/>
-      <c r="F13" s="12">
+      <c r="C13" s="56"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="11">
         <v>4.8897411E-3</v>
       </c>
-      <c r="G13" s="12">
+      <c r="G13" s="11">
         <v>6.7114099999999999E-4</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="11">
         <v>0.28513902209999997</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="11">
         <v>0.50209830020000001</v>
       </c>
-      <c r="J13" s="12">
+      <c r="J13" s="11">
         <v>0.48819923679999999</v>
       </c>
-      <c r="K13" s="12">
+      <c r="K13" s="11">
         <f>SUM(F13*1/3,G13*1/3,I13*1/3)</f>
         <v>0.16921972743333333</v>
       </c>
-      <c r="L13" s="12">
+      <c r="L13" s="11">
         <f>SUM(H13*1/2,J13*1/2)</f>
         <v>0.38666912944999998</v>
       </c>
-      <c r="M13" s="12">
+      <c r="M13" s="11">
         <f>SUM(F13*1/5,G13*1/5,H13*1/5,I13*1/5,J13*1/5)</f>
         <v>0.25619948824</v>
       </c>
-      <c r="N13" s="58"/>
+      <c r="N13" s="63"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -4107,37 +4093,37 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="56"/>
-      <c r="E14" s="56"/>
-      <c r="F14" s="12">
+      <c r="C14" s="56"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="11">
         <v>1.917546E-4</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G14" s="11">
         <v>1.4381591000000001E-3</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="11">
         <v>2.5503355700000001E-2</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="11">
         <v>0.50824655649999995</v>
       </c>
-      <c r="J14" s="12">
+      <c r="J14" s="11">
         <v>0.46527030559999999</v>
       </c>
-      <c r="K14" s="12">
+      <c r="K14" s="11">
         <f>SUM(F14*1/3,G14*1/3,I14*1/3)</f>
         <v>0.16995882339999999</v>
       </c>
-      <c r="L14" s="12">
+      <c r="L14" s="11">
         <f>SUM(H14*1/2,J14*1/2)</f>
         <v>0.24538683065</v>
       </c>
-      <c r="M14" s="12">
+      <c r="M14" s="11">
         <f>SUM(F14*1/5,G14*1/5,H14*1/5,I14*1/5,J14*1/5)</f>
         <v>0.20013002629999999</v>
       </c>
-      <c r="N14" s="58"/>
+      <c r="N14" s="63"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -4146,43 +4132,43 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="60" t="s">
+      <c r="C16" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="56" t="s">
+      <c r="D16" s="57" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="56" t="s">
+      <c r="E16" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="F16" s="12">
+      <c r="F16" s="11">
         <v>4.5445829299999997E-2</v>
       </c>
-      <c r="G16" s="12">
+      <c r="G16" s="11">
         <v>6.6155322000000004E-3</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="11">
         <v>0.45714285710000002</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="11">
         <v>0.70717096769999999</v>
       </c>
-      <c r="J16" s="12">
+      <c r="J16" s="11">
         <v>0.50964245389999996</v>
       </c>
-      <c r="K16" s="12">
+      <c r="K16" s="11">
         <f>SUM(F16*1/3,G16*1/3,I16*1/3)</f>
         <v>0.25307744306666669</v>
       </c>
-      <c r="L16" s="12">
+      <c r="L16" s="11">
         <f>SUM(H16*1/2,J16*1/2)</f>
         <v>0.48339265549999999</v>
       </c>
-      <c r="M16" s="12">
+      <c r="M16" s="11">
         <f>SUM(F16*1/5,G16*1/5,H16*1/5,I16*1/5,J16*1/5)</f>
         <v>0.34520352803999999</v>
       </c>
-      <c r="N16" s="58" t="s">
+      <c r="N16" s="63" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4193,37 +4179,37 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="60"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="12">
+      <c r="C17" s="56"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="11">
         <v>2.85714286E-2</v>
       </c>
-      <c r="G17" s="12">
+      <c r="G17" s="11">
         <v>1.9175456000000001E-3</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="11">
         <v>0.45043144769999999</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="11">
         <v>0.74414334049999997</v>
       </c>
-      <c r="J17" s="12">
+      <c r="J17" s="11">
         <v>0.46137624570000002</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="11">
         <f>SUM(F17*1/3,G17*1/3,I17*1/3)</f>
         <v>0.25821077156666666</v>
       </c>
-      <c r="L17" s="12">
+      <c r="L17" s="11">
         <f>SUM(H17*1/2,J17*1/2)</f>
         <v>0.4559038467</v>
       </c>
-      <c r="M17" s="12">
+      <c r="M17" s="11">
         <f>SUM(F17*1/5,G17*1/5,H17*1/5,I17*1/5,J17*1/5)</f>
         <v>0.33728800162</v>
       </c>
-      <c r="N17" s="58"/>
+      <c r="N17" s="63"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -4232,37 +4218,37 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="60"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="56"/>
-      <c r="F18" s="12">
+      <c r="C18" s="56"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
-      <c r="G18" s="12">
+      <c r="G18" s="11">
         <v>1.3422817999999999E-3</v>
       </c>
-      <c r="H18" s="20">
+      <c r="H18" s="19">
         <v>0.79022051770000001</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="11">
         <v>0.49764374880000001</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="11">
         <v>0.48742542859999999</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="11">
         <f>SUM(F18*1/3,G18*1/3,I18*1/3)</f>
         <v>0.16645651323333333</v>
       </c>
-      <c r="L18" s="20">
+      <c r="L18" s="19">
         <f>SUM(H18*1/2,J18*1/2)</f>
         <v>0.63882297315000003</v>
       </c>
-      <c r="M18" s="12">
+      <c r="M18" s="11">
         <f>SUM(F18*1/5,G18*1/5,H18*1/5,I18*1/5,J18*1/5)</f>
         <v>0.35540309720000007</v>
       </c>
-      <c r="N18" s="58"/>
+      <c r="N18" s="63"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -4271,43 +4257,43 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="60" t="s">
+      <c r="C20" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="56" t="s">
+      <c r="D20" s="57" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="56" t="s">
+      <c r="E20" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="12">
+      <c r="F20" s="11">
         <v>7.2003835099999997E-2</v>
       </c>
-      <c r="G20" s="12">
+      <c r="G20" s="11">
         <v>7.3825504E-3</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="11">
         <v>0.3771812081</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="11">
         <v>0.74268293880000003</v>
       </c>
-      <c r="J20" s="12">
+      <c r="J20" s="11">
         <v>0.45190041990000002</v>
       </c>
-      <c r="K20" s="12">
+      <c r="K20" s="11">
         <f>SUM(F20*1/3,G20*1/3,I20*1/3)</f>
         <v>0.27402310810000002</v>
       </c>
-      <c r="L20" s="12">
+      <c r="L20" s="11">
         <f>SUM(H20*1/2,J20*1/2)</f>
         <v>0.41454081399999998</v>
       </c>
-      <c r="M20" s="12">
+      <c r="M20" s="11">
         <f>SUM(F20*1/5,G20*1/5,H20*1/5,I20*1/5,J20*1/5)</f>
         <v>0.33023019046000002</v>
       </c>
-      <c r="N20" s="58" t="s">
+      <c r="N20" s="63" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4318,37 +4304,37 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="60"/>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="12">
+      <c r="C21" s="56"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="11">
         <v>8.59060403E-2</v>
       </c>
-      <c r="G21" s="12">
+      <c r="G21" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="11">
         <v>0.59731543620000005</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="11">
         <v>0.8594864566</v>
       </c>
-      <c r="J21" s="12">
+      <c r="J21" s="11">
         <v>0.43209071430000001</v>
       </c>
-      <c r="K21" s="12">
+      <c r="K21" s="11">
         <f>SUM(F21*1/3,G21*1/3,I21*1/3)</f>
         <v>0.31532258686666664</v>
       </c>
-      <c r="L21" s="12">
+      <c r="L21" s="11">
         <f>SUM(H21*1/2,J21*1/2)</f>
         <v>0.51470307525000003</v>
       </c>
-      <c r="M21" s="20">
+      <c r="M21" s="19">
         <f>SUM(F21*1/5,G21*1/5,H21*1/5,I21*1/5,J21*1/5)</f>
         <v>0.39507478221999998</v>
       </c>
-      <c r="N21" s="58"/>
+      <c r="N21" s="63"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -4357,37 +4343,37 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="60"/>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="12">
+      <c r="C22" s="56"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
-      <c r="G22" s="12">
+      <c r="G22" s="11">
         <v>1.1505274000000001E-3</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="11">
         <v>0.4678811122</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="11">
         <v>0.50554854299999996</v>
       </c>
-      <c r="J22" s="12">
+      <c r="J22" s="11">
         <v>0.48466990739999999</v>
       </c>
-      <c r="K22" s="12">
+      <c r="K22" s="11">
         <f>SUM(F22*1/3,G22*1/3,I22*1/3)</f>
         <v>0.1690275265</v>
       </c>
-      <c r="L22" s="12">
+      <c r="L22" s="11">
         <f>SUM(H22*1/2,J22*1/2)</f>
         <v>0.4762755098</v>
       </c>
-      <c r="M22" s="12">
+      <c r="M22" s="11">
         <f>SUM(F22*1/5,G22*1/5,H22*1/5,I22*1/5,J22*1/5)</f>
         <v>0.29192671981999996</v>
       </c>
-      <c r="N22" s="58"/>
+      <c r="N22" s="63"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -4396,39 +4382,39 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="60" t="s">
+      <c r="C24" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="56" t="s">
+      <c r="D24" s="57" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="56" t="s">
+      <c r="E24" s="57" t="s">
         <v>32</v>
       </c>
-      <c r="F24" s="12">
+      <c r="F24" s="11">
         <v>5.5704697999999997E-2</v>
       </c>
-      <c r="G24" s="12">
+      <c r="G24" s="11">
         <v>4.4103546999999998E-3</v>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="11">
         <v>0.32636625120000001</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="11">
         <v>0.6999883965</v>
       </c>
-      <c r="J24" s="12">
+      <c r="J24" s="11">
         <v>0.44519748980000001</v>
       </c>
-      <c r="K24" s="12">
+      <c r="K24" s="11">
         <f>SUM(F24*1/3,G24*1/3,I24*1/3)</f>
         <v>0.2533678164</v>
       </c>
-      <c r="L24" s="12">
+      <c r="L24" s="11">
         <f>SUM(H24*1/2,J24*1/2)</f>
         <v>0.38578187050000001</v>
       </c>
-      <c r="M24" s="12">
+      <c r="M24" s="11">
         <f>SUM(F24*1/5,G24*1/5,H24*1/5,I24*1/5,J24*1/5)</f>
         <v>0.30633343804000002</v>
       </c>
@@ -4440,33 +4426,33 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="60"/>
-      <c r="D25" s="56"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="12">
+      <c r="C25" s="56"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="11">
         <v>1.04506232E-2</v>
       </c>
-      <c r="G25" s="12">
+      <c r="G25" s="11">
         <v>3.9309682999999996E-3</v>
       </c>
-      <c r="H25" s="12">
+      <c r="H25" s="11">
         <v>0.42320230110000001</v>
       </c>
-      <c r="I25" s="12">
+      <c r="I25" s="11">
         <v>0.61751341709999996</v>
       </c>
-      <c r="J25" s="12">
+      <c r="J25" s="11">
         <v>0.48597102069999998</v>
       </c>
-      <c r="K25" s="12">
+      <c r="K25" s="11">
         <f>SUM(F25*1/3,G25*1/3,I25*1/3)</f>
         <v>0.21063166953333332</v>
       </c>
-      <c r="L25" s="12">
+      <c r="L25" s="11">
         <f>SUM(H25*1/2,J25*1/2)</f>
         <v>0.45458666089999999</v>
       </c>
-      <c r="M25" s="12">
+      <c r="M25" s="11">
         <f>SUM(F25*1/5,G25*1/5,H25*1/5,I25*1/5,J25*1/5)</f>
         <v>0.30821366608</v>
       </c>
@@ -4478,33 +4464,33 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="60"/>
-      <c r="D26" s="56"/>
-      <c r="E26" s="56"/>
-      <c r="F26" s="12">
+      <c r="C26" s="56"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="11">
         <v>2.876318E-4</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="11">
         <v>1.9175455000000001E-3</v>
       </c>
-      <c r="H26" s="12">
+      <c r="H26" s="11">
         <v>2.5503355700000001E-2</v>
       </c>
-      <c r="I26" s="12">
+      <c r="I26" s="11">
         <v>0.50272315249999999</v>
       </c>
-      <c r="J26" s="12">
+      <c r="J26" s="11">
         <v>0.47244179800000002</v>
       </c>
-      <c r="K26" s="12">
+      <c r="K26" s="11">
         <f>SUM(F26*1/3,G26*1/3,I26*1/3)</f>
         <v>0.16830944326666666</v>
       </c>
-      <c r="L26" s="12">
+      <c r="L26" s="11">
         <f>SUM(H26*1/2,J26*1/2)</f>
         <v>0.24897257685000002</v>
       </c>
-      <c r="M26" s="12">
+      <c r="M26" s="11">
         <f>SUM(F26*1/5,G26*1/5,H26*1/5,I26*1/5,J26*1/5)</f>
         <v>0.2005746967</v>
       </c>
@@ -4516,39 +4502,39 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="60" t="s">
+      <c r="C28" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="56" t="s">
+      <c r="D28" s="57" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="56" t="s">
+      <c r="E28" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="11">
         <v>5.2828379699999997E-2</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="11">
         <v>3.8350911000000001E-3</v>
       </c>
-      <c r="H28" s="12">
+      <c r="H28" s="11">
         <v>0.37583892619999998</v>
       </c>
-      <c r="I28" s="12">
+      <c r="I28" s="11">
         <v>0.69028312150000004</v>
       </c>
-      <c r="J28" s="12">
+      <c r="J28" s="11">
         <v>0.46388489960000001</v>
       </c>
-      <c r="K28" s="12">
+      <c r="K28" s="11">
         <f>SUM(F28*1/3,G28*1/3,I28*1/3)</f>
         <v>0.24898219743333333</v>
       </c>
-      <c r="L28" s="12">
+      <c r="L28" s="11">
         <f>SUM(H28*1/2,J28*1/2)</f>
         <v>0.41986191289999997</v>
       </c>
-      <c r="M28" s="12">
+      <c r="M28" s="11">
         <f>SUM(F28*1/5,G28*1/5,H28*1/5,I28*1/5,J28*1/5)</f>
         <v>0.31733408362000004</v>
       </c>
@@ -4560,33 +4546,33 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="60"/>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="12">
+      <c r="C29" s="56"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="11">
         <v>5.7526366000000004E-3</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="11">
         <v>4.3144773999999999E-3</v>
       </c>
-      <c r="H29" s="12">
+      <c r="H29" s="11">
         <v>0.37257909880000001</v>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="11">
         <v>0.59623182129999996</v>
       </c>
-      <c r="J29" s="12">
+      <c r="J29" s="11">
         <v>0.47859825140000001</v>
       </c>
-      <c r="K29" s="12">
+      <c r="K29" s="11">
         <f>SUM(F29*1/3,G29*1/3,I29*1/3)</f>
         <v>0.20209964509999997</v>
       </c>
-      <c r="L29" s="12">
+      <c r="L29" s="11">
         <f>SUM(H29*1/2,J29*1/2)</f>
         <v>0.42558867509999998</v>
       </c>
-      <c r="M29" s="12">
+      <c r="M29" s="11">
         <f>SUM(F29*1/5,G29*1/5,H29*1/5,I29*1/5,J29*1/5)</f>
         <v>0.29149525710000002</v>
       </c>
@@ -4598,33 +4584,33 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="60"/>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="12">
+      <c r="C30" s="56"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="11">
         <v>9.5877299999999998E-5</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="11">
         <v>2.2051774000000001E-3</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H30" s="11">
         <v>0.67516778519999998</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I30" s="11">
         <v>0.4935165554</v>
       </c>
-      <c r="J30" s="12">
+      <c r="J30" s="11">
         <v>0.48308613979999998</v>
       </c>
-      <c r="K30" s="12">
+      <c r="K30" s="11">
         <f>SUM(F30*1/3,G30*1/3,I30*1/3)</f>
         <v>0.1652725367</v>
       </c>
-      <c r="L30" s="12">
+      <c r="L30" s="11">
         <f>SUM(H30*1/2,J30*1/2)</f>
         <v>0.57912696249999995</v>
       </c>
-      <c r="M30" s="12">
+      <c r="M30" s="11">
         <f>SUM(F30*1/5,G30*1/5,H30*1/5,I30*1/5,J30*1/5)</f>
         <v>0.33081430702000003</v>
       </c>
@@ -4636,39 +4622,39 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="60" t="s">
+      <c r="C32" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="56" t="s">
+      <c r="D32" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="56" t="s">
+      <c r="E32" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="11">
         <v>6.1553211900000002E-2</v>
       </c>
-      <c r="G32" s="12">
+      <c r="G32" s="11">
         <v>4.6979865999999997E-3</v>
       </c>
-      <c r="H32" s="12">
+      <c r="H32" s="11">
         <v>0.47286673060000001</v>
       </c>
-      <c r="I32" s="12">
+      <c r="I32" s="11">
         <v>0.83432698849999998</v>
       </c>
-      <c r="J32" s="12">
+      <c r="J32" s="11">
         <v>0.44045914829999999</v>
       </c>
-      <c r="K32" s="12">
+      <c r="K32" s="11">
         <f>SUM(F32*1/3,G32*1/3,I32*1/3)</f>
         <v>0.30019272899999999</v>
       </c>
-      <c r="L32" s="12">
+      <c r="L32" s="11">
         <f>SUM(H32*1/2,J32*1/2)</f>
         <v>0.45666293945000003</v>
       </c>
-      <c r="M32" s="12">
+      <c r="M32" s="11">
         <f>SUM(F32*1/5,G32*1/5,H32*1/5,I32*1/5,J32*1/5)</f>
         <v>0.36278081317999999</v>
       </c>
@@ -4680,33 +4666,33 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="60"/>
-      <c r="D33" s="56"/>
-      <c r="E33" s="56"/>
-      <c r="F33" s="12">
+      <c r="C33" s="56"/>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="11">
         <v>7.6701821700000006E-2</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="11">
         <v>5.1773729999999999E-3</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="11">
         <v>0.4302972196</v>
       </c>
-      <c r="I33" s="20">
+      <c r="I33" s="19">
         <v>0.90418992629999995</v>
       </c>
-      <c r="J33" s="12">
+      <c r="J33" s="11">
         <v>0.3758758888</v>
       </c>
-      <c r="K33" s="20">
+      <c r="K33" s="19">
         <f>SUM(F33*1/3,G33*1/3,I33*1/3)</f>
         <v>0.328689707</v>
       </c>
-      <c r="L33" s="12">
+      <c r="L33" s="11">
         <f>SUM(H33*1/2,J33*1/2)</f>
         <v>0.4030865542</v>
       </c>
-      <c r="M33" s="12">
+      <c r="M33" s="11">
         <f>SUM(F33*1/5,G33*1/5,H33*1/5,I33*1/5,J33*1/5)</f>
         <v>0.35844844587999997</v>
       </c>
@@ -4718,33 +4704,33 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="60"/>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="12">
+      <c r="C34" s="56"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="11">
         <v>1.917546E-4</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="11">
         <v>1.5340364E-3</v>
       </c>
-      <c r="H34" s="12">
+      <c r="H34" s="11">
         <v>0.32617449659999997</v>
       </c>
-      <c r="I34" s="12">
+      <c r="I34" s="11">
         <v>0.49067845249999997</v>
       </c>
-      <c r="J34" s="12">
+      <c r="J34" s="11">
         <v>0.48153125829999999</v>
       </c>
-      <c r="K34" s="12">
+      <c r="K34" s="11">
         <f>SUM(F34*1/3,G34*1/3,I34*1/3)</f>
         <v>0.16413474783333332</v>
       </c>
-      <c r="L34" s="12">
+      <c r="L34" s="11">
         <f>SUM(H34*1/2,J34*1/2)</f>
         <v>0.40385287744999998</v>
       </c>
-      <c r="M34" s="12">
+      <c r="M34" s="11">
         <f>SUM(F34*1/5,G34*1/5,H34*1/5,I34*1/5,J34*1/5)</f>
         <v>0.26002199968</v>
       </c>
@@ -4756,39 +4742,39 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="60" t="s">
+      <c r="C36" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="56" t="s">
+      <c r="D36" s="57" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="56" t="s">
+      <c r="E36" s="57" t="s">
         <v>34</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="11">
         <v>4.53499521E-2</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G36" s="11">
         <v>9.7794822E-3</v>
       </c>
-      <c r="H36" s="12">
+      <c r="H36" s="11">
         <v>0.39827420899999999</v>
       </c>
-      <c r="I36" s="12">
+      <c r="I36" s="11">
         <v>0.79343004689999996</v>
       </c>
-      <c r="J36" s="12">
+      <c r="J36" s="11">
         <v>0.42229783360000001</v>
       </c>
-      <c r="K36" s="12">
+      <c r="K36" s="11">
         <f>SUM(F36*1/3,G36*1/3,I36*1/3)</f>
         <v>0.28285316039999997</v>
       </c>
-      <c r="L36" s="12">
+      <c r="L36" s="11">
         <f>SUM(H36*1/2,J36*1/2)</f>
         <v>0.41028602130000003</v>
       </c>
-      <c r="M36" s="12">
+      <c r="M36" s="11">
         <f>SUM(F36*1/5,G36*1/5,H36*1/5,I36*1/5,J36*1/5)</f>
         <v>0.33382630475999997</v>
       </c>
@@ -4800,33 +4786,33 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="60"/>
-      <c r="D37" s="56"/>
-      <c r="E37" s="56"/>
-      <c r="F37" s="12">
+      <c r="C37" s="56"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="11">
         <v>1.0546500000000001E-3</v>
       </c>
-      <c r="G37" s="12">
+      <c r="G37" s="11">
         <v>2.4928093E-3</v>
       </c>
-      <c r="H37" s="12">
+      <c r="H37" s="11">
         <v>0.36970278039999999</v>
       </c>
-      <c r="I37" s="12">
+      <c r="I37" s="11">
         <v>0.49925761699999999</v>
       </c>
-      <c r="J37" s="12">
+      <c r="J37" s="11">
         <v>0.47275161110000002</v>
       </c>
-      <c r="K37" s="12">
+      <c r="K37" s="11">
         <f>SUM(F37*1/3,G37*1/3,I37*1/3)</f>
         <v>0.16760169209999998</v>
       </c>
-      <c r="L37" s="12">
+      <c r="L37" s="11">
         <f>SUM(H37*1/2,J37*1/2)</f>
         <v>0.42122719575000001</v>
       </c>
-      <c r="M37" s="12">
+      <c r="M37" s="11">
         <f>SUM(F37*1/5,G37*1/5,H37*1/5,I37*1/5,J37*1/5)</f>
         <v>0.26905189356000003</v>
       </c>
@@ -4838,53 +4824,53 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="60"/>
-      <c r="D38" s="56"/>
-      <c r="E38" s="56"/>
-      <c r="F38" s="12">
+      <c r="C38" s="56"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="11">
         <v>1.917546E-4</v>
       </c>
-      <c r="G38" s="12">
+      <c r="G38" s="11">
         <v>1.5340365000000001E-3</v>
       </c>
-      <c r="H38" s="12">
+      <c r="H38" s="11">
         <v>0.77392138060000004</v>
       </c>
-      <c r="I38" s="12">
+      <c r="I38" s="11">
         <v>0.49696577879999998</v>
       </c>
-      <c r="J38" s="12">
+      <c r="J38" s="11">
         <v>0.48572782920000002</v>
       </c>
-      <c r="K38" s="12">
+      <c r="K38" s="11">
         <f>SUM(F38*1/3,G38*1/3,I38*1/3)</f>
         <v>0.16623052329999999</v>
       </c>
-      <c r="L38" s="12">
+      <c r="L38" s="11">
         <f>SUM(H38*1/2,J38*1/2)</f>
         <v>0.62982460490000003</v>
       </c>
-      <c r="M38" s="12">
+      <c r="M38" s="11">
         <f>SUM(F38*1/5,G38*1/5,H38*1/5,I38*1/5,J38*1/5)</f>
         <v>0.35166815594</v>
       </c>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="61" t="s">
+      <c r="A40" s="58" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="61"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="61"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
       <c r="E40" s="5"/>
-      <c r="F40" s="14"/>
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="14"/>
-      <c r="J40" s="14"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="14"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
+      <c r="H40" s="13"/>
+      <c r="I40" s="13"/>
+      <c r="J40" s="13"/>
+      <c r="K40" s="13"/>
+      <c r="L40" s="13"/>
+      <c r="M40" s="13"/>
       <c r="N40" s="5"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
@@ -4894,43 +4880,43 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="60" t="s">
+      <c r="C42" s="56" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="56" t="s">
+      <c r="D42" s="57" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="56" t="s">
+      <c r="E42" s="57" t="s">
         <v>27</v>
       </c>
-      <c r="F42" s="12">
+      <c r="F42" s="11">
         <v>3.33397203E-2</v>
       </c>
-      <c r="G42" s="12">
+      <c r="G42" s="11">
         <v>3.3531327999999998E-3</v>
       </c>
-      <c r="H42" s="12">
+      <c r="H42" s="11">
         <v>0.39394520020000001</v>
       </c>
-      <c r="I42" s="12">
+      <c r="I42" s="11">
         <v>0.66282251810000004</v>
       </c>
-      <c r="J42" s="12">
+      <c r="J42" s="11">
         <v>0.47587735599999997</v>
       </c>
-      <c r="K42" s="12">
+      <c r="K42" s="11">
         <f>SUM(F42*1/3,G42*1/3,I42*1/3)</f>
         <v>0.2331717904</v>
       </c>
-      <c r="L42" s="12">
+      <c r="L42" s="11">
         <f>SUM(H42*1/2,J42*1/2)</f>
         <v>0.43491127809999997</v>
       </c>
-      <c r="M42" s="12">
+      <c r="M42" s="11">
         <f>SUM(F42*1/5,G42*1/5,H42*1/5,I42*1/5,J42*1/5)</f>
         <v>0.31386758548000004</v>
       </c>
-      <c r="N42" s="58" t="s">
+      <c r="N42" s="63" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4941,37 +4927,37 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="60"/>
-      <c r="D43" s="56"/>
-      <c r="E43" s="56"/>
-      <c r="F43" s="12">
+      <c r="C43" s="56"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="11">
         <v>2.93159609E-2</v>
       </c>
-      <c r="G43" s="12">
+      <c r="G43" s="11">
         <v>3.5447403999999999E-3</v>
       </c>
-      <c r="H43" s="12">
+      <c r="H43" s="11">
         <v>0.33148112670000002</v>
       </c>
-      <c r="I43" s="12">
+      <c r="I43" s="11">
         <v>0.63471454110000003</v>
       </c>
-      <c r="J43" s="12">
+      <c r="J43" s="11">
         <v>0.46225641890000002</v>
       </c>
-      <c r="K43" s="12">
+      <c r="K43" s="11">
         <f>SUM(F43*1/3,G43*1/3,I43*1/3)</f>
         <v>0.22252508080000002</v>
       </c>
-      <c r="L43" s="12">
+      <c r="L43" s="11">
         <f>SUM(H43*1/2,J43*1/2)</f>
         <v>0.39686877279999999</v>
       </c>
-      <c r="M43" s="12">
+      <c r="M43" s="11">
         <f>SUM(F43*1/5,G43*1/5,H43*1/5,I43*1/5,J43*1/5)</f>
         <v>0.29226255760000003</v>
       </c>
-      <c r="N43" s="58"/>
+      <c r="N43" s="63"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -4980,37 +4966,37 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="60"/>
-      <c r="D44" s="56"/>
-      <c r="E44" s="56"/>
-      <c r="F44" s="15">
+      <c r="C44" s="56"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="14">
         <v>9.5803800000000006E-5</v>
       </c>
-      <c r="G44" s="12">
+      <c r="G44" s="11">
         <v>1.6286645000000001E-3</v>
       </c>
-      <c r="H44" s="12">
+      <c r="H44" s="11">
         <v>0.72868365589999995</v>
       </c>
-      <c r="I44" s="12">
+      <c r="I44" s="11">
         <v>0.49091622530000001</v>
       </c>
-      <c r="J44" s="12">
+      <c r="J44" s="11">
         <v>0.49152655340000001</v>
       </c>
-      <c r="K44" s="12">
+      <c r="K44" s="11">
         <f>SUM(F44*1/3,G44*1/3,I44*1/3)</f>
         <v>0.16421356453333336</v>
       </c>
-      <c r="L44" s="12">
+      <c r="L44" s="11">
         <f>SUM(H44*1/2,J44*1/2)</f>
         <v>0.61010510465000001</v>
       </c>
-      <c r="M44" s="12">
+      <c r="M44" s="11">
         <f>SUM(F44*1/5,G44*1/5,H44*1/5,I44*1/5,J44*1/5)</f>
         <v>0.34257018057999999</v>
       </c>
-      <c r="N44" s="58"/>
+      <c r="N44" s="63"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -5019,43 +5005,43 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="60" t="s">
+      <c r="C46" s="56" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="56" t="s">
+      <c r="D46" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="56" t="s">
+      <c r="E46" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="11">
         <v>6.1027016699999999E-2</v>
       </c>
-      <c r="G46" s="20">
+      <c r="G46" s="19">
         <v>1.2550297E-2</v>
       </c>
-      <c r="H46" s="12">
+      <c r="H46" s="11">
         <v>0.28721977389999997</v>
       </c>
-      <c r="I46" s="12">
+      <c r="I46" s="11">
         <v>0.74670598939999999</v>
       </c>
-      <c r="J46" s="12">
+      <c r="J46" s="11">
         <v>0.4446678791</v>
       </c>
-      <c r="K46" s="12">
+      <c r="K46" s="11">
         <f>SUM(F46*1/3,G46*1/3,I46*1/3)</f>
         <v>0.27342776769999999</v>
       </c>
-      <c r="L46" s="12">
+      <c r="L46" s="11">
         <f>SUM(H46*1/2,J46*1/2)</f>
         <v>0.36594382650000001</v>
       </c>
-      <c r="M46" s="12">
+      <c r="M46" s="11">
         <f>SUM(F46*1/5,G46*1/5,H46*1/5,I46*1/5,J46*1/5)</f>
         <v>0.31043419121999999</v>
       </c>
-      <c r="N46" s="58" t="s">
+      <c r="N46" s="63" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5066,37 +5052,37 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="60"/>
-      <c r="D47" s="56"/>
-      <c r="E47" s="56"/>
-      <c r="F47" s="12">
+      <c r="C47" s="56"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="11">
         <v>5.5853611800000001E-2</v>
       </c>
-      <c r="G47" s="12">
+      <c r="G47" s="11">
         <v>2.1076835000000001E-3</v>
       </c>
-      <c r="H47" s="12">
+      <c r="H47" s="11">
         <v>0.59417512930000005</v>
       </c>
-      <c r="I47" s="12">
+      <c r="I47" s="11">
         <v>0.81578619870000002</v>
       </c>
-      <c r="J47" s="12">
+      <c r="J47" s="11">
         <v>0.46039752070000001</v>
       </c>
-      <c r="K47" s="12">
+      <c r="K47" s="11">
         <f>SUM(F47*1/3,G47*1/3,I47*1/3)</f>
         <v>0.29124916466666667</v>
       </c>
-      <c r="L47" s="12">
+      <c r="L47" s="11">
         <f>SUM(H47*1/2,J47*1/2)</f>
         <v>0.52728632500000006</v>
       </c>
-      <c r="M47" s="12">
+      <c r="M47" s="11">
         <f>SUM(F47*1/5,G47*1/5,H47*1/5,I47*1/5,J47*1/5)</f>
         <v>0.38566402880000006</v>
       </c>
-      <c r="N47" s="58"/>
+      <c r="N47" s="63"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -5105,37 +5091,37 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="60"/>
-      <c r="D48" s="56"/>
-      <c r="E48" s="56"/>
-      <c r="F48" s="12">
+      <c r="C48" s="56"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="11">
         <v>9.5803800000000006E-5</v>
       </c>
-      <c r="G48" s="12">
+      <c r="G48" s="11">
         <v>1.7244682999999999E-3</v>
       </c>
-      <c r="H48" s="12">
+      <c r="H48" s="11">
         <v>0.34086989839999998</v>
       </c>
-      <c r="I48" s="12">
+      <c r="I48" s="11">
         <v>0.52181910850000002</v>
       </c>
-      <c r="J48" s="12">
+      <c r="J48" s="11">
         <v>0.46620327220000002</v>
       </c>
-      <c r="K48" s="12">
+      <c r="K48" s="11">
         <f>SUM(F48*1/3,G48*1/3,I48*1/3)</f>
         <v>0.1745464602</v>
       </c>
-      <c r="L48" s="12">
+      <c r="L48" s="11">
         <f>SUM(H48*1/2,J48*1/2)</f>
         <v>0.40353658530000003</v>
       </c>
-      <c r="M48" s="12">
+      <c r="M48" s="11">
         <f>SUM(F48*1/5,G48*1/5,H48*1/5,I48*1/5,J48*1/5)</f>
         <v>0.26614251024000002</v>
       </c>
-      <c r="N48" s="58"/>
+      <c r="N48" s="63"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -5144,39 +5130,39 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="60" t="s">
+      <c r="C50" s="56" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="56" t="s">
+      <c r="D50" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="56" t="s">
+      <c r="E50" s="57" t="s">
         <v>29</v>
       </c>
-      <c r="F50" s="12">
+      <c r="F50" s="11">
         <v>1.9160760000000001E-4</v>
       </c>
-      <c r="G50" s="12">
+      <c r="G50" s="11">
         <v>2.2034872000000001E-3</v>
       </c>
-      <c r="H50" s="12">
+      <c r="H50" s="11">
         <v>3.1998467099999997E-2</v>
       </c>
-      <c r="I50" s="12">
+      <c r="I50" s="11">
         <v>0.39272417920000002</v>
       </c>
-      <c r="J50" s="12">
+      <c r="J50" s="11">
         <v>0.34620542589999997</v>
       </c>
-      <c r="K50" s="12">
+      <c r="K50" s="11">
         <f>SUM(F50*1/3,G50*1/3,I50*1/3)</f>
         <v>0.13170642466666665</v>
       </c>
-      <c r="L50" s="12">
+      <c r="L50" s="11">
         <f>SUM(H50*1/2,J50*1/2)</f>
         <v>0.18910194649999998</v>
       </c>
-      <c r="M50" s="12">
+      <c r="M50" s="11">
         <f>SUM(F50*1/5,G50*1/5,H50*1/5,I50*1/5,J50*1/5)</f>
         <v>0.1546646334</v>
       </c>
@@ -5188,33 +5174,33 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="60"/>
-      <c r="D51" s="56"/>
-      <c r="E51" s="56"/>
-      <c r="F51" s="12">
+      <c r="C51" s="56"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="11">
         <v>4.4452960299999997E-2</v>
       </c>
-      <c r="G51" s="12">
+      <c r="G51" s="11">
         <v>2.8741139999999998E-4</v>
       </c>
-      <c r="H51" s="12">
+      <c r="H51" s="11">
         <v>0.53918375169999999</v>
       </c>
-      <c r="I51" s="12">
+      <c r="I51" s="11">
         <v>0.8902503168</v>
       </c>
-      <c r="J51" s="12">
+      <c r="J51" s="11">
         <v>0.40300200349999998</v>
       </c>
-      <c r="K51" s="12">
+      <c r="K51" s="11">
         <f>SUM(F51*1/3,G51*1/3,I51*1/3)</f>
         <v>0.3116635628333333</v>
       </c>
-      <c r="L51" s="12">
+      <c r="L51" s="11">
         <f>SUM(H51*1/2,J51*1/2)</f>
         <v>0.47109287759999996</v>
       </c>
-      <c r="M51" s="12">
+      <c r="M51" s="11">
         <f>SUM(F51*1/5,G51*1/5,H51*1/5,I51*1/5,J51*1/5)</f>
         <v>0.37543528873999998</v>
       </c>
@@ -5226,122 +5212,122 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="60"/>
-      <c r="D52" s="56"/>
-      <c r="E52" s="56"/>
-      <c r="F52" s="15">
+      <c r="C52" s="56"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="57"/>
+      <c r="F52" s="14">
         <v>0</v>
       </c>
-      <c r="G52" s="12">
+      <c r="G52" s="11">
         <v>3.4489365999999999E-3</v>
       </c>
-      <c r="H52" s="12">
+      <c r="H52" s="11">
         <v>2.5867024299999999E-2</v>
       </c>
-      <c r="I52" s="12">
+      <c r="I52" s="11">
         <v>0.47478388980000003</v>
       </c>
-      <c r="J52" s="12">
+      <c r="J52" s="11">
         <v>0.46033189099999999</v>
       </c>
-      <c r="K52" s="12">
+      <c r="K52" s="11">
         <f>SUM(F52*1/3,G52*1/3,I52*1/3)</f>
         <v>0.15941094213333334</v>
       </c>
-      <c r="L52" s="12">
+      <c r="L52" s="11">
         <f>SUM(H52*1/2,J52*1/2)</f>
         <v>0.24309945764999999</v>
       </c>
-      <c r="M52" s="12">
+      <c r="M52" s="11">
         <f>SUM(F52*1/5,G52*1/5,H52*1/5,I52*1/5,J52*1/5)</f>
         <v>0.19288634834000001</v>
       </c>
     </row>
-    <row r="55" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="70" t="s">
+    <row r="55" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="67" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="70"/>
-      <c r="C55" s="70"/>
-      <c r="D55" s="70"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="18">
+      <c r="B55" s="67"/>
+      <c r="C55" s="67"/>
+      <c r="D55" s="67"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="17">
         <f t="shared" ref="F55:M55" si="0">MAX(F2:F52)</f>
         <v>9.1179290499999996E-2</v>
       </c>
-      <c r="G55" s="18">
+      <c r="G55" s="17">
         <f t="shared" si="0"/>
         <v>1.2550297E-2</v>
       </c>
-      <c r="H55" s="18">
+      <c r="H55" s="17">
         <f t="shared" si="0"/>
         <v>0.79022051770000001</v>
       </c>
-      <c r="I55" s="18">
+      <c r="I55" s="17">
         <f t="shared" si="0"/>
         <v>0.90418992629999995</v>
       </c>
-      <c r="J55" s="18">
+      <c r="J55" s="17">
         <f t="shared" si="0"/>
         <v>0.51830085319999997</v>
       </c>
-      <c r="K55" s="18">
+      <c r="K55" s="17">
         <f t="shared" si="0"/>
         <v>0.328689707</v>
       </c>
-      <c r="L55" s="18">
+      <c r="L55" s="17">
         <f t="shared" si="0"/>
         <v>0.63882297315000003</v>
       </c>
-      <c r="M55" s="18">
+      <c r="M55" s="17">
         <f t="shared" si="0"/>
         <v>0.39507478221999998</v>
       </c>
-      <c r="N55" s="19"/>
-    </row>
-    <row r="56" spans="1:14" s="21" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="69" t="s">
+      <c r="N55" s="18"/>
+    </row>
+    <row r="56" spans="1:14" s="20" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="68" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="69"/>
-      <c r="C56" s="69"/>
-      <c r="D56" s="69"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="23">
+      <c r="B56" s="68"/>
+      <c r="C56" s="68"/>
+      <c r="D56" s="68"/>
+      <c r="E56" s="21"/>
+      <c r="F56" s="22">
         <f t="shared" ref="F56:M56" si="1">AVERAGE(F2:F52)</f>
         <v>3.2159416908333328E-2</v>
       </c>
-      <c r="G56" s="23">
+      <c r="G56" s="22">
         <f t="shared" si="1"/>
         <v>3.0273973416666666E-3</v>
       </c>
-      <c r="H56" s="23">
+      <c r="H56" s="22">
         <f t="shared" si="1"/>
         <v>0.37973669030833329</v>
       </c>
-      <c r="I56" s="23">
+      <c r="I56" s="22">
         <f t="shared" si="1"/>
         <v>0.61381284023055549</v>
       </c>
-      <c r="J56" s="23">
+      <c r="J56" s="22">
         <f t="shared" si="1"/>
         <v>0.45620981558055551</v>
       </c>
-      <c r="K56" s="23">
+      <c r="K56" s="22">
         <f t="shared" si="1"/>
         <v>0.21633321816018516</v>
       </c>
-      <c r="L56" s="23">
+      <c r="L56" s="22">
         <f t="shared" si="1"/>
         <v>0.41797325294444426</v>
       </c>
-      <c r="M56" s="23">
+      <c r="M56" s="22">
         <f t="shared" si="1"/>
         <v>0.296989232073889</v>
       </c>
-      <c r="N56" s="24"/>
-    </row>
-    <row r="58" spans="1:14" s="25" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="N56" s="23"/>
+    </row>
+    <row r="58" spans="1:14" s="24" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A58" s="64" t="s">
         <v>68</v>
       </c>
@@ -5349,20 +5335,20 @@
       <c r="C58" s="64"/>
       <c r="D58" s="64"/>
       <c r="E58" s="64"/>
-      <c r="F58" s="32">
+      <c r="F58" s="31">
         <f>SUM(F55*(1/3),  G55*(1/3), I55*(1/3))</f>
         <v>0.33597317126666659</v>
       </c>
-      <c r="G58" s="26"/>
-      <c r="H58" s="26"/>
-      <c r="I58" s="26"/>
-      <c r="J58" s="26"/>
-      <c r="K58" s="26"/>
-      <c r="L58" s="26"/>
-      <c r="M58" s="26"/>
-      <c r="N58" s="27"/>
-    </row>
-    <row r="59" spans="1:14" s="30" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G58" s="25"/>
+      <c r="H58" s="25"/>
+      <c r="I58" s="25"/>
+      <c r="J58" s="25"/>
+      <c r="K58" s="25"/>
+      <c r="L58" s="25"/>
+      <c r="M58" s="25"/>
+      <c r="N58" s="26"/>
+    </row>
+    <row r="59" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A59" s="65" t="s">
         <v>69</v>
       </c>
@@ -5370,20 +5356,20 @@
       <c r="C59" s="65"/>
       <c r="D59" s="65"/>
       <c r="E59" s="65"/>
-      <c r="F59" s="31">
+      <c r="F59" s="30">
         <f>SUM(H55*(1/2),  J55*(1/2))</f>
         <v>0.65426068544999993</v>
       </c>
-      <c r="G59" s="28"/>
-      <c r="H59" s="28"/>
-      <c r="I59" s="28"/>
-      <c r="J59" s="28"/>
-      <c r="K59" s="28"/>
-      <c r="L59" s="28"/>
-      <c r="M59" s="28"/>
-      <c r="N59" s="29"/>
-    </row>
-    <row r="60" spans="1:14" s="36" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="G59" s="27"/>
+      <c r="H59" s="27"/>
+      <c r="I59" s="27"/>
+      <c r="J59" s="27"/>
+      <c r="K59" s="27"/>
+      <c r="L59" s="27"/>
+      <c r="M59" s="27"/>
+      <c r="N59" s="28"/>
+    </row>
+    <row r="60" spans="1:14" s="35" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A60" s="66" t="s">
         <v>70</v>
       </c>
@@ -5391,106 +5377,81 @@
       <c r="C60" s="66"/>
       <c r="D60" s="66"/>
       <c r="E60" s="66"/>
-      <c r="F60" s="33">
+      <c r="F60" s="32">
         <f>SUM(F55*1/5, G55*1/5, H55*1/5, I55*1/5,J55*1/5)</f>
         <v>0.46328817694000002</v>
       </c>
-      <c r="G60" s="34"/>
-      <c r="H60" s="34"/>
-      <c r="I60" s="34"/>
-      <c r="J60" s="34"/>
-      <c r="K60" s="34"/>
-      <c r="L60" s="34"/>
-      <c r="M60" s="34"/>
-      <c r="N60" s="35"/>
-    </row>
-    <row r="62" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="67" t="s">
+      <c r="G60" s="33"/>
+      <c r="H60" s="33"/>
+      <c r="I60" s="33"/>
+      <c r="J60" s="33"/>
+      <c r="K60" s="33"/>
+      <c r="L60" s="33"/>
+      <c r="M60" s="33"/>
+      <c r="N60" s="34"/>
+    </row>
+    <row r="62" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="B62" s="67"/>
-      <c r="C62" s="67"/>
-      <c r="D62" s="67"/>
-      <c r="E62" s="37"/>
-      <c r="F62" s="38"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="38"/>
-      <c r="I62" s="38"/>
-      <c r="J62" s="38"/>
-      <c r="K62" s="38"/>
-      <c r="L62" s="38"/>
-      <c r="M62" s="38"/>
-      <c r="N62" s="39"/>
-    </row>
-    <row r="63" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="67" t="s">
+      <c r="B62" s="69"/>
+      <c r="C62" s="69"/>
+      <c r="D62" s="69"/>
+      <c r="E62" s="36"/>
+      <c r="F62" s="37"/>
+      <c r="G62" s="37"/>
+      <c r="H62" s="37"/>
+      <c r="I62" s="37"/>
+      <c r="J62" s="37"/>
+      <c r="K62" s="37"/>
+      <c r="L62" s="37"/>
+      <c r="M62" s="37"/>
+      <c r="N62" s="38"/>
+    </row>
+    <row r="63" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="69" t="s">
         <v>66</v>
       </c>
-      <c r="B63" s="68"/>
-      <c r="C63" s="68"/>
-      <c r="D63" s="68"/>
-      <c r="E63" s="41"/>
-      <c r="F63" s="38"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="38"/>
-      <c r="I63" s="38"/>
-      <c r="J63" s="38"/>
-      <c r="K63" s="38"/>
-      <c r="L63" s="38"/>
-      <c r="M63" s="38"/>
-      <c r="N63" s="39"/>
-    </row>
-    <row r="64" spans="1:14" s="40" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="67" t="s">
+      <c r="B63" s="70"/>
+      <c r="C63" s="70"/>
+      <c r="D63" s="70"/>
+      <c r="E63" s="40"/>
+      <c r="F63" s="37"/>
+      <c r="G63" s="37"/>
+      <c r="H63" s="37"/>
+      <c r="I63" s="37"/>
+      <c r="J63" s="37"/>
+      <c r="K63" s="37"/>
+      <c r="L63" s="37"/>
+      <c r="M63" s="37"/>
+      <c r="N63" s="38"/>
+    </row>
+    <row r="64" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="69" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="68"/>
-      <c r="C64" s="68"/>
-      <c r="D64" s="68"/>
-      <c r="E64" s="41"/>
-      <c r="F64" s="38"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="38"/>
-      <c r="I64" s="38"/>
-      <c r="J64" s="38"/>
-      <c r="K64" s="38"/>
-      <c r="L64" s="38"/>
-      <c r="M64" s="38"/>
-      <c r="N64" s="39"/>
+      <c r="B64" s="70"/>
+      <c r="C64" s="70"/>
+      <c r="D64" s="70"/>
+      <c r="E64" s="40"/>
+      <c r="F64" s="37"/>
+      <c r="G64" s="37"/>
+      <c r="H64" s="37"/>
+      <c r="I64" s="37"/>
+      <c r="J64" s="37"/>
+      <c r="K64" s="37"/>
+      <c r="L64" s="37"/>
+      <c r="M64" s="37"/>
+      <c r="N64" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="N42:N44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="N46:N48"/>
-    <mergeCell ref="E50:E52"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="N12:N14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="N20:N22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="N16:N18"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A62:D62"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C12:C14"/>
@@ -5507,12 +5468,37 @@
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D50:D52"/>
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="N6:N8"/>
+    <mergeCell ref="N12:N14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="N20:N22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="N16:N18"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="N42:N44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="N46:N48"/>
+    <mergeCell ref="E50:E52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5520,21 +5506,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84CDC51E-177F-BF40-BC8B-54510E0AFA97}">
-  <dimension ref="A1:N54"/>
+  <dimension ref="A1:N70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="51.33203125" defaultRowHeight="21" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="28.1640625" style="1" customWidth="1"/>
     <col min="2" max="2" width="15.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="36.1640625" style="3" customWidth="1"/>
     <col min="4" max="4" width="39.6640625" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="27.83203125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="28.1640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="30.83203125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="27.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="28.6640625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="27.1640625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="24.83203125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="25.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="27.83203125" style="11" customWidth="1"/>
+    <col min="6" max="6" width="28.1640625" style="11" customWidth="1"/>
+    <col min="7" max="7" width="30.83203125" style="11" customWidth="1"/>
+    <col min="8" max="8" width="27.83203125" style="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="28.6640625" style="11" customWidth="1"/>
+    <col min="10" max="10" width="27.1640625" style="11" customWidth="1"/>
+    <col min="11" max="11" width="24.83203125" style="11" customWidth="1"/>
+    <col min="12" max="12" width="25.5" style="11" customWidth="1"/>
     <col min="13" max="16384" width="51.33203125" style="1"/>
   </cols>
   <sheetData>
@@ -5551,71 +5537,76 @@
       <c r="D1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" s="12" t="s">
         <v>57</v>
       </c>
-      <c r="J1" s="13" t="s">
+      <c r="J1" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="K1" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="L1" s="12" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:14" s="8" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="10"/>
-      <c r="B2" s="10"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="10"/>
-      <c r="L2" s="10"/>
-      <c r="M2" s="10"/>
-      <c r="N2" s="10"/>
-    </row>
-    <row r="3" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="69" t="s">
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
+      <c r="J2" s="71"/>
+      <c r="K2" s="73"/>
+      <c r="L2" s="73"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+    </row>
+    <row r="3" spans="1:14" s="49" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="69"/>
-      <c r="I3" s="69"/>
-      <c r="J3" s="52"/>
-    </row>
-    <row r="4" spans="1:14" s="51" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="68"/>
+      <c r="C3" s="68"/>
+      <c r="D3" s="68"/>
+      <c r="E3" s="68"/>
+      <c r="F3" s="68"/>
+      <c r="G3" s="68"/>
+      <c r="H3" s="68"/>
+      <c r="I3" s="68"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="74"/>
+      <c r="L3" s="74"/>
+    </row>
+    <row r="4" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
-      <c r="D4" s="54"/>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
-      <c r="I4" s="8"/>
+      <c r="D4" s="53"/>
+      <c r="E4" s="72"/>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="75"/>
+      <c r="L4" s="75"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -5624,36 +5615,36 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="63" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="58" t="s">
+      <c r="D5" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="E5" s="12">
+      <c r="E5" s="11">
         <v>2.6558005799999999E-2</v>
       </c>
-      <c r="F5" s="12">
+      <c r="F5" s="11">
         <v>7.9290508100000004E-2</v>
       </c>
-      <c r="G5" s="12">
+      <c r="G5" s="11">
         <v>0.42742090119999998</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="11">
         <v>0.89827844270000001</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <v>0.34608643859999999</v>
       </c>
-      <c r="J5" s="12">
+      <c r="J5" s="11">
         <f>SUM(E5*1/3,F5*1/3,H5*1/3)</f>
         <v>0.33470898553333334</v>
       </c>
-      <c r="K5" s="12">
+      <c r="K5" s="11">
         <f>SUM(G5*1/2,I5*1/2)</f>
         <v>0.38675366989999999</v>
       </c>
-      <c r="L5" s="12">
+      <c r="L5" s="11">
         <f>SUM(E5*1/5,F5*1/5,G5*1/5,H5*1/5,I5*1/5)</f>
         <v>0.35552685928000005</v>
       </c>
@@ -5665,32 +5656,32 @@
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="12">
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="11">
         <v>6.2032598299999998E-2</v>
       </c>
-      <c r="F6" s="12">
+      <c r="F6" s="11">
         <v>9.9712367999999999E-3</v>
       </c>
-      <c r="G6" s="12">
+      <c r="G6" s="11">
         <v>0.22109300100000001</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <v>0.83613638540000002</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <v>0.38036204509999999</v>
       </c>
-      <c r="J6" s="12">
+      <c r="J6" s="11">
         <f>SUM(E6*1/3,F6*1/3,H6*1/3)</f>
         <v>0.30271340683333331</v>
       </c>
-      <c r="K6" s="12">
+      <c r="K6" s="11">
         <f>SUM(G6*1/2,I6*1/2)</f>
         <v>0.30072752305</v>
       </c>
-      <c r="L6" s="12">
+      <c r="L6" s="11">
         <f>SUM(E6*1/5,F6*1/5,G6*1/5,H6*1/5,I6*1/5)</f>
         <v>0.30191905332000002</v>
       </c>
@@ -5702,32 +5693,32 @@
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="12">
+      <c r="C7" s="63"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
-      <c r="F7" s="12">
+      <c r="F7" s="11">
         <v>1.1505273E-3</v>
       </c>
-      <c r="G7" s="12">
+      <c r="G7" s="11">
         <v>0.6839884947</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <v>0.50245971249999999</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <v>0.48181687890000002</v>
       </c>
-      <c r="J7" s="12">
+      <c r="J7" s="11">
         <f>SUM(E7*1/3,F7*1/3,H7*1/3)</f>
         <v>0.16806183449999998</v>
       </c>
-      <c r="K7" s="12">
+      <c r="K7" s="11">
         <f>SUM(G7*1/2,I7*1/2)</f>
         <v>0.58290268680000001</v>
       </c>
-      <c r="L7" s="12">
+      <c r="L7" s="11">
         <f>SUM(E7*1/5,F7*1/5,G7*1/5,H7*1/5,I7*1/5)</f>
         <v>0.33399817541999999</v>
       </c>
@@ -5739,36 +5730,36 @@
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="63" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="58" t="s">
+      <c r="D9" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="E9" s="12">
+      <c r="E9" s="11">
         <v>6.1553211900000002E-2</v>
       </c>
-      <c r="F9" s="12">
+      <c r="F9" s="11">
         <v>4.6979865999999997E-3</v>
       </c>
-      <c r="G9" s="12">
+      <c r="G9" s="11">
         <v>0.47286673060000001</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="11">
         <v>0.83432698849999998</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="11">
         <v>0.44045914829999999</v>
       </c>
-      <c r="J9" s="12">
+      <c r="J9" s="11">
         <f>SUM(E9*1/3,F9*1/3,H9*1/3)</f>
         <v>0.30019272899999999</v>
       </c>
-      <c r="K9" s="12">
+      <c r="K9" s="11">
         <f>SUM(G9*1/2,I9*1/2)</f>
         <v>0.45666293945000003</v>
       </c>
-      <c r="L9" s="12">
+      <c r="L9" s="11">
         <f>SUM(E9*1/5,F9*1/5,G9*1/5,H9*1/5,I9*1/5)</f>
         <v>0.36278081317999999</v>
       </c>
@@ -5780,32 +5771,32 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="12">
+      <c r="C10" s="63"/>
+      <c r="D10" s="63"/>
+      <c r="E10" s="11">
         <v>7.6701821700000006E-2</v>
       </c>
-      <c r="F10" s="12">
+      <c r="F10" s="11">
         <v>5.1773729999999999E-3</v>
       </c>
-      <c r="G10" s="12">
+      <c r="G10" s="11">
         <v>0.4302972196</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="11">
         <v>0.90418992629999995</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="11">
         <v>0.3758758888</v>
       </c>
-      <c r="J10" s="12">
+      <c r="J10" s="11">
         <f>SUM(E10*1/3,F10*1/3,H10*1/3)</f>
         <v>0.328689707</v>
       </c>
-      <c r="K10" s="12">
+      <c r="K10" s="11">
         <f>SUM(G10*1/2,I10*1/2)</f>
         <v>0.4030865542</v>
       </c>
-      <c r="L10" s="12">
+      <c r="L10" s="11">
         <f>SUM(E10*1/5,F10*1/5,G10*1/5,H10*1/5,I10*1/5)</f>
         <v>0.35844844587999997</v>
       </c>
@@ -5817,32 +5808,32 @@
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="12">
+      <c r="C11" s="63"/>
+      <c r="D11" s="63"/>
+      <c r="E11" s="11">
         <v>1.917546E-4</v>
       </c>
-      <c r="F11" s="12">
+      <c r="F11" s="11">
         <v>1.5340364E-3</v>
       </c>
-      <c r="G11" s="12">
+      <c r="G11" s="11">
         <v>0.32617449659999997</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="11">
         <v>0.49067845249999997</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="11">
         <v>0.48153125829999999</v>
       </c>
-      <c r="J11" s="12">
+      <c r="J11" s="11">
         <f>SUM(E11*1/3,F11*1/3,H11*1/3)</f>
         <v>0.16413474783333332</v>
       </c>
-      <c r="K11" s="12">
+      <c r="K11" s="11">
         <f>SUM(G11*1/2,I11*1/2)</f>
         <v>0.40385287744999998</v>
       </c>
-      <c r="L11" s="12">
+      <c r="L11" s="11">
         <f>SUM(E11*1/5,F11*1/5,G11*1/5,H11*1/5,I11*1/5)</f>
         <v>0.26002199968</v>
       </c>
@@ -5854,23 +5845,38 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="63" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="58" t="s">
-        <v>91</v>
-      </c>
-      <c r="J13" s="12">
+      <c r="D13" s="63" t="s">
+        <v>99</v>
+      </c>
+      <c r="E13" s="11">
+        <v>2.9626078600000001E-2</v>
+      </c>
+      <c r="F13" s="11">
+        <v>1.6299137E-3</v>
+      </c>
+      <c r="G13" s="11">
+        <v>0.65867689360000004</v>
+      </c>
+      <c r="H13" s="11">
+        <v>0.63355129020000001</v>
+      </c>
+      <c r="I13" s="11">
+        <v>0.6395845147</v>
+      </c>
+      <c r="J13" s="11">
         <f>SUM(E13*1/3,F13*1/3,H13*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K13" s="12">
+        <v>0.2216024275</v>
+      </c>
+      <c r="K13" s="11">
         <f>SUM(G13*1/2,I13*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L13" s="12">
+        <v>0.64913070415000007</v>
+      </c>
+      <c r="L13" s="11">
         <f>SUM(E13*1/5,F13*1/5,G13*1/5,H13*1/5,I13*1/5)</f>
-        <v>0</v>
+        <v>0.39261373816</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -5880,19 +5886,34 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="J14" s="12">
+      <c r="C14" s="63"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="11">
+        <v>4.53499521E-2</v>
+      </c>
+      <c r="F14" s="11">
+        <v>9.5877299999999998E-5</v>
+      </c>
+      <c r="G14" s="11">
+        <v>0.37737296259999997</v>
+      </c>
+      <c r="H14" s="11">
+        <v>0.5184065833</v>
+      </c>
+      <c r="I14" s="11">
+        <v>0.5126336454</v>
+      </c>
+      <c r="J14" s="11">
         <f>SUM(E14*1/3,F14*1/3,H14*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K14" s="12">
+        <v>0.18795080423333332</v>
+      </c>
+      <c r="K14" s="11">
         <f>SUM(G14*1/2,I14*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L14" s="12">
+        <v>0.44500330399999999</v>
+      </c>
+      <c r="L14" s="11">
         <f>SUM(E14*1/5,F14*1/5,G14*1/5,H14*1/5,I14*1/5)</f>
-        <v>0</v>
+        <v>0.29077180413999998</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -5902,31 +5923,32 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="F15" s="9"/>
-      <c r="J15" s="12">
+      <c r="C15" s="63"/>
+      <c r="D15" s="63"/>
+      <c r="E15" s="11">
+        <v>5.7526370000000003E-4</v>
+      </c>
+      <c r="F15" s="11">
+        <v>9.5877280000000004E-4</v>
+      </c>
+      <c r="H15" s="11">
+        <v>0.54132662050000002</v>
+      </c>
+      <c r="I15" s="11">
+        <v>0.44638545810000002</v>
+      </c>
+      <c r="J15" s="11">
         <f>SUM(E15*1/3,F15*1/3,H15*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K15" s="12">
+        <v>0.18095355233333335</v>
+      </c>
+      <c r="K15" s="11">
         <f>SUM(G15*1/2,I15*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L15" s="12">
+        <v>0.22319272905000001</v>
+      </c>
+      <c r="L15" s="11">
         <f>SUM(E15*1/5,F15*1/5,G15*1/5,H15*1/5,I15*1/5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="E16" s="12"/>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12"/>
-      <c r="H16" s="12"/>
-      <c r="I16" s="12"/>
-      <c r="J16" s="12"/>
-      <c r="K16" s="12"/>
-      <c r="L16" s="12"/>
+        <v>0.19784922302000002</v>
+      </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
@@ -5935,28 +5957,29 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="58" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" s="58" t="s">
-        <v>86</v>
-      </c>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12">
+      <c r="C17" s="63" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="63" t="s">
+        <v>89</v>
+      </c>
+      <c r="G17" s="11">
+        <v>0.66366251200000004</v>
+      </c>
+      <c r="I17" s="11">
+        <v>0.62260342189999995</v>
+      </c>
+      <c r="J17" s="11">
         <f>SUM(E17*1/3,F17*1/3,H17*1/3)</f>
         <v>0</v>
       </c>
-      <c r="K17" s="12">
+      <c r="K17" s="11">
         <f>SUM(G17*1/2,I17*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L17" s="12">
+        <v>0.64313296695</v>
+      </c>
+      <c r="L17" s="11">
         <f>SUM(E17*1/5,F17*1/5,G17*1/5,H17*1/5,I17*1/5)</f>
-        <v>0</v>
+        <v>0.25725318677999998</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
@@ -5966,22 +5989,17 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12">
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="J18" s="11">
         <f>SUM(E18*1/3,F18*1/3,H18*1/3)</f>
         <v>0</v>
       </c>
-      <c r="K18" s="12">
+      <c r="K18" s="11">
         <f>SUM(G18*1/2,I18*1/2)</f>
         <v>0</v>
       </c>
-      <c r="L18" s="12">
+      <c r="L18" s="11">
         <f>SUM(E18*1/5,F18*1/5,G18*1/5,H18*1/5,I18*1/5)</f>
         <v>0</v>
       </c>
@@ -5993,28 +6011,23 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12">
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="J19" s="11">
         <f>SUM(E19*1/3,F19*1/3,H19*1/3)</f>
         <v>0</v>
       </c>
-      <c r="K19" s="12">
+      <c r="K19" s="11">
         <f>SUM(G19*1/2,I19*1/2)</f>
         <v>0</v>
       </c>
-      <c r="L19" s="12">
+      <c r="L19" s="11">
         <f>SUM(E19*1/5,F19*1/5,G19*1/5,H19*1/5,I19*1/5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="C20" s="53"/>
+      <c r="C20" s="52"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
@@ -6023,23 +6036,38 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="63" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="58" t="s">
+      <c r="D21" s="63" t="s">
         <v>77</v>
       </c>
-      <c r="J21" s="12">
+      <c r="E21" s="11">
+        <v>7.3441994199999999E-2</v>
+      </c>
+      <c r="F21" s="11">
+        <v>6.1361458000000002E-3</v>
+      </c>
+      <c r="G21" s="11">
+        <v>0.25407478430000002</v>
+      </c>
+      <c r="H21" s="11">
+        <v>0.80810120569999999</v>
+      </c>
+      <c r="I21" s="11">
+        <v>0.38413781809999997</v>
+      </c>
+      <c r="J21" s="11">
         <f>SUM(E21*1/3,F21*1/3,H21*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K21" s="12">
+        <v>0.29589311523333334</v>
+      </c>
+      <c r="K21" s="11">
         <f>SUM(G21*1/2,I21*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L21" s="12">
+        <v>0.3191063012</v>
+      </c>
+      <c r="L21" s="11">
         <f>SUM(E21*1/5,F21*1/5,G21*1/5,H21*1/5,I21*1/5)</f>
-        <v>0</v>
+        <v>0.30517838961999999</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
@@ -6049,19 +6077,34 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="J22" s="12">
+      <c r="C22" s="63"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="11">
+        <v>2.95302013E-2</v>
+      </c>
+      <c r="F22" s="11">
+        <v>2.9913710400000001E-2</v>
+      </c>
+      <c r="G22" s="11">
+        <v>0.40134228189999999</v>
+      </c>
+      <c r="H22" s="11">
+        <v>0.69029157640000005</v>
+      </c>
+      <c r="I22" s="11">
+        <v>0.46189783290000003</v>
+      </c>
+      <c r="J22" s="11">
         <f>SUM(E22*1/3,F22*1/3,H22*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K22" s="12">
+        <v>0.24991182936666667</v>
+      </c>
+      <c r="K22" s="11">
         <f>SUM(G22*1/2,I22*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L22" s="12">
+        <v>0.43162005739999998</v>
+      </c>
+      <c r="L22" s="11">
         <f>SUM(E22*1/5,F22*1/5,G22*1/5,H22*1/5,I22*1/5)</f>
-        <v>0</v>
+        <v>0.32259512058000001</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
@@ -6071,19 +6114,34 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="J23" s="12">
+      <c r="C23" s="63"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="11">
+        <v>0</v>
+      </c>
+      <c r="F23" s="11">
+        <v>3.2598274E-3</v>
+      </c>
+      <c r="G23" s="11">
+        <v>0.2101629914</v>
+      </c>
+      <c r="H23" s="11">
+        <v>0.52068192690000004</v>
+      </c>
+      <c r="I23" s="11">
+        <v>0.4777149504</v>
+      </c>
+      <c r="J23" s="11">
         <f>SUM(E23*1/3,F23*1/3,H23*1/3)</f>
-        <v>0</v>
-      </c>
-      <c r="K23" s="12">
+        <v>0.17464725143333334</v>
+      </c>
+      <c r="K23" s="11">
         <f>SUM(G23*1/2,I23*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L23" s="12">
+        <v>0.34393897090000003</v>
+      </c>
+      <c r="L23" s="11">
         <f>SUM(E23*1/5,F23*1/5,G23*1/5,H23*1/5,I23*1/5)</f>
-        <v>0</v>
+        <v>0.24236393921999999</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
@@ -6093,23 +6151,29 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="58" t="s">
-        <v>89</v>
-      </c>
-      <c r="D25" s="58" t="s">
+      <c r="C25" s="63" t="s">
         <v>87</v>
       </c>
-      <c r="J25" s="12">
+      <c r="D25" s="63" t="s">
+        <v>85</v>
+      </c>
+      <c r="G25" s="11">
+        <v>0.66366251200000004</v>
+      </c>
+      <c r="I25" s="11">
+        <v>0.68586700889999996</v>
+      </c>
+      <c r="J25" s="11">
         <f>SUM(E25*1/3,F25*1/3,H25*1/3)</f>
         <v>0</v>
       </c>
-      <c r="K25" s="12">
+      <c r="K25" s="11">
         <f>SUM(G25*1/2,I25*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L25" s="12">
+        <v>0.67476476045</v>
+      </c>
+      <c r="L25" s="11">
         <f>SUM(E25*1/5,F25*1/5,G25*1/5,H25*1/5,I25*1/5)</f>
-        <v>0</v>
+        <v>0.26990590417999999</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
@@ -6119,17 +6183,17 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="J26" s="12">
+      <c r="C26" s="63"/>
+      <c r="D26" s="63"/>
+      <c r="J26" s="11">
         <f>SUM(E26*1/3,F26*1/3,H26*1/3)</f>
         <v>0</v>
       </c>
-      <c r="K26" s="12">
+      <c r="K26" s="11">
         <f>SUM(G26*1/2,I26*1/2)</f>
         <v>0</v>
       </c>
-      <c r="L26" s="12">
+      <c r="L26" s="11">
         <f>SUM(E26*1/5,F26*1/5,G26*1/5,H26*1/5,I26*1/5)</f>
         <v>0</v>
       </c>
@@ -6141,18 +6205,17 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="F27" s="9"/>
-      <c r="J27" s="12">
+      <c r="C27" s="63"/>
+      <c r="D27" s="63"/>
+      <c r="J27" s="11">
         <f>SUM(E27*1/3,F27*1/3,H27*1/3)</f>
         <v>0</v>
       </c>
-      <c r="K27" s="12">
+      <c r="K27" s="11">
         <f>SUM(G27*1/2,I27*1/2)</f>
         <v>0</v>
       </c>
-      <c r="L27" s="12">
+      <c r="L27" s="11">
         <f>SUM(E27*1/5,F27*1/5,G27*1/5,H27*1/5,I27*1/5)</f>
         <v>0</v>
       </c>
@@ -6164,23 +6227,29 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="58" t="s">
-        <v>90</v>
-      </c>
-      <c r="D29" s="58" t="s">
+      <c r="C29" s="63" t="s">
         <v>88</v>
       </c>
-      <c r="J29" s="12">
+      <c r="D29" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="G29" s="11">
+        <v>0.42895493769999998</v>
+      </c>
+      <c r="I29" s="11">
+        <v>0.48918897379999998</v>
+      </c>
+      <c r="J29" s="11">
         <f>SUM(E29*1/3,F29*1/3,H29*1/3)</f>
         <v>0</v>
       </c>
-      <c r="K29" s="12">
+      <c r="K29" s="11">
         <f>SUM(G29*1/2,I29*1/2)</f>
-        <v>0</v>
-      </c>
-      <c r="L29" s="12">
+        <v>0.45907195574999998</v>
+      </c>
+      <c r="L29" s="11">
         <f>SUM(E29*1/5,F29*1/5,G29*1/5,H29*1/5,I29*1/5)</f>
-        <v>0</v>
+        <v>0.18362878230000002</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
@@ -6190,17 +6259,17 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="58"/>
-      <c r="D30" s="58"/>
-      <c r="J30" s="12">
+      <c r="C30" s="63"/>
+      <c r="D30" s="63"/>
+      <c r="J30" s="11">
         <f>SUM(E30*1/3,F30*1/3,H30*1/3)</f>
         <v>0</v>
       </c>
-      <c r="K30" s="12">
+      <c r="K30" s="11">
         <f>SUM(G30*1/2,I30*1/2)</f>
         <v>0</v>
       </c>
-      <c r="L30" s="12">
+      <c r="L30" s="11">
         <f>SUM(E30*1/5,F30*1/5,G30*1/5,H30*1/5,I30*1/5)</f>
         <v>0</v>
       </c>
@@ -6212,558 +6281,931 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="F31" s="9"/>
-      <c r="J31" s="12">
+      <c r="C31" s="63"/>
+      <c r="D31" s="63"/>
+      <c r="J31" s="11">
         <f>SUM(E31*1/3,F31*1/3,H31*1/3)</f>
         <v>0</v>
       </c>
-      <c r="K31" s="12">
+      <c r="K31" s="11">
         <f>SUM(G31*1/2,I31*1/2)</f>
         <v>0</v>
       </c>
-      <c r="L31" s="12">
+      <c r="L31" s="11">
         <f>SUM(E31*1/5,F31*1/5,G31*1/5,H31*1/5,I31*1/5)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="F33" s="8"/>
-      <c r="H33" s="8"/>
-    </row>
-    <row r="34" spans="1:12" s="50" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="69" t="s">
-        <v>79</v>
-      </c>
-      <c r="B34" s="69"/>
-      <c r="C34" s="69"/>
-      <c r="D34" s="69"/>
-      <c r="E34" s="69"/>
-      <c r="F34" s="69"/>
-      <c r="G34" s="69"/>
-      <c r="H34" s="69"/>
-      <c r="I34" s="69"/>
-      <c r="J34" s="52"/>
-    </row>
-    <row r="35" spans="1:12" s="51" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="8"/>
-      <c r="B35" s="8"/>
-      <c r="C35" s="8"/>
-      <c r="D35" s="54"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="8"/>
-      <c r="H35" s="8"/>
-      <c r="I35" s="8"/>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A36" s="1" t="s">
+    <row r="33" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="58" t="s">
-        <v>80</v>
-      </c>
-      <c r="D36" s="58" t="s">
-        <v>72</v>
-      </c>
-      <c r="E36" s="12">
-        <v>5.6663470799999997E-2</v>
-      </c>
-      <c r="F36" s="12">
-        <v>9.2042185999999995E-3</v>
-      </c>
-      <c r="G36" s="12">
-        <v>0.42109300100000002</v>
-      </c>
-      <c r="H36" s="12">
-        <v>0.81920023559999999</v>
-      </c>
-      <c r="I36" s="12">
-        <v>0.44493382850000002</v>
-      </c>
-      <c r="J36" s="12">
-        <f>SUM(E36*1/3,F36*1/3,H36*1/3)</f>
-        <v>0.2950226416666667</v>
-      </c>
-      <c r="K36" s="12">
-        <f>SUM(G36*1/2,I36*1/2)</f>
-        <v>0.43301341474999999</v>
-      </c>
-      <c r="L36" s="12">
-        <f>SUM(E36*1/5,F36*1/5,G36*1/5,H36*1/5,I36*1/5)</f>
-        <v>0.35021895089999999</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="C33" s="63" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" s="63" t="s">
+        <v>92</v>
+      </c>
+      <c r="J33" s="11">
+        <f>SUM(E33*1/3,F33*1/3,H33*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="11">
+        <f>SUM(G33*1/2,I33*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L33" s="11">
+        <f>SUM(E33*1/5,F33*1/5,G33*1/5,H33*1/5,I33*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C34" s="63"/>
+      <c r="D34" s="63"/>
+      <c r="J34" s="11">
+        <f>SUM(E34*1/3,F34*1/3,H34*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="11">
+        <f>SUM(G34*1/2,I34*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="11">
+        <f>SUM(E34*1/5,F34*1/5,G34*1/5,H34*1/5,I34*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A35" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C35" s="63"/>
+      <c r="D35" s="63"/>
+      <c r="J35" s="11">
+        <f>SUM(E35*1/3,F35*1/3,H35*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="11">
+        <f>SUM(G35*1/2,I35*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L35" s="11">
+        <f>SUM(E35*1/5,F35*1/5,G35*1/5,H35*1/5,I35*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C37" s="58"/>
-      <c r="D37" s="58"/>
-      <c r="E37" s="12">
-        <v>8.2166826499999998E-2</v>
-      </c>
-      <c r="F37" s="12">
-        <v>9.5877299999999998E-5</v>
-      </c>
-      <c r="G37" s="12">
-        <v>0.42070949190000001</v>
-      </c>
-      <c r="H37" s="12">
-        <v>0.81290296760000003</v>
-      </c>
-      <c r="I37" s="12">
-        <v>0.4417925586</v>
-      </c>
-      <c r="J37" s="12">
+        <v>5</v>
+      </c>
+      <c r="C37" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="D37" s="77" t="s">
+        <v>94</v>
+      </c>
+      <c r="J37" s="11">
         <f>SUM(E37*1/3,F37*1/3,H37*1/3)</f>
-        <v>0.29838855713333334</v>
-      </c>
-      <c r="K37" s="12">
+        <v>0</v>
+      </c>
+      <c r="K37" s="11">
         <f>SUM(G37*1/2,I37*1/2)</f>
-        <v>0.43125102525000003</v>
-      </c>
-      <c r="L37" s="12">
+        <v>0</v>
+      </c>
+      <c r="L37" s="11">
         <f>SUM(E37*1/5,F37*1/5,G37*1/5,H37*1/5,I37*1/5)</f>
-        <v>0.35153354437999995</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C38" s="63"/>
+      <c r="D38" s="77"/>
+      <c r="J38" s="11">
+        <f>SUM(E38*1/3,F38*1/3,H38*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K38" s="11">
+        <f>SUM(G38*1/2,I38*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L38" s="11">
+        <f>SUM(E38*1/5,F38*1/5,G38*1/5,H38*1/5,I38*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A39" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="58"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="12">
-        <v>7.6701820000000002E-4</v>
-      </c>
-      <c r="F38" s="12">
-        <v>2.0134227999999998E-3</v>
-      </c>
-      <c r="G38" s="12">
-        <v>0.1702780441</v>
-      </c>
-      <c r="H38" s="12">
-        <v>0.46493483429999999</v>
-      </c>
-      <c r="I38" s="12">
-        <v>0.47127738250000001</v>
-      </c>
-      <c r="J38" s="12">
-        <f>SUM(E38*1/3,F38*1/3,H38*1/3)</f>
-        <v>0.15590509176666667</v>
-      </c>
-      <c r="K38" s="12">
-        <f>SUM(G38*1/2,I38*1/2)</f>
-        <v>0.32077771329999999</v>
-      </c>
-      <c r="L38" s="12">
-        <f>SUM(E38*1/5,F38*1/5,G38*1/5,H38*1/5,I38*1/5)</f>
-        <v>0.22185414038000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A40" s="1" t="s">
+      <c r="C39" s="63"/>
+      <c r="D39" s="77"/>
+      <c r="J39" s="11">
+        <f>SUM(E39*1/3,F39*1/3,H39*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K39" s="11">
+        <f>SUM(G39*1/2,I39*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L39" s="11">
+        <f>SUM(E39*1/5,F39*1/5,G39*1/5,H39*1/5,I39*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B41" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C40" s="58" t="s">
-        <v>81</v>
-      </c>
-      <c r="D40" s="58" t="s">
-        <v>74</v>
-      </c>
-      <c r="E40" s="12">
-        <v>4.5445829299999997E-2</v>
-      </c>
-      <c r="F40" s="12">
-        <v>6.6155322000000004E-3</v>
-      </c>
-      <c r="G40" s="12">
-        <v>0.45714285710000002</v>
-      </c>
-      <c r="H40" s="12">
-        <v>0.70717096769999999</v>
-      </c>
-      <c r="I40" s="12">
-        <v>0.50964245389999996</v>
-      </c>
-      <c r="J40" s="12">
-        <f>SUM(E40*1/3,F40*1/3,H40*1/3)</f>
-        <v>0.25307744306666669</v>
-      </c>
-      <c r="K40" s="12">
-        <f>SUM(G40*1/2,I40*1/2)</f>
-        <v>0.48339265549999999</v>
-      </c>
-      <c r="L40" s="12">
-        <f>SUM(E40*1/5,F40*1/5,G40*1/5,H40*1/5,I40*1/5)</f>
-        <v>0.34520352803999999</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C41" s="58"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="12">
-        <v>2.85714286E-2</v>
-      </c>
-      <c r="F41" s="12">
-        <v>1.9175456000000001E-3</v>
-      </c>
-      <c r="G41" s="12">
-        <v>0.45043144769999999</v>
-      </c>
-      <c r="H41" s="12">
-        <v>0.74414334049999997</v>
-      </c>
-      <c r="I41" s="12">
-        <v>0.46137624570000002</v>
-      </c>
-      <c r="J41" s="12">
+      <c r="C41" s="63" t="s">
+        <v>95</v>
+      </c>
+      <c r="D41" s="77" t="s">
+        <v>96</v>
+      </c>
+      <c r="J41" s="11">
         <f>SUM(E41*1/3,F41*1/3,H41*1/3)</f>
-        <v>0.25821077156666666</v>
-      </c>
-      <c r="K41" s="12">
+        <v>0</v>
+      </c>
+      <c r="K41" s="11">
         <f>SUM(G41*1/2,I41*1/2)</f>
-        <v>0.4559038467</v>
-      </c>
-      <c r="L41" s="12">
+        <v>0</v>
+      </c>
+      <c r="L41" s="11">
         <f>SUM(E41*1/5,F41*1/5,G41*1/5,H41*1/5,I41*1/5)</f>
-        <v>0.33728800162</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C42" s="63"/>
+      <c r="D42" s="77"/>
+      <c r="J42" s="11">
+        <f>SUM(E42*1/3,F42*1/3,H42*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="11">
+        <f>SUM(G42*1/2,I42*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="11">
+        <f>SUM(E42*1/5,F42*1/5,G42*1/5,H42*1/5,I42*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A43" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C42" s="58"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="12">
-        <v>3.8350910000000001E-4</v>
-      </c>
-      <c r="F42" s="12">
-        <v>1.3422817999999999E-3</v>
-      </c>
-      <c r="G42" s="12">
-        <v>0.79022051770000001</v>
-      </c>
-      <c r="H42" s="12">
-        <v>0.49764374880000001</v>
-      </c>
-      <c r="I42" s="12">
-        <v>0.48742542859999999</v>
-      </c>
-      <c r="J42" s="12">
-        <f>SUM(E42*1/3,F42*1/3,H42*1/3)</f>
-        <v>0.16645651323333333</v>
-      </c>
-      <c r="K42" s="12">
-        <f>SUM(G42*1/2,I42*1/2)</f>
-        <v>0.63882297315000003</v>
-      </c>
-      <c r="L42" s="12">
-        <f>SUM(E42*1/5,F42*1/5,G42*1/5,H42*1/5,I42*1/5)</f>
-        <v>0.35540309720000007</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
-      <c r="H43" s="12"/>
-      <c r="I43" s="12"/>
-      <c r="J43" s="12"/>
-      <c r="K43" s="12"/>
-      <c r="L43" s="12"/>
-    </row>
-    <row r="45" spans="1:12" s="50" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="69" t="s">
-        <v>82</v>
-      </c>
-      <c r="B45" s="69"/>
-      <c r="C45" s="69"/>
-      <c r="D45" s="69"/>
-      <c r="E45" s="69"/>
-      <c r="F45" s="69"/>
-      <c r="G45" s="69"/>
-      <c r="H45" s="69"/>
-      <c r="I45" s="69"/>
-      <c r="J45" s="52"/>
-    </row>
-    <row r="46" spans="1:12" s="51" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="8"/>
-      <c r="B46" s="8"/>
-      <c r="C46" s="8"/>
-      <c r="D46" s="54"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="8"/>
-      <c r="H46" s="8"/>
-      <c r="I46" s="8"/>
+      <c r="C43" s="63"/>
+      <c r="D43" s="77"/>
+      <c r="J43" s="11">
+        <f>SUM(E43*1/3,F43*1/3,H43*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K43" s="11">
+        <f>SUM(G43*1/2,I43*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L43" s="11">
+        <f>SUM(E43*1/5,F43*1/5,G43*1/5,H43*1/5,I43*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C45" s="63" t="s">
+        <v>97</v>
+      </c>
+      <c r="D45" s="77" t="s">
+        <v>98</v>
+      </c>
+      <c r="J45" s="11">
+        <f>SUM(E45*1/3,F45*1/3,H45*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K45" s="11">
+        <f>SUM(G45*1/2,I45*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L45" s="11">
+        <f>SUM(E45*1/5,F45*1/5,G45*1/5,H45*1/5,I45*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A46" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C46" s="63"/>
+      <c r="D46" s="77"/>
+      <c r="J46" s="11">
+        <f>SUM(E46*1/3,F46*1/3,H46*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K46" s="11">
+        <f>SUM(G46*1/2,I46*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L46" s="11">
+        <f>SUM(E46*1/5,F46*1/5,G46*1/5,H46*1/5,I46*1/5)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="63"/>
+      <c r="D47" s="77"/>
+      <c r="J47" s="11">
+        <f>SUM(E47*1/3,F47*1/3,H47*1/3)</f>
+        <v>0</v>
+      </c>
+      <c r="K47" s="11">
+        <f>SUM(G47*1/2,I47*1/2)</f>
+        <v>0</v>
+      </c>
+      <c r="L47" s="11">
+        <f>SUM(E47*1/5,F47*1/5,G47*1/5,H47*1/5,I47*1/5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="67" t="s">
+        <v>60</v>
+      </c>
+      <c r="B49" s="67"/>
+      <c r="C49" s="67"/>
+      <c r="D49" s="67"/>
+      <c r="E49" s="17">
+        <f>MAX(E4:E35)</f>
+        <v>7.6701821700000006E-2</v>
+      </c>
+      <c r="F49" s="17">
+        <f>MAX(F4:F35)</f>
+        <v>7.9290508100000004E-2</v>
+      </c>
+      <c r="G49" s="17">
+        <f>MAX(G4:G35)</f>
+        <v>0.6839884947</v>
+      </c>
+      <c r="H49" s="17">
+        <f>MAX(H4:H35)</f>
+        <v>0.90418992629999995</v>
+      </c>
+      <c r="I49" s="17">
+        <f>MAX(I4:I35)</f>
+        <v>0.68586700889999996</v>
+      </c>
+      <c r="J49" s="17">
+        <f>MAX(J4:J35)</f>
+        <v>0.33470898553333334</v>
+      </c>
+      <c r="K49" s="17">
+        <f>MAX(K4:K35)</f>
+        <v>0.67476476045</v>
+      </c>
+      <c r="L49" s="17">
+        <f>MAX(L4:L35)</f>
+        <v>0.39261373816</v>
+      </c>
+      <c r="M49" s="17"/>
+      <c r="N49" s="18"/>
+    </row>
+    <row r="50" spans="1:14" s="54" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="64" t="s">
+        <v>61</v>
+      </c>
+      <c r="B50" s="64"/>
+      <c r="C50" s="64"/>
+      <c r="D50" s="64"/>
+      <c r="E50" s="31">
+        <f>AVERAGE(E5:E35)</f>
+        <v>3.3844678824999995E-2</v>
+      </c>
+      <c r="F50" s="31">
+        <f>AVERAGE(F5:F35)</f>
+        <v>1.1984659633333332E-2</v>
+      </c>
+      <c r="G50" s="31">
+        <f>AVERAGE(G5:G35)</f>
+        <v>0.44426790851428571</v>
+      </c>
+      <c r="H50" s="31">
+        <f>AVERAGE(H5:H35)</f>
+        <v>0.68153575924166665</v>
+      </c>
+      <c r="I50" s="31">
+        <f>AVERAGE(I5:I35)</f>
+        <v>0.48174301881333342</v>
+      </c>
+      <c r="J50" s="31">
+        <f>AVERAGE(J5:J35)</f>
+        <v>0.12122751628333334</v>
+      </c>
+      <c r="K50" s="31">
+        <f>AVERAGE(K5:K35)</f>
+        <v>0.28012283336249993</v>
+      </c>
+      <c r="L50" s="31">
+        <f>AVERAGE(L5:L35)</f>
+        <v>0.18478564311499998</v>
+      </c>
+      <c r="M50" s="31"/>
+      <c r="N50" s="76"/>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="F51" s="72"/>
+      <c r="H51" s="72"/>
+    </row>
+    <row r="52" spans="1:14" s="49" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="68" t="s">
+        <v>79</v>
+      </c>
+      <c r="B52" s="68"/>
+      <c r="C52" s="68"/>
+      <c r="D52" s="68"/>
+      <c r="E52" s="68"/>
+      <c r="F52" s="68"/>
+      <c r="G52" s="68"/>
+      <c r="H52" s="68"/>
+      <c r="I52" s="68"/>
+      <c r="J52" s="51"/>
+      <c r="K52" s="74"/>
+      <c r="L52" s="74"/>
+    </row>
+    <row r="53" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="8"/>
+      <c r="B53" s="8"/>
+      <c r="C53" s="8"/>
+      <c r="D53" s="53"/>
+      <c r="E53" s="72"/>
+      <c r="F53" s="72"/>
+      <c r="G53" s="72"/>
+      <c r="H53" s="72"/>
+      <c r="I53" s="72"/>
+      <c r="J53" s="75"/>
+      <c r="K53" s="75"/>
+      <c r="L53" s="75"/>
+    </row>
+    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A54" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C47" s="58" t="s">
+      <c r="C54" s="63" t="s">
+        <v>80</v>
+      </c>
+      <c r="D54" s="63" t="s">
+        <v>72</v>
+      </c>
+      <c r="E54" s="11">
+        <v>5.6663470799999997E-2</v>
+      </c>
+      <c r="F54" s="11">
+        <v>9.2042185999999995E-3</v>
+      </c>
+      <c r="G54" s="11">
+        <v>0.42109300100000002</v>
+      </c>
+      <c r="H54" s="11">
+        <v>0.81920023559999999</v>
+      </c>
+      <c r="I54" s="11">
+        <v>0.44493382850000002</v>
+      </c>
+      <c r="J54" s="11">
+        <f>SUM(E54*1/3,F54*1/3,H54*1/3)</f>
+        <v>0.2950226416666667</v>
+      </c>
+      <c r="K54" s="11">
+        <f>SUM(G54*1/2,I54*1/2)</f>
+        <v>0.43301341474999999</v>
+      </c>
+      <c r="L54" s="11">
+        <f>SUM(E54*1/5,F54*1/5,G54*1/5,H54*1/5,I54*1/5)</f>
+        <v>0.35021895089999999</v>
+      </c>
+    </row>
+    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C55" s="63"/>
+      <c r="D55" s="63"/>
+      <c r="E55" s="11">
+        <v>8.2166826499999998E-2</v>
+      </c>
+      <c r="F55" s="11">
+        <v>9.5877299999999998E-5</v>
+      </c>
+      <c r="G55" s="11">
+        <v>0.42070949190000001</v>
+      </c>
+      <c r="H55" s="11">
+        <v>0.81290296760000003</v>
+      </c>
+      <c r="I55" s="11">
+        <v>0.4417925586</v>
+      </c>
+      <c r="J55" s="11">
+        <f>SUM(E55*1/3,F55*1/3,H55*1/3)</f>
+        <v>0.29838855713333334</v>
+      </c>
+      <c r="K55" s="11">
+        <f>SUM(G55*1/2,I55*1/2)</f>
+        <v>0.43125102525000003</v>
+      </c>
+      <c r="L55" s="11">
+        <f>SUM(E55*1/5,F55*1/5,G55*1/5,H55*1/5,I55*1/5)</f>
+        <v>0.35153354437999995</v>
+      </c>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A56" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C56" s="63"/>
+      <c r="D56" s="63"/>
+      <c r="E56" s="11">
+        <v>7.6701820000000002E-4</v>
+      </c>
+      <c r="F56" s="11">
+        <v>2.0134227999999998E-3</v>
+      </c>
+      <c r="G56" s="11">
+        <v>0.1702780441</v>
+      </c>
+      <c r="H56" s="11">
+        <v>0.46493483429999999</v>
+      </c>
+      <c r="I56" s="11">
+        <v>0.47127738250000001</v>
+      </c>
+      <c r="J56" s="11">
+        <f>SUM(E56*1/3,F56*1/3,H56*1/3)</f>
+        <v>0.15590509176666667</v>
+      </c>
+      <c r="K56" s="11">
+        <f>SUM(G56*1/2,I56*1/2)</f>
+        <v>0.32077771329999999</v>
+      </c>
+      <c r="L56" s="11">
+        <f>SUM(E56*1/5,F56*1/5,G56*1/5,H56*1/5,I56*1/5)</f>
+        <v>0.22185414038000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C58" s="63" t="s">
+        <v>81</v>
+      </c>
+      <c r="D58" s="63" t="s">
+        <v>74</v>
+      </c>
+      <c r="E58" s="11">
+        <v>4.5445829299999997E-2</v>
+      </c>
+      <c r="F58" s="11">
+        <v>6.6155322000000004E-3</v>
+      </c>
+      <c r="G58" s="11">
+        <v>0.45714285710000002</v>
+      </c>
+      <c r="H58" s="11">
+        <v>0.70717096769999999</v>
+      </c>
+      <c r="I58" s="11">
+        <v>0.50964245389999996</v>
+      </c>
+      <c r="J58" s="11">
+        <f>SUM(E58*1/3,F58*1/3,H58*1/3)</f>
+        <v>0.25307744306666669</v>
+      </c>
+      <c r="K58" s="11">
+        <f>SUM(G58*1/2,I58*1/2)</f>
+        <v>0.48339265549999999</v>
+      </c>
+      <c r="L58" s="11">
+        <f>SUM(E58*1/5,F58*1/5,G58*1/5,H58*1/5,I58*1/5)</f>
+        <v>0.34520352803999999</v>
+      </c>
+    </row>
+    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A59" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C59" s="63"/>
+      <c r="D59" s="63"/>
+      <c r="E59" s="11">
+        <v>2.85714286E-2</v>
+      </c>
+      <c r="F59" s="11">
+        <v>1.9175456000000001E-3</v>
+      </c>
+      <c r="G59" s="11">
+        <v>0.45043144769999999</v>
+      </c>
+      <c r="H59" s="11">
+        <v>0.74414334049999997</v>
+      </c>
+      <c r="I59" s="11">
+        <v>0.46137624570000002</v>
+      </c>
+      <c r="J59" s="11">
+        <f>SUM(E59*1/3,F59*1/3,H59*1/3)</f>
+        <v>0.25821077156666666</v>
+      </c>
+      <c r="K59" s="11">
+        <f>SUM(G59*1/2,I59*1/2)</f>
+        <v>0.4559038467</v>
+      </c>
+      <c r="L59" s="11">
+        <f>SUM(E59*1/5,F59*1/5,G59*1/5,H59*1/5,I59*1/5)</f>
+        <v>0.33728800162</v>
+      </c>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A60" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="63"/>
+      <c r="D60" s="63"/>
+      <c r="E60" s="11">
+        <v>3.8350910000000001E-4</v>
+      </c>
+      <c r="F60" s="11">
+        <v>1.3422817999999999E-3</v>
+      </c>
+      <c r="G60" s="11">
+        <v>0.79022051770000001</v>
+      </c>
+      <c r="H60" s="11">
+        <v>0.49764374880000001</v>
+      </c>
+      <c r="I60" s="11">
+        <v>0.48742542859999999</v>
+      </c>
+      <c r="J60" s="11">
+        <f>SUM(E60*1/3,F60*1/3,H60*1/3)</f>
+        <v>0.16645651323333333</v>
+      </c>
+      <c r="K60" s="11">
+        <f>SUM(G60*1/2,I60*1/2)</f>
+        <v>0.63882297315000003</v>
+      </c>
+      <c r="L60" s="11">
+        <f>SUM(E60*1/5,F60*1/5,G60*1/5,H60*1/5,I60*1/5)</f>
+        <v>0.35540309720000007</v>
+      </c>
+    </row>
+    <row r="62" spans="1:14" s="49" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="68" t="s">
+        <v>82</v>
+      </c>
+      <c r="B62" s="68"/>
+      <c r="C62" s="68"/>
+      <c r="D62" s="68"/>
+      <c r="E62" s="68"/>
+      <c r="F62" s="68"/>
+      <c r="G62" s="68"/>
+      <c r="H62" s="68"/>
+      <c r="I62" s="68"/>
+      <c r="J62" s="51"/>
+      <c r="K62" s="74"/>
+      <c r="L62" s="74"/>
+    </row>
+    <row r="63" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="8"/>
+      <c r="B63" s="8"/>
+      <c r="C63" s="8"/>
+      <c r="D63" s="53"/>
+      <c r="E63" s="72"/>
+      <c r="F63" s="72"/>
+      <c r="G63" s="72"/>
+      <c r="H63" s="72"/>
+      <c r="I63" s="72"/>
+      <c r="J63" s="75"/>
+      <c r="K63" s="75"/>
+      <c r="L63" s="75"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A64" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" s="63" t="s">
         <v>83</v>
       </c>
-      <c r="D47" s="58" t="s">
+      <c r="D64" s="63" t="s">
         <v>72</v>
       </c>
-      <c r="E47" s="12">
+      <c r="E64" s="11">
         <v>2.0997123699999998E-2</v>
       </c>
-      <c r="F47" s="12">
+      <c r="F64" s="11">
         <v>2.3010547000000001E-3</v>
       </c>
-      <c r="G47" s="12">
+      <c r="G64" s="11">
         <v>0.3390220518</v>
       </c>
-      <c r="H47" s="12">
+      <c r="H64" s="11">
         <v>0.80129368079999996</v>
       </c>
-      <c r="I47" s="12">
+      <c r="I64" s="11">
         <v>0.42862661320000001</v>
       </c>
-      <c r="J47" s="12">
-        <f>SUM(E47*1/3,F47*1/3,H47*1/3)</f>
+      <c r="J64" s="11">
+        <f>SUM(E64*1/3,F64*1/3,H64*1/3)</f>
         <v>0.27486395306666661</v>
       </c>
-      <c r="K47" s="12">
-        <f>SUM(G47*1/2,I47*1/2)</f>
+      <c r="K64" s="11">
+        <f>SUM(G64*1/2,I64*1/2)</f>
         <v>0.38382433250000003</v>
       </c>
-      <c r="L47" s="12">
-        <f>SUM(E47*1/5,F47*1/5,G47*1/5,H47*1/5,I47*1/5)</f>
+      <c r="L64" s="11">
+        <f>SUM(E64*1/5,F64*1/5,G64*1/5,H64*1/5,I64*1/5)</f>
         <v>0.31844810483999997</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A48" s="1" t="s">
+    <row r="65" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A65" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B65" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C48" s="58"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="12">
+      <c r="C65" s="63"/>
+      <c r="D65" s="63"/>
+      <c r="E65" s="11">
         <v>3.2598274E-3</v>
       </c>
-      <c r="F48" s="12">
+      <c r="F65" s="11">
         <v>4.1227229000000004E-3</v>
       </c>
-      <c r="G48" s="12">
+      <c r="G65" s="11">
         <v>0.25656759350000002</v>
       </c>
-      <c r="H48" s="12">
+      <c r="H65" s="11">
         <v>0.5509203869</v>
       </c>
-      <c r="I48" s="12">
+      <c r="I65" s="11">
         <v>0.4742471747</v>
       </c>
-      <c r="J48" s="12">
-        <f>SUM(E48*1/3,F48*1/3,H48*1/3)</f>
+      <c r="J65" s="11">
+        <f>SUM(E65*1/3,F65*1/3,H65*1/3)</f>
         <v>0.18610097906666667</v>
       </c>
-      <c r="K48" s="12">
-        <f>SUM(G48*1/2,I48*1/2)</f>
+      <c r="K65" s="11">
+        <f>SUM(G65*1/2,I65*1/2)</f>
         <v>0.36540738410000001</v>
       </c>
-      <c r="L48" s="12">
-        <f>SUM(E48*1/5,F48*1/5,G48*1/5,H48*1/5,I48*1/5)</f>
+      <c r="L65" s="11">
+        <f>SUM(E65*1/5,F65*1/5,G65*1/5,H65*1/5,I65*1/5)</f>
         <v>0.25782354108</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A49" s="1" t="s">
+    <row r="66" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A66" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B66" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C49" s="58"/>
-      <c r="D49" s="58"/>
-      <c r="E49" s="12">
+      <c r="C66" s="63"/>
+      <c r="D66" s="63"/>
+      <c r="E66" s="11">
         <v>0</v>
       </c>
-      <c r="F49" s="12">
+      <c r="F66" s="11">
         <v>9.5877280000000004E-4</v>
       </c>
-      <c r="G49" s="12">
+      <c r="G66" s="11">
         <v>0.35321188879999998</v>
       </c>
-      <c r="H49" s="12">
+      <c r="H66" s="11">
         <v>0.55203139629999998</v>
       </c>
-      <c r="I49" s="12">
+      <c r="I66" s="11">
         <v>0.4477544779</v>
       </c>
-      <c r="J49" s="12">
-        <f>SUM(E49*1/3,F49*1/3,H49*1/3)</f>
+      <c r="J66" s="11">
+        <f>SUM(E66*1/3,F66*1/3,H66*1/3)</f>
         <v>0.18433005636666666</v>
       </c>
-      <c r="K49" s="12">
-        <f>SUM(G49*1/2,I49*1/2)</f>
+      <c r="K66" s="11">
+        <f>SUM(G66*1/2,I66*1/2)</f>
         <v>0.40048318334999999</v>
       </c>
-      <c r="L49" s="12">
-        <f>SUM(E49*1/5,F49*1/5,G49*1/5,H49*1/5,I49*1/5)</f>
+      <c r="L66" s="11">
+        <f>SUM(E66*1/5,F66*1/5,G66*1/5,H66*1/5,I66*1/5)</f>
         <v>0.27079130715999999</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A51" s="1" t="s">
+    <row r="68" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A68" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B68" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C51" s="58" t="s">
+      <c r="C68" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="D51" s="58" t="s">
+      <c r="D68" s="63" t="s">
         <v>74</v>
       </c>
-      <c r="E51" s="12">
+      <c r="E68" s="11">
         <v>7.2003835099999997E-2</v>
       </c>
-      <c r="F51" s="12">
+      <c r="F68" s="11">
         <v>7.3825504E-3</v>
       </c>
-      <c r="G51" s="12">
+      <c r="G68" s="11">
         <v>0.3771812081</v>
       </c>
-      <c r="H51" s="12">
+      <c r="H68" s="11">
         <v>0.74268293880000003</v>
       </c>
-      <c r="I51" s="12">
+      <c r="I68" s="11">
         <v>0.45190041990000002</v>
       </c>
-      <c r="J51" s="12">
-        <f>SUM(E51*1/3,F51*1/3,H51*1/3)</f>
+      <c r="J68" s="11">
+        <f>SUM(E68*1/3,F68*1/3,H68*1/3)</f>
         <v>0.27402310810000002</v>
       </c>
-      <c r="K51" s="12">
-        <f>SUM(G51*1/2,I51*1/2)</f>
+      <c r="K68" s="11">
+        <f>SUM(G68*1/2,I68*1/2)</f>
         <v>0.41454081399999998</v>
       </c>
-      <c r="L51" s="12">
-        <f>SUM(E51*1/5,F51*1/5,G51*1/5,H51*1/5,I51*1/5)</f>
+      <c r="L68" s="11">
+        <f>SUM(E68*1/5,F68*1/5,G68*1/5,H68*1/5,I68*1/5)</f>
         <v>0.33023019046000002</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A52" s="1" t="s">
+    <row r="69" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A69" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B69" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C52" s="58"/>
-      <c r="D52" s="58"/>
-      <c r="E52" s="12">
+      <c r="C69" s="63"/>
+      <c r="D69" s="63"/>
+      <c r="E69" s="11">
         <v>8.59060403E-2</v>
       </c>
-      <c r="F52" s="12">
+      <c r="F69" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
-      <c r="G52" s="12">
+      <c r="G69" s="11">
         <v>0.59731543620000005</v>
       </c>
-      <c r="H52" s="12">
+      <c r="H69" s="11">
         <v>0.8594864566</v>
       </c>
-      <c r="I52" s="12">
+      <c r="I69" s="11">
         <v>0.43209071430000001</v>
       </c>
-      <c r="J52" s="12">
-        <f>SUM(E52*1/3,F52*1/3,H52*1/3)</f>
+      <c r="J69" s="11">
+        <f>SUM(E69*1/3,F69*1/3,H69*1/3)</f>
         <v>0.31532258686666664</v>
       </c>
-      <c r="K52" s="12">
-        <f>SUM(G52*1/2,I52*1/2)</f>
+      <c r="K69" s="11">
+        <f>SUM(G69*1/2,I69*1/2)</f>
         <v>0.51470307525000003</v>
       </c>
-      <c r="L52" s="12">
-        <f>SUM(E52*1/5,F52*1/5,G52*1/5,H52*1/5,I52*1/5)</f>
+      <c r="L69" s="11">
+        <f>SUM(E69*1/5,F69*1/5,G69*1/5,H69*1/5,I69*1/5)</f>
         <v>0.39507478221999998</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A53" s="1" t="s">
+    <row r="70" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A70" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B70" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="58"/>
-      <c r="D53" s="58"/>
-      <c r="E53" s="12">
+      <c r="C70" s="63"/>
+      <c r="D70" s="63"/>
+      <c r="E70" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
-      <c r="F53" s="12">
+      <c r="F70" s="11">
         <v>1.1505274000000001E-3</v>
       </c>
-      <c r="G53" s="12">
+      <c r="G70" s="11">
         <v>0.4678811122</v>
       </c>
-      <c r="H53" s="12">
+      <c r="H70" s="11">
         <v>0.50554854299999996</v>
       </c>
-      <c r="I53" s="12">
+      <c r="I70" s="11">
         <v>0.48466990739999999</v>
       </c>
-      <c r="J53" s="12">
-        <f>SUM(E53*1/3,F53*1/3,H53*1/3)</f>
+      <c r="J70" s="11">
+        <f>SUM(E70*1/3,F70*1/3,H70*1/3)</f>
         <v>0.1690275265</v>
       </c>
-      <c r="K53" s="12">
-        <f>SUM(G53*1/2,I53*1/2)</f>
+      <c r="K70" s="11">
+        <f>SUM(G70*1/2,I70*1/2)</f>
         <v>0.4762755098</v>
       </c>
-      <c r="L53" s="12">
-        <f>SUM(E53*1/5,F53*1/5,G53*1/5,H53*1/5,I53*1/5)</f>
+      <c r="L70" s="11">
+        <f>SUM(E70*1/5,F70*1/5,G70*1/5,H70*1/5,I70*1/5)</f>
         <v>0.29192671981999996</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
-      <c r="H54" s="12"/>
-      <c r="I54" s="12"/>
-      <c r="J54" s="12"/>
-      <c r="K54" s="12"/>
-      <c r="L54" s="12"/>
-    </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="35">
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="D41:D43"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="D45:D47"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="D64:D66"/>
+    <mergeCell ref="C68:C70"/>
+    <mergeCell ref="D68:D70"/>
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="D54:D56"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="D58:D60"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="D13:D15"/>
     <mergeCell ref="C29:C31"/>
@@ -6779,16 +7221,6 @@
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="D17:D19"/>
     <mergeCell ref="C17:C19"/>
-    <mergeCell ref="A34:I34"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="C40:C42"/>
-    <mergeCell ref="D40:D42"/>
-    <mergeCell ref="A45:I45"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="D47:D49"/>
-    <mergeCell ref="C51:C53"/>
-    <mergeCell ref="D51:D53"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/benchmarking/search_for_best_combination/results_basic.xlsx
+++ b/benchmarking/search_for_best_combination/results_basic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7C33681-DB34-E047-9FC8-1F0AD9059E62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9831C867-36F4-254A-ADE1-FC03E5C00DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="3" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="3" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>
@@ -712,6 +712,24 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -739,6 +757,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -747,36 +777,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1161,13 +1161,13 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="65" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="11">
@@ -1185,7 +1185,7 @@
       <c r="J2" s="11">
         <v>0.51636704079999995</v>
       </c>
-      <c r="K2" s="62" t="s">
+      <c r="K2" s="68" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1196,9 +1196,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
       <c r="F3" s="11">
         <v>5.23489933E-2</v>
       </c>
@@ -1214,7 +1214,7 @@
       <c r="J3" s="11">
         <v>0.49172142549999998</v>
       </c>
-      <c r="K3" s="63"/>
+      <c r="K3" s="69"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1223,9 +1223,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="56"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
       <c r="F4" s="11">
         <v>3.73921381E-2</v>
       </c>
@@ -1241,7 +1241,7 @@
       <c r="J4" s="11">
         <v>0.44867621930000001</v>
       </c>
-      <c r="K4" s="63"/>
+      <c r="K4" s="69"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -1250,13 +1250,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="57" t="s">
+      <c r="D6" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="57" t="s">
+      <c r="E6" s="63" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -1274,7 +1274,7 @@
       <c r="J6" s="11">
         <v>0.49915964429999998</v>
       </c>
-      <c r="K6" s="63" t="s">
+      <c r="K6" s="69" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1285,9 +1285,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="56"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
       <c r="F7" s="11">
         <v>2.7399884999999999E-2</v>
       </c>
@@ -1303,7 +1303,7 @@
       <c r="J7" s="11">
         <v>0.48493602559999999</v>
       </c>
-      <c r="K7" s="63"/>
+      <c r="K7" s="69"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -1312,9 +1312,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="56"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
       <c r="F8" s="11">
         <v>2.4717378799999998E-2</v>
       </c>
@@ -1330,15 +1330,15 @@
       <c r="J8" s="11">
         <v>0.43282600290000001</v>
       </c>
-      <c r="K8" s="63"/>
+      <c r="K8" s="69"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
       <c r="E10" s="5"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
@@ -1354,13 +1354,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="57" t="s">
+      <c r="D12" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="57" t="s">
+      <c r="E12" s="63" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -1378,7 +1378,7 @@
       <c r="J12" s="11">
         <v>0.45356946819999999</v>
       </c>
-      <c r="K12" s="63" t="s">
+      <c r="K12" s="69" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1389,9 +1389,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="56"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
       <c r="F13" s="11">
         <v>5.4569232000000002E-2</v>
       </c>
@@ -1407,7 +1407,7 @@
       <c r="J13" s="11">
         <v>0.2490125493</v>
       </c>
-      <c r="K13" s="63"/>
+      <c r="K13" s="69"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -1416,9 +1416,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="56"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
       <c r="F14" s="11">
         <v>0.2933740192</v>
       </c>
@@ -1434,7 +1434,7 @@
       <c r="J14" s="11">
         <v>0.33911636109999999</v>
       </c>
-      <c r="K14" s="63"/>
+      <c r="K14" s="69"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -1443,13 +1443,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="56" t="s">
+      <c r="C16" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="57" t="s">
+      <c r="D16" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="57" t="s">
+      <c r="E16" s="63" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -1467,7 +1467,7 @@
       <c r="J16" s="11">
         <v>0.46862206229999998</v>
       </c>
-      <c r="K16" s="63" t="s">
+      <c r="K16" s="69" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1478,9 +1478,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="56"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="11">
         <v>0.2220972487</v>
       </c>
@@ -1496,7 +1496,7 @@
       <c r="J17" s="11">
         <v>0.61463971539999995</v>
       </c>
-      <c r="K17" s="63"/>
+      <c r="K17" s="69"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -1505,9 +1505,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
       <c r="F18" s="11">
         <v>0.12510815019999999</v>
       </c>
@@ -1523,7 +1523,7 @@
       <c r="J18" s="11">
         <v>0.40298454760000002</v>
       </c>
-      <c r="K18" s="63"/>
+      <c r="K18" s="69"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -1532,13 +1532,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="56" t="s">
+      <c r="C20" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="57" t="s">
+      <c r="D20" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="57" t="s">
+      <c r="E20" s="63" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -1556,7 +1556,7 @@
       <c r="J20" s="11">
         <v>0.42112340529999998</v>
       </c>
-      <c r="K20" s="63" t="s">
+      <c r="K20" s="69" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1567,9 +1567,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="56"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="63"/>
       <c r="F21" s="11">
         <v>0.28648624509999998</v>
       </c>
@@ -1585,7 +1585,7 @@
       <c r="J21" s="19">
         <v>0.71830903779999999</v>
       </c>
-      <c r="K21" s="63"/>
+      <c r="K21" s="69"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -1594,9 +1594,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="56"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
       <c r="F22" s="11">
         <v>4.4658810000000002E-4</v>
       </c>
@@ -1609,7 +1609,7 @@
       <c r="J22" s="11">
         <v>0.41851161510000001</v>
       </c>
-      <c r="K22" s="63"/>
+      <c r="K22" s="69"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -1618,13 +1618,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="56" t="s">
+      <c r="C24" s="62" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="57" t="s">
+      <c r="D24" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="57" t="s">
+      <c r="E24" s="63" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -1650,9 +1650,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="56"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="63"/>
+      <c r="E25" s="63"/>
       <c r="F25" s="11">
         <v>0.1240506329</v>
       </c>
@@ -1676,9 +1676,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="56"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
       <c r="F26" s="11">
         <v>0.13367616030000001</v>
       </c>
@@ -1702,13 +1702,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="56" t="s">
+      <c r="C28" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="57" t="s">
+      <c r="D28" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="57" t="s">
+      <c r="E28" s="63" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -1734,9 +1734,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="56"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="63"/>
       <c r="F29" s="11">
         <v>0.20128508440000001</v>
       </c>
@@ -1760,9 +1760,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="56"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="63"/>
       <c r="F30" s="11">
         <v>0.1974137004</v>
       </c>
@@ -1786,13 +1786,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="56" t="s">
+      <c r="C32" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="57" t="s">
+      <c r="D32" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="57" t="s">
+      <c r="E32" s="63" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="19">
@@ -1818,9 +1818,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="56"/>
-      <c r="D33" s="57"/>
-      <c r="E33" s="57"/>
+      <c r="C33" s="62"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="63"/>
       <c r="F33" s="11">
         <v>0.4661326187</v>
       </c>
@@ -1844,9 +1844,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="56"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="57"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="63"/>
       <c r="F34" s="11">
         <v>2.2806319999999999E-4</v>
       </c>
@@ -1870,13 +1870,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="56" t="s">
+      <c r="C36" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="57" t="s">
+      <c r="D36" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="57" t="s">
+      <c r="E36" s="63" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -1902,9 +1902,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="56"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
+      <c r="C37" s="62"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="63"/>
       <c r="F37" s="11">
         <v>0.29922617379999999</v>
       </c>
@@ -1928,9 +1928,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="56"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
+      <c r="C38" s="62"/>
+      <c r="D38" s="63"/>
+      <c r="E38" s="63"/>
       <c r="F38" s="11">
         <v>0.1553265707</v>
       </c>
@@ -1948,12 +1948,12 @@
       </c>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="58" t="s">
+      <c r="A40" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="58"/>
-      <c r="C40" s="58"/>
-      <c r="D40" s="58"/>
+      <c r="B40" s="64"/>
+      <c r="C40" s="64"/>
+      <c r="D40" s="64"/>
       <c r="E40" s="5"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
@@ -1969,13 +1969,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="56" t="s">
+      <c r="C42" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="57" t="s">
+      <c r="D42" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="57" t="s">
+      <c r="E42" s="63" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -1993,7 +1993,7 @@
       <c r="J42" s="11">
         <v>0.50415219909999998</v>
       </c>
-      <c r="K42" s="63" t="s">
+      <c r="K42" s="69" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2004,9 +2004,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="56"/>
-      <c r="D43" s="57"/>
-      <c r="E43" s="57"/>
+      <c r="C43" s="62"/>
+      <c r="D43" s="63"/>
+      <c r="E43" s="63"/>
       <c r="F43" s="11">
         <v>0.27900922929999999</v>
       </c>
@@ -2022,7 +2022,7 @@
       <c r="J43" s="11">
         <v>0.6867986989</v>
       </c>
-      <c r="K43" s="63"/>
+      <c r="K43" s="69"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -2031,9 +2031,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="56"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
+      <c r="C44" s="62"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
       <c r="F44" s="11">
         <v>1.08858563E-2</v>
       </c>
@@ -2049,7 +2049,7 @@
       <c r="J44" s="11">
         <v>0.34279394219999998</v>
       </c>
-      <c r="K44" s="63"/>
+      <c r="K44" s="69"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -2058,13 +2058,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="56" t="s">
+      <c r="C46" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="57" t="s">
+      <c r="D46" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="57" t="s">
+      <c r="E46" s="63" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -2082,7 +2082,7 @@
       <c r="J46" s="11">
         <v>0.43511184339999998</v>
       </c>
-      <c r="K46" s="63" t="s">
+      <c r="K46" s="69" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2093,9 +2093,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="56"/>
-      <c r="D47" s="57"/>
-      <c r="E47" s="57"/>
+      <c r="C47" s="62"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="63"/>
       <c r="F47" s="11">
         <v>0.36941770550000003</v>
       </c>
@@ -2111,7 +2111,7 @@
       <c r="J47" s="11">
         <v>0.67778323610000002</v>
       </c>
-      <c r="K47" s="63"/>
+      <c r="K47" s="69"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -2120,9 +2120,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="56"/>
-      <c r="D48" s="57"/>
-      <c r="E48" s="57"/>
+      <c r="C48" s="62"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="63"/>
       <c r="F48" s="11">
         <v>7.1050970500000005E-2</v>
       </c>
@@ -2138,7 +2138,7 @@
       <c r="J48" s="11">
         <v>0.33626401280000001</v>
       </c>
-      <c r="K48" s="63"/>
+      <c r="K48" s="69"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -2147,13 +2147,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="56" t="s">
+      <c r="C50" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="57" t="s">
+      <c r="D50" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="57" t="s">
+      <c r="E50" s="63" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -2179,9 +2179,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="56"/>
-      <c r="D51" s="57"/>
-      <c r="E51" s="57"/>
+      <c r="C51" s="62"/>
+      <c r="D51" s="63"/>
+      <c r="E51" s="63"/>
       <c r="F51" s="11">
         <v>0.46868170079999999</v>
       </c>
@@ -2205,9 +2205,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="56"/>
-      <c r="D52" s="57"/>
-      <c r="E52" s="57"/>
+      <c r="C52" s="62"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="63"/>
       <c r="F52" s="11">
         <v>4.2022650500000001E-2</v>
       </c>
@@ -2225,12 +2225,12 @@
       </c>
     </row>
     <row r="55" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="55" t="s">
+      <c r="A55" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="55"/>
-      <c r="C55" s="55"/>
-      <c r="D55" s="55"/>
+      <c r="B55" s="61"/>
+      <c r="C55" s="61"/>
+      <c r="D55" s="61"/>
       <c r="E55" s="41"/>
       <c r="F55" s="42">
         <f>MAX(F2:F52)</f>
@@ -2255,12 +2255,12 @@
       <c r="K55" s="43"/>
     </row>
     <row r="56" spans="1:11" s="48" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="61" t="s">
+      <c r="A56" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="61"/>
-      <c r="C56" s="61"/>
-      <c r="D56" s="61"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="67"/>
+      <c r="D56" s="67"/>
       <c r="E56" s="45"/>
       <c r="F56" s="46">
         <f>AVERAGE(F2:F52)</f>
@@ -2400,13 +2400,13 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="65" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="11">
@@ -2424,7 +2424,7 @@
       <c r="J2" s="11">
         <v>0.49946558660000001</v>
       </c>
-      <c r="K2" s="62" t="s">
+      <c r="K2" s="68" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2435,9 +2435,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
       <c r="F3" s="11">
         <v>3.1543624200000002E-2</v>
       </c>
@@ -2453,7 +2453,7 @@
       <c r="J3" s="19">
         <v>0.51222158829999997</v>
       </c>
-      <c r="K3" s="63"/>
+      <c r="K3" s="69"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2462,9 +2462,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="56"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
       <c r="F4" s="11">
         <v>1.70661553E-2</v>
       </c>
@@ -2480,7 +2480,7 @@
       <c r="J4" s="11">
         <v>0.46528456299999998</v>
       </c>
-      <c r="K4" s="63"/>
+      <c r="K4" s="69"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G5" s="11"/>
@@ -2495,13 +2495,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="57" t="s">
+      <c r="D6" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="57" t="s">
+      <c r="E6" s="63" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -2519,7 +2519,7 @@
       <c r="J6" s="11">
         <v>0.5044039011</v>
       </c>
-      <c r="K6" s="63" t="s">
+      <c r="K6" s="69" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2530,9 +2530,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="56"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
       <c r="F7" s="11">
         <v>4.3303314799999999E-2</v>
       </c>
@@ -2548,7 +2548,7 @@
       <c r="J7" s="11">
         <v>0.43858537390000002</v>
       </c>
-      <c r="K7" s="63"/>
+      <c r="K7" s="69"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -2557,9 +2557,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="56"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
       <c r="F8" s="11">
         <v>1.6669860099999999E-2</v>
       </c>
@@ -2575,7 +2575,7 @@
       <c r="J8" s="11">
         <v>0.47867128799999997</v>
       </c>
-      <c r="K8" s="63"/>
+      <c r="K8" s="69"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G9" s="11"/>
@@ -2584,12 +2584,12 @@
       <c r="J9" s="11"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
       <c r="E10" s="5"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
@@ -2611,13 +2611,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="57" t="s">
+      <c r="D12" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="57" t="s">
+      <c r="E12" s="63" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -2635,7 +2635,7 @@
       <c r="J12" s="11">
         <v>0.49020679299999997</v>
       </c>
-      <c r="K12" s="63" t="s">
+      <c r="K12" s="69" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2646,9 +2646,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="56"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
       <c r="F13" s="11">
         <v>1.0546500000000001E-3</v>
       </c>
@@ -2664,7 +2664,7 @@
       <c r="J13" s="11">
         <v>0.48910588160000001</v>
       </c>
-      <c r="K13" s="63"/>
+      <c r="K13" s="69"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2673,9 +2673,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="56"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
       <c r="F14" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2691,7 +2691,7 @@
       <c r="J14" s="11">
         <v>0.46995530219999998</v>
       </c>
-      <c r="K14" s="63"/>
+      <c r="K14" s="69"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G15" s="11"/>
@@ -2706,13 +2706,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="56" t="s">
+      <c r="C16" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="57" t="s">
+      <c r="D16" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="57" t="s">
+      <c r="E16" s="63" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -2730,7 +2730,7 @@
       <c r="J16" s="11">
         <v>0.44493382850000002</v>
       </c>
-      <c r="K16" s="63" t="s">
+      <c r="K16" s="69" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2741,9 +2741,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="56"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="19">
         <v>8.2166826499999998E-2</v>
       </c>
@@ -2759,7 +2759,7 @@
       <c r="J17" s="11">
         <v>0.4417925586</v>
       </c>
-      <c r="K17" s="63"/>
+      <c r="K17" s="69"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -2768,9 +2768,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
       <c r="F18" s="11">
         <v>7.6701820000000002E-4</v>
       </c>
@@ -2786,7 +2786,7 @@
       <c r="J18" s="11">
         <v>0.47127738250000001</v>
       </c>
-      <c r="K18" s="63"/>
+      <c r="K18" s="69"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G19" s="11"/>
@@ -2801,13 +2801,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="56" t="s">
+      <c r="C20" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="57" t="s">
+      <c r="D20" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="57" t="s">
+      <c r="E20" s="63" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -2825,7 +2825,7 @@
       <c r="J20" s="11">
         <v>0.42862661320000001</v>
       </c>
-      <c r="K20" s="63" t="s">
+      <c r="K20" s="69" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2836,9 +2836,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="56"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="63"/>
       <c r="F21" s="11">
         <v>3.2598274E-3</v>
       </c>
@@ -2854,7 +2854,7 @@
       <c r="J21" s="11">
         <v>0.4742471747</v>
       </c>
-      <c r="K21" s="63"/>
+      <c r="K21" s="69"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -2863,9 +2863,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="56"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
       <c r="F22" s="11">
         <v>0</v>
       </c>
@@ -2881,7 +2881,7 @@
       <c r="J22" s="11">
         <v>0.4477544779</v>
       </c>
-      <c r="K22" s="63"/>
+      <c r="K22" s="69"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G23" s="11"/>
@@ -2896,13 +2896,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="56" t="s">
+      <c r="C24" s="62" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="57" t="s">
+      <c r="D24" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="57" t="s">
+      <c r="E24" s="63" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -2928,9 +2928,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="56"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="63"/>
+      <c r="E25" s="63"/>
       <c r="F25" s="11">
         <v>6.8744007699999998E-2</v>
       </c>
@@ -2954,9 +2954,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="56"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
       <c r="F26" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2984,13 +2984,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="56" t="s">
+      <c r="C28" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="57" t="s">
+      <c r="D28" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="57" t="s">
+      <c r="E28" s="63" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -3016,9 +3016,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="56"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="63"/>
       <c r="F29" s="11">
         <v>2.9721956000000002E-3</v>
       </c>
@@ -3042,9 +3042,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="56"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="63"/>
       <c r="F30" s="11">
         <v>0</v>
       </c>
@@ -3074,13 +3074,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="56" t="s">
+      <c r="C32" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="57" t="s">
+      <c r="D32" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="57" t="s">
+      <c r="E32" s="63" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -3106,9 +3106,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="56"/>
-      <c r="D33" s="57"/>
-      <c r="E33" s="57"/>
+      <c r="C33" s="62"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="63"/>
       <c r="F33" s="11">
         <v>6.2032598299999998E-2</v>
       </c>
@@ -3132,9 +3132,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="56"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="57"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="63"/>
       <c r="F34" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
@@ -3164,13 +3164,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="56" t="s">
+      <c r="C36" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="57" t="s">
+      <c r="D36" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="57" t="s">
+      <c r="E36" s="63" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -3196,9 +3196,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="56"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
+      <c r="C37" s="62"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="63"/>
       <c r="F37" s="11">
         <v>6.1361456999999998E-3</v>
       </c>
@@ -3222,9 +3222,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="56"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
+      <c r="C38" s="62"/>
+      <c r="D38" s="63"/>
+      <c r="E38" s="63"/>
       <c r="F38" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -3248,12 +3248,12 @@
       <c r="J39" s="11"/>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="58" t="s">
+      <c r="A40" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="58"/>
-      <c r="C40" s="58"/>
-      <c r="D40" s="58"/>
+      <c r="B40" s="64"/>
+      <c r="C40" s="64"/>
+      <c r="D40" s="64"/>
       <c r="E40" s="5"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
@@ -3275,13 +3275,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="56" t="s">
+      <c r="C42" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="57" t="s">
+      <c r="D42" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="57" t="s">
+      <c r="E42" s="63" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -3299,7 +3299,7 @@
       <c r="J42" s="11">
         <v>0.46282180270000001</v>
       </c>
-      <c r="K42" s="63" t="s">
+      <c r="K42" s="69" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3310,9 +3310,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="56"/>
-      <c r="D43" s="57"/>
-      <c r="E43" s="57"/>
+      <c r="C43" s="62"/>
+      <c r="D43" s="63"/>
+      <c r="E43" s="63"/>
       <c r="F43" s="11">
         <v>1.18796704E-2</v>
       </c>
@@ -3328,7 +3328,7 @@
       <c r="J43" s="11">
         <v>0.45564674030000002</v>
       </c>
-      <c r="K43" s="63"/>
+      <c r="K43" s="69"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -3337,9 +3337,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="56"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
+      <c r="C44" s="62"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
       <c r="F44" s="11">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -3353,7 +3353,7 @@
       <c r="J44" s="11">
         <v>0.47630425310000002</v>
       </c>
-      <c r="K44" s="63"/>
+      <c r="K44" s="69"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G45" s="11"/>
@@ -3368,13 +3368,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="56" t="s">
+      <c r="C46" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="57" t="s">
+      <c r="D46" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="57" t="s">
+      <c r="E46" s="63" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -3392,7 +3392,7 @@
       <c r="J46" s="11">
         <v>0.44950493489999999</v>
       </c>
-      <c r="K46" s="63" t="s">
+      <c r="K46" s="69" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3403,9 +3403,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="56"/>
-      <c r="D47" s="57"/>
-      <c r="E47" s="57"/>
+      <c r="C47" s="62"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="63"/>
       <c r="F47" s="11">
         <v>2.2322284000000001E-2</v>
       </c>
@@ -3421,7 +3421,7 @@
       <c r="J47" s="11">
         <v>0.45333713520000002</v>
       </c>
-      <c r="K47" s="63"/>
+      <c r="K47" s="69"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -3430,9 +3430,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="56"/>
-      <c r="D48" s="57"/>
-      <c r="E48" s="57"/>
+      <c r="C48" s="62"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="63"/>
       <c r="F48" s="11">
         <v>4.7901900000000002E-4</v>
       </c>
@@ -3448,7 +3448,7 @@
       <c r="J48" s="11">
         <v>0.47522234359999999</v>
       </c>
-      <c r="K48" s="63"/>
+      <c r="K48" s="69"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G49" s="11"/>
@@ -3463,13 +3463,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="56" t="s">
+      <c r="C50" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="57" t="s">
+      <c r="D50" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="57" t="s">
+      <c r="E50" s="63" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -3495,9 +3495,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="56"/>
-      <c r="D51" s="57"/>
-      <c r="E51" s="57"/>
+      <c r="C51" s="62"/>
+      <c r="D51" s="63"/>
+      <c r="E51" s="63"/>
       <c r="F51" s="11">
         <v>5.7482279999999995E-4</v>
       </c>
@@ -3521,9 +3521,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="56"/>
-      <c r="D52" s="57"/>
-      <c r="E52" s="57"/>
+      <c r="C52" s="62"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="63"/>
       <c r="F52" s="11">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -3551,12 +3551,12 @@
       <c r="J54" s="11"/>
     </row>
     <row r="55" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="55" t="s">
+      <c r="A55" s="61" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="55"/>
-      <c r="C55" s="55"/>
-      <c r="D55" s="55"/>
+      <c r="B55" s="61"/>
+      <c r="C55" s="61"/>
+      <c r="D55" s="61"/>
       <c r="E55" s="41"/>
       <c r="F55" s="42">
         <f>MAX(F2:F52)</f>
@@ -3581,12 +3581,12 @@
       <c r="K55" s="43"/>
     </row>
     <row r="56" spans="1:11" s="48" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="61" t="s">
+      <c r="A56" s="67" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="61"/>
-      <c r="C56" s="61"/>
-      <c r="D56" s="61"/>
+      <c r="B56" s="67"/>
+      <c r="C56" s="67"/>
+      <c r="D56" s="67"/>
       <c r="E56" s="45"/>
       <c r="F56" s="46">
         <f>AVERAGE(F2:F52)</f>
@@ -3625,6 +3625,9 @@
     <mergeCell ref="E28:E30"/>
     <mergeCell ref="C32:C34"/>
     <mergeCell ref="D32:D34"/>
+    <mergeCell ref="E32:E34"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D50:D52"/>
     <mergeCell ref="C2:C4"/>
     <mergeCell ref="D2:D4"/>
     <mergeCell ref="E2:E4"/>
@@ -3642,10 +3645,6 @@
     <mergeCell ref="D16:D18"/>
     <mergeCell ref="E16:E18"/>
     <mergeCell ref="K16:K18"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="E50:E52"/>
     <mergeCell ref="C36:C38"/>
     <mergeCell ref="D36:D38"/>
     <mergeCell ref="E36:E38"/>
@@ -3659,6 +3658,7 @@
     <mergeCell ref="D46:D48"/>
     <mergeCell ref="E46:E48"/>
     <mergeCell ref="K46:K48"/>
+    <mergeCell ref="E50:E52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3739,13 +3739,13 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="60" t="s">
+      <c r="C2" s="66" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="65" t="s">
         <v>13</v>
       </c>
       <c r="F2" s="19">
@@ -3775,7 +3775,7 @@
         <f>SUM(F2*1/5,G2*1/5,H2*1/5,I2*1/5,J2*1/5)</f>
         <v>0.28479454145999999</v>
       </c>
-      <c r="N2" s="62" t="s">
+      <c r="N2" s="68" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3786,9 +3786,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="56"/>
-      <c r="D3" s="57"/>
-      <c r="E3" s="57"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="63"/>
+      <c r="E3" s="63"/>
       <c r="F3" s="11">
         <v>8.3029722E-2</v>
       </c>
@@ -3816,7 +3816,7 @@
         <f>SUM(F3*1/5,G3*1/5,H3*1/5,I3*1/5,J3*1/5)</f>
         <v>0.24688138529999998</v>
       </c>
-      <c r="N3" s="63"/>
+      <c r="N3" s="69"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3825,9 +3825,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="56"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
+      <c r="C4" s="62"/>
+      <c r="D4" s="63"/>
+      <c r="E4" s="63"/>
       <c r="F4" s="11">
         <v>2.2051773699999999E-2</v>
       </c>
@@ -3855,7 +3855,7 @@
         <f>SUM(F4*1/5,G4*1/5,H4*1/5,I4*1/5,J4*1/5)</f>
         <v>0.24577994555999999</v>
       </c>
-      <c r="N4" s="63"/>
+      <c r="N4" s="69"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -3864,13 +3864,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="56" t="s">
+      <c r="C6" s="62" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="57" t="s">
+      <c r="D6" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="57" t="s">
+      <c r="E6" s="63" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -3900,7 +3900,7 @@
         <f>SUM(F6*1/5,G6*1/5,H6*1/5,I6*1/5,J6*1/5)</f>
         <v>0.21462878724000001</v>
       </c>
-      <c r="N6" s="63" t="s">
+      <c r="N6" s="69" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3911,9 +3911,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="56"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
+      <c r="C7" s="62"/>
+      <c r="D7" s="63"/>
+      <c r="E7" s="63"/>
       <c r="F7" s="11">
         <v>4.4165548999999998E-2</v>
       </c>
@@ -3941,7 +3941,7 @@
         <f>SUM(F7*1/5,G7*1/5,H7*1/5,I7*1/5,J7*1/5)</f>
         <v>0.27318294232000001</v>
       </c>
-      <c r="N7" s="63"/>
+      <c r="N7" s="69"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -3950,9 +3950,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="56"/>
-      <c r="D8" s="57"/>
-      <c r="E8" s="57"/>
+      <c r="C8" s="62"/>
+      <c r="D8" s="63"/>
+      <c r="E8" s="63"/>
       <c r="F8" s="11">
         <v>3.7171872000000002E-2</v>
       </c>
@@ -3980,15 +3980,15 @@
         <f>SUM(F8*1/5,G8*1/5,H8*1/5,I8*1/5,J8*1/5)</f>
         <v>0.26231643128000004</v>
       </c>
-      <c r="N8" s="63"/>
+      <c r="N8" s="69"/>
     </row>
     <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="58" t="s">
+      <c r="A10" s="64" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
       <c r="E10" s="5"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
@@ -4007,13 +4007,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="56" t="s">
+      <c r="C12" s="62" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="57" t="s">
+      <c r="D12" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="57" t="s">
+      <c r="E12" s="63" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -4043,7 +4043,7 @@
         <f>SUM(F12*1/5,G12*1/5,H12*1/5,I12*1/5,J12*1/5)</f>
         <v>0.32808210163999996</v>
       </c>
-      <c r="N12" s="63" t="s">
+      <c r="N12" s="69" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4054,9 +4054,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="56"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="63"/>
+      <c r="E13" s="63"/>
       <c r="F13" s="11">
         <v>4.8897411E-3</v>
       </c>
@@ -4084,7 +4084,7 @@
         <f>SUM(F13*1/5,G13*1/5,H13*1/5,I13*1/5,J13*1/5)</f>
         <v>0.25619948824</v>
       </c>
-      <c r="N13" s="63"/>
+      <c r="N13" s="69"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -4093,9 +4093,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="56"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
+      <c r="C14" s="62"/>
+      <c r="D14" s="63"/>
+      <c r="E14" s="63"/>
       <c r="F14" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4123,7 +4123,7 @@
         <f>SUM(F14*1/5,G14*1/5,H14*1/5,I14*1/5,J14*1/5)</f>
         <v>0.20013002629999999</v>
       </c>
-      <c r="N14" s="63"/>
+      <c r="N14" s="69"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -4132,13 +4132,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="56" t="s">
+      <c r="C16" s="62" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="57" t="s">
+      <c r="D16" s="63" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="57" t="s">
+      <c r="E16" s="63" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -4168,7 +4168,7 @@
         <f>SUM(F16*1/5,G16*1/5,H16*1/5,I16*1/5,J16*1/5)</f>
         <v>0.34520352803999999</v>
       </c>
-      <c r="N16" s="63" t="s">
+      <c r="N16" s="69" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4179,9 +4179,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="56"/>
-      <c r="D17" s="57"/>
-      <c r="E17" s="57"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="63"/>
+      <c r="E17" s="63"/>
       <c r="F17" s="11">
         <v>2.85714286E-2</v>
       </c>
@@ -4209,7 +4209,7 @@
         <f>SUM(F17*1/5,G17*1/5,H17*1/5,I17*1/5,J17*1/5)</f>
         <v>0.33728800162</v>
       </c>
-      <c r="N17" s="63"/>
+      <c r="N17" s="69"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -4218,9 +4218,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="56"/>
-      <c r="D18" s="57"/>
-      <c r="E18" s="57"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
       <c r="F18" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4248,7 +4248,7 @@
         <f>SUM(F18*1/5,G18*1/5,H18*1/5,I18*1/5,J18*1/5)</f>
         <v>0.35540309720000007</v>
       </c>
-      <c r="N18" s="63"/>
+      <c r="N18" s="69"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -4257,13 +4257,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="56" t="s">
+      <c r="C20" s="62" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="57" t="s">
+      <c r="D20" s="63" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="57" t="s">
+      <c r="E20" s="63" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -4293,7 +4293,7 @@
         <f>SUM(F20*1/5,G20*1/5,H20*1/5,I20*1/5,J20*1/5)</f>
         <v>0.33023019046000002</v>
       </c>
-      <c r="N20" s="63" t="s">
+      <c r="N20" s="69" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4304,9 +4304,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="56"/>
-      <c r="D21" s="57"/>
-      <c r="E21" s="57"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="63"/>
+      <c r="E21" s="63"/>
       <c r="F21" s="11">
         <v>8.59060403E-2</v>
       </c>
@@ -4334,7 +4334,7 @@
         <f>SUM(F21*1/5,G21*1/5,H21*1/5,I21*1/5,J21*1/5)</f>
         <v>0.39507478221999998</v>
       </c>
-      <c r="N21" s="63"/>
+      <c r="N21" s="69"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -4343,9 +4343,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="56"/>
-      <c r="D22" s="57"/>
-      <c r="E22" s="57"/>
+      <c r="C22" s="62"/>
+      <c r="D22" s="63"/>
+      <c r="E22" s="63"/>
       <c r="F22" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4373,7 +4373,7 @@
         <f>SUM(F22*1/5,G22*1/5,H22*1/5,I22*1/5,J22*1/5)</f>
         <v>0.29192671981999996</v>
       </c>
-      <c r="N22" s="63"/>
+      <c r="N22" s="69"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -4382,13 +4382,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="56" t="s">
+      <c r="C24" s="62" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="57" t="s">
+      <c r="D24" s="63" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="57" t="s">
+      <c r="E24" s="63" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -4426,9 +4426,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="56"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
+      <c r="C25" s="62"/>
+      <c r="D25" s="63"/>
+      <c r="E25" s="63"/>
       <c r="F25" s="11">
         <v>1.04506232E-2</v>
       </c>
@@ -4464,9 +4464,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="56"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
+      <c r="C26" s="62"/>
+      <c r="D26" s="63"/>
+      <c r="E26" s="63"/>
       <c r="F26" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -4502,13 +4502,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="56" t="s">
+      <c r="C28" s="62" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="57" t="s">
+      <c r="D28" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="57" t="s">
+      <c r="E28" s="63" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -4546,9 +4546,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="56"/>
-      <c r="D29" s="57"/>
-      <c r="E29" s="57"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="63"/>
+      <c r="E29" s="63"/>
       <c r="F29" s="11">
         <v>5.7526366000000004E-3</v>
       </c>
@@ -4584,9 +4584,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="56"/>
-      <c r="D30" s="57"/>
-      <c r="E30" s="57"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="63"/>
+      <c r="E30" s="63"/>
       <c r="F30" s="11">
         <v>9.5877299999999998E-5</v>
       </c>
@@ -4622,13 +4622,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="56" t="s">
+      <c r="C32" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="57" t="s">
+      <c r="D32" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="57" t="s">
+      <c r="E32" s="63" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -4666,9 +4666,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="56"/>
-      <c r="D33" s="57"/>
-      <c r="E33" s="57"/>
+      <c r="C33" s="62"/>
+      <c r="D33" s="63"/>
+      <c r="E33" s="63"/>
       <c r="F33" s="11">
         <v>7.6701821700000006E-2</v>
       </c>
@@ -4704,9 +4704,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="56"/>
-      <c r="D34" s="57"/>
-      <c r="E34" s="57"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="63"/>
+      <c r="E34" s="63"/>
       <c r="F34" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4742,13 +4742,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="56" t="s">
+      <c r="C36" s="62" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="57" t="s">
+      <c r="D36" s="63" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="57" t="s">
+      <c r="E36" s="63" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -4786,9 +4786,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="56"/>
-      <c r="D37" s="57"/>
-      <c r="E37" s="57"/>
+      <c r="C37" s="62"/>
+      <c r="D37" s="63"/>
+      <c r="E37" s="63"/>
       <c r="F37" s="11">
         <v>1.0546500000000001E-3</v>
       </c>
@@ -4824,9 +4824,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="56"/>
-      <c r="D38" s="57"/>
-      <c r="E38" s="57"/>
+      <c r="C38" s="62"/>
+      <c r="D38" s="63"/>
+      <c r="E38" s="63"/>
       <c r="F38" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4856,12 +4856,12 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="58" t="s">
+      <c r="A40" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="58"/>
-      <c r="C40" s="58"/>
-      <c r="D40" s="58"/>
+      <c r="B40" s="64"/>
+      <c r="C40" s="64"/>
+      <c r="D40" s="64"/>
       <c r="E40" s="5"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
@@ -4880,13 +4880,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="56" t="s">
+      <c r="C42" s="62" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="57" t="s">
+      <c r="D42" s="63" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="57" t="s">
+      <c r="E42" s="63" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -4916,7 +4916,7 @@
         <f>SUM(F42*1/5,G42*1/5,H42*1/5,I42*1/5,J42*1/5)</f>
         <v>0.31386758548000004</v>
       </c>
-      <c r="N42" s="63" t="s">
+      <c r="N42" s="69" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4927,9 +4927,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="56"/>
-      <c r="D43" s="57"/>
-      <c r="E43" s="57"/>
+      <c r="C43" s="62"/>
+      <c r="D43" s="63"/>
+      <c r="E43" s="63"/>
       <c r="F43" s="11">
         <v>2.93159609E-2</v>
       </c>
@@ -4957,7 +4957,7 @@
         <f>SUM(F43*1/5,G43*1/5,H43*1/5,I43*1/5,J43*1/5)</f>
         <v>0.29226255760000003</v>
       </c>
-      <c r="N43" s="63"/>
+      <c r="N43" s="69"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -4966,9 +4966,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="56"/>
-      <c r="D44" s="57"/>
-      <c r="E44" s="57"/>
+      <c r="C44" s="62"/>
+      <c r="D44" s="63"/>
+      <c r="E44" s="63"/>
       <c r="F44" s="14">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -4996,7 +4996,7 @@
         <f>SUM(F44*1/5,G44*1/5,H44*1/5,I44*1/5,J44*1/5)</f>
         <v>0.34257018057999999</v>
       </c>
-      <c r="N44" s="63"/>
+      <c r="N44" s="69"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -5005,13 +5005,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="56" t="s">
+      <c r="C46" s="62" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="57" t="s">
+      <c r="D46" s="63" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="57" t="s">
+      <c r="E46" s="63" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -5041,7 +5041,7 @@
         <f>SUM(F46*1/5,G46*1/5,H46*1/5,I46*1/5,J46*1/5)</f>
         <v>0.31043419121999999</v>
       </c>
-      <c r="N46" s="63" t="s">
+      <c r="N46" s="69" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5052,9 +5052,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="56"/>
-      <c r="D47" s="57"/>
-      <c r="E47" s="57"/>
+      <c r="C47" s="62"/>
+      <c r="D47" s="63"/>
+      <c r="E47" s="63"/>
       <c r="F47" s="11">
         <v>5.5853611800000001E-2</v>
       </c>
@@ -5082,7 +5082,7 @@
         <f>SUM(F47*1/5,G47*1/5,H47*1/5,I47*1/5,J47*1/5)</f>
         <v>0.38566402880000006</v>
       </c>
-      <c r="N47" s="63"/>
+      <c r="N47" s="69"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -5091,9 +5091,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="56"/>
-      <c r="D48" s="57"/>
-      <c r="E48" s="57"/>
+      <c r="C48" s="62"/>
+      <c r="D48" s="63"/>
+      <c r="E48" s="63"/>
       <c r="F48" s="11">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -5121,7 +5121,7 @@
         <f>SUM(F48*1/5,G48*1/5,H48*1/5,I48*1/5,J48*1/5)</f>
         <v>0.26614251024000002</v>
       </c>
-      <c r="N48" s="63"/>
+      <c r="N48" s="69"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -5130,13 +5130,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="56" t="s">
+      <c r="C50" s="62" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="57" t="s">
+      <c r="D50" s="63" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="57" t="s">
+      <c r="E50" s="63" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -5174,9 +5174,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="56"/>
-      <c r="D51" s="57"/>
-      <c r="E51" s="57"/>
+      <c r="C51" s="62"/>
+      <c r="D51" s="63"/>
+      <c r="E51" s="63"/>
       <c r="F51" s="11">
         <v>4.4452960299999997E-2</v>
       </c>
@@ -5212,9 +5212,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="56"/>
-      <c r="D52" s="57"/>
-      <c r="E52" s="57"/>
+      <c r="C52" s="62"/>
+      <c r="D52" s="63"/>
+      <c r="E52" s="63"/>
       <c r="F52" s="14">
         <v>0</v>
       </c>
@@ -5244,12 +5244,12 @@
       </c>
     </row>
     <row r="55" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="67" t="s">
+      <c r="A55" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="67"/>
-      <c r="C55" s="67"/>
-      <c r="D55" s="67"/>
+      <c r="B55" s="70"/>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
       <c r="E55" s="16"/>
       <c r="F55" s="17">
         <f t="shared" ref="F55:M55" si="0">MAX(F2:F52)</f>
@@ -5286,12 +5286,12 @@
       <c r="N55" s="18"/>
     </row>
     <row r="56" spans="1:14" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="68" t="s">
+      <c r="A56" s="71" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="68"/>
-      <c r="C56" s="68"/>
-      <c r="D56" s="68"/>
+      <c r="B56" s="71"/>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
       <c r="E56" s="21"/>
       <c r="F56" s="22">
         <f t="shared" ref="F56:M56" si="1">AVERAGE(F2:F52)</f>
@@ -5328,13 +5328,13 @@
       <c r="N56" s="23"/>
     </row>
     <row r="58" spans="1:14" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="64" t="s">
+      <c r="A58" s="74" t="s">
         <v>68</v>
       </c>
-      <c r="B58" s="64"/>
-      <c r="C58" s="64"/>
-      <c r="D58" s="64"/>
-      <c r="E58" s="64"/>
+      <c r="B58" s="74"/>
+      <c r="C58" s="74"/>
+      <c r="D58" s="74"/>
+      <c r="E58" s="74"/>
       <c r="F58" s="31">
         <f>SUM(F55*(1/3),  G55*(1/3), I55*(1/3))</f>
         <v>0.33597317126666659</v>
@@ -5349,13 +5349,13 @@
       <c r="N58" s="26"/>
     </row>
     <row r="59" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="65" t="s">
+      <c r="A59" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="B59" s="65"/>
-      <c r="C59" s="65"/>
-      <c r="D59" s="65"/>
-      <c r="E59" s="65"/>
+      <c r="B59" s="75"/>
+      <c r="C59" s="75"/>
+      <c r="D59" s="75"/>
+      <c r="E59" s="75"/>
       <c r="F59" s="30">
         <f>SUM(H55*(1/2),  J55*(1/2))</f>
         <v>0.65426068544999993</v>
@@ -5370,13 +5370,13 @@
       <c r="N59" s="28"/>
     </row>
     <row r="60" spans="1:14" s="35" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="66" t="s">
+      <c r="A60" s="76" t="s">
         <v>70</v>
       </c>
-      <c r="B60" s="66"/>
-      <c r="C60" s="66"/>
-      <c r="D60" s="66"/>
-      <c r="E60" s="66"/>
+      <c r="B60" s="76"/>
+      <c r="C60" s="76"/>
+      <c r="D60" s="76"/>
+      <c r="E60" s="76"/>
       <c r="F60" s="32">
         <f>SUM(F55*1/5, G55*1/5, H55*1/5, I55*1/5,J55*1/5)</f>
         <v>0.46328817694000002</v>
@@ -5391,12 +5391,12 @@
       <c r="N60" s="34"/>
     </row>
     <row r="62" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="69" t="s">
+      <c r="A62" s="72" t="s">
         <v>65</v>
       </c>
-      <c r="B62" s="69"/>
-      <c r="C62" s="69"/>
-      <c r="D62" s="69"/>
+      <c r="B62" s="72"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="72"/>
       <c r="E62" s="36"/>
       <c r="F62" s="37"/>
       <c r="G62" s="37"/>
@@ -5409,12 +5409,12 @@
       <c r="N62" s="38"/>
     </row>
     <row r="63" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="69" t="s">
+      <c r="A63" s="72" t="s">
         <v>66</v>
       </c>
-      <c r="B63" s="70"/>
-      <c r="C63" s="70"/>
-      <c r="D63" s="70"/>
+      <c r="B63" s="73"/>
+      <c r="C63" s="73"/>
+      <c r="D63" s="73"/>
       <c r="E63" s="40"/>
       <c r="F63" s="37"/>
       <c r="G63" s="37"/>
@@ -5427,12 +5427,12 @@
       <c r="N63" s="38"/>
     </row>
     <row r="64" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="69" t="s">
+      <c r="A64" s="72" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="70"/>
-      <c r="C64" s="70"/>
-      <c r="D64" s="70"/>
+      <c r="B64" s="73"/>
+      <c r="C64" s="73"/>
+      <c r="D64" s="73"/>
       <c r="E64" s="40"/>
       <c r="F64" s="37"/>
       <c r="G64" s="37"/>
@@ -5567,46 +5567,46 @@
       <c r="B2" s="9"/>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-      <c r="J2" s="71"/>
-      <c r="K2" s="73"/>
-      <c r="L2" s="73"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+      <c r="J2" s="55"/>
+      <c r="K2" s="57"/>
+      <c r="L2" s="57"/>
       <c r="M2" s="9"/>
       <c r="N2" s="9"/>
     </row>
     <row r="3" spans="1:14" s="49" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="71" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
+      <c r="B3" s="71"/>
+      <c r="C3" s="71"/>
+      <c r="D3" s="71"/>
+      <c r="E3" s="71"/>
+      <c r="F3" s="71"/>
+      <c r="G3" s="71"/>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
       <c r="J3" s="51"/>
-      <c r="K3" s="74"/>
-      <c r="L3" s="74"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
     </row>
     <row r="4" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="8"/>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
       <c r="D4" s="53"/>
-      <c r="E4" s="72"/>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="75"/>
-      <c r="K4" s="75"/>
-      <c r="L4" s="75"/>
+      <c r="E4" s="56"/>
+      <c r="F4" s="56"/>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+      <c r="J4" s="59"/>
+      <c r="K4" s="59"/>
+      <c r="L4" s="59"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
@@ -5615,10 +5615,10 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="63" t="s">
+      <c r="C5" s="69" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="63" t="s">
+      <c r="D5" s="69" t="s">
         <v>72</v>
       </c>
       <c r="E5" s="11">
@@ -5656,8 +5656,8 @@
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
+      <c r="C6" s="69"/>
+      <c r="D6" s="69"/>
       <c r="E6" s="11">
         <v>6.2032598299999998E-2</v>
       </c>
@@ -5693,8 +5693,8 @@
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="63"/>
-      <c r="D7" s="63"/>
+      <c r="C7" s="69"/>
+      <c r="D7" s="69"/>
       <c r="E7" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
@@ -5730,10 +5730,10 @@
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="63" t="s">
+      <c r="C9" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="63" t="s">
+      <c r="D9" s="69" t="s">
         <v>74</v>
       </c>
       <c r="E9" s="11">
@@ -5771,8 +5771,8 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="63"/>
-      <c r="D10" s="63"/>
+      <c r="C10" s="69"/>
+      <c r="D10" s="69"/>
       <c r="E10" s="11">
         <v>7.6701821700000006E-2</v>
       </c>
@@ -5808,8 +5808,8 @@
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="63"/>
-      <c r="D11" s="63"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
       <c r="E11" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -5845,10 +5845,10 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="63" t="s">
+      <c r="C13" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="63" t="s">
+      <c r="D13" s="69" t="s">
         <v>99</v>
       </c>
       <c r="E13" s="11">
@@ -5886,8 +5886,8 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="63"/>
-      <c r="D14" s="63"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
       <c r="E14" s="11">
         <v>4.53499521E-2</v>
       </c>
@@ -5923,8 +5923,8 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="63"/>
-      <c r="D15" s="63"/>
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
       <c r="E15" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
@@ -5957,29 +5957,38 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="63" t="s">
+      <c r="C17" s="69" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="63" t="s">
+      <c r="D17" s="69" t="s">
         <v>89</v>
       </c>
+      <c r="E17" s="11">
+        <v>3.07766059E-2</v>
+      </c>
+      <c r="F17" s="11">
+        <v>1.02588686E-2</v>
+      </c>
       <c r="G17" s="11">
-        <v>0.66366251200000004</v>
+        <v>0.74285714290000004</v>
+      </c>
+      <c r="H17" s="11">
+        <v>0.80666563540000003</v>
       </c>
       <c r="I17" s="11">
         <v>0.62260342189999995</v>
       </c>
       <c r="J17" s="11">
         <f>SUM(E17*1/3,F17*1/3,H17*1/3)</f>
-        <v>0</v>
+        <v>0.28256703663333332</v>
       </c>
       <c r="K17" s="11">
         <f>SUM(G17*1/2,I17*1/2)</f>
-        <v>0.64313296695</v>
+        <v>0.6827302824</v>
       </c>
       <c r="L17" s="11">
         <f>SUM(E17*1/5,F17*1/5,G17*1/5,H17*1/5,I17*1/5)</f>
-        <v>0.25725318677999998</v>
+        <v>0.44263233493999998</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
@@ -5989,19 +5998,34 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
+      <c r="C18" s="69"/>
+      <c r="D18" s="69"/>
+      <c r="E18" s="11">
+        <v>5.5608821000000001E-3</v>
+      </c>
+      <c r="F18" s="11">
+        <v>3.0680728000000001E-3</v>
+      </c>
+      <c r="G18" s="11">
+        <v>0.53192713329999997</v>
+      </c>
+      <c r="H18" s="11">
+        <v>0.6349892587</v>
+      </c>
+      <c r="I18" s="11">
+        <v>0.54291867670000005</v>
+      </c>
       <c r="J18" s="11">
         <f>SUM(E18*1/3,F18*1/3,H18*1/3)</f>
-        <v>0</v>
+        <v>0.21453940453333331</v>
       </c>
       <c r="K18" s="11">
         <f>SUM(G18*1/2,I18*1/2)</f>
-        <v>0</v>
+        <v>0.53742290500000001</v>
       </c>
       <c r="L18" s="11">
         <f>SUM(E18*1/5,F18*1/5,G18*1/5,H18*1/5,I18*1/5)</f>
-        <v>0</v>
+        <v>0.34369280471999997</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
@@ -6011,19 +6035,34 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
+      <c r="C19" s="69"/>
+      <c r="D19" s="69"/>
+      <c r="E19" s="11">
+        <v>5.7526370000000003E-4</v>
+      </c>
+      <c r="F19" s="11">
+        <v>9.5877280000000004E-4</v>
+      </c>
+      <c r="G19" s="11">
+        <v>0.12905081500000001</v>
+      </c>
+      <c r="H19" s="11">
+        <v>0.58629108279999997</v>
+      </c>
+      <c r="I19" s="11">
+        <v>0.61704570000000003</v>
+      </c>
       <c r="J19" s="11">
         <f>SUM(E19*1/3,F19*1/3,H19*1/3)</f>
-        <v>0</v>
+        <v>0.19594170643333333</v>
       </c>
       <c r="K19" s="11">
         <f>SUM(G19*1/2,I19*1/2)</f>
-        <v>0</v>
+        <v>0.37304825750000004</v>
       </c>
       <c r="L19" s="11">
         <f>SUM(E19*1/5,F19*1/5,G19*1/5,H19*1/5,I19*1/5)</f>
-        <v>0</v>
+        <v>0.26678432685999998</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
@@ -6036,10 +6075,10 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="63" t="s">
+      <c r="C21" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="63" t="s">
+      <c r="D21" s="69" t="s">
         <v>77</v>
       </c>
       <c r="E21" s="11">
@@ -6077,8 +6116,8 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="63"/>
-      <c r="D22" s="63"/>
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
       <c r="E22" s="11">
         <v>2.95302013E-2</v>
       </c>
@@ -6114,8 +6153,8 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
+      <c r="C23" s="69"/>
+      <c r="D23" s="69"/>
       <c r="E23" s="11">
         <v>0</v>
       </c>
@@ -6151,21 +6190,30 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="63" t="s">
+      <c r="C25" s="69" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="63" t="s">
+      <c r="D25" s="69" t="s">
         <v>85</v>
+      </c>
+      <c r="E25" s="11">
+        <v>3.2118887800000002E-2</v>
+      </c>
+      <c r="F25" s="11">
+        <v>2.9721956000000002E-3</v>
       </c>
       <c r="G25" s="11">
         <v>0.66366251200000004</v>
       </c>
+      <c r="H25" s="11">
+        <v>0.65897583790000003</v>
+      </c>
       <c r="I25" s="11">
         <v>0.68586700889999996</v>
       </c>
       <c r="J25" s="11">
         <f>SUM(E25*1/3,F25*1/3,H25*1/3)</f>
-        <v>0</v>
+        <v>0.23135564043333334</v>
       </c>
       <c r="K25" s="11">
         <f>SUM(G25*1/2,I25*1/2)</f>
@@ -6173,7 +6221,7 @@
       </c>
       <c r="L25" s="11">
         <f>SUM(E25*1/5,F25*1/5,G25*1/5,H25*1/5,I25*1/5)</f>
-        <v>0.26990590417999999</v>
+        <v>0.40871928843999999</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
@@ -6183,19 +6231,34 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="63"/>
-      <c r="D26" s="63"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="11">
+        <v>9.5877280000000004E-4</v>
+      </c>
+      <c r="F26" s="11">
+        <v>1.4381591999999999E-3</v>
+      </c>
+      <c r="G26" s="11">
+        <v>0.401725791</v>
+      </c>
+      <c r="H26" s="11">
+        <v>0.50036687729999996</v>
+      </c>
+      <c r="I26" s="11">
+        <v>0.49902492320000003</v>
+      </c>
       <c r="J26" s="11">
         <f>SUM(E26*1/3,F26*1/3,H26*1/3)</f>
-        <v>0</v>
+        <v>0.16758793643333333</v>
       </c>
       <c r="K26" s="11">
         <f>SUM(G26*1/2,I26*1/2)</f>
-        <v>0</v>
+        <v>0.45037535709999998</v>
       </c>
       <c r="L26" s="11">
         <f>SUM(E26*1/5,F26*1/5,G26*1/5,H26*1/5,I26*1/5)</f>
-        <v>0</v>
+        <v>0.28070290470000003</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
@@ -6205,19 +6268,34 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="63"/>
-      <c r="D27" s="63"/>
+      <c r="C27" s="69"/>
+      <c r="D27" s="69"/>
+      <c r="E27" s="11">
+        <v>2.4928092E-3</v>
+      </c>
+      <c r="F27" s="11">
+        <v>1.3422818999999999E-3</v>
+      </c>
+      <c r="G27" s="11">
+        <v>0.38408437200000001</v>
+      </c>
+      <c r="H27" s="11">
+        <v>0.63660849249999996</v>
+      </c>
+      <c r="I27" s="11">
+        <v>0.43824183929999999</v>
+      </c>
       <c r="J27" s="11">
         <f>SUM(E27*1/3,F27*1/3,H27*1/3)</f>
-        <v>0</v>
+        <v>0.21348119453333333</v>
       </c>
       <c r="K27" s="11">
         <f>SUM(G27*1/2,I27*1/2)</f>
-        <v>0</v>
+        <v>0.41116310565000003</v>
       </c>
       <c r="L27" s="11">
         <f>SUM(E27*1/5,F27*1/5,G27*1/5,H27*1/5,I27*1/5)</f>
-        <v>0</v>
+        <v>0.29255395898000003</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
@@ -6227,21 +6305,30 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="63" t="s">
+      <c r="C29" s="69" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="63" t="s">
+      <c r="D29" s="69" t="s">
         <v>86</v>
+      </c>
+      <c r="E29" s="11">
+        <v>9.4534995199999999E-2</v>
+      </c>
+      <c r="F29" s="11">
+        <v>1.1217641400000001E-2</v>
       </c>
       <c r="G29" s="11">
         <v>0.42895493769999998</v>
       </c>
+      <c r="H29" s="11">
+        <v>0.71427506419999998</v>
+      </c>
       <c r="I29" s="11">
         <v>0.48918897379999998</v>
       </c>
       <c r="J29" s="11">
         <f>SUM(E29*1/3,F29*1/3,H29*1/3)</f>
-        <v>0</v>
+        <v>0.27334256693333336</v>
       </c>
       <c r="K29" s="11">
         <f>SUM(G29*1/2,I29*1/2)</f>
@@ -6249,7 +6336,7 @@
       </c>
       <c r="L29" s="11">
         <f>SUM(E29*1/5,F29*1/5,G29*1/5,H29*1/5,I29*1/5)</f>
-        <v>0.18362878230000002</v>
+        <v>0.34763432245999998</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
@@ -6259,19 +6346,34 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="63"/>
-      <c r="D30" s="63"/>
+      <c r="C30" s="69"/>
+      <c r="D30" s="69"/>
+      <c r="E30" s="11">
+        <v>4.6979865999999997E-3</v>
+      </c>
+      <c r="F30" s="11">
+        <v>3.0680729000000001E-3</v>
+      </c>
+      <c r="G30" s="11">
+        <v>0.31716203259999998</v>
+      </c>
+      <c r="H30" s="11">
+        <v>0.49463574069999999</v>
+      </c>
+      <c r="I30" s="11">
+        <v>0.48499855330000002</v>
+      </c>
       <c r="J30" s="11">
         <f>SUM(E30*1/3,F30*1/3,H30*1/3)</f>
-        <v>0</v>
+        <v>0.16746726673333331</v>
       </c>
       <c r="K30" s="11">
         <f>SUM(G30*1/2,I30*1/2)</f>
-        <v>0</v>
+        <v>0.40108029295000003</v>
       </c>
       <c r="L30" s="11">
         <f>SUM(E30*1/5,F30*1/5,G30*1/5,H30*1/5,I30*1/5)</f>
-        <v>0</v>
+        <v>0.26091247721999999</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
@@ -6281,19 +6383,34 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="63"/>
-      <c r="D31" s="63"/>
+      <c r="C31" s="69"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="11">
+        <v>6.7114089999999996E-4</v>
+      </c>
+      <c r="F31" s="11">
+        <v>2.2051774000000001E-3</v>
+      </c>
+      <c r="G31" s="11">
+        <v>0.44122722910000001</v>
+      </c>
+      <c r="H31" s="11">
+        <v>0.49157918290000002</v>
+      </c>
+      <c r="I31" s="11">
+        <v>0.48140953619999999</v>
+      </c>
       <c r="J31" s="11">
         <f>SUM(E31*1/3,F31*1/3,H31*1/3)</f>
-        <v>0</v>
+        <v>0.16481850040000001</v>
       </c>
       <c r="K31" s="11">
         <f>SUM(G31*1/2,I31*1/2)</f>
-        <v>0</v>
+        <v>0.46131838265000003</v>
       </c>
       <c r="L31" s="11">
         <f>SUM(E31*1/5,F31*1/5,G31*1/5,H31*1/5,I31*1/5)</f>
-        <v>0</v>
+        <v>0.28341845330000004</v>
       </c>
     </row>
     <row r="33" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -6303,10 +6420,10 @@
       <c r="B33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="63" t="s">
+      <c r="C33" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="D33" s="63" t="s">
+      <c r="D33" s="69" t="s">
         <v>92</v>
       </c>
       <c r="J33" s="11">
@@ -6329,8 +6446,8 @@
       <c r="B34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="63"/>
-      <c r="D34" s="63"/>
+      <c r="C34" s="69"/>
+      <c r="D34" s="69"/>
       <c r="J34" s="11">
         <f>SUM(E34*1/3,F34*1/3,H34*1/3)</f>
         <v>0</v>
@@ -6351,8 +6468,8 @@
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="63"/>
-      <c r="D35" s="63"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="69"/>
       <c r="J35" s="11">
         <f>SUM(E35*1/3,F35*1/3,H35*1/3)</f>
         <v>0</v>
@@ -6373,7 +6490,7 @@
       <c r="B37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="63" t="s">
+      <c r="C37" s="69" t="s">
         <v>93</v>
       </c>
       <c r="D37" s="77" t="s">
@@ -6399,7 +6516,7 @@
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="63"/>
+      <c r="C38" s="69"/>
       <c r="D38" s="77"/>
       <c r="J38" s="11">
         <f>SUM(E38*1/3,F38*1/3,H38*1/3)</f>
@@ -6421,7 +6538,7 @@
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="63"/>
+      <c r="C39" s="69"/>
       <c r="D39" s="77"/>
       <c r="J39" s="11">
         <f>SUM(E39*1/3,F39*1/3,H39*1/3)</f>
@@ -6443,7 +6560,7 @@
       <c r="B41" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C41" s="63" t="s">
+      <c r="C41" s="69" t="s">
         <v>95</v>
       </c>
       <c r="D41" s="77" t="s">
@@ -6469,7 +6586,7 @@
       <c r="B42" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="63"/>
+      <c r="C42" s="69"/>
       <c r="D42" s="77"/>
       <c r="J42" s="11">
         <f>SUM(E42*1/3,F42*1/3,H42*1/3)</f>
@@ -6491,7 +6608,7 @@
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="63"/>
+      <c r="C43" s="69"/>
       <c r="D43" s="77"/>
       <c r="J43" s="11">
         <f>SUM(E43*1/3,F43*1/3,H43*1/3)</f>
@@ -6513,7 +6630,7 @@
       <c r="B45" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C45" s="63" t="s">
+      <c r="C45" s="69" t="s">
         <v>97</v>
       </c>
       <c r="D45" s="77" t="s">
@@ -6539,7 +6656,7 @@
       <c r="B46" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C46" s="63"/>
+      <c r="C46" s="69"/>
       <c r="D46" s="77"/>
       <c r="J46" s="11">
         <f>SUM(E46*1/3,F46*1/3,H46*1/3)</f>
@@ -6561,7 +6678,7 @@
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C47" s="63"/>
+      <c r="C47" s="69"/>
       <c r="D47" s="77"/>
       <c r="J47" s="11">
         <f>SUM(E47*1/3,F47*1/3,H47*1/3)</f>
@@ -6577,122 +6694,122 @@
       </c>
     </row>
     <row r="49" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="67" t="s">
+      <c r="A49" s="70" t="s">
         <v>60</v>
       </c>
-      <c r="B49" s="67"/>
-      <c r="C49" s="67"/>
-      <c r="D49" s="67"/>
+      <c r="B49" s="70"/>
+      <c r="C49" s="70"/>
+      <c r="D49" s="70"/>
       <c r="E49" s="17">
-        <f>MAX(E4:E35)</f>
-        <v>7.6701821700000006E-2</v>
+        <f t="shared" ref="E49:L49" si="0">MAX(E4:E35)</f>
+        <v>9.4534995199999999E-2</v>
       </c>
       <c r="F49" s="17">
-        <f>MAX(F4:F35)</f>
+        <f t="shared" si="0"/>
         <v>7.9290508100000004E-2</v>
       </c>
       <c r="G49" s="17">
-        <f>MAX(G4:G35)</f>
-        <v>0.6839884947</v>
+        <f t="shared" si="0"/>
+        <v>0.74285714290000004</v>
       </c>
       <c r="H49" s="17">
-        <f>MAX(H4:H35)</f>
+        <f t="shared" si="0"/>
         <v>0.90418992629999995</v>
       </c>
       <c r="I49" s="17">
-        <f>MAX(I4:I35)</f>
+        <f t="shared" si="0"/>
         <v>0.68586700889999996</v>
       </c>
       <c r="J49" s="17">
-        <f>MAX(J4:J35)</f>
+        <f t="shared" si="0"/>
         <v>0.33470898553333334</v>
       </c>
       <c r="K49" s="17">
-        <f>MAX(K4:K35)</f>
-        <v>0.67476476045</v>
+        <f t="shared" si="0"/>
+        <v>0.6827302824</v>
       </c>
       <c r="L49" s="17">
-        <f>MAX(L4:L35)</f>
-        <v>0.39261373816</v>
+        <f t="shared" si="0"/>
+        <v>0.44263233493999998</v>
       </c>
       <c r="M49" s="17"/>
       <c r="N49" s="18"/>
     </row>
     <row r="50" spans="1:14" s="54" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="64" t="s">
+      <c r="A50" s="74" t="s">
         <v>61</v>
       </c>
-      <c r="B50" s="64"/>
-      <c r="C50" s="64"/>
-      <c r="D50" s="64"/>
+      <c r="B50" s="74"/>
+      <c r="C50" s="74"/>
+      <c r="D50" s="74"/>
       <c r="E50" s="31">
-        <f>AVERAGE(E5:E35)</f>
-        <v>3.3844678824999995E-2</v>
+        <f t="shared" ref="E50:L50" si="1">AVERAGE(E5:E35)</f>
+        <v>2.7548737623809522E-2</v>
       </c>
       <c r="F50" s="31">
-        <f>AVERAGE(F5:F35)</f>
-        <v>1.1984659633333332E-2</v>
+        <f t="shared" si="1"/>
+        <v>8.5878646761904775E-3</v>
       </c>
       <c r="G50" s="31">
-        <f>AVERAGE(G5:G35)</f>
-        <v>0.44426790851428571</v>
+        <f t="shared" si="1"/>
+        <v>0.42520613615500008</v>
       </c>
       <c r="H50" s="31">
-        <f>AVERAGE(H5:H35)</f>
-        <v>0.68153575924166665</v>
+        <f t="shared" si="1"/>
+        <v>0.65251506110952384</v>
       </c>
       <c r="I50" s="31">
-        <f>AVERAGE(I5:I35)</f>
-        <v>0.48174301881333342</v>
+        <f t="shared" si="1"/>
+        <v>0.48998973861428574</v>
       </c>
       <c r="J50" s="31">
-        <f>AVERAGE(J5:J35)</f>
-        <v>0.12122751628333334</v>
+        <f t="shared" si="1"/>
+        <v>0.20085673516111116</v>
       </c>
       <c r="K50" s="31">
-        <f>AVERAGE(K5:K35)</f>
-        <v>0.28012283336249993</v>
+        <f t="shared" si="1"/>
+        <v>0.39153973404166659</v>
       </c>
       <c r="L50" s="31">
-        <f>AVERAGE(L5:L35)</f>
-        <v>0.18478564311499998</v>
+        <f t="shared" si="1"/>
+        <v>0.2771299347133333</v>
       </c>
       <c r="M50" s="31"/>
-      <c r="N50" s="76"/>
+      <c r="N50" s="60"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="F51" s="72"/>
-      <c r="H51" s="72"/>
+      <c r="F51" s="56"/>
+      <c r="H51" s="56"/>
     </row>
     <row r="52" spans="1:14" s="49" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="68" t="s">
+      <c r="A52" s="71" t="s">
         <v>79</v>
       </c>
-      <c r="B52" s="68"/>
-      <c r="C52" s="68"/>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68"/>
-      <c r="F52" s="68"/>
-      <c r="G52" s="68"/>
-      <c r="H52" s="68"/>
-      <c r="I52" s="68"/>
+      <c r="B52" s="71"/>
+      <c r="C52" s="71"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="71"/>
+      <c r="F52" s="71"/>
+      <c r="G52" s="71"/>
+      <c r="H52" s="71"/>
+      <c r="I52" s="71"/>
       <c r="J52" s="51"/>
-      <c r="K52" s="74"/>
-      <c r="L52" s="74"/>
+      <c r="K52" s="58"/>
+      <c r="L52" s="58"/>
     </row>
     <row r="53" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A53" s="8"/>
       <c r="B53" s="8"/>
       <c r="C53" s="8"/>
       <c r="D53" s="53"/>
-      <c r="E53" s="72"/>
-      <c r="F53" s="72"/>
-      <c r="G53" s="72"/>
-      <c r="H53" s="72"/>
-      <c r="I53" s="72"/>
-      <c r="J53" s="75"/>
-      <c r="K53" s="75"/>
-      <c r="L53" s="75"/>
+      <c r="E53" s="56"/>
+      <c r="F53" s="56"/>
+      <c r="G53" s="56"/>
+      <c r="H53" s="56"/>
+      <c r="I53" s="56"/>
+      <c r="J53" s="59"/>
+      <c r="K53" s="59"/>
+      <c r="L53" s="59"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
@@ -6701,10 +6818,10 @@
       <c r="B54" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="63" t="s">
+      <c r="C54" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="D54" s="63" t="s">
+      <c r="D54" s="69" t="s">
         <v>72</v>
       </c>
       <c r="E54" s="11">
@@ -6742,8 +6859,8 @@
       <c r="B55" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C55" s="63"/>
-      <c r="D55" s="63"/>
+      <c r="C55" s="69"/>
+      <c r="D55" s="69"/>
       <c r="E55" s="11">
         <v>8.2166826499999998E-2</v>
       </c>
@@ -6779,8 +6896,8 @@
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C56" s="63"/>
-      <c r="D56" s="63"/>
+      <c r="C56" s="69"/>
+      <c r="D56" s="69"/>
       <c r="E56" s="11">
         <v>7.6701820000000002E-4</v>
       </c>
@@ -6816,10 +6933,10 @@
       <c r="B58" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C58" s="63" t="s">
+      <c r="C58" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="D58" s="63" t="s">
+      <c r="D58" s="69" t="s">
         <v>74</v>
       </c>
       <c r="E58" s="11">
@@ -6857,8 +6974,8 @@
       <c r="B59" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="63"/>
-      <c r="D59" s="63"/>
+      <c r="C59" s="69"/>
+      <c r="D59" s="69"/>
       <c r="E59" s="11">
         <v>2.85714286E-2</v>
       </c>
@@ -6894,8 +7011,8 @@
       <c r="B60" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C60" s="63"/>
-      <c r="D60" s="63"/>
+      <c r="C60" s="69"/>
+      <c r="D60" s="69"/>
       <c r="E60" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -6925,34 +7042,34 @@
       </c>
     </row>
     <row r="62" spans="1:14" s="49" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="68" t="s">
+      <c r="A62" s="71" t="s">
         <v>82</v>
       </c>
-      <c r="B62" s="68"/>
-      <c r="C62" s="68"/>
-      <c r="D62" s="68"/>
-      <c r="E62" s="68"/>
-      <c r="F62" s="68"/>
-      <c r="G62" s="68"/>
-      <c r="H62" s="68"/>
-      <c r="I62" s="68"/>
+      <c r="B62" s="71"/>
+      <c r="C62" s="71"/>
+      <c r="D62" s="71"/>
+      <c r="E62" s="71"/>
+      <c r="F62" s="71"/>
+      <c r="G62" s="71"/>
+      <c r="H62" s="71"/>
+      <c r="I62" s="71"/>
       <c r="J62" s="51"/>
-      <c r="K62" s="74"/>
-      <c r="L62" s="74"/>
+      <c r="K62" s="58"/>
+      <c r="L62" s="58"/>
     </row>
     <row r="63" spans="1:14" s="50" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A63" s="8"/>
       <c r="B63" s="8"/>
       <c r="C63" s="8"/>
       <c r="D63" s="53"/>
-      <c r="E63" s="72"/>
-      <c r="F63" s="72"/>
-      <c r="G63" s="72"/>
-      <c r="H63" s="72"/>
-      <c r="I63" s="72"/>
-      <c r="J63" s="75"/>
-      <c r="K63" s="75"/>
-      <c r="L63" s="75"/>
+      <c r="E63" s="56"/>
+      <c r="F63" s="56"/>
+      <c r="G63" s="56"/>
+      <c r="H63" s="56"/>
+      <c r="I63" s="56"/>
+      <c r="J63" s="59"/>
+      <c r="K63" s="59"/>
+      <c r="L63" s="59"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
@@ -6961,10 +7078,10 @@
       <c r="B64" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="63" t="s">
+      <c r="C64" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="D64" s="63" t="s">
+      <c r="D64" s="69" t="s">
         <v>72</v>
       </c>
       <c r="E64" s="11">
@@ -7002,8 +7119,8 @@
       <c r="B65" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C65" s="63"/>
-      <c r="D65" s="63"/>
+      <c r="C65" s="69"/>
+      <c r="D65" s="69"/>
       <c r="E65" s="11">
         <v>3.2598274E-3</v>
       </c>
@@ -7039,8 +7156,8 @@
       <c r="B66" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="63"/>
-      <c r="D66" s="63"/>
+      <c r="C66" s="69"/>
+      <c r="D66" s="69"/>
       <c r="E66" s="11">
         <v>0</v>
       </c>
@@ -7076,10 +7193,10 @@
       <c r="B68" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C68" s="63" t="s">
+      <c r="C68" s="69" t="s">
         <v>84</v>
       </c>
-      <c r="D68" s="63" t="s">
+      <c r="D68" s="69" t="s">
         <v>74</v>
       </c>
       <c r="E68" s="11">
@@ -7117,8 +7234,8 @@
       <c r="B69" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C69" s="63"/>
-      <c r="D69" s="63"/>
+      <c r="C69" s="69"/>
+      <c r="D69" s="69"/>
       <c r="E69" s="11">
         <v>8.59060403E-2</v>
       </c>
@@ -7154,8 +7271,8 @@
       <c r="B70" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C70" s="63"/>
-      <c r="D70" s="63"/>
+      <c r="C70" s="69"/>
+      <c r="D70" s="69"/>
       <c r="E70" s="11">
         <v>3.8350910000000001E-4</v>
       </c>

--- a/benchmarking/search_for_best_combination/results_basic.xlsx
+++ b/benchmarking/search_for_best_combination/results_basic.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9831C867-36F4-254A-ADE1-FC03E5C00DF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84555B7F-16CF-3F48-8852-034E2F91B029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="30240" windowHeight="18900" activeTab="3" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="3" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
   <sheets>
     <sheet name="Results BASIC" sheetId="1" r:id="rId1"/>
@@ -548,7 +548,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -730,56 +730,59 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1161,7 +1164,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="66" t="s">
+      <c r="C2" s="68" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="65" t="s">
@@ -1185,7 +1188,7 @@
       <c r="J2" s="11">
         <v>0.51636704079999995</v>
       </c>
-      <c r="K2" s="68" t="s">
+      <c r="K2" s="63" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1196,9 +1199,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
       <c r="F3" s="11">
         <v>5.23489933E-2</v>
       </c>
@@ -1214,7 +1217,7 @@
       <c r="J3" s="11">
         <v>0.49172142549999998</v>
       </c>
-      <c r="K3" s="69"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -1223,9 +1226,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
       <c r="F4" s="11">
         <v>3.73921381E-2</v>
       </c>
@@ -1241,7 +1244,7 @@
       <c r="J4" s="11">
         <v>0.44867621930000001</v>
       </c>
-      <c r="K4" s="69"/>
+      <c r="K4" s="64"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -1250,13 +1253,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="62" t="s">
+      <c r="C6" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="63" t="s">
+      <c r="E6" s="62" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -1274,7 +1277,7 @@
       <c r="J6" s="11">
         <v>0.49915964429999998</v>
       </c>
-      <c r="K6" s="69" t="s">
+      <c r="K6" s="64" t="s">
         <v>16</v>
       </c>
     </row>
@@ -1285,9 +1288,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="62"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
       <c r="F7" s="11">
         <v>2.7399884999999999E-2</v>
       </c>
@@ -1303,7 +1306,7 @@
       <c r="J7" s="11">
         <v>0.48493602559999999</v>
       </c>
-      <c r="K7" s="69"/>
+      <c r="K7" s="64"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -1312,9 +1315,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="62"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
       <c r="F8" s="11">
         <v>2.4717378799999998E-2</v>
       </c>
@@ -1330,15 +1333,15 @@
       <c r="J8" s="11">
         <v>0.43282600290000001</v>
       </c>
-      <c r="K8" s="69"/>
+      <c r="K8" s="64"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="64" t="s">
+      <c r="A10" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
       <c r="E10" s="5"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
@@ -1354,13 +1357,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="63" t="s">
+      <c r="D12" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="63" t="s">
+      <c r="E12" s="62" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -1378,7 +1381,7 @@
       <c r="J12" s="11">
         <v>0.45356946819999999</v>
       </c>
-      <c r="K12" s="69" t="s">
+      <c r="K12" s="64" t="s">
         <v>18</v>
       </c>
     </row>
@@ -1389,9 +1392,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="62"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
       <c r="F13" s="11">
         <v>5.4569232000000002E-2</v>
       </c>
@@ -1407,7 +1410,7 @@
       <c r="J13" s="11">
         <v>0.2490125493</v>
       </c>
-      <c r="K13" s="69"/>
+      <c r="K13" s="64"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -1416,9 +1419,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
       <c r="F14" s="11">
         <v>0.2933740192</v>
       </c>
@@ -1434,7 +1437,7 @@
       <c r="J14" s="11">
         <v>0.33911636109999999</v>
       </c>
-      <c r="K14" s="69"/>
+      <c r="K14" s="64"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -1443,13 +1446,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="62" t="s">
+      <c r="C16" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="63" t="s">
+      <c r="D16" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="63" t="s">
+      <c r="E16" s="62" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -1467,7 +1470,7 @@
       <c r="J16" s="11">
         <v>0.46862206229999998</v>
       </c>
-      <c r="K16" s="69" t="s">
+      <c r="K16" s="64" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1478,9 +1481,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
       <c r="F17" s="11">
         <v>0.2220972487</v>
       </c>
@@ -1496,7 +1499,7 @@
       <c r="J17" s="11">
         <v>0.61463971539999995</v>
       </c>
-      <c r="K17" s="69"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -1505,9 +1508,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="62"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
       <c r="F18" s="11">
         <v>0.12510815019999999</v>
       </c>
@@ -1523,7 +1526,7 @@
       <c r="J18" s="11">
         <v>0.40298454760000002</v>
       </c>
-      <c r="K18" s="69"/>
+      <c r="K18" s="64"/>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -1532,13 +1535,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="62" t="s">
+      <c r="C20" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="63" t="s">
+      <c r="D20" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="63" t="s">
+      <c r="E20" s="62" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -1556,7 +1559,7 @@
       <c r="J20" s="11">
         <v>0.42112340529999998</v>
       </c>
-      <c r="K20" s="69" t="s">
+      <c r="K20" s="64" t="s">
         <v>35</v>
       </c>
     </row>
@@ -1567,9 +1570,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="62"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="63"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
       <c r="F21" s="11">
         <v>0.28648624509999998</v>
       </c>
@@ -1585,7 +1588,7 @@
       <c r="J21" s="19">
         <v>0.71830903779999999</v>
       </c>
-      <c r="K21" s="69"/>
+      <c r="K21" s="64"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -1594,9 +1597,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="62"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
       <c r="F22" s="11">
         <v>4.4658810000000002E-4</v>
       </c>
@@ -1609,7 +1612,7 @@
       <c r="J22" s="11">
         <v>0.41851161510000001</v>
       </c>
-      <c r="K22" s="69"/>
+      <c r="K22" s="64"/>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -1618,13 +1621,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="63" t="s">
+      <c r="D24" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="63" t="s">
+      <c r="E24" s="62" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -1650,9 +1653,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="62"/>
-      <c r="D25" s="63"/>
-      <c r="E25" s="63"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
       <c r="F25" s="11">
         <v>0.1240506329</v>
       </c>
@@ -1676,9 +1679,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="62"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
       <c r="F26" s="11">
         <v>0.13367616030000001</v>
       </c>
@@ -1702,13 +1705,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="62" t="s">
+      <c r="C28" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="63" t="s">
+      <c r="D28" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="63" t="s">
+      <c r="E28" s="62" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -1734,9 +1737,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="62"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="63"/>
+      <c r="C29" s="66"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
       <c r="F29" s="11">
         <v>0.20128508440000001</v>
       </c>
@@ -1760,9 +1763,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="62"/>
-      <c r="D30" s="63"/>
-      <c r="E30" s="63"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="62"/>
       <c r="F30" s="11">
         <v>0.1974137004</v>
       </c>
@@ -1786,13 +1789,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="62" t="s">
+      <c r="C32" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="63" t="s">
+      <c r="D32" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="63" t="s">
+      <c r="E32" s="62" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="19">
@@ -1818,9 +1821,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="62"/>
-      <c r="D33" s="63"/>
-      <c r="E33" s="63"/>
+      <c r="C33" s="66"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="62"/>
       <c r="F33" s="11">
         <v>0.4661326187</v>
       </c>
@@ -1844,9 +1847,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="62"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="63"/>
+      <c r="C34" s="66"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
       <c r="F34" s="11">
         <v>2.2806319999999999E-4</v>
       </c>
@@ -1870,13 +1873,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="62" t="s">
+      <c r="C36" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="63" t="s">
+      <c r="D36" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="63" t="s">
+      <c r="E36" s="62" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -1902,9 +1905,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="62"/>
-      <c r="D37" s="63"/>
-      <c r="E37" s="63"/>
+      <c r="C37" s="66"/>
+      <c r="D37" s="62"/>
+      <c r="E37" s="62"/>
       <c r="F37" s="11">
         <v>0.29922617379999999</v>
       </c>
@@ -1928,9 +1931,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="62"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="63"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
       <c r="F38" s="11">
         <v>0.1553265707</v>
       </c>
@@ -1948,12 +1951,12 @@
       </c>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="64" t="s">
+      <c r="A40" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="64"/>
-      <c r="C40" s="64"/>
-      <c r="D40" s="64"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
       <c r="E40" s="5"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
@@ -1969,13 +1972,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="62" t="s">
+      <c r="C42" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="63" t="s">
+      <c r="D42" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="63" t="s">
+      <c r="E42" s="62" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -1993,7 +1996,7 @@
       <c r="J42" s="11">
         <v>0.50415219909999998</v>
       </c>
-      <c r="K42" s="69" t="s">
+      <c r="K42" s="64" t="s">
         <v>30</v>
       </c>
     </row>
@@ -2004,9 +2007,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="62"/>
-      <c r="D43" s="63"/>
-      <c r="E43" s="63"/>
+      <c r="C43" s="66"/>
+      <c r="D43" s="62"/>
+      <c r="E43" s="62"/>
       <c r="F43" s="11">
         <v>0.27900922929999999</v>
       </c>
@@ -2022,7 +2025,7 @@
       <c r="J43" s="11">
         <v>0.6867986989</v>
       </c>
-      <c r="K43" s="69"/>
+      <c r="K43" s="64"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -2031,9 +2034,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="62"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="63"/>
+      <c r="C44" s="66"/>
+      <c r="D44" s="62"/>
+      <c r="E44" s="62"/>
       <c r="F44" s="11">
         <v>1.08858563E-2</v>
       </c>
@@ -2049,7 +2052,7 @@
       <c r="J44" s="11">
         <v>0.34279394219999998</v>
       </c>
-      <c r="K44" s="69"/>
+      <c r="K44" s="64"/>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -2058,13 +2061,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="62" t="s">
+      <c r="C46" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="63" t="s">
+      <c r="D46" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="63" t="s">
+      <c r="E46" s="62" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -2082,7 +2085,7 @@
       <c r="J46" s="11">
         <v>0.43511184339999998</v>
       </c>
-      <c r="K46" s="69" t="s">
+      <c r="K46" s="64" t="s">
         <v>31</v>
       </c>
     </row>
@@ -2093,9 +2096,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="62"/>
-      <c r="D47" s="63"/>
-      <c r="E47" s="63"/>
+      <c r="C47" s="66"/>
+      <c r="D47" s="62"/>
+      <c r="E47" s="62"/>
       <c r="F47" s="11">
         <v>0.36941770550000003</v>
       </c>
@@ -2111,7 +2114,7 @@
       <c r="J47" s="11">
         <v>0.67778323610000002</v>
       </c>
-      <c r="K47" s="69"/>
+      <c r="K47" s="64"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -2120,9 +2123,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="62"/>
-      <c r="D48" s="63"/>
-      <c r="E48" s="63"/>
+      <c r="C48" s="66"/>
+      <c r="D48" s="62"/>
+      <c r="E48" s="62"/>
       <c r="F48" s="11">
         <v>7.1050970500000005E-2</v>
       </c>
@@ -2138,7 +2141,7 @@
       <c r="J48" s="11">
         <v>0.33626401280000001</v>
       </c>
-      <c r="K48" s="69"/>
+      <c r="K48" s="64"/>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -2147,13 +2150,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="62" t="s">
+      <c r="C50" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="63" t="s">
+      <c r="D50" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="63" t="s">
+      <c r="E50" s="62" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -2179,9 +2182,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="62"/>
-      <c r="D51" s="63"/>
-      <c r="E51" s="63"/>
+      <c r="C51" s="66"/>
+      <c r="D51" s="62"/>
+      <c r="E51" s="62"/>
       <c r="F51" s="11">
         <v>0.46868170079999999</v>
       </c>
@@ -2205,9 +2208,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="62"/>
-      <c r="D52" s="63"/>
-      <c r="E52" s="63"/>
+      <c r="C52" s="66"/>
+      <c r="D52" s="62"/>
+      <c r="E52" s="62"/>
       <c r="F52" s="11">
         <v>4.2022650500000001E-2</v>
       </c>
@@ -2225,12 +2228,12 @@
       </c>
     </row>
     <row r="55" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="61" t="s">
+      <c r="A55" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="61"/>
-      <c r="C55" s="61"/>
-      <c r="D55" s="61"/>
+      <c r="B55" s="69"/>
+      <c r="C55" s="69"/>
+      <c r="D55" s="69"/>
       <c r="E55" s="41"/>
       <c r="F55" s="42">
         <f>MAX(F2:F52)</f>
@@ -2255,12 +2258,12 @@
       <c r="K55" s="43"/>
     </row>
     <row r="56" spans="1:11" s="48" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="67" t="s">
+      <c r="A56" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="67"/>
-      <c r="C56" s="67"/>
-      <c r="D56" s="67"/>
+      <c r="B56" s="61"/>
+      <c r="C56" s="61"/>
+      <c r="D56" s="61"/>
       <c r="E56" s="45"/>
       <c r="F56" s="46">
         <f>AVERAGE(F2:F52)</f>
@@ -2286,6 +2289,37 @@
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="C12:C14"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="C50:C52"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="D28:D30"/>
+    <mergeCell ref="D32:D34"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="D50:D52"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="D12:D14"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="E12:E14"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="C28:C30"/>
+    <mergeCell ref="C32:C34"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="E46:E48"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="E50:E52"/>
     <mergeCell ref="K2:K4"/>
@@ -2302,37 +2336,6 @@
     <mergeCell ref="E42:E44"/>
     <mergeCell ref="E2:E4"/>
     <mergeCell ref="E6:E8"/>
-    <mergeCell ref="E12:E14"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="C28:C30"/>
-    <mergeCell ref="C32:C34"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="D12:D14"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="C12:C14"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="C50:C52"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="D28:D30"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="D50:D52"/>
-    <mergeCell ref="A40:D40"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2400,7 +2403,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="66" t="s">
+      <c r="C2" s="68" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="65" t="s">
@@ -2424,7 +2427,7 @@
       <c r="J2" s="11">
         <v>0.49946558660000001</v>
       </c>
-      <c r="K2" s="68" t="s">
+      <c r="K2" s="63" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2435,9 +2438,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
       <c r="F3" s="11">
         <v>3.1543624200000002E-2</v>
       </c>
@@ -2453,7 +2456,7 @@
       <c r="J3" s="19">
         <v>0.51222158829999997</v>
       </c>
-      <c r="K3" s="69"/>
+      <c r="K3" s="64"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -2462,9 +2465,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
       <c r="F4" s="11">
         <v>1.70661553E-2</v>
       </c>
@@ -2480,7 +2483,7 @@
       <c r="J4" s="11">
         <v>0.46528456299999998</v>
       </c>
-      <c r="K4" s="69"/>
+      <c r="K4" s="64"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G5" s="11"/>
@@ -2495,13 +2498,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="62" t="s">
+      <c r="C6" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="63" t="s">
+      <c r="E6" s="62" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -2519,7 +2522,7 @@
       <c r="J6" s="11">
         <v>0.5044039011</v>
       </c>
-      <c r="K6" s="69" t="s">
+      <c r="K6" s="64" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2530,9 +2533,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="62"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
       <c r="F7" s="11">
         <v>4.3303314799999999E-2</v>
       </c>
@@ -2548,7 +2551,7 @@
       <c r="J7" s="11">
         <v>0.43858537390000002</v>
       </c>
-      <c r="K7" s="69"/>
+      <c r="K7" s="64"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -2557,9 +2560,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="62"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
       <c r="F8" s="11">
         <v>1.6669860099999999E-2</v>
       </c>
@@ -2575,7 +2578,7 @@
       <c r="J8" s="11">
         <v>0.47867128799999997</v>
       </c>
-      <c r="K8" s="69"/>
+      <c r="K8" s="64"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G9" s="11"/>
@@ -2584,12 +2587,12 @@
       <c r="J9" s="11"/>
     </row>
     <row r="10" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="64" t="s">
+      <c r="A10" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
       <c r="E10" s="5"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
@@ -2611,13 +2614,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="63" t="s">
+      <c r="D12" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="63" t="s">
+      <c r="E12" s="62" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -2635,7 +2638,7 @@
       <c r="J12" s="11">
         <v>0.49020679299999997</v>
       </c>
-      <c r="K12" s="69" t="s">
+      <c r="K12" s="64" t="s">
         <v>18</v>
       </c>
     </row>
@@ -2646,9 +2649,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="62"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
       <c r="F13" s="11">
         <v>1.0546500000000001E-3</v>
       </c>
@@ -2664,7 +2667,7 @@
       <c r="J13" s="11">
         <v>0.48910588160000001</v>
       </c>
-      <c r="K13" s="69"/>
+      <c r="K13" s="64"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -2673,9 +2676,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
       <c r="F14" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2691,7 +2694,7 @@
       <c r="J14" s="11">
         <v>0.46995530219999998</v>
       </c>
-      <c r="K14" s="69"/>
+      <c r="K14" s="64"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G15" s="11"/>
@@ -2706,13 +2709,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="62" t="s">
+      <c r="C16" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="63" t="s">
+      <c r="D16" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="63" t="s">
+      <c r="E16" s="62" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -2730,7 +2733,7 @@
       <c r="J16" s="11">
         <v>0.44493382850000002</v>
       </c>
-      <c r="K16" s="69" t="s">
+      <c r="K16" s="64" t="s">
         <v>36</v>
       </c>
     </row>
@@ -2741,9 +2744,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
       <c r="F17" s="19">
         <v>8.2166826499999998E-2</v>
       </c>
@@ -2759,7 +2762,7 @@
       <c r="J17" s="11">
         <v>0.4417925586</v>
       </c>
-      <c r="K17" s="69"/>
+      <c r="K17" s="64"/>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -2768,9 +2771,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="62"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
       <c r="F18" s="11">
         <v>7.6701820000000002E-4</v>
       </c>
@@ -2786,7 +2789,7 @@
       <c r="J18" s="11">
         <v>0.47127738250000001</v>
       </c>
-      <c r="K18" s="69"/>
+      <c r="K18" s="64"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G19" s="11"/>
@@ -2801,13 +2804,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="62" t="s">
+      <c r="C20" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="63" t="s">
+      <c r="D20" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="63" t="s">
+      <c r="E20" s="62" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -2825,7 +2828,7 @@
       <c r="J20" s="11">
         <v>0.42862661320000001</v>
       </c>
-      <c r="K20" s="69" t="s">
+      <c r="K20" s="64" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2836,9 +2839,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="62"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="63"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
       <c r="F21" s="11">
         <v>3.2598274E-3</v>
       </c>
@@ -2854,7 +2857,7 @@
       <c r="J21" s="11">
         <v>0.4742471747</v>
       </c>
-      <c r="K21" s="69"/>
+      <c r="K21" s="64"/>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -2863,9 +2866,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="62"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
       <c r="F22" s="11">
         <v>0</v>
       </c>
@@ -2881,7 +2884,7 @@
       <c r="J22" s="11">
         <v>0.4477544779</v>
       </c>
-      <c r="K22" s="69"/>
+      <c r="K22" s="64"/>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G23" s="11"/>
@@ -2896,13 +2899,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="63" t="s">
+      <c r="D24" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="63" t="s">
+      <c r="E24" s="62" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -2928,9 +2931,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="62"/>
-      <c r="D25" s="63"/>
-      <c r="E25" s="63"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
       <c r="F25" s="11">
         <v>6.8744007699999998E-2</v>
       </c>
@@ -2954,9 +2957,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="62"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
       <c r="F26" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -2984,13 +2987,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="62" t="s">
+      <c r="C28" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="63" t="s">
+      <c r="D28" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="63" t="s">
+      <c r="E28" s="62" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -3016,9 +3019,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="62"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="63"/>
+      <c r="C29" s="66"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
       <c r="F29" s="11">
         <v>2.9721956000000002E-3</v>
       </c>
@@ -3042,9 +3045,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="62"/>
-      <c r="D30" s="63"/>
-      <c r="E30" s="63"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="62"/>
       <c r="F30" s="11">
         <v>0</v>
       </c>
@@ -3074,13 +3077,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="62" t="s">
+      <c r="C32" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="63" t="s">
+      <c r="D32" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="63" t="s">
+      <c r="E32" s="62" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -3106,9 +3109,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="62"/>
-      <c r="D33" s="63"/>
-      <c r="E33" s="63"/>
+      <c r="C33" s="66"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="62"/>
       <c r="F33" s="11">
         <v>6.2032598299999998E-2</v>
       </c>
@@ -3132,9 +3135,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="62"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="63"/>
+      <c r="C34" s="66"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
       <c r="F34" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
@@ -3164,13 +3167,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="62" t="s">
+      <c r="C36" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="63" t="s">
+      <c r="D36" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="63" t="s">
+      <c r="E36" s="62" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -3196,9 +3199,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="62"/>
-      <c r="D37" s="63"/>
-      <c r="E37" s="63"/>
+      <c r="C37" s="66"/>
+      <c r="D37" s="62"/>
+      <c r="E37" s="62"/>
       <c r="F37" s="11">
         <v>6.1361456999999998E-3</v>
       </c>
@@ -3222,9 +3225,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="62"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="63"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
       <c r="F38" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -3248,12 +3251,12 @@
       <c r="J39" s="11"/>
     </row>
     <row r="40" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="64" t="s">
+      <c r="A40" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="64"/>
-      <c r="C40" s="64"/>
-      <c r="D40" s="64"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
       <c r="E40" s="5"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
@@ -3275,13 +3278,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="62" t="s">
+      <c r="C42" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="63" t="s">
+      <c r="D42" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="63" t="s">
+      <c r="E42" s="62" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -3299,7 +3302,7 @@
       <c r="J42" s="11">
         <v>0.46282180270000001</v>
       </c>
-      <c r="K42" s="69" t="s">
+      <c r="K42" s="64" t="s">
         <v>30</v>
       </c>
     </row>
@@ -3310,9 +3313,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="62"/>
-      <c r="D43" s="63"/>
-      <c r="E43" s="63"/>
+      <c r="C43" s="66"/>
+      <c r="D43" s="62"/>
+      <c r="E43" s="62"/>
       <c r="F43" s="11">
         <v>1.18796704E-2</v>
       </c>
@@ -3328,7 +3331,7 @@
       <c r="J43" s="11">
         <v>0.45564674030000002</v>
       </c>
-      <c r="K43" s="69"/>
+      <c r="K43" s="64"/>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -3337,9 +3340,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="62"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="63"/>
+      <c r="C44" s="66"/>
+      <c r="D44" s="62"/>
+      <c r="E44" s="62"/>
       <c r="F44" s="11">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -3353,7 +3356,7 @@
       <c r="J44" s="11">
         <v>0.47630425310000002</v>
       </c>
-      <c r="K44" s="69"/>
+      <c r="K44" s="64"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G45" s="11"/>
@@ -3368,13 +3371,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="62" t="s">
+      <c r="C46" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="63" t="s">
+      <c r="D46" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="63" t="s">
+      <c r="E46" s="62" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -3392,7 +3395,7 @@
       <c r="J46" s="11">
         <v>0.44950493489999999</v>
       </c>
-      <c r="K46" s="69" t="s">
+      <c r="K46" s="64" t="s">
         <v>31</v>
       </c>
     </row>
@@ -3403,9 +3406,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="62"/>
-      <c r="D47" s="63"/>
-      <c r="E47" s="63"/>
+      <c r="C47" s="66"/>
+      <c r="D47" s="62"/>
+      <c r="E47" s="62"/>
       <c r="F47" s="11">
         <v>2.2322284000000001E-2</v>
       </c>
@@ -3421,7 +3424,7 @@
       <c r="J47" s="11">
         <v>0.45333713520000002</v>
       </c>
-      <c r="K47" s="69"/>
+      <c r="K47" s="64"/>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -3430,9 +3433,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="62"/>
-      <c r="D48" s="63"/>
-      <c r="E48" s="63"/>
+      <c r="C48" s="66"/>
+      <c r="D48" s="62"/>
+      <c r="E48" s="62"/>
       <c r="F48" s="11">
         <v>4.7901900000000002E-4</v>
       </c>
@@ -3448,7 +3451,7 @@
       <c r="J48" s="11">
         <v>0.47522234359999999</v>
       </c>
-      <c r="K48" s="69"/>
+      <c r="K48" s="64"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.2">
       <c r="G49" s="11"/>
@@ -3463,13 +3466,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="62" t="s">
+      <c r="C50" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="63" t="s">
+      <c r="D50" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="63" t="s">
+      <c r="E50" s="62" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -3495,9 +3498,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="62"/>
-      <c r="D51" s="63"/>
-      <c r="E51" s="63"/>
+      <c r="C51" s="66"/>
+      <c r="D51" s="62"/>
+      <c r="E51" s="62"/>
       <c r="F51" s="11">
         <v>5.7482279999999995E-4</v>
       </c>
@@ -3521,9 +3524,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="62"/>
-      <c r="D52" s="63"/>
-      <c r="E52" s="63"/>
+      <c r="C52" s="66"/>
+      <c r="D52" s="62"/>
+      <c r="E52" s="62"/>
       <c r="F52" s="11">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -3551,12 +3554,12 @@
       <c r="J54" s="11"/>
     </row>
     <row r="55" spans="1:11" s="44" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="61" t="s">
+      <c r="A55" s="69" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="61"/>
-      <c r="C55" s="61"/>
-      <c r="D55" s="61"/>
+      <c r="B55" s="69"/>
+      <c r="C55" s="69"/>
+      <c r="D55" s="69"/>
       <c r="E55" s="41"/>
       <c r="F55" s="42">
         <f>MAX(F2:F52)</f>
@@ -3581,12 +3584,12 @@
       <c r="K55" s="43"/>
     </row>
     <row r="56" spans="1:11" s="48" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="67" t="s">
+      <c r="A56" s="61" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="67"/>
-      <c r="C56" s="67"/>
-      <c r="D56" s="67"/>
+      <c r="B56" s="61"/>
+      <c r="C56" s="61"/>
+      <c r="D56" s="61"/>
       <c r="E56" s="45"/>
       <c r="F56" s="46">
         <f>AVERAGE(F2:F52)</f>
@@ -3612,6 +3615,37 @@
     </row>
   </sheetData>
   <mergeCells count="47">
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="K42:K44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="K46:K48"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="K12:K14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="K20:K22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="K16:K18"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="K2:K4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="K6:K8"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C12:C14"/>
@@ -3628,37 +3662,6 @@
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D50:D52"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="K2:K4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="K6:K8"/>
-    <mergeCell ref="K12:K14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="K20:K22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="K16:K18"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="K42:K44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="K46:K48"/>
-    <mergeCell ref="E50:E52"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -3739,7 +3742,7 @@
       <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="66" t="s">
+      <c r="C2" s="68" t="s">
         <v>41</v>
       </c>
       <c r="D2" s="65" t="s">
@@ -3775,7 +3778,7 @@
         <f>SUM(F2*1/5,G2*1/5,H2*1/5,I2*1/5,J2*1/5)</f>
         <v>0.28479454145999999</v>
       </c>
-      <c r="N2" s="68" t="s">
+      <c r="N2" s="63" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3786,9 +3789,9 @@
       <c r="B3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="62"/>
-      <c r="D3" s="63"/>
-      <c r="E3" s="63"/>
+      <c r="C3" s="66"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
       <c r="F3" s="11">
         <v>8.3029722E-2</v>
       </c>
@@ -3816,7 +3819,7 @@
         <f>SUM(F3*1/5,G3*1/5,H3*1/5,I3*1/5,J3*1/5)</f>
         <v>0.24688138529999998</v>
       </c>
-      <c r="N3" s="69"/>
+      <c r="N3" s="64"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
@@ -3825,9 +3828,9 @@
       <c r="B4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="62"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
+      <c r="C4" s="66"/>
+      <c r="D4" s="62"/>
+      <c r="E4" s="62"/>
       <c r="F4" s="11">
         <v>2.2051773699999999E-2</v>
       </c>
@@ -3855,7 +3858,7 @@
         <f>SUM(F4*1/5,G4*1/5,H4*1/5,I4*1/5,J4*1/5)</f>
         <v>0.24577994555999999</v>
       </c>
-      <c r="N4" s="69"/>
+      <c r="N4" s="64"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
@@ -3864,13 +3867,13 @@
       <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="62" t="s">
+      <c r="C6" s="66" t="s">
         <v>42</v>
       </c>
-      <c r="D6" s="63" t="s">
+      <c r="D6" s="62" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="63" t="s">
+      <c r="E6" s="62" t="s">
         <v>13</v>
       </c>
       <c r="F6" s="11">
@@ -3900,7 +3903,7 @@
         <f>SUM(F6*1/5,G6*1/5,H6*1/5,I6*1/5,J6*1/5)</f>
         <v>0.21462878724000001</v>
       </c>
-      <c r="N6" s="69" t="s">
+      <c r="N6" s="64" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3911,9 +3914,9 @@
       <c r="B7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="62"/>
-      <c r="D7" s="63"/>
-      <c r="E7" s="63"/>
+      <c r="C7" s="66"/>
+      <c r="D7" s="62"/>
+      <c r="E7" s="62"/>
       <c r="F7" s="11">
         <v>4.4165548999999998E-2</v>
       </c>
@@ -3941,7 +3944,7 @@
         <f>SUM(F7*1/5,G7*1/5,H7*1/5,I7*1/5,J7*1/5)</f>
         <v>0.27318294232000001</v>
       </c>
-      <c r="N7" s="69"/>
+      <c r="N7" s="64"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
@@ -3950,9 +3953,9 @@
       <c r="B8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="62"/>
-      <c r="D8" s="63"/>
-      <c r="E8" s="63"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="62"/>
+      <c r="E8" s="62"/>
       <c r="F8" s="11">
         <v>3.7171872000000002E-2</v>
       </c>
@@ -3980,15 +3983,15 @@
         <f>SUM(F8*1/5,G8*1/5,H8*1/5,I8*1/5,J8*1/5)</f>
         <v>0.26231643128000004</v>
       </c>
-      <c r="N8" s="69"/>
+      <c r="N8" s="64"/>
     </row>
     <row r="10" spans="1:15" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="64" t="s">
+      <c r="A10" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="B10" s="64"/>
-      <c r="C10" s="64"/>
-      <c r="D10" s="64"/>
+      <c r="B10" s="67"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
       <c r="E10" s="5"/>
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
@@ -4007,13 +4010,13 @@
       <c r="B12" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="62" t="s">
+      <c r="C12" s="66" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="63" t="s">
+      <c r="D12" s="62" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="63" t="s">
+      <c r="E12" s="62" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="11">
@@ -4043,7 +4046,7 @@
         <f>SUM(F12*1/5,G12*1/5,H12*1/5,I12*1/5,J12*1/5)</f>
         <v>0.32808210163999996</v>
       </c>
-      <c r="N12" s="69" t="s">
+      <c r="N12" s="64" t="s">
         <v>18</v>
       </c>
     </row>
@@ -4054,9 +4057,9 @@
       <c r="B13" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="62"/>
-      <c r="D13" s="63"/>
-      <c r="E13" s="63"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
       <c r="F13" s="11">
         <v>4.8897411E-3</v>
       </c>
@@ -4084,7 +4087,7 @@
         <f>SUM(F13*1/5,G13*1/5,H13*1/5,I13*1/5,J13*1/5)</f>
         <v>0.25619948824</v>
       </c>
-      <c r="N13" s="69"/>
+      <c r="N13" s="64"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
@@ -4093,9 +4096,9 @@
       <c r="B14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="62"/>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="62"/>
+      <c r="E14" s="62"/>
       <c r="F14" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4123,7 +4126,7 @@
         <f>SUM(F14*1/5,G14*1/5,H14*1/5,I14*1/5,J14*1/5)</f>
         <v>0.20013002629999999</v>
       </c>
-      <c r="N14" s="69"/>
+      <c r="N14" s="64"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
@@ -4132,13 +4135,13 @@
       <c r="B16" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C16" s="62" t="s">
+      <c r="C16" s="66" t="s">
         <v>44</v>
       </c>
-      <c r="D16" s="63" t="s">
+      <c r="D16" s="62" t="s">
         <v>19</v>
       </c>
-      <c r="E16" s="63" t="s">
+      <c r="E16" s="62" t="s">
         <v>27</v>
       </c>
       <c r="F16" s="11">
@@ -4168,7 +4171,7 @@
         <f>SUM(F16*1/5,G16*1/5,H16*1/5,I16*1/5,J16*1/5)</f>
         <v>0.34520352803999999</v>
       </c>
-      <c r="N16" s="69" t="s">
+      <c r="N16" s="64" t="s">
         <v>36</v>
       </c>
     </row>
@@ -4179,9 +4182,9 @@
       <c r="B17" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="62"/>
-      <c r="D17" s="63"/>
-      <c r="E17" s="63"/>
+      <c r="C17" s="66"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
       <c r="F17" s="11">
         <v>2.85714286E-2</v>
       </c>
@@ -4209,7 +4212,7 @@
         <f>SUM(F17*1/5,G17*1/5,H17*1/5,I17*1/5,J17*1/5)</f>
         <v>0.33728800162</v>
       </c>
-      <c r="N17" s="69"/>
+      <c r="N17" s="64"/>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
@@ -4218,9 +4221,9 @@
       <c r="B18" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="62"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
+      <c r="C18" s="66"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
       <c r="F18" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4248,7 +4251,7 @@
         <f>SUM(F18*1/5,G18*1/5,H18*1/5,I18*1/5,J18*1/5)</f>
         <v>0.35540309720000007</v>
       </c>
-      <c r="N18" s="69"/>
+      <c r="N18" s="64"/>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
@@ -4257,13 +4260,13 @@
       <c r="B20" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C20" s="62" t="s">
+      <c r="C20" s="66" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="63" t="s">
+      <c r="D20" s="62" t="s">
         <v>20</v>
       </c>
-      <c r="E20" s="63" t="s">
+      <c r="E20" s="62" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="11">
@@ -4293,7 +4296,7 @@
         <f>SUM(F20*1/5,G20*1/5,H20*1/5,I20*1/5,J20*1/5)</f>
         <v>0.33023019046000002</v>
       </c>
-      <c r="N20" s="69" t="s">
+      <c r="N20" s="64" t="s">
         <v>35</v>
       </c>
     </row>
@@ -4304,9 +4307,9 @@
       <c r="B21" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C21" s="62"/>
-      <c r="D21" s="63"/>
-      <c r="E21" s="63"/>
+      <c r="C21" s="66"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
       <c r="F21" s="11">
         <v>8.59060403E-2</v>
       </c>
@@ -4334,7 +4337,7 @@
         <f>SUM(F21*1/5,G21*1/5,H21*1/5,I21*1/5,J21*1/5)</f>
         <v>0.39507478221999998</v>
       </c>
-      <c r="N21" s="69"/>
+      <c r="N21" s="64"/>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
@@ -4343,9 +4346,9 @@
       <c r="B22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="62"/>
-      <c r="D22" s="63"/>
-      <c r="E22" s="63"/>
+      <c r="C22" s="66"/>
+      <c r="D22" s="62"/>
+      <c r="E22" s="62"/>
       <c r="F22" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -4373,7 +4376,7 @@
         <f>SUM(F22*1/5,G22*1/5,H22*1/5,I22*1/5,J22*1/5)</f>
         <v>0.29192671981999996</v>
       </c>
-      <c r="N22" s="69"/>
+      <c r="N22" s="64"/>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
@@ -4382,13 +4385,13 @@
       <c r="B24" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="66" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="63" t="s">
+      <c r="D24" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="E24" s="63" t="s">
+      <c r="E24" s="62" t="s">
         <v>32</v>
       </c>
       <c r="F24" s="11">
@@ -4426,9 +4429,9 @@
       <c r="B25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="62"/>
-      <c r="D25" s="63"/>
-      <c r="E25" s="63"/>
+      <c r="C25" s="66"/>
+      <c r="D25" s="62"/>
+      <c r="E25" s="62"/>
       <c r="F25" s="11">
         <v>1.04506232E-2</v>
       </c>
@@ -4464,9 +4467,9 @@
       <c r="B26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C26" s="62"/>
-      <c r="D26" s="63"/>
-      <c r="E26" s="63"/>
+      <c r="C26" s="66"/>
+      <c r="D26" s="62"/>
+      <c r="E26" s="62"/>
       <c r="F26" s="11">
         <v>2.876318E-4</v>
       </c>
@@ -4502,13 +4505,13 @@
       <c r="B28" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C28" s="62" t="s">
+      <c r="C28" s="66" t="s">
         <v>47</v>
       </c>
-      <c r="D28" s="63" t="s">
+      <c r="D28" s="62" t="s">
         <v>22</v>
       </c>
-      <c r="E28" s="63" t="s">
+      <c r="E28" s="62" t="s">
         <v>33</v>
       </c>
       <c r="F28" s="11">
@@ -4546,9 +4549,9 @@
       <c r="B29" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="62"/>
-      <c r="D29" s="63"/>
-      <c r="E29" s="63"/>
+      <c r="C29" s="66"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
       <c r="F29" s="11">
         <v>5.7526366000000004E-3</v>
       </c>
@@ -4584,9 +4587,9 @@
       <c r="B30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="62"/>
-      <c r="D30" s="63"/>
-      <c r="E30" s="63"/>
+      <c r="C30" s="66"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="62"/>
       <c r="F30" s="11">
         <v>9.5877299999999998E-5</v>
       </c>
@@ -4622,13 +4625,13 @@
       <c r="B32" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="62" t="s">
+      <c r="C32" s="66" t="s">
         <v>48</v>
       </c>
-      <c r="D32" s="63" t="s">
+      <c r="D32" s="62" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="63" t="s">
+      <c r="E32" s="62" t="s">
         <v>29</v>
       </c>
       <c r="F32" s="11">
@@ -4666,9 +4669,9 @@
       <c r="B33" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C33" s="62"/>
-      <c r="D33" s="63"/>
-      <c r="E33" s="63"/>
+      <c r="C33" s="66"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="62"/>
       <c r="F33" s="11">
         <v>7.6701821700000006E-2</v>
       </c>
@@ -4704,9 +4707,9 @@
       <c r="B34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="62"/>
-      <c r="D34" s="63"/>
-      <c r="E34" s="63"/>
+      <c r="C34" s="66"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
       <c r="F34" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4742,13 +4745,13 @@
       <c r="B36" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C36" s="62" t="s">
+      <c r="C36" s="66" t="s">
         <v>49</v>
       </c>
-      <c r="D36" s="63" t="s">
+      <c r="D36" s="62" t="s">
         <v>24</v>
       </c>
-      <c r="E36" s="63" t="s">
+      <c r="E36" s="62" t="s">
         <v>34</v>
       </c>
       <c r="F36" s="11">
@@ -4786,9 +4789,9 @@
       <c r="B37" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C37" s="62"/>
-      <c r="D37" s="63"/>
-      <c r="E37" s="63"/>
+      <c r="C37" s="66"/>
+      <c r="D37" s="62"/>
+      <c r="E37" s="62"/>
       <c r="F37" s="11">
         <v>1.0546500000000001E-3</v>
       </c>
@@ -4824,9 +4827,9 @@
       <c r="B38" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C38" s="62"/>
-      <c r="D38" s="63"/>
-      <c r="E38" s="63"/>
+      <c r="C38" s="66"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
       <c r="F38" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -4856,12 +4859,12 @@
       </c>
     </row>
     <row r="40" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="64" t="s">
+      <c r="A40" s="67" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="64"/>
-      <c r="C40" s="64"/>
-      <c r="D40" s="64"/>
+      <c r="B40" s="67"/>
+      <c r="C40" s="67"/>
+      <c r="D40" s="67"/>
       <c r="E40" s="5"/>
       <c r="F40" s="13"/>
       <c r="G40" s="13"/>
@@ -4880,13 +4883,13 @@
       <c r="B42" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C42" s="62" t="s">
+      <c r="C42" s="66" t="s">
         <v>50</v>
       </c>
-      <c r="D42" s="63" t="s">
+      <c r="D42" s="62" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="63" t="s">
+      <c r="E42" s="62" t="s">
         <v>27</v>
       </c>
       <c r="F42" s="11">
@@ -4916,7 +4919,7 @@
         <f>SUM(F42*1/5,G42*1/5,H42*1/5,I42*1/5,J42*1/5)</f>
         <v>0.31386758548000004</v>
       </c>
-      <c r="N42" s="69" t="s">
+      <c r="N42" s="64" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4927,9 +4930,9 @@
       <c r="B43" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C43" s="62"/>
-      <c r="D43" s="63"/>
-      <c r="E43" s="63"/>
+      <c r="C43" s="66"/>
+      <c r="D43" s="62"/>
+      <c r="E43" s="62"/>
       <c r="F43" s="11">
         <v>2.93159609E-2</v>
       </c>
@@ -4957,7 +4960,7 @@
         <f>SUM(F43*1/5,G43*1/5,H43*1/5,I43*1/5,J43*1/5)</f>
         <v>0.29226255760000003</v>
       </c>
-      <c r="N43" s="69"/>
+      <c r="N43" s="64"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
@@ -4966,9 +4969,9 @@
       <c r="B44" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C44" s="62"/>
-      <c r="D44" s="63"/>
-      <c r="E44" s="63"/>
+      <c r="C44" s="66"/>
+      <c r="D44" s="62"/>
+      <c r="E44" s="62"/>
       <c r="F44" s="14">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -4996,7 +4999,7 @@
         <f>SUM(F44*1/5,G44*1/5,H44*1/5,I44*1/5,J44*1/5)</f>
         <v>0.34257018057999999</v>
       </c>
-      <c r="N44" s="69"/>
+      <c r="N44" s="64"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
@@ -5005,13 +5008,13 @@
       <c r="B46" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C46" s="62" t="s">
+      <c r="C46" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="D46" s="63" t="s">
+      <c r="D46" s="62" t="s">
         <v>26</v>
       </c>
-      <c r="E46" s="63" t="s">
+      <c r="E46" s="62" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="11">
@@ -5041,7 +5044,7 @@
         <f>SUM(F46*1/5,G46*1/5,H46*1/5,I46*1/5,J46*1/5)</f>
         <v>0.31043419121999999</v>
       </c>
-      <c r="N46" s="69" t="s">
+      <c r="N46" s="64" t="s">
         <v>31</v>
       </c>
     </row>
@@ -5052,9 +5055,9 @@
       <c r="B47" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C47" s="62"/>
-      <c r="D47" s="63"/>
-      <c r="E47" s="63"/>
+      <c r="C47" s="66"/>
+      <c r="D47" s="62"/>
+      <c r="E47" s="62"/>
       <c r="F47" s="11">
         <v>5.5853611800000001E-2</v>
       </c>
@@ -5082,7 +5085,7 @@
         <f>SUM(F47*1/5,G47*1/5,H47*1/5,I47*1/5,J47*1/5)</f>
         <v>0.38566402880000006</v>
       </c>
-      <c r="N47" s="69"/>
+      <c r="N47" s="64"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
@@ -5091,9 +5094,9 @@
       <c r="B48" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C48" s="62"/>
-      <c r="D48" s="63"/>
-      <c r="E48" s="63"/>
+      <c r="C48" s="66"/>
+      <c r="D48" s="62"/>
+      <c r="E48" s="62"/>
       <c r="F48" s="11">
         <v>9.5803800000000006E-5</v>
       </c>
@@ -5121,7 +5124,7 @@
         <f>SUM(F48*1/5,G48*1/5,H48*1/5,I48*1/5,J48*1/5)</f>
         <v>0.26614251024000002</v>
       </c>
-      <c r="N48" s="69"/>
+      <c r="N48" s="64"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
@@ -5130,13 +5133,13 @@
       <c r="B50" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C50" s="62" t="s">
+      <c r="C50" s="66" t="s">
         <v>52</v>
       </c>
-      <c r="D50" s="63" t="s">
+      <c r="D50" s="62" t="s">
         <v>39</v>
       </c>
-      <c r="E50" s="63" t="s">
+      <c r="E50" s="62" t="s">
         <v>29</v>
       </c>
       <c r="F50" s="11">
@@ -5174,9 +5177,9 @@
       <c r="B51" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C51" s="62"/>
-      <c r="D51" s="63"/>
-      <c r="E51" s="63"/>
+      <c r="C51" s="66"/>
+      <c r="D51" s="62"/>
+      <c r="E51" s="62"/>
       <c r="F51" s="11">
         <v>4.4452960299999997E-2</v>
       </c>
@@ -5212,9 +5215,9 @@
       <c r="B52" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C52" s="62"/>
-      <c r="D52" s="63"/>
-      <c r="E52" s="63"/>
+      <c r="C52" s="66"/>
+      <c r="D52" s="62"/>
+      <c r="E52" s="62"/>
       <c r="F52" s="14">
         <v>0</v>
       </c>
@@ -5244,12 +5247,12 @@
       </c>
     </row>
     <row r="55" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="70" t="s">
+      <c r="A55" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="B55" s="70"/>
-      <c r="C55" s="70"/>
-      <c r="D55" s="70"/>
+      <c r="B55" s="76"/>
+      <c r="C55" s="76"/>
+      <c r="D55" s="76"/>
       <c r="E55" s="16"/>
       <c r="F55" s="17">
         <f t="shared" ref="F55:M55" si="0">MAX(F2:F52)</f>
@@ -5286,12 +5289,12 @@
       <c r="N55" s="18"/>
     </row>
     <row r="56" spans="1:14" s="20" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="71" t="s">
+      <c r="A56" s="75" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="71"/>
-      <c r="C56" s="71"/>
-      <c r="D56" s="71"/>
+      <c r="B56" s="75"/>
+      <c r="C56" s="75"/>
+      <c r="D56" s="75"/>
       <c r="E56" s="21"/>
       <c r="F56" s="22">
         <f t="shared" ref="F56:M56" si="1">AVERAGE(F2:F52)</f>
@@ -5328,13 +5331,13 @@
       <c r="N56" s="23"/>
     </row>
     <row r="58" spans="1:14" s="24" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="74" t="s">
+      <c r="A58" s="72" t="s">
         <v>68</v>
       </c>
-      <c r="B58" s="74"/>
-      <c r="C58" s="74"/>
-      <c r="D58" s="74"/>
-      <c r="E58" s="74"/>
+      <c r="B58" s="72"/>
+      <c r="C58" s="72"/>
+      <c r="D58" s="72"/>
+      <c r="E58" s="72"/>
       <c r="F58" s="31">
         <f>SUM(F55*(1/3),  G55*(1/3), I55*(1/3))</f>
         <v>0.33597317126666659</v>
@@ -5349,13 +5352,13 @@
       <c r="N58" s="26"/>
     </row>
     <row r="59" spans="1:14" s="29" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="75" t="s">
+      <c r="A59" s="73" t="s">
         <v>69</v>
       </c>
-      <c r="B59" s="75"/>
-      <c r="C59" s="75"/>
-      <c r="D59" s="75"/>
-      <c r="E59" s="75"/>
+      <c r="B59" s="73"/>
+      <c r="C59" s="73"/>
+      <c r="D59" s="73"/>
+      <c r="E59" s="73"/>
       <c r="F59" s="30">
         <f>SUM(H55*(1/2),  J55*(1/2))</f>
         <v>0.65426068544999993</v>
@@ -5370,13 +5373,13 @@
       <c r="N59" s="28"/>
     </row>
     <row r="60" spans="1:14" s="35" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="76" t="s">
+      <c r="A60" s="74" t="s">
         <v>70</v>
       </c>
-      <c r="B60" s="76"/>
-      <c r="C60" s="76"/>
-      <c r="D60" s="76"/>
-      <c r="E60" s="76"/>
+      <c r="B60" s="74"/>
+      <c r="C60" s="74"/>
+      <c r="D60" s="74"/>
+      <c r="E60" s="74"/>
       <c r="F60" s="32">
         <f>SUM(F55*1/5, G55*1/5, H55*1/5, I55*1/5,J55*1/5)</f>
         <v>0.46328817694000002</v>
@@ -5391,12 +5394,12 @@
       <c r="N60" s="34"/>
     </row>
     <row r="62" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="72" t="s">
+      <c r="A62" s="70" t="s">
         <v>65</v>
       </c>
-      <c r="B62" s="72"/>
-      <c r="C62" s="72"/>
-      <c r="D62" s="72"/>
+      <c r="B62" s="70"/>
+      <c r="C62" s="70"/>
+      <c r="D62" s="70"/>
       <c r="E62" s="36"/>
       <c r="F62" s="37"/>
       <c r="G62" s="37"/>
@@ -5409,12 +5412,12 @@
       <c r="N62" s="38"/>
     </row>
     <row r="63" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="72" t="s">
+      <c r="A63" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="B63" s="73"/>
-      <c r="C63" s="73"/>
-      <c r="D63" s="73"/>
+      <c r="B63" s="71"/>
+      <c r="C63" s="71"/>
+      <c r="D63" s="71"/>
       <c r="E63" s="40"/>
       <c r="F63" s="37"/>
       <c r="G63" s="37"/>
@@ -5427,12 +5430,12 @@
       <c r="N63" s="38"/>
     </row>
     <row r="64" spans="1:14" s="39" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="72" t="s">
+      <c r="A64" s="70" t="s">
         <v>67</v>
       </c>
-      <c r="B64" s="73"/>
-      <c r="C64" s="73"/>
-      <c r="D64" s="73"/>
+      <c r="B64" s="71"/>
+      <c r="C64" s="71"/>
+      <c r="D64" s="71"/>
       <c r="E64" s="40"/>
       <c r="F64" s="37"/>
       <c r="G64" s="37"/>
@@ -5446,12 +5449,37 @@
     </row>
   </sheetData>
   <mergeCells count="53">
-    <mergeCell ref="A63:D63"/>
-    <mergeCell ref="A64:D64"/>
-    <mergeCell ref="A58:E58"/>
-    <mergeCell ref="A59:E59"/>
-    <mergeCell ref="A60:E60"/>
-    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A55:D55"/>
+    <mergeCell ref="N42:N44"/>
+    <mergeCell ref="C46:C48"/>
+    <mergeCell ref="D46:D48"/>
+    <mergeCell ref="E46:E48"/>
+    <mergeCell ref="N46:N48"/>
+    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="C36:C38"/>
+    <mergeCell ref="D36:D38"/>
+    <mergeCell ref="E36:E38"/>
+    <mergeCell ref="A40:D40"/>
+    <mergeCell ref="C42:C44"/>
+    <mergeCell ref="D42:D44"/>
+    <mergeCell ref="E42:E44"/>
+    <mergeCell ref="N12:N14"/>
+    <mergeCell ref="C20:C22"/>
+    <mergeCell ref="D20:D22"/>
+    <mergeCell ref="E20:E22"/>
+    <mergeCell ref="N20:N22"/>
+    <mergeCell ref="C16:C18"/>
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="N16:N18"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="N2:N4"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:E8"/>
+    <mergeCell ref="N6:N8"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="C12:C14"/>
@@ -5468,37 +5496,12 @@
     <mergeCell ref="E32:E34"/>
     <mergeCell ref="C50:C52"/>
     <mergeCell ref="D50:D52"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="N2:N4"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:E8"/>
-    <mergeCell ref="N6:N8"/>
-    <mergeCell ref="N12:N14"/>
-    <mergeCell ref="C20:C22"/>
-    <mergeCell ref="D20:D22"/>
-    <mergeCell ref="E20:E22"/>
-    <mergeCell ref="N20:N22"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="N16:N18"/>
-    <mergeCell ref="C36:C38"/>
-    <mergeCell ref="D36:D38"/>
-    <mergeCell ref="E36:E38"/>
-    <mergeCell ref="A40:D40"/>
-    <mergeCell ref="C42:C44"/>
-    <mergeCell ref="D42:D44"/>
-    <mergeCell ref="E42:E44"/>
-    <mergeCell ref="A55:D55"/>
-    <mergeCell ref="N42:N44"/>
-    <mergeCell ref="C46:C48"/>
-    <mergeCell ref="D46:D48"/>
-    <mergeCell ref="E46:E48"/>
-    <mergeCell ref="N46:N48"/>
-    <mergeCell ref="E50:E52"/>
+    <mergeCell ref="A63:D63"/>
+    <mergeCell ref="A64:D64"/>
+    <mergeCell ref="A58:E58"/>
+    <mergeCell ref="A59:E59"/>
+    <mergeCell ref="A60:E60"/>
+    <mergeCell ref="A62:D62"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5579,17 +5582,17 @@
       <c r="N2" s="9"/>
     </row>
     <row r="3" spans="1:14" s="49" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="71" t="s">
+      <c r="A3" s="75" t="s">
         <v>75</v>
       </c>
-      <c r="B3" s="71"/>
-      <c r="C3" s="71"/>
-      <c r="D3" s="71"/>
-      <c r="E3" s="71"/>
-      <c r="F3" s="71"/>
-      <c r="G3" s="71"/>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
+      <c r="B3" s="75"/>
+      <c r="C3" s="75"/>
+      <c r="D3" s="75"/>
+      <c r="E3" s="75"/>
+      <c r="F3" s="75"/>
+      <c r="G3" s="75"/>
+      <c r="H3" s="75"/>
+      <c r="I3" s="75"/>
       <c r="J3" s="51"/>
       <c r="K3" s="58"/>
       <c r="L3" s="58"/>
@@ -5615,16 +5618,16 @@
       <c r="B5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="69" t="s">
+      <c r="C5" s="64" t="s">
         <v>71</v>
       </c>
-      <c r="D5" s="69" t="s">
+      <c r="D5" s="64" t="s">
         <v>72</v>
       </c>
       <c r="E5" s="11">
         <v>2.6558005799999999E-2</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="78">
         <v>7.9290508100000004E-2</v>
       </c>
       <c r="G5" s="11">
@@ -5656,8 +5659,8 @@
       <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="69"/>
-      <c r="D6" s="69"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
       <c r="E6" s="11">
         <v>6.2032598299999998E-2</v>
       </c>
@@ -5693,8 +5696,8 @@
       <c r="B7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="69"/>
-      <c r="D7" s="69"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
       <c r="E7" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
@@ -5730,10 +5733,10 @@
       <c r="B9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="69" t="s">
+      <c r="C9" s="64" t="s">
         <v>73</v>
       </c>
-      <c r="D9" s="69" t="s">
+      <c r="D9" s="64" t="s">
         <v>74</v>
       </c>
       <c r="E9" s="11">
@@ -5771,8 +5774,8 @@
       <c r="B10" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="69"/>
-      <c r="D10" s="69"/>
+      <c r="C10" s="64"/>
+      <c r="D10" s="64"/>
       <c r="E10" s="11">
         <v>7.6701821700000006E-2</v>
       </c>
@@ -5782,7 +5785,7 @@
       <c r="G10" s="11">
         <v>0.4302972196</v>
       </c>
-      <c r="H10" s="11">
+      <c r="H10" s="78">
         <v>0.90418992629999995</v>
       </c>
       <c r="I10" s="11">
@@ -5808,8 +5811,8 @@
       <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
+      <c r="C11" s="64"/>
+      <c r="D11" s="64"/>
       <c r="E11" s="11">
         <v>1.917546E-4</v>
       </c>
@@ -5845,10 +5848,10 @@
       <c r="B13" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="69" t="s">
+      <c r="C13" s="64" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="69" t="s">
+      <c r="D13" s="64" t="s">
         <v>99</v>
       </c>
       <c r="E13" s="11">
@@ -5886,8 +5889,8 @@
       <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
+      <c r="C14" s="64"/>
+      <c r="D14" s="64"/>
       <c r="E14" s="11">
         <v>4.53499521E-2</v>
       </c>
@@ -5923,8 +5926,8 @@
       <c r="B15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="69"/>
-      <c r="D15" s="69"/>
+      <c r="C15" s="64"/>
+      <c r="D15" s="64"/>
       <c r="E15" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
@@ -5957,10 +5960,10 @@
       <c r="B17" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C17" s="69" t="s">
+      <c r="C17" s="64" t="s">
         <v>90</v>
       </c>
-      <c r="D17" s="69" t="s">
+      <c r="D17" s="64" t="s">
         <v>89</v>
       </c>
       <c r="E17" s="11">
@@ -5969,7 +5972,7 @@
       <c r="F17" s="11">
         <v>1.02588686E-2</v>
       </c>
-      <c r="G17" s="11">
+      <c r="G17" s="78">
         <v>0.74285714290000004</v>
       </c>
       <c r="H17" s="11">
@@ -5998,8 +6001,8 @@
       <c r="B18" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="69"/>
-      <c r="D18" s="69"/>
+      <c r="C18" s="64"/>
+      <c r="D18" s="64"/>
       <c r="E18" s="11">
         <v>5.5608821000000001E-3</v>
       </c>
@@ -6035,8 +6038,8 @@
       <c r="B19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="69"/>
-      <c r="D19" s="69"/>
+      <c r="C19" s="64"/>
+      <c r="D19" s="64"/>
       <c r="E19" s="11">
         <v>5.7526370000000003E-4</v>
       </c>
@@ -6075,10 +6078,10 @@
       <c r="B21" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C21" s="69" t="s">
+      <c r="C21" s="64" t="s">
         <v>76</v>
       </c>
-      <c r="D21" s="69" t="s">
+      <c r="D21" s="64" t="s">
         <v>77</v>
       </c>
       <c r="E21" s="11">
@@ -6116,8 +6119,8 @@
       <c r="B22" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C22" s="69"/>
-      <c r="D22" s="69"/>
+      <c r="C22" s="64"/>
+      <c r="D22" s="64"/>
       <c r="E22" s="11">
         <v>2.95302013E-2</v>
       </c>
@@ -6153,8 +6156,8 @@
       <c r="B23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="69"/>
-      <c r="D23" s="69"/>
+      <c r="C23" s="64"/>
+      <c r="D23" s="64"/>
       <c r="E23" s="11">
         <v>0</v>
       </c>
@@ -6190,10 +6193,10 @@
       <c r="B25" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C25" s="69" t="s">
+      <c r="C25" s="64" t="s">
         <v>87</v>
       </c>
-      <c r="D25" s="69" t="s">
+      <c r="D25" s="64" t="s">
         <v>85</v>
       </c>
       <c r="E25" s="11">
@@ -6208,7 +6211,7 @@
       <c r="H25" s="11">
         <v>0.65897583790000003</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="78">
         <v>0.68586700889999996</v>
       </c>
       <c r="J25" s="11">
@@ -6231,8 +6234,8 @@
       <c r="B26" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="69"/>
-      <c r="D26" s="69"/>
+      <c r="C26" s="64"/>
+      <c r="D26" s="64"/>
       <c r="E26" s="11">
         <v>9.5877280000000004E-4</v>
       </c>
@@ -6268,8 +6271,8 @@
       <c r="B27" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C27" s="69"/>
-      <c r="D27" s="69"/>
+      <c r="C27" s="64"/>
+      <c r="D27" s="64"/>
       <c r="E27" s="11">
         <v>2.4928092E-3</v>
       </c>
@@ -6305,13 +6308,13 @@
       <c r="B29" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C29" s="69" t="s">
+      <c r="C29" s="64" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="69" t="s">
+      <c r="D29" s="64" t="s">
         <v>86</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29" s="78">
         <v>9.4534995199999999E-2</v>
       </c>
       <c r="F29" s="11">
@@ -6346,8 +6349,8 @@
       <c r="B30" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="69"/>
-      <c r="D30" s="69"/>
+      <c r="C30" s="64"/>
+      <c r="D30" s="64"/>
       <c r="E30" s="11">
         <v>4.6979865999999997E-3</v>
       </c>
@@ -6383,8 +6386,8 @@
       <c r="B31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C31" s="69"/>
-      <c r="D31" s="69"/>
+      <c r="C31" s="64"/>
+      <c r="D31" s="64"/>
       <c r="E31" s="11">
         <v>6.7114089999999996E-4</v>
       </c>
@@ -6420,23 +6423,38 @@
       <c r="B33" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="69" t="s">
+      <c r="C33" s="64" t="s">
         <v>91</v>
       </c>
-      <c r="D33" s="69" t="s">
+      <c r="D33" s="64" t="s">
         <v>92</v>
+      </c>
+      <c r="E33" s="11">
+        <v>6.9415148600000004E-2</v>
+      </c>
+      <c r="F33" s="11">
+        <v>4.1227229000000004E-3</v>
+      </c>
+      <c r="G33" s="11">
+        <v>0.55378715239999998</v>
+      </c>
+      <c r="H33" s="11">
+        <v>0.56262506509999999</v>
+      </c>
+      <c r="I33" s="11">
+        <v>0.50162452859999995</v>
       </c>
       <c r="J33" s="11">
         <f>SUM(E33*1/3,F33*1/3,H33*1/3)</f>
-        <v>0</v>
+        <v>0.21205431219999998</v>
       </c>
       <c r="K33" s="11">
         <f>SUM(G33*1/2,I33*1/2)</f>
-        <v>0</v>
+        <v>0.52770584049999991</v>
       </c>
       <c r="L33" s="11">
         <f>SUM(E33*1/5,F33*1/5,G33*1/5,H33*1/5,I33*1/5)</f>
-        <v>0</v>
+        <v>0.33831492352000003</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
@@ -6446,19 +6464,34 @@
       <c r="B34" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C34" s="69"/>
-      <c r="D34" s="69"/>
+      <c r="C34" s="64"/>
+      <c r="D34" s="64"/>
+      <c r="E34" s="11">
+        <v>2.5599232999999999E-2</v>
+      </c>
+      <c r="F34" s="11">
+        <v>1.5340364E-3</v>
+      </c>
+      <c r="G34" s="11">
+        <v>0.21150527329999999</v>
+      </c>
+      <c r="H34" s="11">
+        <v>0.51131380289999995</v>
+      </c>
+      <c r="I34" s="11">
+        <v>0.48718764170000001</v>
+      </c>
       <c r="J34" s="11">
         <f>SUM(E34*1/3,F34*1/3,H34*1/3)</f>
-        <v>0</v>
+        <v>0.17948235743333332</v>
       </c>
       <c r="K34" s="11">
         <f>SUM(G34*1/2,I34*1/2)</f>
-        <v>0</v>
+        <v>0.34934645749999998</v>
       </c>
       <c r="L34" s="11">
         <f>SUM(E34*1/5,F34*1/5,G34*1/5,H34*1/5,I34*1/5)</f>
-        <v>0</v>
+        <v>0.24742799745999997</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.2">
@@ -6468,19 +6501,34 @@
       <c r="B35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="69"/>
-      <c r="D35" s="69"/>
+      <c r="C35" s="64"/>
+      <c r="D35" s="64"/>
+      <c r="E35" s="11">
+        <v>1.725791E-3</v>
+      </c>
+      <c r="F35" s="11">
+        <v>6.2320229999999997E-3</v>
+      </c>
+      <c r="G35" s="11">
+        <v>6.1936721E-2</v>
+      </c>
+      <c r="H35" s="11">
+        <v>0.44348541050000001</v>
+      </c>
+      <c r="I35" s="11">
+        <v>0.31869602450000001</v>
+      </c>
       <c r="J35" s="11">
         <f>SUM(E35*1/3,F35*1/3,H35*1/3)</f>
-        <v>0</v>
+        <v>0.15048107483333334</v>
       </c>
       <c r="K35" s="11">
         <f>SUM(G35*1/2,I35*1/2)</f>
-        <v>0</v>
+        <v>0.19031637275000002</v>
       </c>
       <c r="L35" s="11">
         <f>SUM(E35*1/5,F35*1/5,G35*1/5,H35*1/5,I35*1/5)</f>
-        <v>0</v>
+        <v>0.16641519399999999</v>
       </c>
     </row>
     <row r="37" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -6490,23 +6538,38 @@
       <c r="B37" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="69" t="s">
+      <c r="C37" s="64" t="s">
         <v>93</v>
       </c>
       <c r="D37" s="77" t="s">
         <v>94</v>
       </c>
+      <c r="E37" s="11">
+        <v>6.6634707599999995E-2</v>
+      </c>
+      <c r="F37" s="11">
+        <v>7.2866731000000001E-3</v>
+      </c>
+      <c r="G37" s="11">
+        <v>0.62147651010000005</v>
+      </c>
+      <c r="H37" s="11">
+        <v>0.75344532060000002</v>
+      </c>
+      <c r="I37" s="11">
+        <v>0.58271822760000003</v>
+      </c>
       <c r="J37" s="11">
         <f>SUM(E37*1/3,F37*1/3,H37*1/3)</f>
-        <v>0</v>
+        <v>0.27578890043333332</v>
       </c>
       <c r="K37" s="11">
         <f>SUM(G37*1/2,I37*1/2)</f>
-        <v>0</v>
+        <v>0.60209736884999998</v>
       </c>
       <c r="L37" s="11">
         <f>SUM(E37*1/5,F37*1/5,G37*1/5,H37*1/5,I37*1/5)</f>
-        <v>0</v>
+        <v>0.4063122878</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
@@ -6516,19 +6579,34 @@
       <c r="B38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C38" s="69"/>
+      <c r="C38" s="64"/>
       <c r="D38" s="77"/>
+      <c r="E38" s="11">
+        <v>1.9558964500000001E-2</v>
+      </c>
+      <c r="F38" s="11">
+        <v>3.1639501E-3</v>
+      </c>
+      <c r="G38" s="11">
+        <v>0.40460210930000001</v>
+      </c>
+      <c r="H38" s="11">
+        <v>0.53038608750000005</v>
+      </c>
+      <c r="I38" s="11">
+        <v>0.52302711769999999</v>
+      </c>
       <c r="J38" s="11">
         <f>SUM(E38*1/3,F38*1/3,H38*1/3)</f>
-        <v>0</v>
+        <v>0.18436966736666668</v>
       </c>
       <c r="K38" s="11">
         <f>SUM(G38*1/2,I38*1/2)</f>
-        <v>0</v>
+        <v>0.46381461349999997</v>
       </c>
       <c r="L38" s="11">
         <f>SUM(E38*1/5,F38*1/5,G38*1/5,H38*1/5,I38*1/5)</f>
-        <v>0</v>
+        <v>0.29614764581999997</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
@@ -6538,19 +6616,34 @@
       <c r="B39" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C39" s="69"/>
+      <c r="C39" s="64"/>
       <c r="D39" s="77"/>
+      <c r="E39" s="11">
+        <v>3.2598274E-3</v>
+      </c>
+      <c r="F39" s="11">
+        <v>2.3969319199999999E-2</v>
+      </c>
+      <c r="G39" s="11">
+        <v>0.28130393100000001</v>
+      </c>
+      <c r="H39" s="11">
+        <v>0.53211225539999996</v>
+      </c>
+      <c r="I39" s="11">
+        <v>0.46081575299999999</v>
+      </c>
       <c r="J39" s="11">
         <f>SUM(E39*1/3,F39*1/3,H39*1/3)</f>
-        <v>0</v>
+        <v>0.18644713399999999</v>
       </c>
       <c r="K39" s="11">
         <f>SUM(G39*1/2,I39*1/2)</f>
-        <v>0</v>
+        <v>0.37105984199999997</v>
       </c>
       <c r="L39" s="11">
         <f>SUM(E39*1/5,F39*1/5,G39*1/5,H39*1/5,I39*1/5)</f>
-        <v>0</v>
+        <v>0.26029221719999995</v>
       </c>
     </row>
     <row r="41" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
@@ -6560,7 +6653,7 @@
       <c r="B41" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C41" s="69" t="s">
+      <c r="C41" s="64" t="s">
         <v>95</v>
       </c>
       <c r="D41" s="77" t="s">
@@ -6586,7 +6679,7 @@
       <c r="B42" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C42" s="69"/>
+      <c r="C42" s="64"/>
       <c r="D42" s="77"/>
       <c r="J42" s="11">
         <f>SUM(E42*1/3,F42*1/3,H42*1/3)</f>
@@ -6608,7 +6701,7 @@
       <c r="B43" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C43" s="69"/>
+      <c r="C43" s="64"/>
       <c r="D43" s="77"/>
       <c r="J43" s="11">
         <f>SUM(E43*1/3,F43*1/3,H43*1/3)</f>
@@ -6630,7 +6723,7 @@
       <c r="B45" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C45" s="69" t="s">
+      <c r="C45" s="64" t="s">
         <v>97</v>
       </c>
       <c r="D45" s="77" t="s">
@@ -6656,7 +6749,7 @@
       <c r="B46" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C46" s="69"/>
+      <c r="C46" s="64"/>
       <c r="D46" s="77"/>
       <c r="J46" s="11">
         <f>SUM(E46*1/3,F46*1/3,H46*1/3)</f>
@@ -6678,7 +6771,7 @@
       <c r="B47" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C47" s="69"/>
+      <c r="C47" s="64"/>
       <c r="D47" s="77"/>
       <c r="J47" s="11">
         <f>SUM(E47*1/3,F47*1/3,H47*1/3)</f>
@@ -6694,18 +6787,18 @@
       </c>
     </row>
     <row r="49" spans="1:14" s="15" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="70" t="s">
+      <c r="A49" s="76" t="s">
         <v>60</v>
       </c>
-      <c r="B49" s="70"/>
-      <c r="C49" s="70"/>
-      <c r="D49" s="70"/>
+      <c r="B49" s="76"/>
+      <c r="C49" s="76"/>
+      <c r="D49" s="76"/>
       <c r="E49" s="17">
-        <f t="shared" ref="E49:L49" si="0">MAX(E4:E35)</f>
+        <f>MAX(E4:E35)</f>
         <v>9.4534995199999999E-2</v>
       </c>
       <c r="F49" s="17">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="E49:L49" si="0">MAX(F4:F35)</f>
         <v>7.9290508100000004E-2</v>
       </c>
       <c r="G49" s="17">
@@ -6736,43 +6829,43 @@
       <c r="N49" s="18"/>
     </row>
     <row r="50" spans="1:14" s="54" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="74" t="s">
+      <c r="A50" s="72" t="s">
         <v>61</v>
       </c>
-      <c r="B50" s="74"/>
-      <c r="C50" s="74"/>
-      <c r="D50" s="74"/>
+      <c r="B50" s="72"/>
+      <c r="C50" s="72"/>
+      <c r="D50" s="72"/>
       <c r="E50" s="31">
         <f t="shared" ref="E50:L50" si="1">AVERAGE(E5:E35)</f>
-        <v>2.7548737623809522E-2</v>
+        <v>2.8135985945833331E-2</v>
       </c>
       <c r="F50" s="31">
         <f t="shared" si="1"/>
-        <v>8.5878646761904775E-3</v>
+        <v>8.0097475208333341E-3</v>
       </c>
       <c r="G50" s="31">
         <f t="shared" si="1"/>
-        <v>0.42520613615500008</v>
+        <v>0.40571095086086967</v>
       </c>
       <c r="H50" s="31">
         <f t="shared" si="1"/>
-        <v>0.65251506110952384</v>
+        <v>0.63417669007499999</v>
       </c>
       <c r="I50" s="31">
         <f t="shared" si="1"/>
-        <v>0.48998973861428574</v>
+        <v>0.48322052940416671</v>
       </c>
       <c r="J50" s="31">
         <f t="shared" si="1"/>
-        <v>0.20085673516111116</v>
+        <v>0.22344080784722231</v>
       </c>
       <c r="K50" s="31">
         <f t="shared" si="1"/>
-        <v>0.39153973404166659</v>
+        <v>0.43601342865624987</v>
       </c>
       <c r="L50" s="31">
         <f t="shared" si="1"/>
-        <v>0.2771299347133333</v>
+        <v>0.30846985617083328</v>
       </c>
       <c r="M50" s="31"/>
       <c r="N50" s="60"/>
@@ -6782,17 +6875,17 @@
       <c r="H51" s="56"/>
     </row>
     <row r="52" spans="1:14" s="49" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="71" t="s">
+      <c r="A52" s="75" t="s">
         <v>79</v>
       </c>
-      <c r="B52" s="71"/>
-      <c r="C52" s="71"/>
-      <c r="D52" s="71"/>
-      <c r="E52" s="71"/>
-      <c r="F52" s="71"/>
-      <c r="G52" s="71"/>
-      <c r="H52" s="71"/>
-      <c r="I52" s="71"/>
+      <c r="B52" s="75"/>
+      <c r="C52" s="75"/>
+      <c r="D52" s="75"/>
+      <c r="E52" s="75"/>
+      <c r="F52" s="75"/>
+      <c r="G52" s="75"/>
+      <c r="H52" s="75"/>
+      <c r="I52" s="75"/>
       <c r="J52" s="51"/>
       <c r="K52" s="58"/>
       <c r="L52" s="58"/>
@@ -6818,10 +6911,10 @@
       <c r="B54" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C54" s="69" t="s">
+      <c r="C54" s="64" t="s">
         <v>80</v>
       </c>
-      <c r="D54" s="69" t="s">
+      <c r="D54" s="64" t="s">
         <v>72</v>
       </c>
       <c r="E54" s="11">
@@ -6859,8 +6952,8 @@
       <c r="B55" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C55" s="69"/>
-      <c r="D55" s="69"/>
+      <c r="C55" s="64"/>
+      <c r="D55" s="64"/>
       <c r="E55" s="11">
         <v>8.2166826499999998E-2</v>
       </c>
@@ -6896,8 +6989,8 @@
       <c r="B56" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C56" s="69"/>
-      <c r="D56" s="69"/>
+      <c r="C56" s="64"/>
+      <c r="D56" s="64"/>
       <c r="E56" s="11">
         <v>7.6701820000000002E-4</v>
       </c>
@@ -6933,10 +7026,10 @@
       <c r="B58" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C58" s="69" t="s">
+      <c r="C58" s="64" t="s">
         <v>81</v>
       </c>
-      <c r="D58" s="69" t="s">
+      <c r="D58" s="64" t="s">
         <v>74</v>
       </c>
       <c r="E58" s="11">
@@ -6974,8 +7067,8 @@
       <c r="B59" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="69"/>
-      <c r="D59" s="69"/>
+      <c r="C59" s="64"/>
+      <c r="D59" s="64"/>
       <c r="E59" s="11">
         <v>2.85714286E-2</v>
       </c>
@@ -7011,8 +7104,8 @@
       <c r="B60" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C60" s="69"/>
-      <c r="D60" s="69"/>
+      <c r="C60" s="64"/>
+      <c r="D60" s="64"/>
       <c r="E60" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -7042,17 +7135,17 @@
       </c>
     </row>
     <row r="62" spans="1:14" s="49" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="71" t="s">
+      <c r="A62" s="75" t="s">
         <v>82</v>
       </c>
-      <c r="B62" s="71"/>
-      <c r="C62" s="71"/>
-      <c r="D62" s="71"/>
-      <c r="E62" s="71"/>
-      <c r="F62" s="71"/>
-      <c r="G62" s="71"/>
-      <c r="H62" s="71"/>
-      <c r="I62" s="71"/>
+      <c r="B62" s="75"/>
+      <c r="C62" s="75"/>
+      <c r="D62" s="75"/>
+      <c r="E62" s="75"/>
+      <c r="F62" s="75"/>
+      <c r="G62" s="75"/>
+      <c r="H62" s="75"/>
+      <c r="I62" s="75"/>
       <c r="J62" s="51"/>
       <c r="K62" s="58"/>
       <c r="L62" s="58"/>
@@ -7078,10 +7171,10 @@
       <c r="B64" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C64" s="69" t="s">
+      <c r="C64" s="64" t="s">
         <v>83</v>
       </c>
-      <c r="D64" s="69" t="s">
+      <c r="D64" s="64" t="s">
         <v>72</v>
       </c>
       <c r="E64" s="11">
@@ -7119,8 +7212,8 @@
       <c r="B65" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C65" s="69"/>
-      <c r="D65" s="69"/>
+      <c r="C65" s="64"/>
+      <c r="D65" s="64"/>
       <c r="E65" s="11">
         <v>3.2598274E-3</v>
       </c>
@@ -7156,8 +7249,8 @@
       <c r="B66" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C66" s="69"/>
-      <c r="D66" s="69"/>
+      <c r="C66" s="64"/>
+      <c r="D66" s="64"/>
       <c r="E66" s="11">
         <v>0</v>
       </c>
@@ -7193,10 +7286,10 @@
       <c r="B68" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C68" s="69" t="s">
+      <c r="C68" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="D68" s="69" t="s">
+      <c r="D68" s="64" t="s">
         <v>74</v>
       </c>
       <c r="E68" s="11">
@@ -7234,8 +7327,8 @@
       <c r="B69" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C69" s="69"/>
-      <c r="D69" s="69"/>
+      <c r="C69" s="64"/>
+      <c r="D69" s="64"/>
       <c r="E69" s="11">
         <v>8.59060403E-2</v>
       </c>
@@ -7271,8 +7364,8 @@
       <c r="B70" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C70" s="69"/>
-      <c r="D70" s="69"/>
+      <c r="C70" s="64"/>
+      <c r="D70" s="64"/>
       <c r="E70" s="11">
         <v>3.8350910000000001E-4</v>
       </c>
@@ -7303,26 +7396,6 @@
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="C33:C35"/>
-    <mergeCell ref="D33:D35"/>
-    <mergeCell ref="C37:C39"/>
-    <mergeCell ref="D37:D39"/>
-    <mergeCell ref="C41:C43"/>
-    <mergeCell ref="D41:D43"/>
-    <mergeCell ref="C45:C47"/>
-    <mergeCell ref="D45:D47"/>
-    <mergeCell ref="A49:D49"/>
-    <mergeCell ref="A50:D50"/>
-    <mergeCell ref="A62:I62"/>
-    <mergeCell ref="C64:C66"/>
-    <mergeCell ref="D64:D66"/>
-    <mergeCell ref="C68:C70"/>
-    <mergeCell ref="D68:D70"/>
-    <mergeCell ref="A52:I52"/>
-    <mergeCell ref="C54:C56"/>
-    <mergeCell ref="D54:D56"/>
-    <mergeCell ref="C58:C60"/>
-    <mergeCell ref="D58:D60"/>
     <mergeCell ref="C13:C15"/>
     <mergeCell ref="D13:D15"/>
     <mergeCell ref="C29:C31"/>
@@ -7338,6 +7411,26 @@
     <mergeCell ref="C9:C11"/>
     <mergeCell ref="D17:D19"/>
     <mergeCell ref="C17:C19"/>
+    <mergeCell ref="C64:C66"/>
+    <mergeCell ref="D64:D66"/>
+    <mergeCell ref="C68:C70"/>
+    <mergeCell ref="D68:D70"/>
+    <mergeCell ref="A52:I52"/>
+    <mergeCell ref="C54:C56"/>
+    <mergeCell ref="D54:D56"/>
+    <mergeCell ref="C58:C60"/>
+    <mergeCell ref="D58:D60"/>
+    <mergeCell ref="C45:C47"/>
+    <mergeCell ref="D45:D47"/>
+    <mergeCell ref="A49:D49"/>
+    <mergeCell ref="A50:D50"/>
+    <mergeCell ref="A62:I62"/>
+    <mergeCell ref="C33:C35"/>
+    <mergeCell ref="D33:D35"/>
+    <mergeCell ref="C37:C39"/>
+    <mergeCell ref="D37:D39"/>
+    <mergeCell ref="C41:C43"/>
+    <mergeCell ref="D41:D43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/benchmarking/search_for_best_combination/results_basic.xlsx
+++ b/benchmarking/search_for_best_combination/results_basic.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/deborahdore/Documents/political-debates-graph-analysis/benchmarking/search_for_best_combination/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84555B7F-16CF-3F48-8852-034E2F91B029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A8AE3A6-9085-054D-8617-84D8B1A00FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="51200" windowHeight="28800" activeTab="3" xr2:uid="{E2EDC037-19C4-FE46-A599-BB595128A04F}"/>
   </bookViews>
